--- a/results/level1_emt_comparison/table12_level1_emt_comparison.xlsx
+++ b/results/level1_emt_comparison/table12_level1_emt_comparison.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AR_Fits" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Point_Errors" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By_State" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alpha_Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,19 +471,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.377406608845706</v>
+        <v>3.248199130398963</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1201450626848463</v>
+        <v>0.1142146469445295</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.796697379219327</v>
+        <v>-2.838889215345542</v>
       </c>
       <c r="E2" t="n">
-        <v>10.89503491841374</v>
+        <v>11.09496567262841</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1376449218876121</v>
+        <v>0.2286008301024308</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +493,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.422292762044188</v>
+        <v>3.283255880529584</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1212381889115783</v>
+        <v>0.1153134987572593</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.656038716212926</v>
+        <v>-2.876323777238121</v>
       </c>
       <c r="E3" t="n">
-        <v>10.99426684972992</v>
+        <v>11.19040846154465</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2109544929310813</v>
+        <v>0.2463093236762327</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +515,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.627071252816803</v>
+        <v>8.761256344682623</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2550883215356676</v>
+        <v>0.2393044958229245</v>
       </c>
       <c r="D4" t="n">
-        <v>8.172002836047348</v>
+        <v>7.474935871066526</v>
       </c>
       <c r="E4" t="n">
-        <v>54.81164578728831</v>
+        <v>53.78773008610538</v>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
@@ -581,10 +582,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.05368759472172912</v>
+        <v>0.05666441691476886</v>
       </c>
       <c r="E2" t="n">
-        <v>0.246997391131639</v>
+        <v>0.1578618204724482</v>
       </c>
     </row>
     <row r="3">
@@ -600,10 +601,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.06086240267307132</v>
+        <v>0.06386482684796346</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2479392087459091</v>
+        <v>0.1587387084394845</v>
       </c>
     </row>
     <row r="4">
@@ -620,7 +621,7 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.5806425649747071</v>
+        <v>0.4486895288228592</v>
       </c>
     </row>
     <row r="5">
@@ -636,10 +637,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07468243879496878</v>
+        <v>0.0785681403797011</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2244932234446511</v>
+        <v>0.1832525822951641</v>
       </c>
     </row>
     <row r="6">
@@ -655,10 +656,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.0853200060632492</v>
+        <v>0.08924886172458077</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2256925812507276</v>
+        <v>0.184364795550779</v>
       </c>
     </row>
     <row r="7">
@@ -675,7 +676,7 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0.5025836239332429</v>
+        <v>0.4218503377937282</v>
       </c>
     </row>
     <row r="8">
@@ -691,10 +692,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07769383174897279</v>
+        <v>0.07975437634955759</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4377210023154734</v>
+        <v>0.4129043461096684</v>
       </c>
     </row>
     <row r="9">
@@ -710,10 +711,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1038486195406794</v>
+        <v>0.1059624887607095</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4423627777571408</v>
+        <v>0.4173639020295501</v>
       </c>
     </row>
     <row r="10">
@@ -730,7 +731,7 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>0.724666580075316</v>
+        <v>0.668064401571262</v>
       </c>
     </row>
     <row r="11">
@@ -746,10 +747,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.07164375059462785</v>
+        <v>0.07352012846648061</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5459893494955839</v>
+        <v>0.501375503026221</v>
       </c>
     </row>
     <row r="12">
@@ -765,10 +766,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.09606649406692572</v>
+        <v>0.09799001800823975</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5506727427888749</v>
+        <v>0.5058823287536682</v>
       </c>
     </row>
     <row r="13">
@@ -785,7 +786,7 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.8066447628289657</v>
+        <v>0.7294476150130045</v>
       </c>
     </row>
     <row r="14">
@@ -801,10 +802,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.06415477955232271</v>
+        <v>0.0662995724211108</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3415851380395898</v>
+        <v>0.2449526536739257</v>
       </c>
     </row>
     <row r="15">
@@ -820,10 +821,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.07976770824840715</v>
+        <v>0.08194993605837791</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3443502989961984</v>
+        <v>0.2475917006896253</v>
       </c>
     </row>
     <row r="16">
@@ -840,7 +841,7 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>0.7891239902904501</v>
+        <v>0.6554331814997258</v>
       </c>
     </row>
     <row r="17">
@@ -856,10 +857,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.08493991003089077</v>
+        <v>0.08850039773988014</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2227451741837312</v>
+        <v>0.2235541593239216</v>
       </c>
     </row>
     <row r="18">
@@ -875,10 +876,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.1006439510866089</v>
+        <v>0.1042585113052578</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2246439349593663</v>
+        <v>0.2253346994602143</v>
       </c>
     </row>
     <row r="19">
@@ -895,7 +896,7 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>0.5425134093201498</v>
+        <v>0.5068763313642757</v>
       </c>
     </row>
     <row r="20">
@@ -911,10 +912,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.08276118906439396</v>
+        <v>0.08631537829714603</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3516903015939836</v>
+        <v>0.2750502051737929</v>
       </c>
     </row>
     <row r="21">
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.09759611521820596</v>
+        <v>0.1012018247808178</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3534898116761838</v>
+        <v>0.2767359375840668</v>
       </c>
     </row>
     <row r="22">
@@ -950,7 +951,7 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>0.5739609999665625</v>
+        <v>0.460378011253082</v>
       </c>
     </row>
     <row r="23">
@@ -966,10 +967,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.0686516240624105</v>
+        <v>0.07158956549382131</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4022672001677843</v>
+        <v>0.3045635095545758</v>
       </c>
     </row>
     <row r="24">
@@ -985,10 +986,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.08093469252371924</v>
+        <v>0.08391244363649571</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4039854808116408</v>
+        <v>0.306181146869914</v>
       </c>
     </row>
     <row r="25">
@@ -1005,7 +1006,7 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>0.6644296193662562</v>
+        <v>0.5279381478452496</v>
       </c>
     </row>
     <row r="26">
@@ -1021,10 +1022,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.0673326179058804</v>
+        <v>0.07041259839357857</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5415983644899676</v>
+        <v>0.5364264602899795</v>
       </c>
     </row>
     <row r="27">
@@ -1040,10 +1041,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.07846317333991787</v>
+        <v>0.08158045301163148</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5430947789205662</v>
+        <v>0.5378298389161928</v>
       </c>
     </row>
     <row r="28">
@@ -1060,7 +1061,7 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>0.576131745251502</v>
+        <v>0.5673634416758437</v>
       </c>
     </row>
     <row r="29">
@@ -1076,10 +1077,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.07226117671732123</v>
+        <v>0.07519263589067139</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3214168689528729</v>
+        <v>0.2873466586836653</v>
       </c>
     </row>
     <row r="30">
@@ -1095,10 +1096,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.08606582607634179</v>
+        <v>0.08904076119261407</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3233582409988176</v>
+        <v>0.2891774823790838</v>
       </c>
     </row>
     <row r="31">
@@ -1115,7 +1116,7 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>0.5924339240855145</v>
+        <v>0.5205557766390179</v>
       </c>
     </row>
     <row r="32">
@@ -1131,10 +1132,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.08084776359136987</v>
+        <v>0.08455531212179532</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4480428794973559</v>
+        <v>0.3877543575287179</v>
       </c>
     </row>
     <row r="33">
@@ -1150,10 +1151,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.09422402916391198</v>
+        <v>0.09798106554163073</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4496144817204324</v>
+        <v>0.3892214329300319</v>
       </c>
     </row>
     <row r="34">
@@ -1170,7 +1171,7 @@
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>0.5505305300531642</v>
+        <v>0.452486235092286</v>
       </c>
     </row>
     <row r="35">
@@ -1186,10 +1187,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.07477155005067269</v>
+        <v>0.07649558994396405</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3814288615154227</v>
+        <v>0.3221197757293397</v>
       </c>
     </row>
     <row r="36">
@@ -1205,10 +1206,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.1057255571936795</v>
+        <v>0.1075030182024911</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3875422871891911</v>
+        <v>0.3280258594281007</v>
       </c>
     </row>
     <row r="37">
@@ -1225,7 +1226,7 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>0.8197111940809849</v>
+        <v>0.730563761674206</v>
       </c>
     </row>
     <row r="38">
@@ -1241,10 +1242,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.08351820846465208</v>
+        <v>0.08746020600723745</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1597842641140197</v>
+        <v>0.07013319285547048</v>
       </c>
     </row>
     <row r="39">
@@ -1260,10 +1261,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.09689548616632374</v>
+        <v>0.1008884035969615</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1598088536397526</v>
+        <v>0.07016814373742708</v>
       </c>
     </row>
     <row r="40">
@@ -1280,7 +1281,7 @@
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>0.6376523455426559</v>
+        <v>0.5447983464121351</v>
       </c>
     </row>
     <row r="41">
@@ -1296,10 +1297,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.1329158412060047</v>
+        <v>0.2186428755542171</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2350721378202199</v>
+        <v>0.2306845256826078</v>
       </c>
     </row>
     <row r="42">
@@ -1315,10 +1316,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.2135576073938147</v>
+        <v>0.236819832402668</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2388331169114024</v>
+        <v>0.2310529706696847</v>
       </c>
     </row>
     <row r="43">
@@ -1335,7 +1336,7 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>0.4093656838850572</v>
+        <v>0.3686419342756744</v>
       </c>
     </row>
     <row r="44">
@@ -1351,10 +1352,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.07520476246509329</v>
+        <v>0.07662637658294001</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2746123107583736</v>
+        <v>0.2454568864233364</v>
       </c>
     </row>
     <row r="45">
@@ -1370,10 +1371,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.1186546112797692</v>
+        <v>0.1201360836897293</v>
       </c>
       <c r="E45" t="n">
-        <v>0.28372568229346</v>
+        <v>0.2543144897076088</v>
       </c>
     </row>
     <row r="46">
@@ -1390,7 +1391,7 @@
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>0.8345510040055804</v>
+        <v>0.7800198272534931</v>
       </c>
     </row>
     <row r="47">
@@ -1406,10 +1407,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.3660646295723231</v>
+        <v>0.4825333284192772</v>
       </c>
       <c r="E47" t="n">
-        <v>0.381821414180425</v>
+        <v>0.3598127102142179</v>
       </c>
     </row>
     <row r="48">
@@ -1425,10 +1426,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.3828301430761989</v>
+        <v>0.4981426684592046</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3818925215810904</v>
+        <v>0.3598353617996821</v>
       </c>
     </row>
     <row r="49">
@@ -1445,7 +1446,7 @@
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>0.4151723206711839</v>
+        <v>0.3623312070196065</v>
       </c>
     </row>
     <row r="50">
@@ -1461,10 +1462,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.05585091153844986</v>
+        <v>0.0572653287215627</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2572282075997243</v>
+        <v>0.2362761207079336</v>
       </c>
     </row>
     <row r="51">
@@ -1480,10 +1481,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.07572491001638651</v>
+        <v>0.07717316817023095</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2619227962050303</v>
+        <v>0.2408135416935724</v>
       </c>
     </row>
     <row r="52">
@@ -1500,7 +1501,7 @@
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>0.8524827667041763</v>
+        <v>0.8426693118526383</v>
       </c>
     </row>
     <row r="53">
@@ -1516,10 +1517,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.1279688890847251</v>
+        <v>0.2227214678701133</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1490071113657758</v>
+        <v>0.2457191182242666</v>
       </c>
     </row>
     <row r="54">
@@ -1535,10 +1536,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.2242608781423763</v>
+        <v>0.2448759921893136</v>
       </c>
       <c r="E54" t="n">
-        <v>0.15307132047585</v>
+        <v>0.2462063887984645</v>
       </c>
     </row>
     <row r="55">
@@ -1555,7 +1556,7 @@
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>0.3415804585766149</v>
+        <v>0.3896684154815144</v>
       </c>
     </row>
     <row r="56">
@@ -1571,10 +1572,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.08185432872087021</v>
+        <v>0.08427582850660222</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2073475370124407</v>
+        <v>0.1637237890510823</v>
       </c>
     </row>
     <row r="57">
@@ -1590,10 +1591,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.1055737314840889</v>
+        <v>0.1080509055066162</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2071291335105852</v>
+        <v>0.1673240661858491</v>
       </c>
     </row>
     <row r="58">
@@ -1610,7 +1611,7 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>0.7991600362705735</v>
+        <v>0.6625910010039939</v>
       </c>
     </row>
     <row r="59">
@@ -1626,10 +1627,10 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.08947870343401622</v>
+        <v>0.09214397915035165</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2924453011247989</v>
+        <v>0.3953739497372795</v>
       </c>
     </row>
     <row r="60">
@@ -1645,10 +1646,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.1153960352342452</v>
+        <v>0.1181240394951164</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2962176766867828</v>
+        <v>0.3989724410322442</v>
       </c>
     </row>
     <row r="61">
@@ -1665,7 +1666,7 @@
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>0.518531036701938</v>
+        <v>0.5855627668852905</v>
       </c>
     </row>
     <row r="62">
@@ -1681,10 +1682,10 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.07441064331798346</v>
+        <v>0.07638048100184246</v>
       </c>
       <c r="E62" t="n">
-        <v>0.336109848923893</v>
+        <v>0.4134481225117077</v>
       </c>
     </row>
     <row r="63">
@@ -1700,10 +1701,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.09943493880077356</v>
+        <v>0.1014549402188581</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3407270853976727</v>
+        <v>0.4178871479823627</v>
       </c>
     </row>
     <row r="64">
@@ -1720,7 +1721,7 @@
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>0.6339241364774308</v>
+        <v>0.678967316090761</v>
       </c>
     </row>
     <row r="65">
@@ -1736,10 +1737,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.07775141806413362</v>
+        <v>0.07972957776622766</v>
       </c>
       <c r="E65" t="n">
-        <v>0.2918210374693577</v>
+        <v>0.3890755131440282</v>
       </c>
     </row>
     <row r="66">
@@ -1755,10 +1756,10 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.1055651951327819</v>
+        <v>0.1075983135296858</v>
       </c>
       <c r="E66" t="n">
-        <v>0.2968671480594716</v>
+        <v>0.393931853058483</v>
       </c>
     </row>
     <row r="67">
@@ -1775,7 +1776,7 @@
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>0.6599895563002833</v>
+        <v>0.7083843300090813</v>
       </c>
     </row>
     <row r="68">
@@ -1791,10 +1792,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.06851827165700264</v>
+        <v>0.07110019935028825</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1025973125311728</v>
+        <v>0.03145751620537673</v>
       </c>
     </row>
     <row r="69">
@@ -1810,10 +1811,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.08284595615112531</v>
+        <v>0.08546840709107527</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1026692592875054</v>
+        <v>0.03151455020869909</v>
       </c>
     </row>
     <row r="70">
@@ -1830,7 +1831,7 @@
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>0.8458042335328697</v>
+        <v>0.7308964258071851</v>
       </c>
     </row>
     <row r="71">
@@ -1846,10 +1847,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.06991180165766715</v>
+        <v>0.07216402703380637</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1031997036711925</v>
+        <v>0.02729226510951399</v>
       </c>
     </row>
     <row r="72">
@@ -1865,10 +1866,10 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.08779421922295189</v>
+        <v>0.09009004668823942</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1032225860231208</v>
+        <v>0.02739017736156413</v>
       </c>
     </row>
     <row r="73">
@@ -1885,7 +1886,7 @@
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>0.9334471515831613</v>
+        <v>0.815310932210227</v>
       </c>
     </row>
     <row r="74">
@@ -1901,10 +1902,10 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.06376691369579074</v>
+        <v>0.06864450336153091</v>
       </c>
       <c r="E74" t="n">
-        <v>0.07055750615090961</v>
+        <v>0.0528523480700227</v>
       </c>
     </row>
     <row r="75">
@@ -1920,10 +1921,10 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.06972497661133063</v>
+        <v>0.07463470711230444</v>
       </c>
       <c r="E75" t="n">
-        <v>0.07061609662357116</v>
+        <v>0.05333841545703777</v>
       </c>
     </row>
     <row r="76">
@@ -1940,7 +1941,7 @@
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>0.4438944884946925</v>
+        <v>0.3559010301537064</v>
       </c>
     </row>
     <row r="77">
@@ -1956,10 +1957,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.04685847404322814</v>
+        <v>0.05161121416311337</v>
       </c>
       <c r="E77" t="n">
-        <v>0.08571176384958434</v>
+        <v>0.05811188292933567</v>
       </c>
     </row>
     <row r="78">
@@ -1975,10 +1976,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.05020947065389519</v>
+        <v>0.05498242253594483</v>
       </c>
       <c r="E78" t="n">
-        <v>0.08577525515259765</v>
+        <v>0.05835869515232384</v>
       </c>
     </row>
     <row r="79">
@@ -1995,7 +1996,7 @@
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>0.3724173269415791</v>
+        <v>0.2690454672306748</v>
       </c>
     </row>
     <row r="80">
@@ -2011,10 +2012,10 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.02206948878536812</v>
+        <v>0.02397019273512207</v>
       </c>
       <c r="E80" t="n">
-        <v>0.05010982473529824</v>
+        <v>0.09410409760133609</v>
       </c>
     </row>
     <row r="81">
@@ -2030,10 +2031,10 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.02426330837471627</v>
+        <v>0.02617032869151523</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0502302746300356</v>
+        <v>0.09435507480994509</v>
       </c>
     </row>
     <row r="82">
@@ -2050,7 +2051,7 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>0.4133382899372249</v>
+        <v>0.3538984046651779</v>
       </c>
     </row>
     <row r="83">
@@ -2066,10 +2067,10 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.08644771406997782</v>
+        <v>0.09122256426320441</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1951764304753536</v>
+        <v>0.2365349672944657</v>
       </c>
     </row>
     <row r="84">
@@ -2085,10 +2086,10 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.09801158431932876</v>
+        <v>0.1028391763575825</v>
       </c>
       <c r="E84" t="n">
-        <v>0.1962885472936358</v>
+        <v>0.2375564971107833</v>
       </c>
     </row>
     <row r="85">
@@ -2105,7 +2106,7 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>0.4149557730653841</v>
+        <v>0.4178006730142449</v>
       </c>
     </row>
     <row r="86">
@@ -2121,10 +2122,10 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.08140120033643369</v>
+        <v>0.08540130311845624</v>
       </c>
       <c r="E86" t="n">
-        <v>0.139517229401501</v>
+        <v>0.117535071242191</v>
       </c>
     </row>
     <row r="87">
@@ -2140,10 +2141,10 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.09381973060610525</v>
+        <v>0.09786992411855877</v>
       </c>
       <c r="E87" t="n">
-        <v>0.1395113312550804</v>
+        <v>0.1188116643274797</v>
       </c>
     </row>
     <row r="88">
@@ -2160,7 +2161,7 @@
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>0.5976084327829425</v>
+        <v>0.4534280373846236</v>
       </c>
     </row>
     <row r="89">
@@ -2176,10 +2177,10 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.05365244851449789</v>
+        <v>0.05449563116943758</v>
       </c>
       <c r="E89" t="n">
-        <v>0.2391932108860111</v>
+        <v>0.3107034944707898</v>
       </c>
     </row>
     <row r="90">
@@ -2195,10 +2196,10 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.09628806381888011</v>
+        <v>0.09717239253050693</v>
       </c>
       <c r="E90" t="n">
-        <v>0.2519034982212365</v>
+        <v>0.3231422282963496</v>
       </c>
     </row>
     <row r="91">
@@ -2215,7 +2216,7 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>1.112308161437593</v>
+        <v>1.017395106863452</v>
       </c>
     </row>
     <row r="92">
@@ -2231,10 +2232,10 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.09980731841490169</v>
+        <v>0.1042262168583761</v>
       </c>
       <c r="E92" t="n">
-        <v>0.08673718055430601</v>
+        <v>0.1520996820158946</v>
       </c>
     </row>
     <row r="93">
@@ -2250,10 +2251,10 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.1173245789617089</v>
+        <v>0.1218097151510352</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0885007272687659</v>
+        <v>0.153739793820459</v>
       </c>
     </row>
     <row r="94">
@@ -2270,7 +2271,7 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>0.5148737345241292</v>
+        <v>0.4169271309976064</v>
       </c>
     </row>
     <row r="95">
@@ -2286,10 +2287,10 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.08797208990274272</v>
+        <v>0.09372630077322572</v>
       </c>
       <c r="E95" t="n">
-        <v>0.09534236330560253</v>
+        <v>0.02618922200018581</v>
       </c>
     </row>
     <row r="96">
@@ -2305,10 +2306,10 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.09772460496354667</v>
+        <v>0.1035325935966191</v>
       </c>
       <c r="E96" t="n">
-        <v>0.09533119943228785</v>
+        <v>0.02616915901125472</v>
       </c>
     </row>
     <row r="97">
@@ -2325,7 +2326,7 @@
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>0.5616613649675979</v>
+        <v>0.4468668091321804</v>
       </c>
     </row>
     <row r="98">
@@ -2341,10 +2342,10 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.1054749501105286</v>
+        <v>0.1095102904351769</v>
       </c>
       <c r="E98" t="n">
-        <v>0.2034047817800571</v>
+        <v>0.2750656180479267</v>
       </c>
     </row>
     <row r="99">
@@ -2360,10 +2361,10 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.1278415647582374</v>
+        <v>0.1319493824569777</v>
       </c>
       <c r="E99" t="n">
-        <v>0.2057668385211837</v>
+        <v>0.2772805254001374</v>
       </c>
     </row>
     <row r="100">
@@ -2380,7 +2381,7 @@
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
-        <v>0.5272736715281252</v>
+        <v>0.5658989273937407</v>
       </c>
     </row>
   </sheetData>
@@ -2467,22 +2468,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.05368759472172912</v>
+        <v>0.05666441691476886</v>
       </c>
       <c r="F2" t="n">
         <v>2.472887500000001</v>
       </c>
       <c r="G2" t="n">
-        <v>2.472889392378866</v>
+        <v>2.472889942683989</v>
       </c>
       <c r="H2" t="n">
-        <v>1.892378865164801e-06</v>
+        <v>2.442683987968763e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>7.652506897967662e-05</v>
+        <v>9.877861358305879e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>7.652506897967662e-05</v>
+        <v>9.877861358305879e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2503,22 +2504,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.05368759472172912</v>
+        <v>0.05666441691476886</v>
       </c>
       <c r="F3" t="n">
         <v>2.668884574253278</v>
       </c>
       <c r="G3" t="n">
-        <v>2.591859652123895</v>
+        <v>2.584048673232694</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.07702492212938328</v>
+        <v>-0.08483590102058436</v>
       </c>
       <c r="I3" t="n">
-        <v>2.886034220904211</v>
+        <v>3.178702512615048</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.886034220904211</v>
+        <v>-3.178702512615048</v>
       </c>
     </row>
     <row r="4">
@@ -2535,26 +2536,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05368759472172912</v>
+        <v>0.05666441691476886</v>
       </c>
       <c r="F4" t="n">
-        <v>2.966437500000001</v>
+        <v>2.853091666666666</v>
       </c>
       <c r="G4" t="n">
-        <v>2.79646692337661</v>
+        <v>2.78006818989879</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1699705766233905</v>
+        <v>-0.07302347676787591</v>
       </c>
       <c r="I4" t="n">
-        <v>5.729787889459681</v>
+        <v>2.55945077478674</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.729787889459681</v>
+        <v>-2.55945077478674</v>
       </c>
     </row>
     <row r="5">
@@ -2575,22 +2576,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.06086240267307132</v>
+        <v>0.06386482684796346</v>
       </c>
       <c r="F5" t="n">
         <v>2.472887500000001</v>
       </c>
       <c r="G5" t="n">
-        <v>2.472888735373726</v>
+        <v>2.472887645142705</v>
       </c>
       <c r="H5" t="n">
-        <v>1.235373725094746e-06</v>
+        <v>1.451427045218168e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>4.995672973779623e-05</v>
+        <v>5.869361405313292e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>4.995672973779623e-05</v>
+        <v>5.869361405313292e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2611,22 +2612,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.06086240267307132</v>
+        <v>0.06386482684796346</v>
       </c>
       <c r="F6" t="n">
         <v>2.668884574253278</v>
       </c>
       <c r="G6" t="n">
-        <v>2.591317004266254</v>
+        <v>2.583547370525208</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.07756756998702441</v>
+        <v>-0.08533720372806997</v>
       </c>
       <c r="I6" t="n">
-        <v>2.90636660481006</v>
+        <v>3.197485741845778</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.90636660481006</v>
+        <v>-3.197485741845778</v>
       </c>
     </row>
     <row r="7">
@@ -2643,26 +2644,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.06086240267307132</v>
+        <v>0.06386482684796346</v>
       </c>
       <c r="F7" t="n">
-        <v>2.966437500000001</v>
+        <v>2.853091666666666</v>
       </c>
       <c r="G7" t="n">
-        <v>2.796067096614841</v>
+        <v>2.779690307097956</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1703704033851596</v>
+        <v>-0.07340135956870997</v>
       </c>
       <c r="I7" t="n">
-        <v>5.743266237200669</v>
+        <v>2.572695452665441</v>
       </c>
       <c r="J7" t="n">
-        <v>-5.743266237200669</v>
+        <v>-2.572695452665441</v>
       </c>
     </row>
     <row r="8">
@@ -2687,16 +2688,16 @@
         <v>2.472887500000001</v>
       </c>
       <c r="G8" t="n">
-        <v>2.798974103471928</v>
+        <v>2.780331490519747</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3260866034719272</v>
+        <v>0.3074439905197468</v>
       </c>
       <c r="I8" t="n">
-        <v>13.18647142144263</v>
+        <v>12.43259107095437</v>
       </c>
       <c r="J8" t="n">
-        <v>13.18647142144263</v>
+        <v>12.43259107095437</v>
       </c>
     </row>
     <row r="9">
@@ -2721,16 +2722,16 @@
         <v>2.668884574253278</v>
       </c>
       <c r="G9" t="n">
-        <v>2.809607760781981</v>
+        <v>2.790963090955654</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1407231865287031</v>
+        <v>0.1220785167023761</v>
       </c>
       <c r="I9" t="n">
-        <v>5.272734080981218</v>
+        <v>4.574139993916082</v>
       </c>
       <c r="J9" t="n">
-        <v>5.272734080981218</v>
+        <v>4.574139993916082</v>
       </c>
     </row>
     <row r="10">
@@ -2747,24 +2748,24 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>2.966437500000001</v>
+        <v>2.853091666666666</v>
       </c>
       <c r="G10" t="n">
-        <v>2.852604725025924</v>
+        <v>2.83392464506593</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1138327749740768</v>
+        <v>-0.01916702160073624</v>
       </c>
       <c r="I10" t="n">
-        <v>3.837356255578512</v>
+        <v>0.6717983100462217</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.837356255578512</v>
+        <v>-0.6717983100462217</v>
       </c>
     </row>
     <row r="11">
@@ -2785,22 +2786,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.07468243879496878</v>
+        <v>0.0785681403797011</v>
       </c>
       <c r="F11" t="n">
         <v>2.404575</v>
       </c>
       <c r="G11" t="n">
-        <v>2.40457527126751</v>
+        <v>2.404576854037716</v>
       </c>
       <c r="H11" t="n">
-        <v>2.712675097882311e-07</v>
+        <v>1.854037715798285e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>1.12813079146307e-05</v>
+        <v>7.710459086525828e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>1.12813079146307e-05</v>
+        <v>7.710459086525828e-05</v>
       </c>
     </row>
     <row r="12">
@@ -2821,22 +2822,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.07468243879496878</v>
+        <v>0.0785681403797011</v>
       </c>
       <c r="F12" t="n">
         <v>2.600887636781521</v>
       </c>
       <c r="G12" t="n">
-        <v>2.507948930691978</v>
+        <v>2.501643196623343</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.09293870608954258</v>
+        <v>-0.09924444015817846</v>
       </c>
       <c r="I12" t="n">
-        <v>3.573345683035733</v>
+        <v>3.815791145863914</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.573345683035733</v>
+        <v>-3.815791145863914</v>
       </c>
     </row>
     <row r="13">
@@ -2853,26 +2854,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.07468243879496878</v>
+        <v>0.0785681403797011</v>
       </c>
       <c r="F13" t="n">
-        <v>2.857375</v>
+        <v>2.794646875</v>
       </c>
       <c r="G13" t="n">
-        <v>2.725820753912402</v>
+        <v>2.71064058690073</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1315542460875987</v>
+        <v>-0.0840062880992698</v>
       </c>
       <c r="I13" t="n">
-        <v>4.604024536072398</v>
+        <v>3.005971482506884</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.604024536072398</v>
+        <v>-3.005971482506884</v>
       </c>
     </row>
     <row r="14">
@@ -2893,22 +2894,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0853200060632492</v>
+        <v>0.08924886172458077</v>
       </c>
       <c r="F14" t="n">
         <v>2.404575</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4045758775841</v>
+        <v>2.404577084665223</v>
       </c>
       <c r="H14" t="n">
-        <v>8.775841000563389e-07</v>
+        <v>2.084665222223947e-06</v>
       </c>
       <c r="I14" t="n">
-        <v>3.649643284390542e-05</v>
+        <v>8.669578708187297e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>3.649643284390542e-05</v>
+        <v>8.669578708187297e-05</v>
       </c>
     </row>
     <row r="15">
@@ -2929,22 +2930,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0853200060632492</v>
+        <v>0.08924886172458077</v>
       </c>
       <c r="F15" t="n">
         <v>2.600887636781521</v>
       </c>
       <c r="G15" t="n">
-        <v>2.507331733116985</v>
+        <v>2.501076409077493</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09355590366453592</v>
+        <v>-0.09981122770402795</v>
       </c>
       <c r="I15" t="n">
-        <v>3.597075949821003</v>
+        <v>3.837583227068577</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.597075949821003</v>
+        <v>-3.837583227068577</v>
       </c>
     </row>
     <row r="16">
@@ -2961,26 +2962,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.0853200060632492</v>
+        <v>0.08924886172458077</v>
       </c>
       <c r="F16" t="n">
-        <v>2.857375</v>
+        <v>2.794646875</v>
       </c>
       <c r="G16" t="n">
-        <v>2.725239199997909</v>
+        <v>2.710095391818471</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1321358000020916</v>
+        <v>-0.08455148318152883</v>
       </c>
       <c r="I16" t="n">
-        <v>4.624377269420064</v>
+        <v>3.025480032482774</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.624377269420064</v>
+        <v>-3.025480032482774</v>
       </c>
     </row>
     <row r="17">
@@ -3005,16 +3006,16 @@
         <v>2.404575</v>
       </c>
       <c r="G17" t="n">
-        <v>2.712450941200685</v>
+        <v>2.694392824874252</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3078759412006842</v>
+        <v>0.2898178248742518</v>
       </c>
       <c r="I17" t="n">
-        <v>12.80375705480944</v>
+        <v>12.05276711577937</v>
       </c>
       <c r="J17" t="n">
-        <v>12.80375705480944</v>
+        <v>12.05276711577937</v>
       </c>
     </row>
     <row r="18">
@@ -3039,16 +3040,16 @@
         <v>2.600887636781521</v>
       </c>
       <c r="G18" t="n">
-        <v>2.727807352787468</v>
+        <v>2.709746089772996</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1269197160059465</v>
+        <v>0.1088584529914751</v>
       </c>
       <c r="I18" t="n">
-        <v>4.879861559994335</v>
+        <v>4.185434674378415</v>
       </c>
       <c r="J18" t="n">
-        <v>4.879861559994335</v>
+        <v>4.185434674378415</v>
       </c>
     </row>
     <row r="19">
@@ -3065,24 +3066,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2.857375</v>
+        <v>2.794646875</v>
       </c>
       <c r="G19" t="n">
-        <v>2.789587033273388</v>
+        <v>2.771472815071999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.06778796672661214</v>
+        <v>-0.02317405992800126</v>
       </c>
       <c r="I19" t="n">
-        <v>2.372386079062501</v>
+        <v>0.8292303451755869</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.372386079062501</v>
+        <v>-0.8292303451755869</v>
       </c>
     </row>
     <row r="20">
@@ -3103,22 +3104,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.07769383174897279</v>
+        <v>0.07975437634955759</v>
       </c>
       <c r="F20" t="n">
         <v>1.85855</v>
       </c>
       <c r="G20" t="n">
-        <v>1.858551932403911</v>
+        <v>1.858552129540523</v>
       </c>
       <c r="H20" t="n">
-        <v>1.932403911109049e-06</v>
+        <v>2.129540522810558e-06</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0001039737381888595</v>
+        <v>0.000114580749660249</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0001039737381888595</v>
+        <v>0.000114580749660249</v>
       </c>
     </row>
     <row r="21">
@@ -3139,22 +3140,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.07769383174897279</v>
+        <v>0.07975437634955759</v>
       </c>
       <c r="F21" t="n">
         <v>2.23458197098924</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0198035506516</v>
+        <v>2.015458720268363</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2147784203376402</v>
+        <v>-0.2191232507208767</v>
       </c>
       <c r="I21" t="n">
-        <v>9.611570447002158</v>
+        <v>9.806006383550644</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.611570447002158</v>
+        <v>-9.806006383550644</v>
       </c>
     </row>
     <row r="22">
@@ -3171,26 +3172,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.07769383174897279</v>
+        <v>0.07975437634955759</v>
       </c>
       <c r="F22" t="n">
-        <v>2.63095</v>
+        <v>2.589690625</v>
       </c>
       <c r="G22" t="n">
-        <v>2.408009350426078</v>
+        <v>2.395911659151731</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2229406495739221</v>
+        <v>-0.1937789658482689</v>
       </c>
       <c r="I22" t="n">
-        <v>8.473769914818682</v>
+        <v>7.482707161140876</v>
       </c>
       <c r="J22" t="n">
-        <v>-8.473769914818682</v>
+        <v>-7.482707161140876</v>
       </c>
     </row>
     <row r="23">
@@ -3211,22 +3212,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.1038486195406794</v>
+        <v>0.1059624887607095</v>
       </c>
       <c r="F23" t="n">
         <v>1.85855</v>
       </c>
       <c r="G23" t="n">
-        <v>1.8585516233384</v>
+        <v>1.858550076365922</v>
       </c>
       <c r="H23" t="n">
-        <v>1.623338399925345e-06</v>
+        <v>7.636592203041914e-08</v>
       </c>
       <c r="I23" t="n">
-        <v>8.734434908532699e-05</v>
+        <v>4.108897905916932e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>8.734434908532699e-05</v>
+        <v>4.108897905916932e-06</v>
       </c>
     </row>
     <row r="24">
@@ -3247,22 +3248,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.1038486195406794</v>
+        <v>0.1059624887607095</v>
       </c>
       <c r="F24" t="n">
         <v>2.23458197098924</v>
       </c>
       <c r="G24" t="n">
-        <v>2.017612024936595</v>
+        <v>2.013355784773371</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2169699460526449</v>
+        <v>-0.2212261862158695</v>
       </c>
       <c r="I24" t="n">
-        <v>9.709643632208898</v>
+        <v>9.900115059011849</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.709643632208898</v>
+        <v>-9.900115059011849</v>
       </c>
     </row>
     <row r="25">
@@ -3279,26 +3280,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.1038486195406794</v>
+        <v>0.1059624887607095</v>
       </c>
       <c r="F25" t="n">
-        <v>2.63095</v>
+        <v>2.589690625</v>
       </c>
       <c r="G25" t="n">
-        <v>2.405558791633904</v>
+        <v>2.393552985552242</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2253912083660961</v>
+        <v>-0.1961376394477585</v>
       </c>
       <c r="I25" t="n">
-        <v>8.566913410216692</v>
+        <v>7.573786519297397</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.566913410216692</v>
+        <v>-7.573786519297397</v>
       </c>
     </row>
     <row r="26">
@@ -3323,16 +3324,16 @@
         <v>1.85855</v>
       </c>
       <c r="G26" t="n">
-        <v>2.333114080683036</v>
+        <v>2.317620944377673</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4745640806830365</v>
+        <v>0.4590709443776733</v>
       </c>
       <c r="I26" t="n">
-        <v>25.53410350450817</v>
+        <v>24.70048932650041</v>
       </c>
       <c r="J26" t="n">
-        <v>25.53410350450817</v>
+        <v>24.70048932650041</v>
       </c>
     </row>
     <row r="27">
@@ -3357,16 +3358,16 @@
         <v>2.23458197098924</v>
       </c>
       <c r="G27" t="n">
-        <v>2.370466678319909</v>
+        <v>2.354963488088436</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1358847073306686</v>
+        <v>0.120381517099196</v>
       </c>
       <c r="I27" t="n">
-        <v>6.080990050703443</v>
+        <v>5.387205242952157</v>
       </c>
       <c r="J27" t="n">
-        <v>6.080990050703443</v>
+        <v>5.387205242952157</v>
       </c>
     </row>
     <row r="28">
@@ -3383,24 +3384,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>2.63095</v>
+        <v>2.589690625</v>
       </c>
       <c r="G28" t="n">
-        <v>2.516732207938389</v>
+        <v>2.501078684905607</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.114217792061611</v>
+        <v>-0.08861194009439277</v>
       </c>
       <c r="I28" t="n">
-        <v>4.341313672308899</v>
+        <v>3.421719152047081</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.341313672308899</v>
+        <v>-3.421719152047081</v>
       </c>
     </row>
     <row r="29">
@@ -3421,22 +3422,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.07164375059462785</v>
+        <v>0.07352012846648061</v>
       </c>
       <c r="F29" t="n">
         <v>1.867175</v>
       </c>
       <c r="G29" t="n">
-        <v>1.86717476818911</v>
+        <v>1.867176584347419</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.318108902610305e-07</v>
+        <v>1.584347419036902e-06</v>
       </c>
       <c r="I29" t="n">
-        <v>1.241505966291486e-05</v>
+        <v>8.485264739710537e-05</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.241505966291486e-05</v>
+        <v>8.485264739710537e-05</v>
       </c>
     </row>
     <row r="30">
@@ -3457,22 +3458,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.07164375059462785</v>
+        <v>0.07352012846648061</v>
       </c>
       <c r="F30" t="n">
         <v>2.28687304883645</v>
       </c>
       <c r="G30" t="n">
-        <v>2.037717431625926</v>
+        <v>2.033145269091456</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.249155617210524</v>
+        <v>-0.2537277797449948</v>
       </c>
       <c r="I30" t="n">
-        <v>10.89503491841374</v>
+        <v>11.09496567262841</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.89503491841374</v>
+        <v>-11.09496567262841</v>
       </c>
     </row>
     <row r="31">
@@ -3489,26 +3490,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.07164375059462785</v>
+        <v>0.07352012846648061</v>
       </c>
       <c r="F31" t="n">
-        <v>2.7286125</v>
+        <v>2.66701875</v>
       </c>
       <c r="G31" t="n">
-        <v>2.431778999525831</v>
+        <v>2.419372611066193</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2968335004741696</v>
+        <v>-0.2476461389338072</v>
       </c>
       <c r="I31" t="n">
-        <v>10.87855092924223</v>
+        <v>9.285504233286968</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.87855092924223</v>
+        <v>-9.285504233286968</v>
       </c>
     </row>
     <row r="32">
@@ -3529,22 +3530,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.09606649406692572</v>
+        <v>0.09799001800823975</v>
       </c>
       <c r="F32" t="n">
         <v>1.867175</v>
       </c>
       <c r="G32" t="n">
-        <v>1.867177311565664</v>
+        <v>1.867174866042199</v>
       </c>
       <c r="H32" t="n">
-        <v>2.311565663770665e-06</v>
+        <v>-1.339578006298581e-07</v>
       </c>
       <c r="I32" t="n">
-        <v>0.000123800161408045</v>
+        <v>7.174357016876193e-06</v>
       </c>
       <c r="J32" t="n">
-        <v>0.000123800161408045</v>
+        <v>-7.174357016876193e-06</v>
       </c>
     </row>
     <row r="33">
@@ -3565,22 +3566,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.09606649406692572</v>
+        <v>0.09799001800823975</v>
       </c>
       <c r="F33" t="n">
         <v>2.28687304883645</v>
       </c>
       <c r="G33" t="n">
-        <v>2.035448123332817</v>
+        <v>2.030962613674672</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2514249255036338</v>
+        <v>-0.2559104351617782</v>
       </c>
       <c r="I33" t="n">
-        <v>10.99426684972992</v>
+        <v>11.19040846154465</v>
       </c>
       <c r="J33" t="n">
-        <v>-10.99426684972992</v>
+        <v>-11.19040846154465</v>
       </c>
     </row>
     <row r="34">
@@ -3597,26 +3598,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.09606649406692572</v>
+        <v>0.09799001800823975</v>
       </c>
       <c r="F34" t="n">
-        <v>2.7286125</v>
+        <v>2.66701875</v>
       </c>
       <c r="G34" t="n">
-        <v>2.429366994280423</v>
+        <v>2.417046990365911</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2992455057195773</v>
+        <v>-0.2499717596340894</v>
       </c>
       <c r="I34" t="n">
-        <v>10.96694769666185</v>
+        <v>9.372703496519826</v>
       </c>
       <c r="J34" t="n">
-        <v>-10.96694769666185</v>
+        <v>-9.372703496519826</v>
       </c>
     </row>
     <row r="35">
@@ -3641,16 +3642,16 @@
         <v>1.867175</v>
       </c>
       <c r="G35" t="n">
-        <v>2.369975777830198</v>
+        <v>2.35423318914262</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5028007778301977</v>
+        <v>0.48705818914262</v>
       </c>
       <c r="I35" t="n">
-        <v>26.92842276863163</v>
+        <v>26.08529940378486</v>
       </c>
       <c r="J35" t="n">
-        <v>26.92842276863163</v>
+        <v>26.08529940378486</v>
       </c>
     </row>
     <row r="36">
@@ -3675,16 +3676,16 @@
         <v>2.28687304883645</v>
       </c>
       <c r="G36" t="n">
-        <v>2.405084493396822</v>
+        <v>2.389332716211304</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1182114445603717</v>
+        <v>0.1024596673748532</v>
       </c>
       <c r="I36" t="n">
-        <v>5.169130163150818</v>
+        <v>4.480339100020625</v>
       </c>
       <c r="J36" t="n">
-        <v>5.169130163150818</v>
+        <v>4.480339100020625</v>
       </c>
     </row>
     <row r="37">
@@ -3701,24 +3702,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>2.7286125</v>
+        <v>2.66701875</v>
       </c>
       <c r="G37" t="n">
-        <v>2.542979959561604</v>
+        <v>2.527088991504469</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1856325404383963</v>
+        <v>-0.1399297584955312</v>
       </c>
       <c r="I37" t="n">
-        <v>6.803184418395659</v>
+        <v>5.246673218759007</v>
       </c>
       <c r="J37" t="n">
-        <v>-6.803184418395659</v>
+        <v>-5.246673218759007</v>
       </c>
     </row>
     <row r="38">
@@ -3739,22 +3740,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.06415477955232271</v>
+        <v>0.0662995724211108</v>
       </c>
       <c r="F38" t="n">
         <v>2.1235625</v>
       </c>
       <c r="G38" t="n">
-        <v>2.123564840178746</v>
+        <v>2.12356332180337</v>
       </c>
       <c r="H38" t="n">
-        <v>2.340178745896537e-06</v>
+        <v>8.218033702434013e-07</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0001102006060992571</v>
+        <v>3.869927869998652e-05</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0001102006060992571</v>
+        <v>3.869927869998652e-05</v>
       </c>
     </row>
     <row r="39">
@@ -3775,22 +3776,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.06415477955232271</v>
+        <v>0.0662995724211108</v>
       </c>
       <c r="F39" t="n">
         <v>2.4008625</v>
       </c>
       <c r="G39" t="n">
-        <v>2.280046434679316</v>
+        <v>2.274247861392504</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.120816065320684</v>
+        <v>-0.1266146386074958</v>
       </c>
       <c r="I39" t="n">
-        <v>5.032194276876915</v>
+        <v>5.273714700758406</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.032194276876915</v>
+        <v>-5.273714700758406</v>
       </c>
     </row>
     <row r="40">
@@ -3807,26 +3808,26 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.06415477955232271</v>
+        <v>0.0662995724211108</v>
       </c>
       <c r="F40" t="n">
-        <v>2.8231</v>
+        <v>2.706496875</v>
       </c>
       <c r="G40" t="n">
-        <v>2.60233326745984</v>
+        <v>2.58815968173694</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.2207667325401599</v>
+        <v>-0.1183371932630597</v>
       </c>
       <c r="I40" t="n">
-        <v>7.820011070814347</v>
+        <v>4.372338071258985</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.820011070814347</v>
+        <v>-4.372338071258985</v>
       </c>
     </row>
     <row r="41">
@@ -3847,22 +3848,22 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.07976770824840715</v>
+        <v>0.08194993605837791</v>
       </c>
       <c r="F41" t="n">
         <v>2.1235625</v>
       </c>
       <c r="G41" t="n">
-        <v>2.12356451732621</v>
+        <v>2.123562887612386</v>
       </c>
       <c r="H41" t="n">
-        <v>2.017326210079773e-06</v>
+        <v>3.876123852997182e-07</v>
       </c>
       <c r="I41" t="n">
-        <v>9.499726097441317e-05</v>
+        <v>1.825293040820405e-05</v>
       </c>
       <c r="J41" t="n">
-        <v>9.499726097441317e-05</v>
+        <v>1.825293040820405e-05</v>
       </c>
     </row>
     <row r="42">
@@ -3883,22 +3884,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.07976770824840715</v>
+        <v>0.08194993605837791</v>
       </c>
       <c r="F42" t="n">
         <v>2.4008625</v>
       </c>
       <c r="G42" t="n">
-        <v>2.278604956082722</v>
+        <v>2.272877745537396</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1222575439172777</v>
+        <v>-0.127984754462604</v>
       </c>
       <c r="I42" t="n">
-        <v>5.09223430818207</v>
+        <v>5.330782352700501</v>
       </c>
       <c r="J42" t="n">
-        <v>-5.09223430818207</v>
+        <v>-5.330782352700501</v>
       </c>
     </row>
     <row r="43">
@@ -3915,26 +3916,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.07976770824840715</v>
+        <v>0.08194993605837791</v>
       </c>
       <c r="F43" t="n">
-        <v>2.8231</v>
+        <v>2.706496875</v>
       </c>
       <c r="G43" t="n">
-        <v>2.60100926224729</v>
+        <v>2.586890316385364</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.2220907377527106</v>
+        <v>-0.119606558614636</v>
       </c>
       <c r="I43" t="n">
-        <v>7.866910054645977</v>
+        <v>4.419238748045331</v>
       </c>
       <c r="J43" t="n">
-        <v>-7.866910054645977</v>
+        <v>-4.419238748045331</v>
       </c>
     </row>
     <row r="44">
@@ -3959,16 +3960,16 @@
         <v>2.1235625</v>
       </c>
       <c r="G44" t="n">
-        <v>2.581082681353033</v>
+        <v>2.563912362046402</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4575201813530327</v>
+        <v>0.4403498620464017</v>
       </c>
       <c r="I44" t="n">
-        <v>21.54493599096013</v>
+        <v>20.73637399635761</v>
       </c>
       <c r="J44" t="n">
-        <v>21.54493599096013</v>
+        <v>20.73637399635761</v>
       </c>
     </row>
     <row r="45">
@@ -3993,16 +3994,16 @@
         <v>2.4008625</v>
       </c>
       <c r="G45" t="n">
-        <v>2.603801322470008</v>
+        <v>2.586625906351364</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2029388224700082</v>
+        <v>0.1857634063513642</v>
       </c>
       <c r="I45" t="n">
-        <v>8.452746563787313</v>
+        <v>7.737361317083518</v>
       </c>
       <c r="J45" t="n">
-        <v>8.452746563787313</v>
+        <v>7.737361317083518</v>
       </c>
     </row>
     <row r="46">
@@ -4019,24 +4020,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>2.8231</v>
+        <v>2.706496875</v>
       </c>
       <c r="G46" t="n">
-        <v>2.694435013532591</v>
+        <v>2.67717696189804</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.1286649864674092</v>
+        <v>-0.02931991310195992</v>
       </c>
       <c r="I46" t="n">
-        <v>4.557578069052077</v>
+        <v>1.083315978406955</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.557578069052077</v>
+        <v>-1.083315978406955</v>
       </c>
     </row>
     <row r="47">
@@ -4057,22 +4058,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.08493991003089077</v>
+        <v>0.08850039773988014</v>
       </c>
       <c r="F47" t="n">
         <v>2.244775</v>
       </c>
       <c r="G47" t="n">
-        <v>2.244776838250769</v>
+        <v>2.244776304299928</v>
       </c>
       <c r="H47" t="n">
-        <v>1.838250768937399e-06</v>
+        <v>1.304299927618047e-06</v>
       </c>
       <c r="I47" t="n">
-        <v>8.18902014205165e-05</v>
+        <v>5.810381564379711e-05</v>
       </c>
       <c r="J47" t="n">
-        <v>8.18902014205165e-05</v>
+        <v>5.810381564379711e-05</v>
       </c>
     </row>
     <row r="48">
@@ -4093,22 +4094,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.08493991003089077</v>
+        <v>0.08850039773988014</v>
       </c>
       <c r="F48" t="n">
         <v>2.456699651526272</v>
       </c>
       <c r="G48" t="n">
-        <v>2.358155188918248</v>
+        <v>2.352802527307538</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.09854446260802385</v>
+        <v>-0.1038971242187339</v>
       </c>
       <c r="I48" t="n">
-        <v>4.011253982423176</v>
+        <v>4.229134161930856</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.011253982423176</v>
+        <v>-4.229134161930856</v>
       </c>
     </row>
     <row r="49">
@@ -4125,26 +4126,26 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.08493991003089077</v>
+        <v>0.08850039773988014</v>
       </c>
       <c r="F49" t="n">
-        <v>2.7460125</v>
+        <v>2.72750625</v>
       </c>
       <c r="G49" t="n">
-        <v>2.621813626675062</v>
+        <v>2.60785051919474</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1241988733249384</v>
+        <v>-0.1196557308052602</v>
       </c>
       <c r="I49" t="n">
-        <v>4.522880843584594</v>
+        <v>4.387001159218614</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.522880843584594</v>
+        <v>-4.387001159218614</v>
       </c>
     </row>
     <row r="50">
@@ -4165,22 +4166,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.1006439510866089</v>
+        <v>0.1042585113052578</v>
       </c>
       <c r="F50" t="n">
         <v>2.244775</v>
       </c>
       <c r="G50" t="n">
-        <v>2.244777627431825</v>
+        <v>2.244777471000068</v>
       </c>
       <c r="H50" t="n">
-        <v>2.627431824553383e-06</v>
+        <v>2.47100006767198e-06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0001170465558710064</v>
+        <v>0.0001100778504603793</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0001170465558710064</v>
+        <v>0.0001100778504603793</v>
       </c>
     </row>
     <row r="51">
@@ -4201,22 +4202,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.1006439510866089</v>
+        <v>0.1042585113052578</v>
       </c>
       <c r="F51" t="n">
         <v>2.456699651526272</v>
       </c>
       <c r="G51" t="n">
-        <v>2.357236628405331</v>
+        <v>2.351947469376718</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0994630231209408</v>
+        <v>-0.1047521821495541</v>
       </c>
       <c r="I51" t="n">
-        <v>4.048644003313449</v>
+        <v>4.263939309165235</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.048644003313449</v>
+        <v>-4.263939309165235</v>
       </c>
     </row>
     <row r="52">
@@ -4233,26 +4234,26 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.1006439510866089</v>
+        <v>0.1042585113052578</v>
       </c>
       <c r="F52" t="n">
-        <v>2.7460125</v>
+        <v>2.72750625</v>
       </c>
       <c r="G52" t="n">
-        <v>2.620834215593399</v>
+        <v>2.606926203689408</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1251782844066009</v>
+        <v>-0.1205800463105926</v>
       </c>
       <c r="I52" t="n">
-        <v>4.558547508673065</v>
+        <v>4.420889826030375</v>
       </c>
       <c r="J52" t="n">
-        <v>-4.558547508673065</v>
+        <v>-4.420889826030375</v>
       </c>
     </row>
     <row r="53">
@@ -4277,16 +4278,16 @@
         <v>2.244775</v>
       </c>
       <c r="G53" t="n">
-        <v>2.587246182144725</v>
+        <v>2.570034199087754</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3424711821447248</v>
+        <v>0.3252591990877542</v>
       </c>
       <c r="I53" t="n">
-        <v>15.25637011035515</v>
+        <v>14.48961250404848</v>
       </c>
       <c r="J53" t="n">
-        <v>15.25637011035515</v>
+        <v>14.48961250404848</v>
       </c>
     </row>
     <row r="54">
@@ -4311,16 +4312,16 @@
         <v>2.456699651526272</v>
       </c>
       <c r="G54" t="n">
-        <v>2.609613869699913</v>
+        <v>2.592396890285476</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1529142181736409</v>
+        <v>0.1356972387592039</v>
       </c>
       <c r="I54" t="n">
-        <v>6.224375783121881</v>
+        <v>5.523558350932293</v>
       </c>
       <c r="J54" t="n">
-        <v>6.224375783121881</v>
+        <v>5.523558350932293</v>
       </c>
     </row>
     <row r="55">
@@ -4337,24 +4338,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>2.7460125</v>
+        <v>2.72750625</v>
       </c>
       <c r="G55" t="n">
-        <v>2.698884490998216</v>
+        <v>2.681586356482683</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.04712800900178404</v>
+        <v>-0.04591989351731751</v>
       </c>
       <c r="I55" t="n">
-        <v>1.716234321649448</v>
+        <v>1.683585271979396</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.716234321649448</v>
+        <v>-1.683585271979396</v>
       </c>
     </row>
     <row r="56">
@@ -4375,22 +4376,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.08276118906439396</v>
+        <v>0.08631537829714603</v>
       </c>
       <c r="F56" t="n">
         <v>2.26715</v>
       </c>
       <c r="G56" t="n">
-        <v>2.267150526106458</v>
+        <v>2.267151507008899</v>
       </c>
       <c r="H56" t="n">
-        <v>5.261064583983455e-07</v>
+        <v>1.507008899004347e-06</v>
       </c>
       <c r="I56" t="n">
-        <v>2.320563078747968e-05</v>
+        <v>6.647151264823004e-05</v>
       </c>
       <c r="J56" t="n">
-        <v>2.320563078747968e-05</v>
+        <v>6.647151264823004e-05</v>
       </c>
     </row>
     <row r="57">
@@ -4411,22 +4412,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.08276118906439396</v>
+        <v>0.08631537829714603</v>
       </c>
       <c r="F57" t="n">
         <v>2.52625</v>
       </c>
       <c r="G57" t="n">
-        <v>2.380141064700907</v>
+        <v>2.374637713976577</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.1461089352990927</v>
+        <v>-0.1516122860234232</v>
       </c>
       <c r="I57" t="n">
-        <v>5.783629304268886</v>
+        <v>6.001475943529866</v>
       </c>
       <c r="J57" t="n">
-        <v>-5.783629304268886</v>
+        <v>-6.001475943529866</v>
       </c>
     </row>
     <row r="58">
@@ -4443,26 +4444,26 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.08276118906439396</v>
+        <v>0.08631537829714603</v>
       </c>
       <c r="F58" t="n">
-        <v>2.843925</v>
+        <v>2.74761875</v>
       </c>
       <c r="G58" t="n">
-        <v>2.638344159811568</v>
+        <v>2.624182337858529</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.2055808401884325</v>
+        <v>-0.1234364121414706</v>
       </c>
       <c r="I58" t="n">
-        <v>7.22877151079696</v>
+        <v>4.492486890383559</v>
       </c>
       <c r="J58" t="n">
-        <v>-7.22877151079696</v>
+        <v>-4.492486890383559</v>
       </c>
     </row>
     <row r="59">
@@ -4483,22 +4484,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.09759611521820596</v>
+        <v>0.1012018247808178</v>
       </c>
       <c r="F59" t="n">
         <v>2.26715</v>
       </c>
       <c r="G59" t="n">
-        <v>2.267152150661739</v>
+        <v>2.267152033652461</v>
       </c>
       <c r="H59" t="n">
-        <v>2.150661739364068e-06</v>
+        <v>2.033652460653457e-06</v>
       </c>
       <c r="I59" t="n">
-        <v>9.486190765340045e-05</v>
+        <v>8.970083411567196e-05</v>
       </c>
       <c r="J59" t="n">
-        <v>9.486190765340045e-05</v>
+        <v>8.970083411567196e-05</v>
       </c>
     </row>
     <row r="60">
@@ -4519,22 +4520,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.09759611521820596</v>
+        <v>0.1012018247808178</v>
       </c>
       <c r="F60" t="n">
         <v>2.52625</v>
       </c>
       <c r="G60" t="n">
-        <v>2.37926126298398</v>
+        <v>2.373818812401554</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.1469887370160197</v>
+        <v>-0.1524311875984461</v>
       </c>
       <c r="I60" t="n">
-        <v>5.818455695834524</v>
+        <v>6.033891641699993</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.818455695834524</v>
+        <v>-6.033891641699993</v>
       </c>
     </row>
     <row r="61">
@@ -4551,26 +4552,26 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.09759611521820596</v>
+        <v>0.1012018247808178</v>
       </c>
       <c r="F61" t="n">
-        <v>2.843925</v>
+        <v>2.74761875</v>
       </c>
       <c r="G61" t="n">
-        <v>2.637426076001575</v>
+        <v>2.62331603366684</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.2064989239984247</v>
+        <v>-0.12430271633316</v>
       </c>
       <c r="I61" t="n">
-        <v>7.261053790041043</v>
+        <v>4.52401616247378</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.261053790041043</v>
+        <v>-4.52401616247378</v>
       </c>
     </row>
     <row r="62">
@@ -4595,16 +4596,16 @@
         <v>2.26715</v>
       </c>
       <c r="G62" t="n">
-        <v>2.608101343101042</v>
+        <v>2.59074839211692</v>
       </c>
       <c r="H62" t="n">
-        <v>0.3409513431010418</v>
+        <v>0.3235983921169199</v>
       </c>
       <c r="I62" t="n">
-        <v>15.03876422385117</v>
+        <v>14.27335606893765</v>
       </c>
       <c r="J62" t="n">
-        <v>15.03876422385117</v>
+        <v>14.27335606893765</v>
       </c>
     </row>
     <row r="63">
@@ -4629,16 +4630,16 @@
         <v>2.52625</v>
       </c>
       <c r="G63" t="n">
-        <v>2.629285706251272</v>
+        <v>2.611928091879706</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1030357062512715</v>
+        <v>0.08567809187970576</v>
       </c>
       <c r="I63" t="n">
-        <v>4.078602919397188</v>
+        <v>3.391512790883949</v>
       </c>
       <c r="J63" t="n">
-        <v>4.078602919397188</v>
+        <v>3.391512790883949</v>
       </c>
     </row>
     <row r="64">
@@ -4655,24 +4656,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>2.843925</v>
+        <v>2.74761875</v>
       </c>
       <c r="G64" t="n">
-        <v>2.713951049385751</v>
+        <v>2.696517222743544</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.1299739506142492</v>
+        <v>-0.05110152725645634</v>
       </c>
       <c r="I64" t="n">
-        <v>4.570231304069172</v>
+        <v>1.859847813910003</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.570231304069172</v>
+        <v>-1.859847813910003</v>
       </c>
     </row>
     <row r="65">
@@ -4693,22 +4694,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.0686516240624105</v>
+        <v>0.07158956549382131</v>
       </c>
       <c r="F65" t="n">
         <v>2.29725</v>
       </c>
       <c r="G65" t="n">
-        <v>2.297251515968217</v>
+        <v>2.297250261141894</v>
       </c>
       <c r="H65" t="n">
-        <v>1.515968216736496e-06</v>
+        <v>2.611418943310184e-07</v>
       </c>
       <c r="I65" t="n">
-        <v>6.599056335777544e-05</v>
+        <v>1.136758708590787e-05</v>
       </c>
       <c r="J65" t="n">
-        <v>6.599056335777544e-05</v>
+        <v>1.136758708590787e-05</v>
       </c>
     </row>
     <row r="66">
@@ -4729,22 +4730,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.0686516240624105</v>
+        <v>0.07158956549382131</v>
       </c>
       <c r="F66" t="n">
         <v>2.571281674253069</v>
       </c>
       <c r="G66" t="n">
-        <v>2.423216478674765</v>
+        <v>2.417001332812303</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.1480651955783046</v>
+        <v>-0.1542803414407659</v>
       </c>
       <c r="I66" t="n">
-        <v>5.758419898563464</v>
+        <v>6.000133823750861</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.758419898563464</v>
+        <v>-6.000133823750861</v>
       </c>
     </row>
     <row r="67">
@@ -4761,26 +4762,26 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.0686516240624105</v>
+        <v>0.07158956549382131</v>
       </c>
       <c r="F67" t="n">
-        <v>2.9365625</v>
+        <v>2.817765625</v>
       </c>
       <c r="G67" t="n">
-        <v>2.682362011378737</v>
+        <v>2.667482718028084</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.254200488621263</v>
+        <v>-0.1502829069719156</v>
       </c>
       <c r="I67" t="n">
-        <v>8.656396334873275</v>
+        <v>5.333406924925334</v>
       </c>
       <c r="J67" t="n">
-        <v>-8.656396334873275</v>
+        <v>-5.333406924925334</v>
       </c>
     </row>
     <row r="68">
@@ -4801,22 +4802,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.08093469252371924</v>
+        <v>0.08391244363649571</v>
       </c>
       <c r="F68" t="n">
         <v>2.29725</v>
       </c>
       <c r="G68" t="n">
-        <v>2.29724976844685</v>
+        <v>2.297251120734176</v>
       </c>
       <c r="H68" t="n">
-        <v>-2.315531495433731e-07</v>
+        <v>1.120734175685811e-06</v>
       </c>
       <c r="I68" t="n">
-        <v>1.007957991265091e-05</v>
+        <v>4.878590382787295e-05</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.007957991265091e-05</v>
+        <v>4.878590382787295e-05</v>
       </c>
     </row>
     <row r="69">
@@ -4837,22 +4838,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.08093469252371924</v>
+        <v>0.08391244363649571</v>
       </c>
       <c r="F69" t="n">
         <v>2.571281674253069</v>
       </c>
       <c r="G69" t="n">
-        <v>2.42231834822751</v>
+        <v>2.416163507745431</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.1489633260255592</v>
+        <v>-0.1551181665076382</v>
       </c>
       <c r="I69" t="n">
-        <v>5.79334918912886</v>
+        <v>6.032717771097499</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.79334918912886</v>
+        <v>-6.032717771097499</v>
       </c>
     </row>
     <row r="70">
@@ -4869,26 +4870,26 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.08093469252371924</v>
+        <v>0.08391244363649571</v>
       </c>
       <c r="F70" t="n">
-        <v>2.9365625</v>
+        <v>2.817765625</v>
       </c>
       <c r="G70" t="n">
-        <v>2.681540576767068</v>
+        <v>2.6667037653719</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.255021923232932</v>
+        <v>-0.1510618596281001</v>
       </c>
       <c r="I70" t="n">
-        <v>8.68436899377868</v>
+        <v>5.361051263023345</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.68436899377868</v>
+        <v>-5.361051263023345</v>
       </c>
     </row>
     <row r="71">
@@ -4913,16 +4914,16 @@
         <v>2.29725</v>
       </c>
       <c r="G71" t="n">
-        <v>2.667914402818009</v>
+        <v>2.650157217684618</v>
       </c>
       <c r="H71" t="n">
-        <v>0.3706644028180088</v>
+        <v>0.3529072176846175</v>
       </c>
       <c r="I71" t="n">
-        <v>16.13513561075237</v>
+        <v>15.3621598730925</v>
       </c>
       <c r="J71" t="n">
-        <v>16.13513561075237</v>
+        <v>15.3621598730925</v>
       </c>
     </row>
     <row r="72">
@@ -4947,16 +4948,16 @@
         <v>2.571281674253069</v>
       </c>
       <c r="G72" t="n">
-        <v>2.685739757057783</v>
+        <v>2.66797880698259</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1144580828047133</v>
+        <v>0.09669713272952052</v>
       </c>
       <c r="I72" t="n">
-        <v>4.451401958440129</v>
+        <v>3.760658884546752</v>
       </c>
       <c r="J72" t="n">
-        <v>4.451401958440129</v>
+        <v>3.760658884546752</v>
       </c>
     </row>
     <row r="73">
@@ -4973,24 +4974,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>2.9365625</v>
+        <v>2.817765625</v>
       </c>
       <c r="G73" t="n">
-        <v>2.757255366256466</v>
+        <v>2.739431827568888</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.1793071337435341</v>
+        <v>-0.07833379743111157</v>
       </c>
       <c r="I73" t="n">
-        <v>6.106021368301684</v>
+        <v>2.779996914438602</v>
       </c>
       <c r="J73" t="n">
-        <v>-6.106021368301684</v>
+        <v>-2.779996914438602</v>
       </c>
     </row>
     <row r="74">
@@ -5011,22 +5012,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.0673326179058804</v>
+        <v>0.07041259839357857</v>
       </c>
       <c r="F74" t="n">
         <v>2.3428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.342800396380618</v>
+        <v>2.342801509019341</v>
       </c>
       <c r="H74" t="n">
-        <v>3.963806181062068e-07</v>
+        <v>1.509019341039419e-06</v>
       </c>
       <c r="I74" t="n">
-        <v>1.691909758008396e-05</v>
+        <v>6.441093311590489e-05</v>
       </c>
       <c r="J74" t="n">
-        <v>1.691909758008396e-05</v>
+        <v>6.441093311590489e-05</v>
       </c>
     </row>
     <row r="75">
@@ -5047,22 +5048,22 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.0673326179058804</v>
+        <v>0.07041259839357857</v>
       </c>
       <c r="F75" t="n">
         <v>2.72115</v>
       </c>
       <c r="G75" t="n">
-        <v>2.463953680236925</v>
+        <v>2.457505936937394</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.2571963197630751</v>
+        <v>-0.2636440630626056</v>
       </c>
       <c r="I75" t="n">
-        <v>9.451750905428776</v>
+        <v>9.68870011071075</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.451750905428776</v>
+        <v>-9.68870011071075</v>
       </c>
     </row>
     <row r="76">
@@ -5079,26 +5080,26 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.0673326179058804</v>
+        <v>0.07041259839357857</v>
       </c>
       <c r="F76" t="n">
-        <v>2.9926125</v>
+        <v>2.965825</v>
       </c>
       <c r="G76" t="n">
-        <v>2.708210851653726</v>
+        <v>2.693044111791967</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.2844016483462743</v>
+        <v>-0.2727808882080329</v>
       </c>
       <c r="I76" t="n">
-        <v>9.503457208251129</v>
+        <v>9.197470795074993</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.503457208251129</v>
+        <v>-9.197470795074993</v>
       </c>
     </row>
     <row r="77">
@@ -5119,22 +5120,22 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.07846317333991787</v>
+        <v>0.08158045301163148</v>
       </c>
       <c r="F77" t="n">
         <v>2.3428</v>
       </c>
       <c r="G77" t="n">
-        <v>2.342800815080572</v>
+        <v>2.342799813544805</v>
       </c>
       <c r="H77" t="n">
-        <v>8.150805723694532e-07</v>
+        <v>-1.864551943953074e-07</v>
       </c>
       <c r="I77" t="n">
-        <v>3.479087298828126e-05</v>
+        <v>7.95864753266636e-06</v>
       </c>
       <c r="J77" t="n">
-        <v>3.479087298828126e-05</v>
+        <v>-7.95864753266636e-06</v>
       </c>
     </row>
     <row r="78">
@@ -5155,22 +5156,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.07846317333991787</v>
+        <v>0.08158045301163148</v>
       </c>
       <c r="F78" t="n">
         <v>2.72115</v>
       </c>
       <c r="G78" t="n">
-        <v>2.463163364367999</v>
+        <v>2.456769354850167</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.2579866356320011</v>
+        <v>-0.2643806451498323</v>
       </c>
       <c r="I78" t="n">
-        <v>9.480794356503724</v>
+        <v>9.715768889985203</v>
       </c>
       <c r="J78" t="n">
-        <v>-9.480794356503724</v>
+        <v>-9.715768889985203</v>
       </c>
     </row>
     <row r="79">
@@ -5187,26 +5188,26 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.07846317333991787</v>
+        <v>0.08158045301163148</v>
       </c>
       <c r="F79" t="n">
-        <v>2.9926125</v>
+        <v>2.965825</v>
       </c>
       <c r="G79" t="n">
-        <v>2.707505171792008</v>
+        <v>2.692375992688834</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.2851073282079928</v>
+        <v>-0.2734490073111662</v>
       </c>
       <c r="I79" t="n">
-        <v>9.527037937855059</v>
+        <v>9.219998054880723</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.527037937855059</v>
+        <v>-9.219998054880723</v>
       </c>
     </row>
     <row r="80">
@@ -5231,16 +5232,16 @@
         <v>2.3428</v>
       </c>
       <c r="G80" t="n">
-        <v>2.697385813694907</v>
+        <v>2.679429486166996</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3545858136949072</v>
+        <v>0.3366294861669963</v>
       </c>
       <c r="I80" t="n">
-        <v>15.13512949013604</v>
+        <v>14.36868218230307</v>
       </c>
       <c r="J80" t="n">
-        <v>15.13512949013604</v>
+        <v>14.36868218230307</v>
       </c>
     </row>
     <row r="81">
@@ -5265,16 +5266,16 @@
         <v>2.72115</v>
       </c>
       <c r="G81" t="n">
-        <v>2.713574397133322</v>
+        <v>2.695614718390474</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.007575602866678022</v>
+        <v>-0.02553528160952556</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2783971066158802</v>
+        <v>0.9384003678417421</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.2783971066158802</v>
+        <v>-0.9384003678417421</v>
       </c>
     </row>
     <row r="82">
@@ -5291,24 +5292,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2.9926125</v>
+        <v>2.965825</v>
       </c>
       <c r="G82" t="n">
-        <v>2.778642171310084</v>
+        <v>2.760626326100678</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.2139703286899168</v>
+        <v>-0.2051986738993219</v>
       </c>
       <c r="I82" t="n">
-        <v>7.149951044110015</v>
+        <v>6.918772142635587</v>
       </c>
       <c r="J82" t="n">
-        <v>-7.149951044110015</v>
+        <v>-6.918772142635587</v>
       </c>
     </row>
     <row r="83">
@@ -5329,22 +5330,22 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.07226117671732123</v>
+        <v>0.07519263589067139</v>
       </c>
       <c r="F83" t="n">
         <v>2.252275</v>
       </c>
       <c r="G83" t="n">
-        <v>2.252277618126914</v>
+        <v>2.252276590197015</v>
       </c>
       <c r="H83" t="n">
-        <v>2.618126913489505e-06</v>
+        <v>1.590197014955663e-06</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0001162436608979589</v>
+        <v>7.060403436328437e-05</v>
       </c>
       <c r="J83" t="n">
-        <v>0.0001162436608979589</v>
+        <v>7.060403436328437e-05</v>
       </c>
     </row>
     <row r="84">
@@ -5365,22 +5366,22 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.07226117671732123</v>
+        <v>0.07519263589067139</v>
       </c>
       <c r="F84" t="n">
         <v>2.528852109678786</v>
       </c>
       <c r="G84" t="n">
-        <v>2.379496032322244</v>
+        <v>2.373612969180974</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.1493560773565417</v>
+        <v>-0.1552391404978115</v>
       </c>
       <c r="I84" t="n">
-        <v>5.90608192487432</v>
+        <v>6.138719615261722</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.90608192487432</v>
+        <v>-6.138719615261722</v>
       </c>
     </row>
     <row r="85">
@@ -5397,26 +5398,26 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.07226117671732123</v>
+        <v>0.07519263589067139</v>
       </c>
       <c r="F85" t="n">
-        <v>2.82315</v>
+        <v>2.768703125</v>
       </c>
       <c r="G85" t="n">
-        <v>2.651091826530582</v>
+        <v>2.636597197011161</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.1720581734694178</v>
+        <v>-0.1321059279888388</v>
       </c>
       <c r="I85" t="n">
-        <v>6.094545931651445</v>
+        <v>4.771400978168751</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.094545931651445</v>
+        <v>-4.771400978168751</v>
       </c>
     </row>
     <row r="86">
@@ -5437,22 +5438,22 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.08606582607634179</v>
+        <v>0.08904076119261407</v>
       </c>
       <c r="F86" t="n">
         <v>2.252275</v>
       </c>
       <c r="G86" t="n">
-        <v>2.252274575062615</v>
+        <v>2.252276633895959</v>
       </c>
       <c r="H86" t="n">
-        <v>-4.249373852793781e-07</v>
+        <v>1.633895958530474e-06</v>
       </c>
       <c r="I86" t="n">
-        <v>1.886702934940796e-05</v>
+        <v>7.254424786184962e-05</v>
       </c>
       <c r="J86" t="n">
-        <v>-1.886702934940796e-05</v>
+        <v>7.254424786184962e-05</v>
       </c>
     </row>
     <row r="87">
@@ -5473,22 +5474,22 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.08606582607634179</v>
+        <v>0.08904076119261407</v>
       </c>
       <c r="F87" t="n">
         <v>2.528852109678786</v>
       </c>
       <c r="G87" t="n">
-        <v>2.378502925677096</v>
+        <v>2.37268426284412</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.1503491840016902</v>
+        <v>-0.1561678468346654</v>
       </c>
       <c r="I87" t="n">
-        <v>5.945352969683446</v>
+        <v>6.17544403790785</v>
       </c>
       <c r="J87" t="n">
-        <v>-5.945352969683446</v>
+        <v>-6.17544403790785</v>
       </c>
     </row>
     <row r="88">
@@ -5505,26 +5506,26 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.08606582607634179</v>
+        <v>0.08904076119261407</v>
       </c>
       <c r="F88" t="n">
-        <v>2.82315</v>
+        <v>2.768703125</v>
       </c>
       <c r="G88" t="n">
-        <v>2.650141367940258</v>
+        <v>2.63569512335154</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.1730086320597422</v>
+        <v>-0.1330080016484598</v>
       </c>
       <c r="I88" t="n">
-        <v>6.128212530674677</v>
+        <v>4.803982068263813</v>
       </c>
       <c r="J88" t="n">
-        <v>-6.128212530674677</v>
+        <v>-4.803982068263813</v>
       </c>
     </row>
     <row r="89">
@@ -5549,16 +5550,16 @@
         <v>2.252275</v>
       </c>
       <c r="G89" t="n">
-        <v>2.630206581689275</v>
+        <v>2.612704225994188</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3779315816892752</v>
+        <v>0.3604292259941877</v>
       </c>
       <c r="I89" t="n">
-        <v>16.77999274907705</v>
+        <v>16.00289600489228</v>
       </c>
       <c r="J89" t="n">
-        <v>16.77999274907705</v>
+        <v>16.00289600489228</v>
       </c>
     </row>
     <row r="90">
@@ -5583,16 +5584,16 @@
         <v>2.528852109678786</v>
       </c>
       <c r="G90" t="n">
-        <v>2.650143623737185</v>
+        <v>2.632636946221275</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1212915140583997</v>
+        <v>0.1037848365424896</v>
       </c>
       <c r="I90" t="n">
-        <v>4.796307130582108</v>
+        <v>4.10402949801886</v>
       </c>
       <c r="J90" t="n">
-        <v>4.796307130582108</v>
+        <v>4.10402949801886</v>
       </c>
     </row>
     <row r="91">
@@ -5609,24 +5610,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
-        <v>2.82315</v>
+        <v>2.768703125</v>
       </c>
       <c r="G91" t="n">
-        <v>2.72993917166216</v>
+        <v>2.712361410897659</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.09321082833783967</v>
+        <v>-0.05634171410234057</v>
       </c>
       <c r="I91" t="n">
-        <v>3.301660497594519</v>
+        <v>2.03494963376908</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.301660497594519</v>
+        <v>-2.03494963376908</v>
       </c>
     </row>
     <row r="92">
@@ -5647,22 +5648,22 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.08084776359136987</v>
+        <v>0.08455531212179532</v>
       </c>
       <c r="F92" t="n">
         <v>2.31575</v>
       </c>
       <c r="G92" t="n">
-        <v>2.315751302417919</v>
+        <v>2.315750635678214</v>
       </c>
       <c r="H92" t="n">
-        <v>1.302417918846999e-06</v>
+        <v>6.35678213622981e-07</v>
       </c>
       <c r="I92" t="n">
-        <v>5.624173243428689e-05</v>
+        <v>2.745020894409936e-05</v>
       </c>
       <c r="J92" t="n">
-        <v>5.624173243428689e-05</v>
+        <v>2.745020894409936e-05</v>
       </c>
     </row>
     <row r="93">
@@ -5683,22 +5684,22 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.08084776359136987</v>
+        <v>0.08455531212179532</v>
       </c>
       <c r="F93" t="n">
         <v>2.621187071667337</v>
       </c>
       <c r="G93" t="n">
-        <v>2.424723000878434</v>
+        <v>2.418984344459306</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.1964640707889029</v>
+        <v>-0.2022027272080309</v>
       </c>
       <c r="I93" t="n">
-        <v>7.495232710114511</v>
+        <v>7.714166203307639</v>
       </c>
       <c r="J93" t="n">
-        <v>-7.495232710114511</v>
+        <v>-7.714166203307639</v>
       </c>
     </row>
     <row r="94">
@@ -5715,26 +5716,26 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.08084776359136987</v>
+        <v>0.08455531212179532</v>
       </c>
       <c r="F94" t="n">
-        <v>2.92005</v>
+        <v>2.839534374999999</v>
       </c>
       <c r="G94" t="n">
-        <v>2.668472493709466</v>
+        <v>2.653983380357526</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.2515775062905341</v>
+        <v>-0.1855509946424734</v>
       </c>
       <c r="I94" t="n">
-        <v>8.615520497612511</v>
+        <v>6.534557083587813</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.615520497612511</v>
+        <v>-6.534557083587813</v>
       </c>
     </row>
     <row r="95">
@@ -5755,22 +5756,22 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.09422402916391198</v>
+        <v>0.09798106554163073</v>
       </c>
       <c r="F95" t="n">
         <v>2.31575</v>
       </c>
       <c r="G95" t="n">
-        <v>2.31575310895884</v>
+        <v>2.315752347417197</v>
       </c>
       <c r="H95" t="n">
-        <v>3.108958839703746e-06</v>
+        <v>2.347417196624235e-06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0001342527837505666</v>
+        <v>0.0001013674704361108</v>
       </c>
       <c r="J95" t="n">
-        <v>0.0001342527837505666</v>
+        <v>0.0001013674704361108</v>
       </c>
     </row>
     <row r="96">
@@ -5791,22 +5792,22 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.09422402916391198</v>
+        <v>0.09798106554163073</v>
       </c>
       <c r="F96" t="n">
         <v>2.621187071667337</v>
       </c>
       <c r="G96" t="n">
-        <v>2.423944251804883</v>
+        <v>2.418263409140534</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.1972428198624541</v>
+        <v>-0.2029236625268029</v>
       </c>
       <c r="I96" t="n">
-        <v>7.524942496263264</v>
+        <v>7.741670356924322</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.524942496263264</v>
+        <v>-7.741670356924322</v>
       </c>
     </row>
     <row r="97">
@@ -5823,26 +5824,26 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.09422402916391198</v>
+        <v>0.09798106554163073</v>
       </c>
       <c r="F97" t="n">
-        <v>2.92005</v>
+        <v>2.839534374999999</v>
       </c>
       <c r="G97" t="n">
-        <v>2.667681447100861</v>
+        <v>2.653238952013967</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.2523685528991386</v>
+        <v>-0.1862954229860323</v>
       </c>
       <c r="I97" t="n">
-        <v>8.642610671020655</v>
+        <v>6.560773647476352</v>
       </c>
       <c r="J97" t="n">
-        <v>-8.642610671020655</v>
+        <v>-6.560773647476352</v>
       </c>
     </row>
     <row r="98">
@@ -5867,16 +5868,16 @@
         <v>2.31575</v>
       </c>
       <c r="G98" t="n">
-        <v>2.644147923665029</v>
+        <v>2.626551348055255</v>
       </c>
       <c r="H98" t="n">
-        <v>0.3283979236650287</v>
+        <v>0.3108013480552549</v>
       </c>
       <c r="I98" t="n">
-        <v>14.18106115362318</v>
+        <v>13.42119607277361</v>
       </c>
       <c r="J98" t="n">
-        <v>14.18106115362318</v>
+        <v>13.42119607277361</v>
       </c>
     </row>
     <row r="99">
@@ -5901,16 +5902,16 @@
         <v>2.621187071667337</v>
       </c>
       <c r="G99" t="n">
-        <v>2.663301904809863</v>
+        <v>2.645701216978256</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0421148331425254</v>
+        <v>0.02451414531091878</v>
       </c>
       <c r="I99" t="n">
-        <v>1.606708410771161</v>
+        <v>0.9352306661319418</v>
       </c>
       <c r="J99" t="n">
-        <v>1.606708410771161</v>
+        <v>0.9352306661319418</v>
       </c>
     </row>
     <row r="100">
@@ -5927,24 +5928,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
-        <v>2.92005</v>
+        <v>2.839534374999999</v>
       </c>
       <c r="G100" t="n">
-        <v>2.74003222675439</v>
+        <v>2.722363633273887</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.1800177732456101</v>
+        <v>-0.1171707417261123</v>
       </c>
       <c r="I100" t="n">
-        <v>6.164886671310768</v>
+        <v>4.126406877046957</v>
       </c>
       <c r="J100" t="n">
-        <v>-6.164886671310768</v>
+        <v>-4.126406877046957</v>
       </c>
     </row>
     <row r="101">
@@ -5965,22 +5966,22 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.07477155005067269</v>
+        <v>0.07649558994396405</v>
       </c>
       <c r="F101" t="n">
         <v>1.7076125</v>
       </c>
       <c r="G101" t="n">
-        <v>1.707615336709844</v>
+        <v>1.707614570246329</v>
       </c>
       <c r="H101" t="n">
-        <v>2.836709844133978e-06</v>
+        <v>2.070246329255454e-06</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0001661214030779218</v>
+        <v>0.0001212363067883056</v>
       </c>
       <c r="J101" t="n">
-        <v>0.0001661214030779218</v>
+        <v>0.0001212363067883056</v>
       </c>
     </row>
     <row r="102">
@@ -6001,22 +6002,22 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.07477155005067269</v>
+        <v>0.07649558994396405</v>
       </c>
       <c r="F102" t="n">
         <v>2.05415</v>
       </c>
       <c r="G102" t="n">
-        <v>1.885017262983104</v>
+        <v>1.881066852545637</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.1691327370168956</v>
+        <v>-0.1730831474543628</v>
       </c>
       <c r="I102" t="n">
-        <v>8.233709174933455</v>
+        <v>8.426022805265577</v>
       </c>
       <c r="J102" t="n">
-        <v>-8.233709174933455</v>
+        <v>-8.426022805265577</v>
       </c>
     </row>
     <row r="103">
@@ -6033,26 +6034,26 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.07477155005067269</v>
+        <v>0.07649558994396405</v>
       </c>
       <c r="F103" t="n">
-        <v>2.5313125</v>
+        <v>2.45671875</v>
       </c>
       <c r="G103" t="n">
-        <v>2.319019212211317</v>
+        <v>2.307684191971352</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.2122932877886829</v>
+        <v>-0.1490345580286476</v>
       </c>
       <c r="I103" t="n">
-        <v>8.386688241324727</v>
+        <v>6.066406992198339</v>
       </c>
       <c r="J103" t="n">
-        <v>-8.386688241324727</v>
+        <v>-6.066406992198339</v>
       </c>
     </row>
     <row r="104">
@@ -6073,22 +6074,22 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.1057255571936795</v>
+        <v>0.1075030182024911</v>
       </c>
       <c r="F104" t="n">
         <v>1.7076125</v>
       </c>
       <c r="G104" t="n">
-        <v>1.707617034689004</v>
+        <v>1.707614667005786</v>
       </c>
       <c r="H104" t="n">
-        <v>4.534689003854453e-06</v>
+        <v>2.167005785924658e-06</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0002655572621923565</v>
+        <v>0.000126902665910718</v>
       </c>
       <c r="J104" t="n">
-        <v>0.0002655572621923565</v>
+        <v>0.000126902665910718</v>
       </c>
     </row>
     <row r="105">
@@ -6109,22 +6110,22 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.1057255571936795</v>
+        <v>0.1075030182024911</v>
       </c>
       <c r="F105" t="n">
         <v>2.05415</v>
       </c>
       <c r="G105" t="n">
-        <v>1.882166169120913</v>
+        <v>1.878313133974517</v>
       </c>
       <c r="H105" t="n">
-        <v>-0.1719838308790866</v>
+        <v>-0.1758368660254825</v>
       </c>
       <c r="I105" t="n">
-        <v>8.37250594548045</v>
+        <v>8.560079158069399</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.37250594548045</v>
+        <v>-8.560079158069399</v>
       </c>
     </row>
     <row r="106">
@@ -6141,26 +6142,26 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.1057255571936795</v>
+        <v>0.1075030182024911</v>
       </c>
       <c r="F106" t="n">
-        <v>2.5313125</v>
+        <v>2.45671875</v>
       </c>
       <c r="G106" t="n">
-        <v>2.315758578378899</v>
+        <v>2.304531923603168</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.2155539216211007</v>
+        <v>-0.1521868263968322</v>
       </c>
       <c r="I106" t="n">
-        <v>8.515500224531767</v>
+        <v>6.19471913082571</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.515500224531767</v>
+        <v>-6.19471913082571</v>
       </c>
     </row>
     <row r="107">
@@ -6185,16 +6186,16 @@
         <v>1.7076125</v>
       </c>
       <c r="G107" t="n">
-        <v>2.221898684349125</v>
+        <v>2.207158491727935</v>
       </c>
       <c r="H107" t="n">
-        <v>0.5142861843491251</v>
+        <v>0.4995459917279352</v>
       </c>
       <c r="I107" t="n">
-        <v>30.11726514938988</v>
+        <v>29.25406037540339</v>
       </c>
       <c r="J107" t="n">
-        <v>30.11726514938988</v>
+        <v>29.25406037540339</v>
       </c>
     </row>
     <row r="108">
@@ -6219,16 +6220,16 @@
         <v>2.05415</v>
       </c>
       <c r="G108" t="n">
-        <v>2.26618579182624</v>
+        <v>2.251432596633856</v>
       </c>
       <c r="H108" t="n">
-        <v>0.2120357918262399</v>
+        <v>0.1972825966338556</v>
       </c>
       <c r="I108" t="n">
-        <v>10.32231296771121</v>
+        <v>9.60409885518855</v>
       </c>
       <c r="J108" t="n">
-        <v>10.32231296771121</v>
+        <v>9.60409885518855</v>
       </c>
     </row>
     <row r="109">
@@ -6245,24 +6246,24 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
-        <v>2.5313125</v>
+        <v>2.45671875</v>
       </c>
       <c r="G109" t="n">
-        <v>2.43792328209438</v>
+        <v>2.422983576687585</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.09338921790561994</v>
+        <v>-0.03373517331241516</v>
       </c>
       <c r="I109" t="n">
-        <v>3.689359488629711</v>
+        <v>1.373180113206494</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.689359488629711</v>
+        <v>-1.373180113206494</v>
       </c>
     </row>
     <row r="110">
@@ -6283,22 +6284,22 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.08351820846465208</v>
+        <v>0.08746020600723745</v>
       </c>
       <c r="F110" t="n">
         <v>2.3283</v>
       </c>
       <c r="G110" t="n">
-        <v>2.328298885339837</v>
+        <v>2.328299080399431</v>
       </c>
       <c r="H110" t="n">
-        <v>-1.114660163281656e-06</v>
+        <v>-9.196005690270681e-07</v>
       </c>
       <c r="I110" t="n">
-        <v>4.787442182200125e-05</v>
+        <v>3.949665288094609e-05</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.787442182200125e-05</v>
+        <v>-3.949665288094609e-05</v>
       </c>
     </row>
     <row r="111">
@@ -6319,22 +6320,22 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.08351820846465208</v>
+        <v>0.08746020600723745</v>
       </c>
       <c r="F111" t="n">
         <v>2.4123875</v>
       </c>
       <c r="G111" t="n">
-        <v>2.433031264075793</v>
+        <v>2.427355269123317</v>
       </c>
       <c r="H111" t="n">
-        <v>0.02064376407579349</v>
+        <v>0.01496776912331743</v>
       </c>
       <c r="I111" t="n">
-        <v>0.8557399702905729</v>
+        <v>0.6204545962585792</v>
       </c>
       <c r="J111" t="n">
-        <v>0.8557399702905729</v>
+        <v>0.6204545962585792</v>
       </c>
     </row>
     <row r="112">
@@ -6351,26 +6352,26 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.08351820846465208</v>
+        <v>0.08746020600723745</v>
       </c>
       <c r="F112" t="n">
-        <v>2.8098625</v>
+        <v>2.71143125</v>
       </c>
       <c r="G112" t="n">
-        <v>2.670723114621937</v>
+        <v>2.656266745868415</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.1391393853780629</v>
+        <v>-0.05516450413158402</v>
       </c>
       <c r="I112" t="n">
-        <v>4.951821855270958</v>
+        <v>2.034516056108155</v>
       </c>
       <c r="J112" t="n">
-        <v>-4.951821855270958</v>
+        <v>-2.034516056108155</v>
       </c>
     </row>
     <row r="113">
@@ -6391,22 +6392,22 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.09689548616632374</v>
+        <v>0.1008884035969615</v>
       </c>
       <c r="F113" t="n">
         <v>2.3283</v>
       </c>
       <c r="G113" t="n">
-        <v>2.328300599395513</v>
+        <v>2.328298088271562</v>
       </c>
       <c r="H113" t="n">
-        <v>5.993955127792105e-07</v>
+        <v>-1.911728438663829e-06</v>
       </c>
       <c r="I113" t="n">
-        <v>2.574391241589187e-05</v>
+        <v>8.21083382151711e-05</v>
       </c>
       <c r="J113" t="n">
-        <v>2.574391241589187e-05</v>
+        <v>-8.21083382151711e-05</v>
       </c>
     </row>
     <row r="114">
@@ -6427,22 +6428,22 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.09689548616632374</v>
+        <v>0.1008884035969615</v>
       </c>
       <c r="F114" t="n">
         <v>2.4123875</v>
       </c>
       <c r="G114" t="n">
-        <v>2.432295742374642</v>
+        <v>2.426674898062199</v>
       </c>
       <c r="H114" t="n">
-        <v>0.01990824237464173</v>
+        <v>0.0142873980621987</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8252506023448443</v>
+        <v>0.5922513718131394</v>
       </c>
       <c r="J114" t="n">
-        <v>0.8252506023448443</v>
+        <v>0.5922513718131394</v>
       </c>
     </row>
     <row r="115">
@@ -6459,26 +6460,26 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.09689548616632374</v>
+        <v>0.1008884035969615</v>
       </c>
       <c r="F115" t="n">
-        <v>2.8098625</v>
+        <v>2.71143125</v>
       </c>
       <c r="G115" t="n">
-        <v>2.669962488130402</v>
+        <v>2.65555241605321</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.1399000118695981</v>
+        <v>-0.05587883394678972</v>
       </c>
       <c r="I115" t="n">
-        <v>4.978891738282499</v>
+        <v>2.060861176059313</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.978891738282499</v>
+        <v>-2.060861176059313</v>
       </c>
     </row>
     <row r="116">
@@ -6503,16 +6504,16 @@
         <v>2.3283</v>
       </c>
       <c r="G116" t="n">
-        <v>2.645016788226815</v>
+        <v>2.6274143407304</v>
       </c>
       <c r="H116" t="n">
-        <v>0.316716788226814</v>
+        <v>0.2991143407303998</v>
       </c>
       <c r="I116" t="n">
-        <v>13.60292008017927</v>
+        <v>12.84689862691233</v>
       </c>
       <c r="J116" t="n">
-        <v>13.60292008017927</v>
+        <v>12.84689862691233</v>
       </c>
     </row>
     <row r="117">
@@ -6537,16 +6538,16 @@
         <v>2.4123875</v>
       </c>
       <c r="G117" t="n">
-        <v>2.664122057829173</v>
+        <v>2.646515511027802</v>
       </c>
       <c r="H117" t="n">
-        <v>0.251734557829173</v>
+        <v>0.2341280110278019</v>
       </c>
       <c r="I117" t="n">
-        <v>10.43507968057258</v>
+        <v>9.705240597864229</v>
       </c>
       <c r="J117" t="n">
-        <v>10.43507968057258</v>
+        <v>9.705240597864229</v>
       </c>
     </row>
     <row r="118">
@@ -6563,24 +6564,24 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
-        <v>2.8098625</v>
+        <v>2.71143125</v>
       </c>
       <c r="G118" t="n">
-        <v>2.740661500513331</v>
+        <v>2.722987244653933</v>
       </c>
       <c r="H118" t="n">
-        <v>-0.06920099948666891</v>
+        <v>0.01155599465393342</v>
       </c>
       <c r="I118" t="n">
-        <v>2.462789531041782</v>
+        <v>0.4261953775864103</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.462789531041782</v>
+        <v>0.4261953775864103</v>
       </c>
     </row>
     <row r="119">
@@ -6601,22 +6602,22 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.1329158412060047</v>
+        <v>0.2186428755542171</v>
       </c>
       <c r="F119" t="n">
         <v>2.3587375</v>
       </c>
       <c r="G119" t="n">
-        <v>2.358737915005936</v>
+        <v>2.455950470799049</v>
       </c>
       <c r="H119" t="n">
-        <v>4.150059362828529e-07</v>
+        <v>0.097212970799049</v>
       </c>
       <c r="I119" t="n">
-        <v>1.759440956371164e-05</v>
+        <v>4.121398451461809</v>
       </c>
       <c r="J119" t="n">
-        <v>1.759440956371164e-05</v>
+        <v>4.121398451461809</v>
       </c>
     </row>
     <row r="120">
@@ -6637,22 +6638,22 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.1329158412060047</v>
+        <v>0.2186428755542171</v>
       </c>
       <c r="F120" t="n">
         <v>2.497631302525579</v>
       </c>
       <c r="G120" t="n">
-        <v>2.429258977943789</v>
+        <v>2.497630668499415</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.06837232458178955</v>
+        <v>-6.34026164014756e-07</v>
       </c>
       <c r="I120" t="n">
-        <v>2.737486694399296</v>
+        <v>2.538509840798501e-05</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.737486694399296</v>
+        <v>-2.538509840798501e-05</v>
       </c>
     </row>
     <row r="121">
@@ -6669,26 +6670,26 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.1329158412060047</v>
+        <v>0.2186428755542171</v>
       </c>
       <c r="F121" t="n">
-        <v>2.7946125</v>
+        <v>2.770865625</v>
       </c>
       <c r="G121" t="n">
-        <v>2.627913101767506</v>
+        <v>2.637394704142605</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.166699398232494</v>
+        <v>-0.1334709208573948</v>
       </c>
       <c r="I121" t="n">
-        <v>5.965027288487903</v>
+        <v>4.816939502701246</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.965027288487903</v>
+        <v>-4.816939502701246</v>
       </c>
     </row>
     <row r="122">
@@ -6709,22 +6710,22 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.2135576073938147</v>
+        <v>0.236819832402668</v>
       </c>
       <c r="F122" t="n">
         <v>2.3587375</v>
       </c>
       <c r="G122" t="n">
-        <v>2.451293337184489</v>
+        <v>2.456130411964771</v>
       </c>
       <c r="H122" t="n">
-        <v>0.09255583718448923</v>
+        <v>0.09739291196477051</v>
       </c>
       <c r="I122" t="n">
-        <v>3.923956658360213</v>
+        <v>4.12902715816281</v>
       </c>
       <c r="J122" t="n">
-        <v>3.923956658360213</v>
+        <v>4.12902715816281</v>
       </c>
     </row>
     <row r="123">
@@ -6745,22 +6746,22 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.2135576073938147</v>
+        <v>0.236819832402668</v>
       </c>
       <c r="F123" t="n">
         <v>2.497631302525579</v>
       </c>
       <c r="G123" t="n">
-        <v>2.497631171149953</v>
+        <v>2.497630544049202</v>
       </c>
       <c r="H123" t="n">
-        <v>-1.313756263776611e-07</v>
+        <v>-7.584763768164748e-07</v>
       </c>
       <c r="I123" t="n">
-        <v>5.260008802933219e-06</v>
+        <v>3.036782795160804e-05</v>
       </c>
       <c r="J123" t="n">
-        <v>-5.260008802933219e-06</v>
+        <v>-3.036782795160804e-05</v>
       </c>
     </row>
     <row r="124">
@@ -6777,26 +6778,26 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.2135576073938147</v>
+        <v>0.236819832402668</v>
       </c>
       <c r="F124" t="n">
-        <v>2.7946125</v>
+        <v>2.770865625</v>
       </c>
       <c r="G124" t="n">
-        <v>2.648335351648714</v>
+        <v>2.637206324771463</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.1462771483512868</v>
+        <v>-0.1336593002285373</v>
       </c>
       <c r="I124" t="n">
-        <v>5.234255137386195</v>
+        <v>4.823738077465858</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.234255137386195</v>
+        <v>-4.823738077465858</v>
       </c>
     </row>
     <row r="125">
@@ -6821,16 +6822,16 @@
         <v>2.3587375</v>
       </c>
       <c r="G125" t="n">
-        <v>2.565259313928121</v>
+        <v>2.548195961611665</v>
       </c>
       <c r="H125" t="n">
-        <v>0.2065218139281204</v>
+        <v>0.189458461611665</v>
       </c>
       <c r="I125" t="n">
-        <v>8.755608198373935</v>
+        <v>8.032197801224807</v>
       </c>
       <c r="J125" t="n">
-        <v>8.755608198373935</v>
+        <v>8.032197801224807</v>
       </c>
     </row>
     <row r="126">
@@ -6855,16 +6856,16 @@
         <v>2.497631302525579</v>
       </c>
       <c r="G126" t="n">
-        <v>2.588881566381812</v>
+        <v>2.571812854971821</v>
       </c>
       <c r="H126" t="n">
-        <v>0.09125026385623292</v>
+        <v>0.07418155244624192</v>
       </c>
       <c r="I126" t="n">
-        <v>3.653472142343892</v>
+        <v>2.970076182630731</v>
       </c>
       <c r="J126" t="n">
-        <v>3.653472142343892</v>
+        <v>2.970076182630731</v>
       </c>
     </row>
     <row r="127">
@@ -6881,24 +6882,24 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>2.7946125</v>
+        <v>2.770865625</v>
       </c>
       <c r="G127" t="n">
-        <v>2.683018893899296</v>
+        <v>2.665863704782232</v>
       </c>
       <c r="H127" t="n">
-        <v>-0.1115936061007039</v>
+        <v>-0.1050019202177674</v>
       </c>
       <c r="I127" t="n">
-        <v>3.993169217582183</v>
+        <v>3.789498821970749</v>
       </c>
       <c r="J127" t="n">
-        <v>-3.993169217582183</v>
+        <v>-3.789498821970749</v>
       </c>
     </row>
     <row r="128">
@@ -6919,22 +6920,22 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.07520476246509329</v>
+        <v>0.07662637658294001</v>
       </c>
       <c r="F128" t="n">
         <v>1.4346</v>
       </c>
       <c r="G128" t="n">
-        <v>1.43460044693192</v>
+        <v>1.434602459183037</v>
       </c>
       <c r="H128" t="n">
-        <v>4.469319196953592e-07</v>
+        <v>2.459183036984669e-06</v>
       </c>
       <c r="I128" t="n">
-        <v>3.115376548831445e-05</v>
+        <v>0.0001714194226254474</v>
       </c>
       <c r="J128" t="n">
-        <v>3.115376548831445e-05</v>
+        <v>0.0001714194226254474</v>
       </c>
     </row>
     <row r="129">
@@ -6955,22 +6956,22 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.07520476246509329</v>
+        <v>0.07662637658294001</v>
       </c>
       <c r="F129" t="n">
         <v>1.737378411525397</v>
       </c>
       <c r="G129" t="n">
-        <v>1.625117841397836</v>
+        <v>1.622019989859314</v>
       </c>
       <c r="H129" t="n">
-        <v>-0.112260570127561</v>
+        <v>-0.1153584216660828</v>
       </c>
       <c r="I129" t="n">
-        <v>6.461492175961689</v>
+        <v>6.639798267367644</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.461492175961689</v>
+        <v>-6.639798267367644</v>
       </c>
     </row>
     <row r="130">
@@ -6987,26 +6988,26 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.07520476246509329</v>
+        <v>0.07662637658294001</v>
       </c>
       <c r="F130" t="n">
-        <v>2.286675</v>
+        <v>2.244778125</v>
       </c>
       <c r="G130" t="n">
-        <v>2.124323706301107</v>
+        <v>2.114682119425783</v>
       </c>
       <c r="H130" t="n">
-        <v>-0.1623512936988929</v>
+        <v>-0.1300960055742166</v>
       </c>
       <c r="I130" t="n">
-        <v>7.099884928942368</v>
+        <v>5.795495070329797</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.099884928942368</v>
+        <v>-5.795495070329797</v>
       </c>
     </row>
     <row r="131">
@@ -7027,22 +7028,22 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.1186546112797692</v>
+        <v>0.1201360836897293</v>
       </c>
       <c r="F131" t="n">
         <v>1.4346</v>
       </c>
       <c r="G131" t="n">
-        <v>1.434601243998256</v>
+        <v>1.434601680361081</v>
       </c>
       <c r="H131" t="n">
-        <v>1.243998255739953e-06</v>
+        <v>1.680361081390913e-06</v>
       </c>
       <c r="I131" t="n">
-        <v>8.671394505367023e-05</v>
+        <v>0.0001171309829493178</v>
       </c>
       <c r="J131" t="n">
-        <v>8.671394505367023e-05</v>
+        <v>0.0001171309829493178</v>
       </c>
     </row>
     <row r="132">
@@ -7063,22 +7064,22 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.1186546112797692</v>
+        <v>0.1201360836897293</v>
       </c>
       <c r="F132" t="n">
         <v>1.737378411525397</v>
       </c>
       <c r="G132" t="n">
-        <v>1.621069649843758</v>
+        <v>1.618080998668611</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.116308761681639</v>
+        <v>-0.1192974128567854</v>
       </c>
       <c r="I132" t="n">
-        <v>6.694497923427131</v>
+        <v>6.866518661990498</v>
       </c>
       <c r="J132" t="n">
-        <v>-6.694497923427131</v>
+        <v>-6.866518661990498</v>
       </c>
     </row>
     <row r="133">
@@ -7095,26 +7096,26 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.1186546112797692</v>
+        <v>0.1201360836897293</v>
       </c>
       <c r="F133" t="n">
-        <v>2.286675</v>
+        <v>2.244778125</v>
       </c>
       <c r="G133" t="n">
-        <v>2.119259323386435</v>
+        <v>2.109762728510258</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.1674156766135653</v>
+        <v>-0.135015396489742</v>
       </c>
       <c r="I133" t="n">
-        <v>7.32135859330973</v>
+        <v>6.014643273029135</v>
       </c>
       <c r="J133" t="n">
-        <v>-7.32135859330973</v>
+        <v>-6.014643273029135</v>
       </c>
     </row>
     <row r="134">
@@ -7139,16 +7140,16 @@
         <v>1.4346</v>
       </c>
       <c r="G134" t="n">
-        <v>1.954265151879351</v>
+        <v>1.941339255315492</v>
       </c>
       <c r="H134" t="n">
-        <v>0.5196651518793505</v>
+        <v>0.5067392553154915</v>
       </c>
       <c r="I134" t="n">
-        <v>36.22369663176846</v>
+        <v>35.322686136588</v>
       </c>
       <c r="J134" t="n">
-        <v>36.22369663176846</v>
+        <v>35.322686136588</v>
       </c>
     </row>
     <row r="135">
@@ -7173,16 +7174,16 @@
         <v>1.737378411525397</v>
       </c>
       <c r="G135" t="n">
-        <v>2.01642645146125</v>
+        <v>2.003477718258847</v>
       </c>
       <c r="H135" t="n">
-        <v>0.2790480399358533</v>
+        <v>0.2660993067334507</v>
       </c>
       <c r="I135" t="n">
-        <v>16.06144280858495</v>
+        <v>15.3161398212505</v>
       </c>
       <c r="J135" t="n">
-        <v>16.06144280858495</v>
+        <v>15.3161398212505</v>
       </c>
     </row>
     <row r="136">
@@ -7199,24 +7200,24 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
-        <v>2.286675</v>
+        <v>2.244778125</v>
       </c>
       <c r="G136" t="n">
-        <v>2.250837187809623</v>
+        <v>2.237596859795449</v>
       </c>
       <c r="H136" t="n">
-        <v>-0.03583781219037663</v>
+        <v>-0.007181265204550868</v>
       </c>
       <c r="I136" t="n">
-        <v>1.567245550433561</v>
+        <v>0.3199097997514061</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.567245550433561</v>
+        <v>-0.3199097997514061</v>
       </c>
     </row>
     <row r="137">
@@ -7237,22 +7238,22 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.3660646295723231</v>
+        <v>0.4825333284192772</v>
       </c>
       <c r="F137" t="n">
         <v>2.3656875</v>
       </c>
       <c r="G137" t="n">
-        <v>2.570646822500085</v>
+        <v>2.574245508661671</v>
       </c>
       <c r="H137" t="n">
-        <v>0.2049593225000854</v>
+        <v>0.2085580086616714</v>
       </c>
       <c r="I137" t="n">
-        <v>8.663837573647635</v>
+        <v>8.815957672417486</v>
       </c>
       <c r="J137" t="n">
-        <v>8.663837573647635</v>
+        <v>8.815957672417486</v>
       </c>
     </row>
     <row r="138">
@@ -7273,22 +7274,22 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.3660646295723231</v>
+        <v>0.4825333284192772</v>
       </c>
       <c r="F138" t="n">
         <v>2.596562490472174</v>
       </c>
       <c r="G138" t="n">
-        <v>2.596561661447085</v>
+        <v>2.596562202770281</v>
       </c>
       <c r="H138" t="n">
-        <v>-8.290250890219397e-07</v>
+        <v>-2.87701892975889e-07</v>
       </c>
       <c r="I138" t="n">
-        <v>3.192779268991077e-05</v>
+        <v>1.108010664220801e-05</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.192779268991077e-05</v>
+        <v>-1.108010664220801e-05</v>
       </c>
     </row>
     <row r="139">
@@ -7305,26 +7306,26 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.3660646295723231</v>
+        <v>0.4825333284192772</v>
       </c>
       <c r="F139" t="n">
-        <v>2.8722</v>
+        <v>2.83653125</v>
       </c>
       <c r="G139" t="n">
-        <v>2.69533873734475</v>
+        <v>2.685276836149347</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.1768612626552506</v>
+        <v>-0.1512544138506535</v>
       </c>
       <c r="I139" t="n">
-        <v>6.157693150033096</v>
+        <v>5.332372553648176</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.157693150033096</v>
+        <v>-5.332372553648176</v>
       </c>
     </row>
     <row r="140">
@@ -7345,22 +7346,22 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.3828301430761989</v>
+        <v>0.4981426684592046</v>
       </c>
       <c r="F140" t="n">
         <v>2.3656875</v>
       </c>
       <c r="G140" t="n">
-        <v>2.570678352122163</v>
+        <v>2.574254740514772</v>
       </c>
       <c r="H140" t="n">
-        <v>0.2049908521221635</v>
+        <v>0.2085672405147716</v>
       </c>
       <c r="I140" t="n">
-        <v>8.665170362618204</v>
+        <v>8.816347912172322</v>
       </c>
       <c r="J140" t="n">
-        <v>8.665170362618204</v>
+        <v>8.816347912172322</v>
       </c>
     </row>
     <row r="141">
@@ -7381,22 +7382,22 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.3828301430761989</v>
+        <v>0.4981426684592046</v>
       </c>
       <c r="F141" t="n">
         <v>2.596562490472174</v>
       </c>
       <c r="G141" t="n">
-        <v>2.596562461127159</v>
+        <v>2.596562184455288</v>
       </c>
       <c r="H141" t="n">
-        <v>-2.934501486251406e-08</v>
+        <v>-3.060168860535839e-07</v>
       </c>
       <c r="I141" t="n">
-        <v>1.130148608793074e-06</v>
+        <v>1.178546201666558e-05</v>
       </c>
       <c r="J141" t="n">
-        <v>-1.130148608793074e-06</v>
+        <v>-1.178546201666558e-05</v>
       </c>
     </row>
     <row r="142">
@@ -7413,26 +7414,26 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.3828301430761989</v>
+        <v>0.4981426684592046</v>
       </c>
       <c r="F142" t="n">
-        <v>2.8722</v>
+        <v>2.83653125</v>
       </c>
       <c r="G142" t="n">
-        <v>2.695298359886088</v>
+        <v>2.685263434731976</v>
       </c>
       <c r="H142" t="n">
-        <v>-0.1769016401139121</v>
+        <v>-0.1512678152680245</v>
       </c>
       <c r="I142" t="n">
-        <v>6.159098952507209</v>
+        <v>5.332845011597332</v>
       </c>
       <c r="J142" t="n">
-        <v>-6.159098952507209</v>
+        <v>-5.332845011597332</v>
       </c>
     </row>
     <row r="143">
@@ -7457,16 +7458,16 @@
         <v>2.3656875</v>
       </c>
       <c r="G143" t="n">
-        <v>2.593181257618392</v>
+        <v>2.575929155914063</v>
       </c>
       <c r="H143" t="n">
-        <v>0.2274937576183924</v>
+        <v>0.2102416559140634</v>
       </c>
       <c r="I143" t="n">
-        <v>9.616390906169661</v>
+        <v>8.887127142281615</v>
       </c>
       <c r="J143" t="n">
-        <v>9.616390906169661</v>
+        <v>8.887127142281615</v>
       </c>
     </row>
     <row r="144">
@@ -7491,16 +7492,16 @@
         <v>2.596562490472174</v>
       </c>
       <c r="G144" t="n">
-        <v>2.615211533796312</v>
+        <v>2.597954531574995</v>
       </c>
       <c r="H144" t="n">
-        <v>0.01864904332413797</v>
+        <v>0.001392041102821207</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7182204700471784</v>
+        <v>0.05361092243799878</v>
       </c>
       <c r="J144" t="n">
-        <v>0.7182204700471784</v>
+        <v>0.05361092243799878</v>
       </c>
     </row>
     <row r="145">
@@ -7517,24 +7518,24 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2.8722</v>
+        <v>2.83653125</v>
       </c>
       <c r="G145" t="n">
-        <v>2.703170480271347</v>
+        <v>2.685833739997278</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.1690295197286535</v>
+        <v>-0.1506975100027219</v>
       </c>
       <c r="I145" t="n">
-        <v>5.885019139636986</v>
+        <v>5.312739283331425</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.885019139636986</v>
+        <v>-5.312739283331425</v>
       </c>
     </row>
     <row r="146">
@@ -7555,22 +7556,22 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.05585091153844986</v>
+        <v>0.0572653287215627</v>
       </c>
       <c r="F146" t="n">
         <v>1.88635</v>
       </c>
       <c r="G146" t="n">
-        <v>1.886352791512826</v>
+        <v>1.886349694177926</v>
       </c>
       <c r="H146" t="n">
-        <v>2.791512826005871e-06</v>
+        <v>-3.058220743312745e-07</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0001479848822331948</v>
+        <v>1.621237174073075e-05</v>
       </c>
       <c r="J146" t="n">
-        <v>0.0001479848822331948</v>
+        <v>-1.621237174073075e-05</v>
       </c>
     </row>
     <row r="147">
@@ -7591,22 +7592,22 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.05585091153844986</v>
+        <v>0.0572653287215627</v>
       </c>
       <c r="F147" t="n">
         <v>2.2409375</v>
       </c>
       <c r="G147" t="n">
-        <v>2.089060420194398</v>
+        <v>2.083740315145221</v>
       </c>
       <c r="H147" t="n">
-        <v>-0.1518770798056024</v>
+        <v>-0.1571971848547791</v>
       </c>
       <c r="I147" t="n">
-        <v>6.777390257675744</v>
+        <v>7.014795586881788</v>
       </c>
       <c r="J147" t="n">
-        <v>-6.777390257675744</v>
+        <v>-7.014795586881788</v>
       </c>
     </row>
     <row r="148">
@@ -7623,26 +7624,26 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.05585091153844986</v>
+        <v>0.0572653287215627</v>
       </c>
       <c r="F148" t="n">
-        <v>2.60505</v>
+        <v>2.565471875</v>
       </c>
       <c r="G148" t="n">
-        <v>2.499701663718704</v>
+        <v>2.48639324496892</v>
       </c>
       <c r="H148" t="n">
-        <v>-0.1053483362812959</v>
+        <v>-0.07907863003108018</v>
       </c>
       <c r="I148" t="n">
-        <v>4.044004386913723</v>
+        <v>3.082420462359587</v>
       </c>
       <c r="J148" t="n">
-        <v>-4.044004386913723</v>
+        <v>-3.082420462359587</v>
       </c>
     </row>
     <row r="149">
@@ -7663,22 +7664,22 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.07572491001638651</v>
+        <v>0.07717316817023095</v>
       </c>
       <c r="F149" t="n">
         <v>1.88635</v>
       </c>
       <c r="G149" t="n">
-        <v>1.886350716945915</v>
+        <v>1.886353589621563</v>
       </c>
       <c r="H149" t="n">
-        <v>7.169459144140689e-07</v>
+        <v>3.589621562660739e-06</v>
       </c>
       <c r="I149" t="n">
-        <v>3.80070461162599e-05</v>
+        <v>0.0001902945668969565</v>
       </c>
       <c r="J149" t="n">
-        <v>3.80070461162599e-05</v>
+        <v>0.0001902945668969565</v>
       </c>
     </row>
     <row r="150">
@@ -7699,22 +7700,22 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.07572491001638651</v>
+        <v>0.07717316817023095</v>
       </c>
       <c r="F150" t="n">
         <v>2.2409375</v>
       </c>
       <c r="G150" t="n">
-        <v>2.086591763469764</v>
+        <v>2.081362044028959</v>
       </c>
       <c r="H150" t="n">
-        <v>-0.1543457365302365</v>
+        <v>-0.1595754559710412</v>
       </c>
       <c r="I150" t="n">
-        <v>6.887552041511043</v>
+        <v>7.120923986993888</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.887552041511043</v>
+        <v>-7.120923986993888</v>
       </c>
     </row>
     <row r="151">
@@ -7731,26 +7732,26 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.07572491001638651</v>
+        <v>0.07717316817023095</v>
       </c>
       <c r="F151" t="n">
-        <v>2.60505</v>
+        <v>2.565471875</v>
       </c>
       <c r="G151" t="n">
-        <v>2.49747365727112</v>
+        <v>2.484237378899032</v>
       </c>
       <c r="H151" t="n">
-        <v>-0.1075763427288794</v>
+        <v>-0.08123449610096856</v>
       </c>
       <c r="I151" t="n">
-        <v>4.129530823933491</v>
+        <v>3.166454362356577</v>
       </c>
       <c r="J151" t="n">
-        <v>-4.129530823933491</v>
+        <v>-3.166454362356577</v>
       </c>
     </row>
     <row r="152">
@@ -7775,16 +7776,16 @@
         <v>1.88635</v>
       </c>
       <c r="G152" t="n">
-        <v>2.470439642904588</v>
+        <v>2.454017432754297</v>
       </c>
       <c r="H152" t="n">
-        <v>0.5840896429045879</v>
+        <v>0.567667432754297</v>
       </c>
       <c r="I152" t="n">
-        <v>30.96401213478876</v>
+        <v>30.09343084551101</v>
       </c>
       <c r="J152" t="n">
-        <v>30.96401213478876</v>
+        <v>30.09343084551101</v>
       </c>
     </row>
     <row r="153">
@@ -7809,16 +7810,16 @@
         <v>2.2409375</v>
       </c>
       <c r="G153" t="n">
-        <v>2.499558860089139</v>
+        <v>2.483129577437567</v>
       </c>
       <c r="H153" t="n">
-        <v>0.2586213600891383</v>
+        <v>0.2421920774375663</v>
       </c>
       <c r="I153" t="n">
-        <v>11.54076631272127</v>
+        <v>10.80762303444725</v>
       </c>
       <c r="J153" t="n">
-        <v>11.54076631272127</v>
+        <v>10.80762303444725</v>
       </c>
     </row>
     <row r="154">
@@ -7835,24 +7836,24 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="n">
-        <v>2.60505</v>
+        <v>2.565471875</v>
       </c>
       <c r="G154" t="n">
-        <v>2.61482176371045</v>
+        <v>2.598281676660775</v>
       </c>
       <c r="H154" t="n">
-        <v>0.009771763710450188</v>
+        <v>0.03280980166077496</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3751084896815872</v>
+        <v>1.278899292582382</v>
       </c>
       <c r="J154" t="n">
-        <v>0.3751084896815872</v>
+        <v>1.278899292582382</v>
       </c>
     </row>
     <row r="155">
@@ -7873,22 +7874,22 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.1279688890847251</v>
+        <v>0.2227214678701133</v>
       </c>
       <c r="F155" t="n">
         <v>2.235925</v>
       </c>
       <c r="G155" t="n">
-        <v>2.235925075463527</v>
+        <v>2.363888913067183</v>
       </c>
       <c r="H155" t="n">
-        <v>7.546352698284409e-08</v>
+        <v>0.1279639130671826</v>
       </c>
       <c r="I155" t="n">
-        <v>3.375047328637771e-06</v>
+        <v>5.723086108307863</v>
       </c>
       <c r="J155" t="n">
-        <v>3.375047328637771e-06</v>
+        <v>5.723086108307863</v>
       </c>
     </row>
     <row r="156">
@@ -7909,22 +7910,22 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.1279688890847251</v>
+        <v>0.2227214678701133</v>
       </c>
       <c r="F156" t="n">
         <v>2.411340264975417</v>
       </c>
       <c r="G156" t="n">
-        <v>2.319524144659907</v>
+        <v>2.411339823758257</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.09181612031550968</v>
+        <v>-4.412171596968051e-07</v>
       </c>
       <c r="I156" t="n">
-        <v>3.807679971554978</v>
+        <v>1.829759018689564e-05</v>
       </c>
       <c r="J156" t="n">
-        <v>-3.807679971554978</v>
+        <v>-1.829759018689564e-05</v>
       </c>
     </row>
     <row r="157">
@@ -7941,26 +7942,26 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.1279688890847251</v>
+        <v>0.2227214678701133</v>
       </c>
       <c r="F157" t="n">
-        <v>2.6124875</v>
+        <v>2.690510416666667</v>
       </c>
       <c r="G157" t="n">
-        <v>2.555296584413261</v>
+        <v>2.572755652726743</v>
       </c>
       <c r="H157" t="n">
-        <v>-0.05719091558673917</v>
+        <v>-0.1177547639399243</v>
       </c>
       <c r="I157" t="n">
-        <v>2.189136429810254</v>
+        <v>4.376670062694399</v>
       </c>
       <c r="J157" t="n">
-        <v>-2.189136429810254</v>
+        <v>-4.376670062694399</v>
       </c>
     </row>
     <row r="158">
@@ -7981,22 +7982,22 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.2242608781423763</v>
+        <v>0.2448759921893136</v>
       </c>
       <c r="F158" t="n">
         <v>2.235925</v>
       </c>
       <c r="G158" t="n">
-        <v>2.359627190918619</v>
+        <v>2.364124019916902</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1237021909186189</v>
+        <v>0.1281990199169023</v>
       </c>
       <c r="I158" t="n">
-        <v>5.532483912412934</v>
+        <v>5.733601078609627</v>
       </c>
       <c r="J158" t="n">
-        <v>5.532483912412934</v>
+        <v>5.733601078609627</v>
       </c>
     </row>
     <row r="159">
@@ -8017,22 +8018,22 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.2242608781423763</v>
+        <v>0.2448759921893136</v>
       </c>
       <c r="F159" t="n">
         <v>2.411340264975417</v>
       </c>
       <c r="G159" t="n">
-        <v>2.411339857427734</v>
+        <v>2.411339883316624</v>
       </c>
       <c r="H159" t="n">
-        <v>-4.07547682268472e-07</v>
+        <v>-3.816587930138837e-07</v>
       </c>
       <c r="I159" t="n">
-        <v>1.690129295264046e-05</v>
+        <v>1.582766225727063e-05</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.690129295264046e-05</v>
+        <v>-1.582766225727063e-05</v>
       </c>
     </row>
     <row r="160">
@@ -8049,26 +8050,26 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.2242608781423763</v>
+        <v>0.2448759921893136</v>
       </c>
       <c r="F160" t="n">
-        <v>2.6124875</v>
+        <v>2.690510416666667</v>
       </c>
       <c r="G160" t="n">
-        <v>2.583118777990451</v>
+        <v>2.572503429443898</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.02936872200954888</v>
+        <v>-0.1180069872227691</v>
       </c>
       <c r="I160" t="n">
-        <v>1.12416698681042</v>
+        <v>4.386044614128297</v>
       </c>
       <c r="J160" t="n">
-        <v>-1.12416698681042</v>
+        <v>-4.386044614128297</v>
       </c>
     </row>
     <row r="161">
@@ -8093,16 +8094,16 @@
         <v>2.235925</v>
       </c>
       <c r="G161" t="n">
-        <v>2.476650547163343</v>
+        <v>2.460186332276165</v>
       </c>
       <c r="H161" t="n">
-        <v>0.2407255471633434</v>
+        <v>0.2242613322761655</v>
       </c>
       <c r="I161" t="n">
-        <v>10.76626215831673</v>
+        <v>10.02991300138267</v>
       </c>
       <c r="J161" t="n">
-        <v>10.76626215831673</v>
+        <v>10.02991300138267</v>
       </c>
     </row>
     <row r="162">
@@ -8127,16 +8128,16 @@
         <v>2.411340264975417</v>
       </c>
       <c r="G162" t="n">
-        <v>2.505405233837632</v>
+        <v>2.488934066582003</v>
       </c>
       <c r="H162" t="n">
-        <v>0.09406496886221571</v>
+        <v>0.07759380160658624</v>
       </c>
       <c r="I162" t="n">
-        <v>3.900941324146748</v>
+        <v>3.217870274619965</v>
       </c>
       <c r="J162" t="n">
-        <v>3.900941324146748</v>
+        <v>3.217870274619965</v>
       </c>
     </row>
     <row r="163">
@@ -8153,24 +8154,24 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>2.6124875</v>
+        <v>2.690510416666667</v>
       </c>
       <c r="G163" t="n">
-        <v>2.619277442551056</v>
+        <v>2.602697135067904</v>
       </c>
       <c r="H163" t="n">
-        <v>0.006789942551055805</v>
+        <v>-0.08781328159876267</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2599033507741493</v>
+        <v>3.263814964431786</v>
       </c>
       <c r="J163" t="n">
-        <v>0.2599033507741493</v>
+        <v>-3.263814964431786</v>
       </c>
     </row>
     <row r="164">
@@ -8191,22 +8192,22 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.08185432872087021</v>
+        <v>0.08427582850660222</v>
       </c>
       <c r="F164" t="n">
         <v>1.9574</v>
       </c>
       <c r="G164" t="n">
-        <v>1.957398910254713</v>
+        <v>1.957401650385331</v>
       </c>
       <c r="H164" t="n">
-        <v>-1.089745287341515e-06</v>
+        <v>1.650385331064541e-06</v>
       </c>
       <c r="I164" t="n">
-        <v>5.567310142748108e-05</v>
+        <v>8.431517988477271e-05</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.567310142748108e-05</v>
+        <v>8.431517988477271e-05</v>
       </c>
     </row>
     <row r="165">
@@ -8227,22 +8228,22 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.08185432872087021</v>
+        <v>0.08427582850660222</v>
       </c>
       <c r="F165" t="n">
         <v>2.2367375</v>
       </c>
       <c r="G165" t="n">
-        <v>2.104086016771145</v>
+        <v>2.099555520196754</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.1326514832288548</v>
+        <v>-0.1371819798032465</v>
       </c>
       <c r="I165" t="n">
-        <v>5.930578944952403</v>
+        <v>6.133128263966895</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.930578944952403</v>
+        <v>-6.133128263966895</v>
       </c>
     </row>
     <row r="166">
@@ -8259,26 +8260,26 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.08185432872087021</v>
+        <v>0.08427582850660222</v>
       </c>
       <c r="F166" t="n">
-        <v>2.3839125</v>
+        <v>2.472651041666666</v>
       </c>
       <c r="G166" t="n">
-        <v>2.458607464038299</v>
+        <v>2.446110882804162</v>
       </c>
       <c r="H166" t="n">
-        <v>0.07469496403829856</v>
+        <v>-0.02654015886250471</v>
       </c>
       <c r="I166" t="n">
-        <v>3.133293023057623</v>
+        <v>1.073348338090424</v>
       </c>
       <c r="J166" t="n">
-        <v>3.133293023057623</v>
+        <v>-1.073348338090424</v>
       </c>
     </row>
     <row r="167">
@@ -8299,22 +8300,22 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.1055737314840889</v>
+        <v>0.1080509055066162</v>
       </c>
       <c r="F167" t="n">
         <v>1.9574</v>
       </c>
       <c r="G167" t="n">
-        <v>1.957400759461791</v>
+        <v>1.957402950459858</v>
       </c>
       <c r="H167" t="n">
-        <v>7.594617914552515e-07</v>
+        <v>2.950459858208632e-06</v>
       </c>
       <c r="I167" t="n">
-        <v>3.879951933458933e-05</v>
+        <v>0.0001507336189950256</v>
       </c>
       <c r="J167" t="n">
-        <v>3.879951933458933e-05</v>
+        <v>0.0001507336189950256</v>
       </c>
     </row>
     <row r="168">
@@ -8335,22 +8336,22 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.1055737314840889</v>
+        <v>0.1080509055066162</v>
       </c>
       <c r="F168" t="n">
         <v>2.2367375</v>
       </c>
       <c r="G168" t="n">
-        <v>2.10231241741235</v>
+        <v>2.09786496083404</v>
       </c>
       <c r="H168" t="n">
-        <v>-0.1344250825876498</v>
+        <v>-0.1388725391659604</v>
       </c>
       <c r="I168" t="n">
-        <v>6.009872977390053</v>
+        <v>6.208709746492846</v>
       </c>
       <c r="J168" t="n">
-        <v>-6.009872977390053</v>
+        <v>-6.208709746492846</v>
       </c>
     </row>
     <row r="169">
@@ -8367,26 +8368,26 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.1055737314840889</v>
+        <v>0.1080509055066162</v>
       </c>
       <c r="F169" t="n">
-        <v>2.3839125</v>
+        <v>2.472651041666666</v>
       </c>
       <c r="G169" t="n">
-        <v>2.456615791461144</v>
+        <v>2.444202465106636</v>
       </c>
       <c r="H169" t="n">
-        <v>0.07270329146114385</v>
+        <v>-0.02844857656003041</v>
       </c>
       <c r="I169" t="n">
-        <v>3.049746643853071</v>
+        <v>1.150529374369581</v>
       </c>
       <c r="J169" t="n">
-        <v>3.049746643853071</v>
+        <v>-1.150529374369581</v>
       </c>
     </row>
     <row r="170">
@@ -8411,16 +8412,16 @@
         <v>1.9574</v>
       </c>
       <c r="G170" t="n">
-        <v>2.392278142541437</v>
+        <v>2.376384652094541</v>
       </c>
       <c r="H170" t="n">
-        <v>0.434878142541437</v>
+        <v>0.4189846520945408</v>
       </c>
       <c r="I170" t="n">
-        <v>22.21713203951348</v>
+        <v>21.40516256741294</v>
       </c>
       <c r="J170" t="n">
-        <v>22.21713203951348</v>
+        <v>21.40516256741294</v>
       </c>
     </row>
     <row r="171">
@@ -8445,16 +8446,16 @@
         <v>2.2367375</v>
       </c>
       <c r="G171" t="n">
-        <v>2.426041634304274</v>
+        <v>2.410139454659309</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1893041343042738</v>
+        <v>0.1734019546593086</v>
       </c>
       <c r="I171" t="n">
-        <v>8.463404145737881</v>
+        <v>7.752449925809739</v>
       </c>
       <c r="J171" t="n">
-        <v>8.463404145737881</v>
+        <v>7.752449925809739</v>
       </c>
     </row>
     <row r="172">
@@ -8471,24 +8472,24 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
-        <v>2.3839125</v>
+        <v>2.472651041666666</v>
       </c>
       <c r="G172" t="n">
-        <v>2.558890259424863</v>
+        <v>2.542855435916811</v>
       </c>
       <c r="H172" t="n">
-        <v>0.1749777594248627</v>
+        <v>0.07020439425014446</v>
       </c>
       <c r="I172" t="n">
-        <v>7.339940514799209</v>
+        <v>2.839235826937548</v>
       </c>
       <c r="J172" t="n">
-        <v>7.339940514799209</v>
+        <v>2.839235826937548</v>
       </c>
     </row>
     <row r="173">
@@ -8509,22 +8510,22 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>0.08947870343401622</v>
+        <v>0.09214397915035165</v>
       </c>
       <c r="F173" t="n">
         <v>1.9375625</v>
       </c>
       <c r="G173" t="n">
-        <v>1.937564607244221</v>
+        <v>1.937566510611282</v>
       </c>
       <c r="H173" t="n">
-        <v>2.107244221116744e-06</v>
+        <v>4.010611281524135e-06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0001087574837517109</v>
+        <v>0.0002069926147685112</v>
       </c>
       <c r="J173" t="n">
-        <v>0.0001087574837517109</v>
+        <v>0.0002069926147685112</v>
       </c>
     </row>
     <row r="174">
@@ -8545,22 +8546,22 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>0.08947870343401622</v>
+        <v>0.09214397915035165</v>
       </c>
       <c r="F174" t="n">
         <v>2.27314447629368</v>
       </c>
       <c r="G174" t="n">
-        <v>2.076387283784475</v>
+        <v>2.072134322987468</v>
       </c>
       <c r="H174" t="n">
-        <v>-0.1967571925092053</v>
+        <v>-0.2010101533062127</v>
       </c>
       <c r="I174" t="n">
-        <v>8.655727542228826</v>
+        <v>8.842823472177891</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.655727542228826</v>
+        <v>-8.842823472177891</v>
       </c>
     </row>
     <row r="175">
@@ -8577,26 +8578,26 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0.08947870343401622</v>
+        <v>0.09214397915035165</v>
       </c>
       <c r="F175" t="n">
-        <v>2.5233375</v>
+        <v>2.609909375</v>
       </c>
       <c r="G175" t="n">
-        <v>2.427651498628628</v>
+        <v>2.415549589180215</v>
       </c>
       <c r="H175" t="n">
-        <v>-0.09568600137137251</v>
+        <v>-0.1943597858197852</v>
       </c>
       <c r="I175" t="n">
-        <v>3.792041348863261</v>
+        <v>7.446993665049584</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.792041348863261</v>
+        <v>-7.446993665049584</v>
       </c>
     </row>
     <row r="176">
@@ -8617,22 +8618,22 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.1153960352342452</v>
+        <v>0.1181240394951164</v>
       </c>
       <c r="F176" t="n">
         <v>1.9375625</v>
       </c>
       <c r="G176" t="n">
-        <v>1.937562941819326</v>
+        <v>1.937563131132626</v>
       </c>
       <c r="H176" t="n">
-        <v>4.418193257915703e-07</v>
+        <v>6.311326261609906e-07</v>
       </c>
       <c r="I176" t="n">
-        <v>2.280284252980589e-05</v>
+        <v>3.257353639745766e-05</v>
       </c>
       <c r="J176" t="n">
-        <v>2.280284252980589e-05</v>
+        <v>3.257353639745766e-05</v>
       </c>
     </row>
     <row r="177">
@@ -8653,22 +8654,22 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0.1153960352342452</v>
+        <v>0.1181240394951164</v>
       </c>
       <c r="F177" t="n">
         <v>2.27314447629368</v>
       </c>
       <c r="G177" t="n">
-        <v>2.074662866384123</v>
+        <v>2.070492713526872</v>
       </c>
       <c r="H177" t="n">
-        <v>-0.1984816099095577</v>
+        <v>-0.2026517627668087</v>
       </c>
       <c r="I177" t="n">
-        <v>8.731587982176048</v>
+        <v>8.915041031497859</v>
       </c>
       <c r="J177" t="n">
-        <v>-8.731587982176048</v>
+        <v>-8.915041031497859</v>
       </c>
     </row>
     <row r="178">
@@ -8685,26 +8686,26 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0.1153960352342452</v>
+        <v>0.1181240394951164</v>
       </c>
       <c r="F178" t="n">
-        <v>2.5233375</v>
+        <v>2.609909375</v>
       </c>
       <c r="G178" t="n">
-        <v>2.425601875042101</v>
+        <v>2.413589327867191</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.09773562495789934</v>
+        <v>-0.1963200471328093</v>
       </c>
       <c r="I178" t="n">
-        <v>3.873268041151821</v>
+        <v>7.522102070414198</v>
       </c>
       <c r="J178" t="n">
-        <v>-3.873268041151821</v>
+        <v>-7.522102070414198</v>
       </c>
     </row>
     <row r="179">
@@ -8729,16 +8730,16 @@
         <v>1.9375625</v>
       </c>
       <c r="G179" t="n">
-        <v>2.345286829263943</v>
+        <v>2.329711311343251</v>
       </c>
       <c r="H179" t="n">
-        <v>0.4077243292639425</v>
+        <v>0.3921488113432512</v>
       </c>
       <c r="I179" t="n">
-        <v>21.04315753757324</v>
+        <v>20.23928576978813</v>
       </c>
       <c r="J179" t="n">
-        <v>21.04315753757324</v>
+        <v>20.23928576978813</v>
       </c>
     </row>
     <row r="180">
@@ -8763,16 +8764,16 @@
         <v>2.27314447629368</v>
       </c>
       <c r="G180" t="n">
-        <v>2.381895566019327</v>
+        <v>2.366310285658055</v>
       </c>
       <c r="H180" t="n">
-        <v>0.1087510897256463</v>
+        <v>0.09316580936437457</v>
       </c>
       <c r="I180" t="n">
-        <v>4.784169719953873</v>
+        <v>4.098543244214714</v>
       </c>
       <c r="J180" t="n">
-        <v>4.784169719953873</v>
+        <v>4.098543244214714</v>
       </c>
     </row>
     <row r="181">
@@ -8789,24 +8790,24 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
-        <v>2.5233375</v>
+        <v>2.609909375</v>
       </c>
       <c r="G181" t="n">
-        <v>2.525393117712349</v>
+        <v>2.509661228822335</v>
       </c>
       <c r="H181" t="n">
-        <v>0.002055617712349189</v>
+        <v>-0.1002481461776648</v>
       </c>
       <c r="I181" t="n">
-        <v>0.08146423981529181</v>
+        <v>3.841058510993883</v>
       </c>
       <c r="J181" t="n">
-        <v>0.08146423981529181</v>
+        <v>-3.841058510993883</v>
       </c>
     </row>
     <row r="182">
@@ -8827,22 +8828,22 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>0.07441064331798346</v>
+        <v>0.07638048100184246</v>
       </c>
       <c r="F182" t="n">
         <v>1.869</v>
       </c>
       <c r="G182" t="n">
-        <v>1.869002849792029</v>
+        <v>1.869000432363893</v>
       </c>
       <c r="H182" t="n">
-        <v>2.849792029469e-06</v>
+        <v>4.323638926884144e-07</v>
       </c>
       <c r="I182" t="n">
-        <v>0.0001524768341074906</v>
+        <v>2.313343460077123e-05</v>
       </c>
       <c r="J182" t="n">
-        <v>0.0001524768341074906</v>
+        <v>2.313343460077123e-05</v>
       </c>
     </row>
     <row r="183">
@@ -8863,22 +8864,22 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>0.07441064331798346</v>
+        <v>0.07638048100184246</v>
       </c>
       <c r="F183" t="n">
         <v>2.254459673470501</v>
       </c>
       <c r="G183" t="n">
-        <v>2.034641766681152</v>
+        <v>2.030155710740681</v>
       </c>
       <c r="H183" t="n">
-        <v>-0.2198179067893498</v>
+        <v>-0.2243039627298202</v>
       </c>
       <c r="I183" t="n">
-        <v>9.750358783351553</v>
+        <v>9.949344642059092</v>
       </c>
       <c r="J183" t="n">
-        <v>-9.750358783351553</v>
+        <v>-9.949344642059092</v>
       </c>
     </row>
     <row r="184">
@@ -8895,26 +8896,26 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0.07441064331798346</v>
+        <v>0.07638048100184246</v>
       </c>
       <c r="F184" t="n">
-        <v>2.540625</v>
+        <v>2.601183333333334</v>
       </c>
       <c r="G184" t="n">
-        <v>2.424335907657486</v>
+        <v>2.412039605915339</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.1162890923425137</v>
+        <v>-0.1891437274179948</v>
       </c>
       <c r="I184" t="n">
-        <v>4.577184446445805</v>
+        <v>7.271449305175008</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.577184446445805</v>
+        <v>-7.271449305175008</v>
       </c>
     </row>
     <row r="185">
@@ -8935,22 +8936,22 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0.09943493880077356</v>
+        <v>0.1014549402188581</v>
       </c>
       <c r="F185" t="n">
         <v>1.869</v>
       </c>
       <c r="G185" t="n">
-        <v>1.869004192262403</v>
+        <v>1.869000565008434</v>
       </c>
       <c r="H185" t="n">
-        <v>4.192262403446279e-06</v>
+        <v>5.650084338171268e-07</v>
       </c>
       <c r="I185" t="n">
-        <v>0.00022430510451826</v>
+        <v>3.023052080348458e-05</v>
       </c>
       <c r="J185" t="n">
-        <v>0.00022430510451826</v>
+        <v>3.023052080348458e-05</v>
       </c>
     </row>
     <row r="186">
@@ -8971,22 +8972,22 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0.09943493880077356</v>
+        <v>0.1014549402188581</v>
       </c>
       <c r="F186" t="n">
         <v>2.254459673470501</v>
       </c>
       <c r="G186" t="n">
-        <v>2.032429762641303</v>
+        <v>2.028032155923051</v>
       </c>
       <c r="H186" t="n">
-        <v>-0.2220299108291988</v>
+        <v>-0.2264275175474508</v>
       </c>
       <c r="I186" t="n">
-        <v>9.848475598918444</v>
+        <v>10.04353815736654</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.848475598918444</v>
+        <v>-10.04353815736654</v>
       </c>
     </row>
     <row r="187">
@@ -9003,26 +9004,26 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>0.09943493880077356</v>
+        <v>0.1014549402188581</v>
       </c>
       <c r="F187" t="n">
-        <v>2.540625</v>
+        <v>2.601183333333334</v>
       </c>
       <c r="G187" t="n">
-        <v>2.421932017693929</v>
+        <v>2.409724267906856</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.1186929823060705</v>
+        <v>-0.1914590654264781</v>
       </c>
       <c r="I187" t="n">
-        <v>4.671802501591952</v>
+        <v>7.360460255645624</v>
       </c>
       <c r="J187" t="n">
-        <v>-4.671802501591952</v>
+        <v>-7.360460255645624</v>
       </c>
     </row>
     <row r="188">
@@ -9047,16 +9048,16 @@
         <v>1.869</v>
       </c>
       <c r="G188" t="n">
-        <v>2.357486236027441</v>
+        <v>2.341828161607408</v>
       </c>
       <c r="H188" t="n">
-        <v>0.4884862360274413</v>
+        <v>0.4728281616074084</v>
       </c>
       <c r="I188" t="n">
-        <v>26.13623520746075</v>
+        <v>25.29845701484261</v>
       </c>
       <c r="J188" t="n">
-        <v>26.13623520746075</v>
+        <v>25.29845701484261</v>
       </c>
     </row>
     <row r="189">
@@ -9081,16 +9082,16 @@
         <v>2.254459673470501</v>
       </c>
       <c r="G189" t="n">
-        <v>2.393352334080062</v>
+        <v>2.377684783663784</v>
       </c>
       <c r="H189" t="n">
-        <v>0.1388926606095606</v>
+        <v>0.1232251101932826</v>
       </c>
       <c r="I189" t="n">
-        <v>6.160795965613797</v>
+        <v>5.465837852117827</v>
       </c>
       <c r="J189" t="n">
-        <v>6.160795965613797</v>
+        <v>5.465837852117827</v>
       </c>
     </row>
     <row r="190">
@@ -9107,24 +9108,24 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="n">
-        <v>2.540625</v>
+        <v>2.601183333333334</v>
       </c>
       <c r="G190" t="n">
-        <v>2.534079760159571</v>
+        <v>2.518269289043264</v>
       </c>
       <c r="H190" t="n">
-        <v>-0.006545239840428874</v>
+        <v>-0.08291404429006999</v>
       </c>
       <c r="I190" t="n">
-        <v>0.257623216351444</v>
+        <v>3.187550959117452</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.257623216351444</v>
+        <v>-3.187550959117452</v>
       </c>
     </row>
     <row r="191">
@@ -9145,22 +9146,22 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>0.07775141806413362</v>
+        <v>0.07972957776622766</v>
       </c>
       <c r="F191" t="n">
         <v>1.8122</v>
       </c>
       <c r="G191" t="n">
-        <v>1.812201618045614</v>
+        <v>1.812200181731645</v>
       </c>
       <c r="H191" t="n">
-        <v>1.61804561349399e-06</v>
+        <v>1.817316448438078e-07</v>
       </c>
       <c r="I191" t="n">
-        <v>8.92862605393439e-05</v>
+        <v>1.002823335414456e-05</v>
       </c>
       <c r="J191" t="n">
-        <v>8.92862605393439e-05</v>
+        <v>1.002823335414456e-05</v>
       </c>
     </row>
     <row r="192">
@@ -9181,22 +9182,22 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>0.07775141806413362</v>
+        <v>0.07972957776622766</v>
       </c>
       <c r="F192" t="n">
         <v>2.166325</v>
       </c>
       <c r="G192" t="n">
-        <v>1.977069709403249</v>
+        <v>1.972873735471231</v>
       </c>
       <c r="H192" t="n">
-        <v>-0.1892552905967506</v>
+        <v>-0.1934512645287687</v>
       </c>
       <c r="I192" t="n">
-        <v>8.736237203409027</v>
+        <v>8.929928082294609</v>
       </c>
       <c r="J192" t="n">
-        <v>-8.736237203409027</v>
+        <v>-8.929928082294609</v>
       </c>
     </row>
     <row r="193">
@@ -9213,26 +9214,26 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>0.07775141806413362</v>
+        <v>0.07972957776622766</v>
       </c>
       <c r="F193" t="n">
-        <v>2.48075</v>
+        <v>2.561983333333334</v>
       </c>
       <c r="G193" t="n">
-        <v>2.378185871173006</v>
+        <v>2.366359266449719</v>
       </c>
       <c r="H193" t="n">
-        <v>-0.1025641288269936</v>
+        <v>-0.1956240668836147</v>
       </c>
       <c r="I193" t="n">
-        <v>4.134400033336435</v>
+        <v>7.6356494727502</v>
       </c>
       <c r="J193" t="n">
-        <v>-4.134400033336435</v>
+        <v>-7.6356494727502</v>
       </c>
     </row>
     <row r="194">
@@ -9253,22 +9254,22 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>0.1055651951327819</v>
+        <v>0.1075983135296858</v>
       </c>
       <c r="F194" t="n">
         <v>1.8122</v>
       </c>
       <c r="G194" t="n">
-        <v>1.812201331745566</v>
+        <v>1.812202321204978</v>
       </c>
       <c r="H194" t="n">
-        <v>1.331745565824605e-06</v>
+        <v>2.321204978006364e-06</v>
       </c>
       <c r="I194" t="n">
-        <v>7.348778091957867e-05</v>
+        <v>0.0001280876822650019</v>
       </c>
       <c r="J194" t="n">
-        <v>7.348778091957867e-05</v>
+        <v>0.0001280876822650019</v>
       </c>
     </row>
     <row r="195">
@@ -9289,22 +9290,22 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>0.1055651951327819</v>
+        <v>0.1075983135296858</v>
       </c>
       <c r="F195" t="n">
         <v>2.166325</v>
       </c>
       <c r="G195" t="n">
-        <v>1.974704670625134</v>
+        <v>1.97060279558481</v>
       </c>
       <c r="H195" t="n">
-        <v>-0.1916203293748664</v>
+        <v>-0.1957222044151898</v>
       </c>
       <c r="I195" t="n">
-        <v>8.845410055040974</v>
+        <v>9.034757223186265</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.845410055040974</v>
+        <v>-9.034757223186265</v>
       </c>
     </row>
     <row r="196">
@@ -9321,26 +9322,26 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>0.1055651951327819</v>
+        <v>0.1075983135296858</v>
       </c>
       <c r="F196" t="n">
-        <v>2.48075</v>
+        <v>2.561983333333334</v>
       </c>
       <c r="G196" t="n">
-        <v>2.375504513060961</v>
+        <v>2.363776005895018</v>
       </c>
       <c r="H196" t="n">
-        <v>-0.1052454869390393</v>
+        <v>-0.1982073274383152</v>
       </c>
       <c r="I196" t="n">
-        <v>4.242486624570769</v>
+        <v>7.736479970790149</v>
       </c>
       <c r="J196" t="n">
-        <v>-4.242486624570769</v>
+        <v>-7.736479970790149</v>
       </c>
     </row>
     <row r="197">
@@ -9365,16 +9366,16 @@
         <v>1.8122</v>
       </c>
       <c r="G197" t="n">
-        <v>2.294964440630856</v>
+        <v>2.279729526623774</v>
       </c>
       <c r="H197" t="n">
-        <v>0.4827644406308556</v>
+        <v>0.4675295266237736</v>
       </c>
       <c r="I197" t="n">
-        <v>26.63968881088487</v>
+        <v>25.79900268313506</v>
       </c>
       <c r="J197" t="n">
-        <v>26.63968881088487</v>
+        <v>25.79900268313506</v>
       </c>
     </row>
     <row r="198">
@@ -9399,16 +9400,16 @@
         <v>2.166325</v>
       </c>
       <c r="G198" t="n">
-        <v>2.334667143564221</v>
+        <v>2.31942122398937</v>
       </c>
       <c r="H198" t="n">
-        <v>0.1683421435642209</v>
+        <v>0.1530962239893698</v>
       </c>
       <c r="I198" t="n">
-        <v>7.770862800559517</v>
+        <v>7.067093995100912</v>
       </c>
       <c r="J198" t="n">
-        <v>7.770862800559517</v>
+        <v>7.067093995100912</v>
       </c>
     </row>
     <row r="199">
@@ -9425,24 +9426,24 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="n">
-        <v>2.48075</v>
+        <v>2.561983333333334</v>
       </c>
       <c r="G199" t="n">
-        <v>2.489632972105207</v>
+        <v>2.474224753937396</v>
       </c>
       <c r="H199" t="n">
-        <v>0.008882972105206832</v>
+        <v>-0.0877585793959379</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3580760699468641</v>
+        <v>3.42541570251971</v>
       </c>
       <c r="J199" t="n">
-        <v>0.3580760699468641</v>
+        <v>-3.42541570251971</v>
       </c>
     </row>
     <row r="200">
@@ -9463,22 +9464,22 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>0.06851827165700264</v>
+        <v>0.07110019935028825</v>
       </c>
       <c r="F200" t="n">
         <v>2.2072875</v>
       </c>
       <c r="G200" t="n">
-        <v>2.207289078664448</v>
+        <v>2.207288582010091</v>
       </c>
       <c r="H200" t="n">
-        <v>1.578664448054212e-06</v>
+        <v>1.082010091746355e-06</v>
       </c>
       <c r="I200" t="n">
-        <v>7.152056304646369e-05</v>
+        <v>4.901989848383389e-05</v>
       </c>
       <c r="J200" t="n">
-        <v>7.152056304646369e-05</v>
+        <v>4.901989848383389e-05</v>
       </c>
     </row>
     <row r="201">
@@ -9499,22 +9500,22 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>0.06851827165700264</v>
+        <v>0.07110019935028825</v>
       </c>
       <c r="F201" t="n">
         <v>2.365288415656712</v>
       </c>
       <c r="G201" t="n">
-        <v>2.345713931228091</v>
+        <v>2.339819610614401</v>
       </c>
       <c r="H201" t="n">
-        <v>-0.0195744844286212</v>
+        <v>-0.02546880504231153</v>
       </c>
       <c r="I201" t="n">
-        <v>0.8275728363209535</v>
+        <v>1.076773761445926</v>
       </c>
       <c r="J201" t="n">
-        <v>-0.8275728363209535</v>
+        <v>-1.076773761445926</v>
       </c>
     </row>
     <row r="202">
@@ -9531,26 +9532,26 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>0.06851827165700264</v>
+        <v>0.07110019935028825</v>
       </c>
       <c r="F202" t="n">
-        <v>2.55265</v>
+        <v>2.615265625</v>
       </c>
       <c r="G202" t="n">
-        <v>2.635671249438103</v>
+        <v>2.621253254152974</v>
       </c>
       <c r="H202" t="n">
-        <v>0.08302124943810352</v>
+        <v>0.005987629152973462</v>
       </c>
       <c r="I202" t="n">
-        <v>3.252355373361155</v>
+        <v>0.2289491780772158</v>
       </c>
       <c r="J202" t="n">
-        <v>3.252355373361155</v>
+        <v>0.2289491780772158</v>
       </c>
     </row>
     <row r="203">
@@ -9571,22 +9572,22 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>0.08284595615112531</v>
+        <v>0.08546840709107527</v>
       </c>
       <c r="F203" t="n">
         <v>2.2072875</v>
       </c>
       <c r="G203" t="n">
-        <v>2.207288582878478</v>
+        <v>2.207289809509084</v>
       </c>
       <c r="H203" t="n">
-        <v>1.08287847844224e-06</v>
+        <v>2.309509084419403e-06</v>
       </c>
       <c r="I203" t="n">
-        <v>4.905924028665228e-05</v>
+        <v>0.000104631095152734</v>
       </c>
       <c r="J203" t="n">
-        <v>4.905924028665228e-05</v>
+        <v>0.000104631095152734</v>
       </c>
     </row>
     <row r="204">
@@ -9607,22 +9608,22 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>0.08284595615112531</v>
+        <v>0.08546840709107527</v>
       </c>
       <c r="F204" t="n">
         <v>2.365288415656712</v>
       </c>
       <c r="G204" t="n">
-        <v>2.344569883097834</v>
+        <v>2.338742266664792</v>
       </c>
       <c r="H204" t="n">
-        <v>-0.0207185325588779</v>
+        <v>-0.02654614899191987</v>
       </c>
       <c r="I204" t="n">
-        <v>0.8759410658647092</v>
+        <v>1.122321862154364</v>
       </c>
       <c r="J204" t="n">
-        <v>-0.8759410658647092</v>
+        <v>-1.122321862154364</v>
       </c>
     </row>
     <row r="205">
@@ -9639,26 +9640,26 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>0.08284595615112531</v>
+        <v>0.08546840709107527</v>
       </c>
       <c r="F205" t="n">
-        <v>2.55265</v>
+        <v>2.615265625</v>
       </c>
       <c r="G205" t="n">
-        <v>2.634599643850149</v>
+        <v>2.620231716707695</v>
       </c>
       <c r="H205" t="n">
-        <v>0.08194964385014902</v>
+        <v>0.004966091707694797</v>
       </c>
       <c r="I205" t="n">
-        <v>3.210375251215365</v>
+        <v>0.1898886162928401</v>
       </c>
       <c r="J205" t="n">
-        <v>3.210375251215365</v>
+        <v>0.1898886162928401</v>
       </c>
     </row>
     <row r="206">
@@ -9683,16 +9684,16 @@
         <v>2.2072875</v>
       </c>
       <c r="G206" t="n">
-        <v>2.615486446795971</v>
+        <v>2.598083579963204</v>
       </c>
       <c r="H206" t="n">
-        <v>0.408198946795971</v>
+        <v>0.3907960799632049</v>
       </c>
       <c r="I206" t="n">
-        <v>18.4932387283474</v>
+        <v>17.70481099372895</v>
       </c>
       <c r="J206" t="n">
-        <v>18.4932387283474</v>
+        <v>17.70481099372895</v>
       </c>
     </row>
     <row r="207">
@@ -9717,16 +9718,16 @@
         <v>2.365288415656712</v>
       </c>
       <c r="G207" t="n">
-        <v>2.636253308244711</v>
+        <v>2.618845893417667</v>
       </c>
       <c r="H207" t="n">
-        <v>0.2709648925879988</v>
+        <v>0.2535574777609546</v>
       </c>
       <c r="I207" t="n">
-        <v>11.4558922622029</v>
+        <v>10.71993910267199</v>
       </c>
       <c r="J207" t="n">
-        <v>11.4558922622029</v>
+        <v>10.71993910267199</v>
       </c>
     </row>
     <row r="208">
@@ -9743,24 +9744,24 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>2.55265</v>
+        <v>2.615265625</v>
       </c>
       <c r="G208" t="n">
-        <v>2.7192903941489</v>
+        <v>2.701808493083026</v>
       </c>
       <c r="H208" t="n">
-        <v>0.1666403941488999</v>
+        <v>0.08654286808302558</v>
       </c>
       <c r="I208" t="n">
-        <v>6.528133279098188</v>
+        <v>3.309142568760126</v>
       </c>
       <c r="J208" t="n">
-        <v>6.528133279098188</v>
+        <v>3.309142568760126</v>
       </c>
     </row>
     <row r="209">
@@ -9781,22 +9782,22 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>0.06991180165766715</v>
+        <v>0.07216402703380637</v>
       </c>
       <c r="F209" t="n">
         <v>2.075675</v>
       </c>
       <c r="G209" t="n">
-        <v>2.075677041982976</v>
+        <v>2.075675983588938</v>
       </c>
       <c r="H209" t="n">
-        <v>2.041982976486167e-06</v>
+        <v>9.835889378528861e-07</v>
       </c>
       <c r="I209" t="n">
-        <v>9.837681604712527e-05</v>
+        <v>4.73864616499638e-05</v>
       </c>
       <c r="J209" t="n">
-        <v>9.837681604712527e-05</v>
+        <v>4.73864616499638e-05</v>
       </c>
     </row>
     <row r="210">
@@ -9817,22 +9818,22 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>0.06991180165766715</v>
+        <v>0.07216402703380637</v>
       </c>
       <c r="F210" t="n">
         <v>2.248592380402163</v>
       </c>
       <c r="G210" t="n">
-        <v>2.228072303109685</v>
+        <v>2.222711070038197</v>
       </c>
       <c r="H210" t="n">
-        <v>-0.02052007729247851</v>
+        <v>-0.02588131036396657</v>
       </c>
       <c r="I210" t="n">
-        <v>0.912574349683088</v>
+        <v>1.151000536581809</v>
       </c>
       <c r="J210" t="n">
-        <v>-0.912574349683088</v>
+        <v>-1.151000536581809</v>
       </c>
     </row>
     <row r="211">
@@ -9849,26 +9850,26 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>0.06991180165766715</v>
+        <v>0.07216402703380637</v>
       </c>
       <c r="F211" t="n">
-        <v>2.4773625</v>
+        <v>2.544978125</v>
       </c>
       <c r="G211" t="n">
-        <v>2.560040084395737</v>
+        <v>2.546388096156609</v>
       </c>
       <c r="H211" t="n">
-        <v>0.08267758439573747</v>
+        <v>0.001409971156609569</v>
       </c>
       <c r="I211" t="n">
-        <v>3.337322834092204</v>
+        <v>0.05540209335235715</v>
       </c>
       <c r="J211" t="n">
-        <v>3.337322834092204</v>
+        <v>0.05540209335235715</v>
       </c>
     </row>
     <row r="212">
@@ -9889,22 +9890,22 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>0.08779421922295189</v>
+        <v>0.09009004668823942</v>
       </c>
       <c r="F212" t="n">
         <v>2.075675</v>
       </c>
       <c r="G212" t="n">
-        <v>2.07567573264516</v>
+        <v>2.075677695368238</v>
       </c>
       <c r="H212" t="n">
-        <v>7.326451596512129e-07</v>
+        <v>2.695368238381235e-06</v>
       </c>
       <c r="I212" t="n">
-        <v>3.529671840009697e-05</v>
+        <v>0.0001298550225050278</v>
       </c>
       <c r="J212" t="n">
-        <v>3.529671840009697e-05</v>
+        <v>0.0001298550225050278</v>
       </c>
     </row>
     <row r="213">
@@ -9925,22 +9926,22 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>0.08779421922295189</v>
+        <v>0.09009004668823942</v>
       </c>
       <c r="F213" t="n">
         <v>2.248592380402163</v>
       </c>
       <c r="G213" t="n">
-        <v>2.226531662374144</v>
+        <v>2.221247759638625</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.0220607180280199</v>
+        <v>-0.02734462076353816</v>
       </c>
       <c r="I213" t="n">
-        <v>0.9810901353349918</v>
+        <v>1.216077266909868</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.9810901353349918</v>
+        <v>-1.216077266909868</v>
       </c>
     </row>
     <row r="214">
@@ -9957,26 +9958,26 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>0.08779421922295189</v>
+        <v>0.09009004668823942</v>
       </c>
       <c r="F214" t="n">
-        <v>2.4773625</v>
+        <v>2.544978125</v>
       </c>
       <c r="G214" t="n">
-        <v>2.558523635349941</v>
+        <v>2.544935263770212</v>
       </c>
       <c r="H214" t="n">
-        <v>0.08116113534994129</v>
+        <v>-4.2861229787583e-05</v>
       </c>
       <c r="I214" t="n">
-        <v>3.276110595439355</v>
+        <v>0.001684149241462851</v>
       </c>
       <c r="J214" t="n">
-        <v>3.276110595439355</v>
+        <v>-0.001684149241462851</v>
       </c>
     </row>
     <row r="215">
@@ -10001,16 +10002,16 @@
         <v>2.075675</v>
       </c>
       <c r="G215" t="n">
-        <v>2.526923629157352</v>
+        <v>2.510119458573358</v>
       </c>
       <c r="H215" t="n">
-        <v>0.4512486291573516</v>
+        <v>0.434444458573358</v>
       </c>
       <c r="I215" t="n">
-        <v>21.73984988774021</v>
+        <v>20.93027369763369</v>
       </c>
       <c r="J215" t="n">
-        <v>21.73984988774021</v>
+        <v>20.93027369763369</v>
       </c>
     </row>
     <row r="216">
@@ -10035,16 +10036,16 @@
         <v>2.248592380402163</v>
       </c>
       <c r="G216" t="n">
-        <v>2.552751035224441</v>
+        <v>2.535940842992425</v>
       </c>
       <c r="H216" t="n">
-        <v>0.3041586548222774</v>
+        <v>0.2873484625902618</v>
       </c>
       <c r="I216" t="n">
-        <v>13.52662481084625</v>
+        <v>12.77903745893105</v>
       </c>
       <c r="J216" t="n">
-        <v>13.52662481084625</v>
+        <v>12.77903745893105</v>
       </c>
     </row>
     <row r="217">
@@ -10061,24 +10062,24 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
-        <v>2.4773625</v>
+        <v>2.544978125</v>
       </c>
       <c r="G217" t="n">
-        <v>2.655402367603532</v>
+        <v>2.638496136046607</v>
       </c>
       <c r="H217" t="n">
-        <v>0.1780398676035322</v>
+        <v>0.09351801104660717</v>
       </c>
       <c r="I217" t="n">
-        <v>7.186670001000346</v>
+        <v>3.674609621511272</v>
       </c>
       <c r="J217" t="n">
-        <v>7.186670001000346</v>
+        <v>3.674609621511272</v>
       </c>
     </row>
     <row r="218">
@@ -10099,22 +10100,22 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>0.06376691369579074</v>
+        <v>0.06864450336153091</v>
       </c>
       <c r="F218" t="n">
         <v>2.598375</v>
       </c>
       <c r="G218" t="n">
-        <v>2.598375497027889</v>
+        <v>2.598376774155647</v>
       </c>
       <c r="H218" t="n">
-        <v>4.970278886240465e-07</v>
+        <v>1.774155646838693e-06</v>
       </c>
       <c r="I218" t="n">
-        <v>1.912841251259139e-05</v>
+        <v>6.827943029157428e-05</v>
       </c>
       <c r="J218" t="n">
-        <v>1.912841251259139e-05</v>
+        <v>6.827943029157428e-05</v>
       </c>
     </row>
     <row r="219">
@@ -10135,22 +10136,22 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>0.06376691369579074</v>
+        <v>0.06864450336153091</v>
       </c>
       <c r="F219" t="n">
         <v>2.715150068499876</v>
       </c>
       <c r="G219" t="n">
-        <v>2.681176324681618</v>
+        <v>2.673577863216871</v>
       </c>
       <c r="H219" t="n">
-        <v>-0.03397374381825768</v>
+        <v>-0.04157220528300476</v>
       </c>
       <c r="I219" t="n">
-        <v>1.251265784989491</v>
+        <v>1.53111998358063</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.251265784989491</v>
+        <v>-1.53111998358063</v>
       </c>
     </row>
     <row r="220">
@@ -10167,26 +10168,26 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>0.06376691369579074</v>
+        <v>0.06864450336153091</v>
       </c>
       <c r="F220" t="n">
-        <v>2.7981125</v>
+        <v>2.829431944444444</v>
       </c>
       <c r="G220" t="n">
-        <v>2.834695765304763</v>
+        <v>2.818153575813073</v>
       </c>
       <c r="H220" t="n">
-        <v>0.0365832653047633</v>
+        <v>-0.01127836863137111</v>
       </c>
       <c r="I220" t="n">
-        <v>1.307426535021851</v>
+        <v>0.3986089382187138</v>
       </c>
       <c r="J220" t="n">
-        <v>1.307426535021851</v>
+        <v>-0.3986089382187138</v>
       </c>
     </row>
     <row r="221">
@@ -10207,22 +10208,22 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>0.06972497661133063</v>
+        <v>0.07463470711230444</v>
       </c>
       <c r="F221" t="n">
         <v>2.598375</v>
       </c>
       <c r="G221" t="n">
-        <v>2.598376008361281</v>
+        <v>2.598374770824879</v>
       </c>
       <c r="H221" t="n">
-        <v>1.008361281584769e-06</v>
+        <v>-2.291751206584536e-07</v>
       </c>
       <c r="I221" t="n">
-        <v>3.880738082781618e-05</v>
+        <v>8.819940180245483e-06</v>
       </c>
       <c r="J221" t="n">
-        <v>3.880738082781618e-05</v>
+        <v>-8.819940180245483e-06</v>
       </c>
     </row>
     <row r="222">
@@ -10243,22 +10244,22 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>0.06972497661133063</v>
+        <v>0.07463470711230444</v>
       </c>
       <c r="F222" t="n">
         <v>2.715150068499876</v>
       </c>
       <c r="G222" t="n">
-        <v>2.680878073661512</v>
+        <v>2.673311859129013</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.03427199483836318</v>
+        <v>-0.04183820937086224</v>
       </c>
       <c r="I222" t="n">
-        <v>1.262250482430922</v>
+        <v>1.540917014357807</v>
       </c>
       <c r="J222" t="n">
-        <v>-1.262250482430922</v>
+        <v>-1.540917014357807</v>
       </c>
     </row>
     <row r="223">
@@ -10275,26 +10276,26 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>0.06972497661133063</v>
+        <v>0.07463470711230444</v>
       </c>
       <c r="F223" t="n">
-        <v>2.7981125</v>
+        <v>2.829431944444444</v>
       </c>
       <c r="G223" t="n">
-        <v>2.834455593423926</v>
+        <v>2.817931967533389</v>
       </c>
       <c r="H223" t="n">
-        <v>0.03634309342392639</v>
+        <v>-0.01149997691105487</v>
       </c>
       <c r="I223" t="n">
-        <v>1.298843181749354</v>
+        <v>0.40644119161922</v>
       </c>
       <c r="J223" t="n">
-        <v>1.298843181749354</v>
+        <v>-0.40644119161922</v>
       </c>
     </row>
     <row r="224">
@@ -10319,16 +10320,16 @@
         <v>2.598375</v>
       </c>
       <c r="G224" t="n">
-        <v>2.834221882257818</v>
+        <v>2.815341205822899</v>
       </c>
       <c r="H224" t="n">
-        <v>0.2358468822578179</v>
+        <v>0.2169662058228994</v>
       </c>
       <c r="I224" t="n">
-        <v>9.076706874789741</v>
+        <v>8.350072865652548</v>
       </c>
       <c r="J224" t="n">
-        <v>9.076706874789741</v>
+        <v>8.350072865652548</v>
       </c>
     </row>
     <row r="225">
@@ -10353,16 +10354,16 @@
         <v>2.715150068499876</v>
       </c>
       <c r="G225" t="n">
-        <v>2.842958064846754</v>
+        <v>2.824075737069516</v>
       </c>
       <c r="H225" t="n">
-        <v>0.1278079963468781</v>
+        <v>0.1089256685696407</v>
       </c>
       <c r="I225" t="n">
-        <v>4.707216659206327</v>
+        <v>4.011773412945175</v>
       </c>
       <c r="J225" t="n">
-        <v>4.707216659206327</v>
+        <v>4.011773412945175</v>
       </c>
     </row>
     <row r="226">
@@ -10379,24 +10380,24 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="n">
-        <v>2.7981125</v>
+        <v>2.829431944444444</v>
       </c>
       <c r="G226" t="n">
-        <v>2.878352109889996</v>
+        <v>2.85944110020561</v>
       </c>
       <c r="H226" t="n">
-        <v>0.08023960988999645</v>
+        <v>0.03000915576116636</v>
       </c>
       <c r="I226" t="n">
-        <v>2.867633445402801</v>
+        <v>1.060607088291662</v>
       </c>
       <c r="J226" t="n">
-        <v>2.867633445402801</v>
+        <v>1.060607088291662</v>
       </c>
     </row>
     <row r="227">
@@ -10417,22 +10418,22 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>0.04685847404322814</v>
+        <v>0.05161121416311337</v>
       </c>
       <c r="F227" t="n">
         <v>2.7035125</v>
       </c>
       <c r="G227" t="n">
-        <v>2.703513315119122</v>
+        <v>2.703512319891357</v>
       </c>
       <c r="H227" t="n">
-        <v>8.151191215333142e-07</v>
+        <v>-1.801086426667098e-07</v>
       </c>
       <c r="I227" t="n">
-        <v>3.015037369101546e-05</v>
+        <v>6.66202366982619e-06</v>
       </c>
       <c r="J227" t="n">
-        <v>3.015037369101546e-05</v>
+        <v>-6.66202366982619e-06</v>
       </c>
     </row>
     <row r="228">
@@ -10453,22 +10454,22 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>0.04685847404322814</v>
+        <v>0.05161121416311337</v>
       </c>
       <c r="F228" t="n">
         <v>2.817383744798192</v>
       </c>
       <c r="G228" t="n">
-        <v>2.781622808848252</v>
+        <v>2.772299718466561</v>
       </c>
       <c r="H228" t="n">
-        <v>-0.03576093594993912</v>
+        <v>-0.04508402633163078</v>
       </c>
       <c r="I228" t="n">
-        <v>1.269295885445689</v>
+        <v>1.600208931952226</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.269295885445689</v>
+        <v>-1.600208931952226</v>
       </c>
     </row>
     <row r="229">
@@ -10485,26 +10486,26 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>0.04685847404322814</v>
+        <v>0.05161121416311337</v>
       </c>
       <c r="F229" t="n">
-        <v>2.8489375</v>
+        <v>2.8942375</v>
       </c>
       <c r="G229" t="n">
-        <v>2.898887512780524</v>
+        <v>2.881209823510938</v>
       </c>
       <c r="H229" t="n">
-        <v>0.04995001278052369</v>
+        <v>-0.01302767648906222</v>
       </c>
       <c r="I229" t="n">
-        <v>1.753285664586313</v>
+        <v>0.45012465248834</v>
       </c>
       <c r="J229" t="n">
-        <v>1.753285664586313</v>
+        <v>-0.45012465248834</v>
       </c>
     </row>
     <row r="230">
@@ -10525,22 +10526,22 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>0.05020947065389519</v>
+        <v>0.05498242253594483</v>
       </c>
       <c r="F230" t="n">
         <v>2.7035125</v>
       </c>
       <c r="G230" t="n">
-        <v>2.703513633942822</v>
+        <v>2.70351262587046</v>
       </c>
       <c r="H230" t="n">
-        <v>1.133942821862632e-06</v>
+        <v>1.258704602769001e-07</v>
       </c>
       <c r="I230" t="n">
-        <v>4.194331714251857e-05</v>
+        <v>4.655812032565045e-06</v>
       </c>
       <c r="J230" t="n">
-        <v>4.194331714251857e-05</v>
+        <v>4.655812032565045e-06</v>
       </c>
     </row>
     <row r="231">
@@ -10561,22 +10562,22 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>0.05020947065389519</v>
+        <v>0.05498242253594483</v>
       </c>
       <c r="F231" t="n">
         <v>2.817383744798192</v>
       </c>
       <c r="G231" t="n">
-        <v>2.781452187677227</v>
+        <v>2.77215149840852</v>
       </c>
       <c r="H231" t="n">
-        <v>-0.03593155712096419</v>
+        <v>-0.04523224638967127</v>
       </c>
       <c r="I231" t="n">
-        <v>1.275351900049312</v>
+        <v>1.605469843189971</v>
       </c>
       <c r="J231" t="n">
-        <v>-1.275351900049312</v>
+        <v>-1.605469843189971</v>
       </c>
     </row>
     <row r="232">
@@ -10593,26 +10594,26 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>0.05020947065389519</v>
+        <v>0.05498242253594483</v>
       </c>
       <c r="F232" t="n">
-        <v>2.8489375</v>
+        <v>2.8942375</v>
       </c>
       <c r="G232" t="n">
-        <v>2.898780064088812</v>
+        <v>2.881111177107808</v>
       </c>
       <c r="H232" t="n">
-        <v>0.0498425640888116</v>
+        <v>-0.01312632289219229</v>
       </c>
       <c r="I232" t="n">
-        <v>1.749514128997621</v>
+        <v>0.4535330252680468</v>
       </c>
       <c r="J232" t="n">
-        <v>1.749514128997621</v>
+        <v>-0.4535330252680468</v>
       </c>
     </row>
     <row r="233">
@@ -10637,16 +10638,16 @@
         <v>2.7035125</v>
       </c>
       <c r="G233" t="n">
-        <v>2.903918715847031</v>
+        <v>2.884567384465444</v>
       </c>
       <c r="H233" t="n">
-        <v>0.2004062158470306</v>
+        <v>0.1810548844654436</v>
       </c>
       <c r="I233" t="n">
-        <v>7.412808923466437</v>
+        <v>6.697024129366652</v>
       </c>
       <c r="J233" t="n">
-        <v>7.412808923466437</v>
+        <v>6.697024129366652</v>
       </c>
     </row>
     <row r="234">
@@ -10671,16 +10672,16 @@
         <v>2.817383744798192</v>
       </c>
       <c r="G234" t="n">
-        <v>2.908945434687692</v>
+        <v>2.889593194814664</v>
       </c>
       <c r="H234" t="n">
-        <v>0.0915616898895002</v>
+        <v>0.0722094500164725</v>
       </c>
       <c r="I234" t="n">
-        <v>3.249883515461922</v>
+        <v>2.562996615203544</v>
       </c>
       <c r="J234" t="n">
-        <v>3.249883515461922</v>
+        <v>2.562996615203544</v>
       </c>
     </row>
     <row r="235">
@@ -10697,24 +10698,24 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2.8489375</v>
+        <v>2.8942375</v>
       </c>
       <c r="G235" t="n">
-        <v>2.929386921205048</v>
+        <v>2.910018632748759</v>
       </c>
       <c r="H235" t="n">
-        <v>0.08044942120504839</v>
+        <v>0.0157811327487587</v>
       </c>
       <c r="I235" t="n">
-        <v>2.823839456114723</v>
+        <v>0.5452604614776325</v>
       </c>
       <c r="J235" t="n">
-        <v>2.823839456114723</v>
+        <v>0.5452604614776325</v>
       </c>
     </row>
     <row r="236">
@@ -10735,22 +10736,22 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>0.02206948878536812</v>
+        <v>0.02397019273512207</v>
       </c>
       <c r="F236" t="n">
         <v>2.659425</v>
       </c>
       <c r="G236" t="n">
-        <v>2.659426060809437</v>
+        <v>2.659424564319452</v>
       </c>
       <c r="H236" t="n">
-        <v>1.060809437181121e-06</v>
+        <v>-4.356805480831838e-07</v>
       </c>
       <c r="I236" t="n">
-        <v>3.988867658163402e-05</v>
+        <v>1.638250930495065e-05</v>
       </c>
       <c r="J236" t="n">
-        <v>3.988867658163402e-05</v>
+        <v>-1.638250930495065e-05</v>
       </c>
     </row>
     <row r="237">
@@ -10771,22 +10772,22 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>0.02206948878536812</v>
+        <v>0.02397019273512207</v>
       </c>
       <c r="F237" t="n">
         <v>2.836889861687792</v>
       </c>
       <c r="G237" t="n">
-        <v>2.797384280347661</v>
+        <v>2.784915451923733</v>
       </c>
       <c r="H237" t="n">
-        <v>-0.03950558134013127</v>
+        <v>-0.05197440976405909</v>
       </c>
       <c r="I237" t="n">
-        <v>1.392566622823617</v>
+        <v>1.832091208967034</v>
       </c>
       <c r="J237" t="n">
-        <v>-1.392566622823617</v>
+        <v>-1.832091208967034</v>
       </c>
     </row>
     <row r="238">
@@ -10803,26 +10804,26 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>0.02206948878536812</v>
+        <v>0.02397019273512207</v>
       </c>
       <c r="F238" t="n">
-        <v>2.9149375</v>
+        <v>2.949019444444444</v>
       </c>
       <c r="G238" t="n">
-        <v>2.92554068258573</v>
+        <v>2.906890192287715</v>
       </c>
       <c r="H238" t="n">
-        <v>0.01060318258572979</v>
+        <v>-0.04212925215672891</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3637533424208851</v>
+        <v>1.428585092448093</v>
       </c>
       <c r="J238" t="n">
-        <v>0.3637533424208851</v>
+        <v>-1.428585092448093</v>
       </c>
     </row>
     <row r="239">
@@ -10843,22 +10844,22 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>0.02426330837471627</v>
+        <v>0.02617032869151523</v>
       </c>
       <c r="F239" t="n">
         <v>2.659425</v>
       </c>
       <c r="G239" t="n">
-        <v>2.659426102619703</v>
+        <v>2.659424818259136</v>
       </c>
       <c r="H239" t="n">
-        <v>1.102619703097218e-06</v>
+        <v>-1.817408641358043e-07</v>
       </c>
       <c r="I239" t="n">
-        <v>4.146083093515397e-05</v>
+        <v>6.833840553345338e-06</v>
       </c>
       <c r="J239" t="n">
-        <v>4.146083093515397e-05</v>
+        <v>-6.833840553345338e-06</v>
       </c>
     </row>
     <row r="240">
@@ -10879,22 +10880,22 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>0.02426330837471627</v>
+        <v>0.02617032869151523</v>
       </c>
       <c r="F240" t="n">
         <v>2.836889861687792</v>
       </c>
       <c r="G240" t="n">
-        <v>2.797188631284807</v>
+        <v>2.784735928838403</v>
       </c>
       <c r="H240" t="n">
-        <v>-0.03970123040298512</v>
+        <v>-0.05215393284938941</v>
       </c>
       <c r="I240" t="n">
-        <v>1.399463226935609</v>
+        <v>1.838419374461041</v>
       </c>
       <c r="J240" t="n">
-        <v>-1.399463226935609</v>
+        <v>-1.838419374461041</v>
       </c>
     </row>
     <row r="241">
@@ -10911,26 +10912,26 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>0.02426330837471627</v>
+        <v>0.02617032869151523</v>
       </c>
       <c r="F241" t="n">
-        <v>2.9149375</v>
+        <v>2.949019444444444</v>
       </c>
       <c r="G241" t="n">
-        <v>2.925465441607347</v>
+        <v>2.906818484224753</v>
       </c>
       <c r="H241" t="n">
-        <v>0.01052794160734738</v>
+        <v>-0.04220096021969155</v>
       </c>
       <c r="I241" t="n">
-        <v>0.3611721214381914</v>
+        <v>1.431016682483816</v>
       </c>
       <c r="J241" t="n">
-        <v>0.3611721214381914</v>
+        <v>-1.431016682483816</v>
       </c>
     </row>
     <row r="242">
@@ -10955,16 +10956,16 @@
         <v>2.659425</v>
       </c>
       <c r="G242" t="n">
-        <v>2.934628380558415</v>
+        <v>2.915069701404654</v>
       </c>
       <c r="H242" t="n">
-        <v>0.2752033805584144</v>
+        <v>0.2556447014046541</v>
       </c>
       <c r="I242" t="n">
-        <v>10.34822867944817</v>
+        <v>9.612781011107819</v>
       </c>
       <c r="J242" t="n">
-        <v>10.34822867944817</v>
+        <v>9.612781011107819</v>
       </c>
     </row>
     <row r="243">
@@ -10989,16 +10990,16 @@
         <v>2.836889861687792</v>
       </c>
       <c r="G243" t="n">
-        <v>2.93803781955409</v>
+        <v>2.918478536082983</v>
       </c>
       <c r="H243" t="n">
-        <v>0.1011479578662975</v>
+        <v>0.08158867439519035</v>
       </c>
       <c r="I243" t="n">
-        <v>3.565452407310591</v>
+        <v>2.875990199586021</v>
       </c>
       <c r="J243" t="n">
-        <v>3.565452407310591</v>
+        <v>2.875990199586021</v>
       </c>
     </row>
     <row r="244">
@@ -11015,24 +11016,24 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>2.9149375</v>
+        <v>2.949019444444444</v>
       </c>
       <c r="G244" t="n">
-        <v>2.951924451512513</v>
+        <v>2.932354415579111</v>
       </c>
       <c r="H244" t="n">
-        <v>0.03698695151251297</v>
+        <v>-0.01666502886533339</v>
       </c>
       <c r="I244" t="n">
-        <v>1.268876314243889</v>
+        <v>0.5651040686329845</v>
       </c>
       <c r="J244" t="n">
-        <v>1.268876314243889</v>
+        <v>-0.5651040686329845</v>
       </c>
     </row>
     <row r="245">
@@ -11053,22 +11054,22 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>0.08644771406997782</v>
+        <v>0.09122256426320441</v>
       </c>
       <c r="F245" t="n">
         <v>2.4153</v>
       </c>
       <c r="G245" t="n">
-        <v>2.415300731036135</v>
+        <v>2.415301916596159</v>
       </c>
       <c r="H245" t="n">
-        <v>7.310361347379057e-07</v>
+        <v>1.916596159112771e-06</v>
       </c>
       <c r="I245" t="n">
-        <v>3.026688753934939e-05</v>
+        <v>7.935230236876458e-05</v>
       </c>
       <c r="J245" t="n">
-        <v>3.026688753934939e-05</v>
+        <v>7.935230236876458e-05</v>
       </c>
     </row>
     <row r="246">
@@ -11089,22 +11090,22 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>0.08644771406997782</v>
+        <v>0.09122256426320441</v>
       </c>
       <c r="F246" t="n">
         <v>2.605161460353123</v>
       </c>
       <c r="G246" t="n">
-        <v>2.506339407008765</v>
+        <v>2.500492926972977</v>
       </c>
       <c r="H246" t="n">
-        <v>-0.09882205334435845</v>
+        <v>-0.104668533380146</v>
       </c>
       <c r="I246" t="n">
-        <v>3.793317798082402</v>
+        <v>4.017736903184438</v>
       </c>
       <c r="J246" t="n">
-        <v>-3.793317798082402</v>
+        <v>-4.017736903184438</v>
       </c>
     </row>
     <row r="247">
@@ -11121,26 +11122,26 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>0.08644771406997782</v>
+        <v>0.09122256426320441</v>
       </c>
       <c r="F247" t="n">
-        <v>2.8097</v>
+        <v>2.830407291666667</v>
       </c>
       <c r="G247" t="n">
-        <v>2.71334635390514</v>
+        <v>2.698542774348506</v>
       </c>
       <c r="H247" t="n">
-        <v>-0.09635364609486041</v>
+        <v>-0.1318645173181605</v>
       </c>
       <c r="I247" t="n">
-        <v>3.429321496774048</v>
+        <v>4.658853081194295</v>
       </c>
       <c r="J247" t="n">
-        <v>-3.429321496774048</v>
+        <v>-4.658853081194295</v>
       </c>
     </row>
     <row r="248">
@@ -11161,22 +11162,22 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>0.09801158431932876</v>
+        <v>0.1028391763575825</v>
       </c>
       <c r="F248" t="n">
         <v>2.4153</v>
       </c>
       <c r="G248" t="n">
-        <v>2.415299900513077</v>
+        <v>2.415300166837147</v>
       </c>
       <c r="H248" t="n">
-        <v>-9.948692358818789e-08</v>
+        <v>1.668371467644647e-07</v>
       </c>
       <c r="I248" t="n">
-        <v>4.119029668703179e-06</v>
+        <v>6.907512390364124e-06</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.119029668703179e-06</v>
+        <v>6.907512390364124e-06</v>
       </c>
     </row>
     <row r="249">
@@ -11197,22 +11198,22 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>0.09801158431932876</v>
+        <v>0.1028391763575825</v>
       </c>
       <c r="F249" t="n">
         <v>2.605161460353123</v>
       </c>
       <c r="G249" t="n">
-        <v>2.505792202503144</v>
+        <v>2.499995119429789</v>
       </c>
       <c r="H249" t="n">
-        <v>-0.09936925784997852</v>
+        <v>-0.1051663409233341</v>
       </c>
       <c r="I249" t="n">
-        <v>3.814322427313556</v>
+        <v>4.036845413377145</v>
       </c>
       <c r="J249" t="n">
-        <v>-3.814322427313556</v>
+        <v>-4.036845413377145</v>
       </c>
     </row>
     <row r="250">
@@ -11229,26 +11230,26 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>0.09801158431932876</v>
+        <v>0.1028391763575825</v>
       </c>
       <c r="F250" t="n">
-        <v>2.8097</v>
+        <v>2.830407291666667</v>
       </c>
       <c r="G250" t="n">
-        <v>2.712780810043267</v>
+        <v>2.698017302316364</v>
       </c>
       <c r="H250" t="n">
-        <v>-0.09691918995673365</v>
+        <v>-0.1323899893503024</v>
       </c>
       <c r="I250" t="n">
-        <v>3.449449761780035</v>
+        <v>4.677418325627103</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.449449761780035</v>
+        <v>-4.677418325627103</v>
       </c>
     </row>
     <row r="251">
@@ -11273,16 +11274,16 @@
         <v>2.4153</v>
       </c>
       <c r="G251" t="n">
-        <v>2.691968651574291</v>
+        <v>2.674048926925646</v>
       </c>
       <c r="H251" t="n">
-        <v>0.2766686515742909</v>
+        <v>0.2587489269256453</v>
       </c>
       <c r="I251" t="n">
-        <v>11.45483590337808</v>
+        <v>10.71291048423158</v>
       </c>
       <c r="J251" t="n">
-        <v>11.45483590337808</v>
+        <v>10.71291048423158</v>
       </c>
     </row>
     <row r="252">
@@ -11307,16 +11308,16 @@
         <v>2.605161460353123</v>
       </c>
       <c r="G252" t="n">
-        <v>2.708457209588594</v>
+        <v>2.690534059044964</v>
       </c>
       <c r="H252" t="n">
-        <v>0.1032957492354707</v>
+        <v>0.08537259869184055</v>
       </c>
       <c r="I252" t="n">
-        <v>3.965042121476387</v>
+        <v>3.277055951851388</v>
       </c>
       <c r="J252" t="n">
-        <v>3.965042121476387</v>
+        <v>3.277055951851388</v>
       </c>
     </row>
     <row r="253">
@@ -11333,24 +11334,24 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="n">
-        <v>2.8097</v>
+        <v>2.830407291666667</v>
       </c>
       <c r="G253" t="n">
-        <v>2.774708627744378</v>
+        <v>2.756728144269908</v>
       </c>
       <c r="H253" t="n">
-        <v>-0.03499137225562254</v>
+        <v>-0.07367914739675907</v>
       </c>
       <c r="I253" t="n">
-        <v>1.245377522711412</v>
+        <v>2.603128801062888</v>
       </c>
       <c r="J253" t="n">
-        <v>-1.245377522711412</v>
+        <v>-2.603128801062888</v>
       </c>
     </row>
     <row r="254">
@@ -11371,22 +11372,22 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>0.08140120033643369</v>
+        <v>0.08540130311845624</v>
       </c>
       <c r="F254" t="n">
         <v>2.357925</v>
       </c>
       <c r="G254" t="n">
-        <v>2.35792535401671</v>
+        <v>2.357924735953093</v>
       </c>
       <c r="H254" t="n">
-        <v>3.540167106130809e-07</v>
+        <v>-2.640469065617879e-07</v>
       </c>
       <c r="I254" t="n">
-        <v>1.501390886534054e-05</v>
+        <v>1.119827418436922e-05</v>
       </c>
       <c r="J254" t="n">
-        <v>1.501390886534054e-05</v>
+        <v>-1.119827418436922e-05</v>
       </c>
     </row>
     <row r="255">
@@ -11407,22 +11408,22 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>0.08140120033643369</v>
+        <v>0.08540130311845624</v>
       </c>
       <c r="F255" t="n">
         <v>2.533756797828872</v>
       </c>
       <c r="G255" t="n">
-        <v>2.460915480949066</v>
+        <v>2.45505842501466</v>
       </c>
       <c r="H255" t="n">
-        <v>-0.07284131687980544</v>
+        <v>-0.07869837281421166</v>
       </c>
       <c r="I255" t="n">
-        <v>2.874834591158149</v>
+        <v>3.105995527338962</v>
       </c>
       <c r="J255" t="n">
-        <v>-2.874834591158149</v>
+        <v>-3.105995527338962</v>
       </c>
     </row>
     <row r="256">
@@ -11439,26 +11440,26 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>0.08140120033643369</v>
+        <v>0.08540130311845624</v>
       </c>
       <c r="F256" t="n">
-        <v>2.6235875</v>
+        <v>2.714411458333333</v>
       </c>
       <c r="G256" t="n">
-        <v>2.690263058504985</v>
+        <v>2.67557502395226</v>
       </c>
       <c r="H256" t="n">
-        <v>0.06667555850498497</v>
+        <v>-0.03883643438107276</v>
       </c>
       <c r="I256" t="n">
-        <v>2.541388785584051</v>
+        <v>1.43074972152227</v>
       </c>
       <c r="J256" t="n">
-        <v>2.541388785584051</v>
+        <v>-1.43074972152227</v>
       </c>
     </row>
     <row r="257">
@@ -11479,22 +11480,22 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>0.09381973060610525</v>
+        <v>0.09786992411855877</v>
       </c>
       <c r="F257" t="n">
         <v>2.357925</v>
       </c>
       <c r="G257" t="n">
-        <v>2.357925229208696</v>
+        <v>2.35792703738119</v>
       </c>
       <c r="H257" t="n">
-        <v>2.292086964672535e-07</v>
+        <v>2.037381190422849e-06</v>
       </c>
       <c r="I257" t="n">
-        <v>9.720779773201162e-06</v>
+        <v>8.640568255660588e-05</v>
       </c>
       <c r="J257" t="n">
-        <v>9.720779773201162e-06</v>
+        <v>8.640568255660588e-05</v>
       </c>
     </row>
     <row r="258">
@@ -11515,22 +11516,22 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>0.09381973060610525</v>
+        <v>0.09786992411855877</v>
       </c>
       <c r="F258" t="n">
         <v>2.533756797828872</v>
       </c>
       <c r="G258" t="n">
-        <v>2.460231151670546</v>
+        <v>2.454430214872558</v>
       </c>
       <c r="H258" t="n">
-        <v>-0.07352564615832557</v>
+        <v>-0.0793265829563139</v>
       </c>
       <c r="I258" t="n">
-        <v>2.901843074336429</v>
+        <v>3.130789151677356</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.901843074336429</v>
+        <v>-3.130789151677356</v>
       </c>
     </row>
     <row r="259">
@@ -11547,26 +11548,26 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>0.09381973060610525</v>
+        <v>0.09786992411855877</v>
       </c>
       <c r="F259" t="n">
-        <v>2.6235875</v>
+        <v>2.714411458333333</v>
       </c>
       <c r="G259" t="n">
-        <v>2.689572955888059</v>
+        <v>2.674928414343358</v>
       </c>
       <c r="H259" t="n">
-        <v>0.06598545588805838</v>
+        <v>-0.03948304398997537</v>
       </c>
       <c r="I259" t="n">
-        <v>2.515085008144701</v>
+        <v>1.454571077231535</v>
       </c>
       <c r="J259" t="n">
-        <v>2.515085008144701</v>
+        <v>-1.454571077231535</v>
       </c>
     </row>
     <row r="260">
@@ -11591,16 +11592,16 @@
         <v>2.357925</v>
       </c>
       <c r="G260" t="n">
-        <v>2.668651720871812</v>
+        <v>2.650889553310626</v>
       </c>
       <c r="H260" t="n">
-        <v>0.3107267208718119</v>
+        <v>0.2929645533106262</v>
       </c>
       <c r="I260" t="n">
-        <v>13.17797304290051</v>
+        <v>12.42467649779472</v>
       </c>
       <c r="J260" t="n">
-        <v>13.17797304290051</v>
+        <v>12.42467649779472</v>
       </c>
     </row>
     <row r="261">
@@ -11625,16 +11626,16 @@
         <v>2.533756797828872</v>
       </c>
       <c r="G261" t="n">
-        <v>2.686435981839573</v>
+        <v>2.668670059912487</v>
       </c>
       <c r="H261" t="n">
-        <v>0.1526791840107009</v>
+        <v>0.1349132620836149</v>
       </c>
       <c r="I261" t="n">
-        <v>6.025802639840131</v>
+        <v>5.324633453345621</v>
       </c>
       <c r="J261" t="n">
-        <v>6.025802639840131</v>
+        <v>5.324633453345621</v>
       </c>
     </row>
     <row r="262">
@@ -11651,24 +11652,24 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="n">
-        <v>2.6235875</v>
+        <v>2.714411458333333</v>
       </c>
       <c r="G262" t="n">
-        <v>2.75779002790043</v>
+        <v>2.739961680323716</v>
       </c>
       <c r="H262" t="n">
-        <v>0.1342025279004297</v>
+        <v>0.02555022199038248</v>
       </c>
       <c r="I262" t="n">
-        <v>5.115229734111393</v>
+        <v>0.9412803616026028</v>
       </c>
       <c r="J262" t="n">
-        <v>5.115229734111393</v>
+        <v>0.9412803616026028</v>
       </c>
     </row>
     <row r="263">
@@ -11689,22 +11690,22 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>0.05365244851449789</v>
+        <v>0.05449563116943758</v>
       </c>
       <c r="F263" t="n">
         <v>1.2605</v>
       </c>
       <c r="G263" t="n">
-        <v>1.260502475123922</v>
+        <v>1.26050312744451</v>
       </c>
       <c r="H263" t="n">
-        <v>2.475123922485167e-06</v>
+        <v>3.127444510253596e-06</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0001963604857187757</v>
+        <v>0.0002481114248515348</v>
       </c>
       <c r="J263" t="n">
-        <v>0.0001963604857187757</v>
+        <v>0.0002481114248515348</v>
       </c>
     </row>
     <row r="264">
@@ -11725,22 +11726,22 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>0.05365244851449789</v>
+        <v>0.05449563116943758</v>
       </c>
       <c r="F264" t="n">
         <v>1.6629125</v>
       </c>
       <c r="G264" t="n">
-        <v>1.507293593618719</v>
+        <v>1.504178206199789</v>
       </c>
       <c r="H264" t="n">
-        <v>-0.155618906381281</v>
+        <v>-0.1587342938002114</v>
       </c>
       <c r="I264" t="n">
-        <v>9.358213759369837</v>
+        <v>9.545558999659418</v>
       </c>
       <c r="J264" t="n">
-        <v>-9.358213759369837</v>
+        <v>-9.545558999659418</v>
       </c>
     </row>
     <row r="265">
@@ -11757,26 +11758,26 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>0.05365244851449789</v>
+        <v>0.05449563116943758</v>
       </c>
       <c r="F265" t="n">
-        <v>2.1783</v>
+        <v>2.2371125</v>
       </c>
       <c r="G265" t="n">
-        <v>2.094728170619192</v>
+        <v>2.085146426773932</v>
       </c>
       <c r="H265" t="n">
-        <v>-0.08357182938080765</v>
+        <v>-0.1519660732260681</v>
       </c>
       <c r="I265" t="n">
-        <v>3.836561969462776</v>
+        <v>6.792956242748996</v>
       </c>
       <c r="J265" t="n">
-        <v>-3.836561969462776</v>
+        <v>-6.792956242748996</v>
       </c>
     </row>
     <row r="266">
@@ -11797,22 +11798,22 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>0.09628806381888011</v>
+        <v>0.09717239253050693</v>
       </c>
       <c r="F266" t="n">
         <v>1.2605</v>
       </c>
       <c r="G266" t="n">
-        <v>1.260505243267369</v>
+        <v>1.260505061716089</v>
       </c>
       <c r="H266" t="n">
-        <v>5.243267368726379e-06</v>
+        <v>5.061716088938795e-06</v>
       </c>
       <c r="I266" t="n">
-        <v>0.0004159672644765076</v>
+        <v>0.0004015641482696386</v>
       </c>
       <c r="J266" t="n">
-        <v>0.0004159672644765076</v>
+        <v>0.0004015641482696386</v>
       </c>
     </row>
     <row r="267">
@@ -11833,22 +11834,22 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>0.09628806381888011</v>
+        <v>0.09717239253050693</v>
       </c>
       <c r="F267" t="n">
         <v>1.6629125</v>
       </c>
       <c r="G267" t="n">
-        <v>1.50127717990096</v>
+        <v>1.498279370583388</v>
       </c>
       <c r="H267" t="n">
-        <v>-0.1616353200990399</v>
+        <v>-0.1646331294166119</v>
       </c>
       <c r="I267" t="n">
-        <v>9.720013536433211</v>
+        <v>9.900288164086318</v>
       </c>
       <c r="J267" t="n">
-        <v>-9.720013536433211</v>
+        <v>-9.900288164086318</v>
       </c>
     </row>
     <row r="268">
@@ -11865,26 +11866,26 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>0.09628806381888011</v>
+        <v>0.09717239253050693</v>
       </c>
       <c r="F268" t="n">
-        <v>2.1783</v>
+        <v>2.2371125</v>
       </c>
       <c r="G268" t="n">
-        <v>2.088037065145172</v>
+        <v>2.078608462836351</v>
       </c>
       <c r="H268" t="n">
-        <v>-0.09026293485482784</v>
+        <v>-0.1585040371636488</v>
       </c>
       <c r="I268" t="n">
-        <v>4.143732950228519</v>
+        <v>7.085206361488249</v>
       </c>
       <c r="J268" t="n">
-        <v>-4.143732950228519</v>
+        <v>-7.085206361488249</v>
       </c>
     </row>
     <row r="269">
@@ -11909,16 +11910,16 @@
         <v>1.2605</v>
       </c>
       <c r="G269" t="n">
-        <v>1.951400795148769</v>
+        <v>1.938494337735358</v>
       </c>
       <c r="H269" t="n">
-        <v>0.6909007951487691</v>
+        <v>0.6779943377353583</v>
       </c>
       <c r="I269" t="n">
-        <v>54.81164578728831</v>
+        <v>53.78773008610538</v>
       </c>
       <c r="J269" t="n">
-        <v>54.81164578728831</v>
+        <v>53.78773008610538</v>
       </c>
     </row>
     <row r="270">
@@ -11943,16 +11944,16 @@
         <v>1.6629125</v>
       </c>
       <c r="G270" t="n">
-        <v>2.013763880557307</v>
+        <v>2.000834454467218</v>
       </c>
       <c r="H270" t="n">
-        <v>0.350851380557307</v>
+        <v>0.3379219544672183</v>
       </c>
       <c r="I270" t="n">
-        <v>21.09860744671214</v>
+        <v>20.3210905244394</v>
       </c>
       <c r="J270" t="n">
-        <v>21.09860744671214</v>
+        <v>20.3210905244394</v>
       </c>
     </row>
     <row r="271">
@@ -11969,24 +11970,24 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="n">
-        <v>2.1783</v>
+        <v>2.2371125</v>
       </c>
       <c r="G271" t="n">
-        <v>2.248855985731517</v>
+        <v>2.235633685339125</v>
       </c>
       <c r="H271" t="n">
-        <v>0.070555985731517</v>
+        <v>-0.001478814660875738</v>
       </c>
       <c r="I271" t="n">
-        <v>3.239038963022403</v>
+        <v>0.06610372347728323</v>
       </c>
       <c r="J271" t="n">
-        <v>3.239038963022403</v>
+        <v>-0.06610372347728323</v>
       </c>
     </row>
     <row r="272">
@@ -12007,22 +12008,22 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>0.09980731841490169</v>
+        <v>0.1042262168583761</v>
       </c>
       <c r="F272" t="n">
         <v>2.2462375</v>
       </c>
       <c r="G272" t="n">
-        <v>2.246237725567757</v>
+        <v>2.246240299890796</v>
       </c>
       <c r="H272" t="n">
-        <v>2.255677564733105e-07</v>
+        <v>2.799890795657234e-06</v>
       </c>
       <c r="I272" t="n">
-        <v>1.004202612027047e-05</v>
+        <v>0.0001246480301240289</v>
       </c>
       <c r="J272" t="n">
-        <v>1.004202612027047e-05</v>
+        <v>0.0001246480301240289</v>
       </c>
     </row>
     <row r="273">
@@ -12043,22 +12044,22 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>0.09980731841490169</v>
+        <v>0.1042262168583761</v>
       </c>
       <c r="F273" t="n">
         <v>2.426137507705096</v>
       </c>
       <c r="G273" t="n">
-        <v>2.346257464667032</v>
+        <v>2.341365007545882</v>
       </c>
       <c r="H273" t="n">
-        <v>-0.0798800430380644</v>
+        <v>-0.08477250015921411</v>
       </c>
       <c r="I273" t="n">
-        <v>3.292477973089975</v>
+        <v>3.494134190250458</v>
       </c>
       <c r="J273" t="n">
-        <v>-3.292477973089975</v>
+        <v>-3.494134190250458</v>
       </c>
     </row>
     <row r="274">
@@ -12075,26 +12076,26 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>0.09980731841490169</v>
+        <v>0.1042262168583761</v>
       </c>
       <c r="F274" t="n">
-        <v>2.604825</v>
+        <v>2.651822916666667</v>
       </c>
       <c r="G274" t="n">
-        <v>2.597968088051515</v>
+        <v>2.584498534700782</v>
       </c>
       <c r="H274" t="n">
-        <v>-0.006856911948485145</v>
+        <v>-0.06732438196588486</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2632388720349791</v>
+        <v>2.53879629528624</v>
       </c>
       <c r="J274" t="n">
-        <v>-0.2632388720349791</v>
+        <v>-2.53879629528624</v>
       </c>
     </row>
     <row r="275">
@@ -12115,22 +12116,22 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>0.1173245789617089</v>
+        <v>0.1218097151510352</v>
       </c>
       <c r="F275" t="n">
         <v>2.2462375</v>
       </c>
       <c r="G275" t="n">
-        <v>2.246238641544342</v>
+        <v>2.246239475390706</v>
       </c>
       <c r="H275" t="n">
-        <v>1.141544342164735e-06</v>
+        <v>1.975390705677427e-06</v>
       </c>
       <c r="I275" t="n">
-        <v>5.082028690931992e-05</v>
+        <v>8.794220137796767e-05</v>
       </c>
       <c r="J275" t="n">
-        <v>5.082028690931992e-05</v>
+        <v>8.794220137796767e-05</v>
       </c>
     </row>
     <row r="276">
@@ -12151,22 +12152,22 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>0.1173245789617089</v>
+        <v>0.1218097151510352</v>
       </c>
       <c r="F276" t="n">
         <v>2.426137507705096</v>
       </c>
       <c r="G276" t="n">
-        <v>2.345447984223022</v>
+        <v>2.340616639292388</v>
       </c>
       <c r="H276" t="n">
-        <v>-0.08068952348207459</v>
+        <v>-0.08552086841270867</v>
       </c>
       <c r="I276" t="n">
-        <v>3.325842959264063</v>
+        <v>3.524980267652</v>
       </c>
       <c r="J276" t="n">
-        <v>-3.325842959264063</v>
+        <v>-3.524980267652</v>
       </c>
     </row>
     <row r="277">
@@ -12183,26 +12184,26 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>0.1173245789617089</v>
+        <v>0.1218097151510352</v>
       </c>
       <c r="F277" t="n">
-        <v>2.604825</v>
+        <v>2.651822916666667</v>
       </c>
       <c r="G277" t="n">
-        <v>2.597014937757651</v>
+        <v>2.583605966649622</v>
       </c>
       <c r="H277" t="n">
-        <v>-0.007810062242349147</v>
+        <v>-0.06821695001704464</v>
       </c>
       <c r="I277" t="n">
-        <v>0.299830592932314</v>
+        <v>2.572454954978409</v>
       </c>
       <c r="J277" t="n">
-        <v>-0.299830592932314</v>
+        <v>-2.572454954978409</v>
       </c>
     </row>
     <row r="278">
@@ -12227,16 +12228,16 @@
         <v>2.2462375</v>
       </c>
       <c r="G278" t="n">
-        <v>2.548331714249985</v>
+        <v>2.531382801555054</v>
       </c>
       <c r="H278" t="n">
-        <v>0.3020942142499843</v>
+        <v>0.2851453015550534</v>
       </c>
       <c r="I278" t="n">
-        <v>13.44889907011098</v>
+        <v>12.69435229155659</v>
       </c>
       <c r="J278" t="n">
-        <v>13.44889907011098</v>
+        <v>12.69435229155659</v>
       </c>
     </row>
     <row r="279">
@@ -12261,16 +12262,16 @@
         <v>2.426137507705096</v>
       </c>
       <c r="G279" t="n">
-        <v>2.572924864841664</v>
+        <v>2.555970305317487</v>
       </c>
       <c r="H279" t="n">
-        <v>0.1467873571365677</v>
+        <v>0.1298327976123903</v>
       </c>
       <c r="I279" t="n">
-        <v>6.050248869670006</v>
+        <v>5.351419579478009</v>
       </c>
       <c r="J279" t="n">
-        <v>6.050248869670006</v>
+        <v>5.351419579478009</v>
       </c>
     </row>
     <row r="280">
@@ -12287,24 +12288,24 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="n">
-        <v>2.604825</v>
+        <v>2.651822916666667</v>
       </c>
       <c r="G280" t="n">
-        <v>2.670817163137577</v>
+        <v>2.653771948496829</v>
       </c>
       <c r="H280" t="n">
-        <v>0.06599216313757728</v>
+        <v>0.001949031830162706</v>
       </c>
       <c r="I280" t="n">
-        <v>2.533458606147333</v>
+        <v>0.07349781231292146</v>
       </c>
       <c r="J280" t="n">
-        <v>2.533458606147333</v>
+        <v>0.07349781231292146</v>
       </c>
     </row>
     <row r="281">
@@ -12325,22 +12326,22 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>0.08797208990274272</v>
+        <v>0.09372630077322572</v>
       </c>
       <c r="F281" t="n">
         <v>2.4985875</v>
       </c>
       <c r="G281" t="n">
-        <v>2.498589858011111</v>
+        <v>2.498588413145333</v>
       </c>
       <c r="H281" t="n">
-        <v>2.358011111258662e-06</v>
+        <v>9.131453331256978e-07</v>
       </c>
       <c r="I281" t="n">
-        <v>9.437376562792626e-05</v>
+        <v>3.654646207610091e-05</v>
       </c>
       <c r="J281" t="n">
-        <v>9.437376562792626e-05</v>
+        <v>3.654646207610091e-05</v>
       </c>
     </row>
     <row r="282">
@@ -12361,22 +12362,22 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>0.08797208990274272</v>
+        <v>0.09372630077322572</v>
       </c>
       <c r="F282" t="n">
         <v>2.578681397618311</v>
       </c>
       <c r="G282" t="n">
-        <v>2.577420600748882</v>
+        <v>2.571365651378545</v>
       </c>
       <c r="H282" t="n">
-        <v>-0.001260796869428926</v>
+        <v>-0.007315746239766163</v>
       </c>
       <c r="I282" t="n">
-        <v>0.04889308429468672</v>
+        <v>0.2837010514956613</v>
       </c>
       <c r="J282" t="n">
-        <v>-0.04889308429468672</v>
+        <v>-0.2837010514956613</v>
       </c>
     </row>
     <row r="283">
@@ -12393,26 +12394,26 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>0.08797208990274272</v>
+        <v>0.09372630077322572</v>
       </c>
       <c r="F283" t="n">
-        <v>2.661575</v>
+        <v>2.72160625</v>
       </c>
       <c r="G283" t="n">
-        <v>2.755654208425062</v>
+        <v>2.740478812615086</v>
       </c>
       <c r="H283" t="n">
-        <v>0.09407920842506234</v>
+        <v>0.01887256261508652</v>
       </c>
       <c r="I283" t="n">
-        <v>3.534719420833992</v>
+        <v>0.6934347176446454</v>
       </c>
       <c r="J283" t="n">
-        <v>3.534719420833992</v>
+        <v>0.6934347176446454</v>
       </c>
     </row>
     <row r="284">
@@ -12433,22 +12434,22 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>0.09772460496354667</v>
+        <v>0.1035325935966191</v>
       </c>
       <c r="F284" t="n">
         <v>2.4985875</v>
       </c>
       <c r="G284" t="n">
-        <v>2.498588267910212</v>
+        <v>2.498587925730706</v>
       </c>
       <c r="H284" t="n">
-        <v>7.679102114188652e-07</v>
+        <v>4.257307053556758e-07</v>
       </c>
       <c r="I284" t="n">
-        <v>3.073377303852137e-05</v>
+        <v>1.703885516739661e-05</v>
       </c>
       <c r="J284" t="n">
-        <v>3.073377303852137e-05</v>
+        <v>1.703885516739661e-05</v>
       </c>
     </row>
     <row r="285">
@@ -12469,22 +12470,22 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>0.09772460496354667</v>
+        <v>0.1035325935966191</v>
       </c>
       <c r="F285" t="n">
         <v>2.578681397618311</v>
       </c>
       <c r="G285" t="n">
-        <v>2.577021653072482</v>
+        <v>2.571010615566995</v>
       </c>
       <c r="H285" t="n">
-        <v>-0.001659744545828623</v>
+        <v>-0.007670782051315328</v>
       </c>
       <c r="I285" t="n">
-        <v>0.0643640795393171</v>
+        <v>0.2974691661560098</v>
       </c>
       <c r="J285" t="n">
-        <v>-0.0643640795393171</v>
+        <v>-0.2974691661560098</v>
       </c>
     </row>
     <row r="286">
@@ -12501,26 +12502,26 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>0.09772460496354667</v>
+        <v>0.1035325935966191</v>
       </c>
       <c r="F286" t="n">
-        <v>2.661575</v>
+        <v>2.72160625</v>
       </c>
       <c r="G286" t="n">
-        <v>2.755245686976248</v>
+        <v>2.740104201229234</v>
       </c>
       <c r="H286" t="n">
-        <v>0.09367068697624781</v>
+        <v>0.01849795122923403</v>
       </c>
       <c r="I286" t="n">
-        <v>3.519370559771858</v>
+        <v>0.67967036852719</v>
       </c>
       <c r="J286" t="n">
-        <v>3.519370559771858</v>
+        <v>0.67967036852719</v>
       </c>
     </row>
     <row r="287">
@@ -12545,16 +12546,16 @@
         <v>2.4985875</v>
       </c>
       <c r="G287" t="n">
-        <v>2.738892617826052</v>
+        <v>2.720655859404284</v>
       </c>
       <c r="H287" t="n">
-        <v>0.2403051178260514</v>
+        <v>0.2220683594042838</v>
       </c>
       <c r="I287" t="n">
-        <v>9.617638678895629</v>
+        <v>8.887755958287785</v>
       </c>
       <c r="J287" t="n">
-        <v>9.617638678895629</v>
+        <v>8.887755958287785</v>
       </c>
     </row>
     <row r="288">
@@ -12579,16 +12580,16 @@
         <v>2.578681397618311</v>
       </c>
       <c r="G288" t="n">
-        <v>2.752795644403889</v>
+        <v>2.734556087326367</v>
       </c>
       <c r="H288" t="n">
-        <v>0.1741142467855781</v>
+        <v>0.1558746897080558</v>
       </c>
       <c r="I288" t="n">
-        <v>6.752065103753852</v>
+        <v>6.044744025067341</v>
       </c>
       <c r="J288" t="n">
-        <v>6.752065103753852</v>
+        <v>6.044744025067341</v>
       </c>
     </row>
     <row r="289">
@@ -12605,24 +12606,24 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="n">
-        <v>2.661575</v>
+        <v>2.72160625</v>
       </c>
       <c r="G289" t="n">
-        <v>2.808817000355968</v>
+        <v>2.79053001001984</v>
       </c>
       <c r="H289" t="n">
-        <v>0.1472420003559685</v>
+        <v>0.06892376001984069</v>
       </c>
       <c r="I289" t="n">
-        <v>5.532137939226528</v>
+        <v>2.532466260313765</v>
       </c>
       <c r="J289" t="n">
-        <v>5.532137939226528</v>
+        <v>2.532466260313765</v>
       </c>
     </row>
     <row r="290">
@@ -12643,22 +12644,22 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>0.1054749501105286</v>
+        <v>0.1095102904351769</v>
       </c>
       <c r="F290" t="n">
         <v>2.1168875</v>
       </c>
       <c r="G290" t="n">
-        <v>2.116887303730121</v>
+        <v>2.116891206340847</v>
       </c>
       <c r="H290" t="n">
-        <v>-1.962698785717976e-07</v>
+        <v>3.706340847120515e-06</v>
       </c>
       <c r="I290" t="n">
-        <v>9.271625373185753e-06</v>
+        <v>0.0001750844505019995</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.271625373185753e-06</v>
+        <v>0.0001750844505019995</v>
       </c>
     </row>
     <row r="291">
@@ -12679,22 +12680,22 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>0.1054749501105286</v>
+        <v>0.1095102904351769</v>
       </c>
       <c r="F291" t="n">
         <v>2.303175230396183</v>
       </c>
       <c r="G291" t="n">
-        <v>2.224900625433799</v>
+        <v>2.220522839792302</v>
       </c>
       <c r="H291" t="n">
-        <v>-0.07827460496238325</v>
+        <v>-0.08265239060388074</v>
       </c>
       <c r="I291" t="n">
-        <v>3.3985518743582</v>
+        <v>3.588627973810886</v>
       </c>
       <c r="J291" t="n">
-        <v>-3.3985518743582</v>
+        <v>-3.588627973810886</v>
       </c>
     </row>
     <row r="292">
@@ -12711,26 +12712,26 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>0.1054749501105286</v>
+        <v>0.1095102904351769</v>
       </c>
       <c r="F292" t="n">
-        <v>2.63515</v>
+        <v>2.689839583333333</v>
       </c>
       <c r="G292" t="n">
-        <v>2.510020019452205</v>
+        <v>2.497430062230134</v>
       </c>
       <c r="H292" t="n">
-        <v>-0.1251299805477952</v>
+        <v>-0.1924095211031989</v>
       </c>
       <c r="I292" t="n">
-        <v>4.748495552351677</v>
+        <v>7.153196878185537</v>
       </c>
       <c r="J292" t="n">
-        <v>-4.748495552351677</v>
+        <v>-7.153196878185537</v>
       </c>
     </row>
     <row r="293">
@@ -12751,22 +12752,22 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>0.1278415647582374</v>
+        <v>0.1319493824569777</v>
       </c>
       <c r="F293" t="n">
         <v>2.1168875</v>
       </c>
       <c r="G293" t="n">
-        <v>2.116892442260044</v>
+        <v>2.116891739070655</v>
       </c>
       <c r="H293" t="n">
-        <v>4.942260043883095e-06</v>
+        <v>4.239070654943333e-06</v>
       </c>
       <c r="I293" t="n">
-        <v>0.0002334682425912145</v>
+        <v>0.0002002501623229073</v>
       </c>
       <c r="J293" t="n">
-        <v>0.0002334682425912145</v>
+        <v>0.0002002501623229073</v>
       </c>
     </row>
     <row r="294">
@@ -12787,22 +12788,22 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>0.1278415647582374</v>
+        <v>0.1319493824569777</v>
       </c>
       <c r="F294" t="n">
         <v>2.303175230396183</v>
       </c>
       <c r="G294" t="n">
-        <v>2.22385534765564</v>
+        <v>2.219545016545049</v>
       </c>
       <c r="H294" t="n">
-        <v>-0.0793198827405428</v>
+        <v>-0.08363021385113401</v>
       </c>
       <c r="I294" t="n">
-        <v>3.443936079796175</v>
+        <v>3.631083416816197</v>
       </c>
       <c r="J294" t="n">
-        <v>-3.443936079796175</v>
+        <v>-3.631083416816197</v>
       </c>
     </row>
     <row r="295">
@@ -12819,26 +12820,26 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>0.1278415647582374</v>
+        <v>0.1319493824569777</v>
       </c>
       <c r="F295" t="n">
-        <v>2.63515</v>
+        <v>2.689839583333333</v>
       </c>
       <c r="G295" t="n">
-        <v>2.508707986479403</v>
+        <v>2.496193510854985</v>
       </c>
       <c r="H295" t="n">
-        <v>-0.126442013520597</v>
+        <v>-0.1936460724783484</v>
       </c>
       <c r="I295" t="n">
-        <v>4.798285240711041</v>
+        <v>7.199168072260137</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.798285240711041</v>
+        <v>-7.199168072260137</v>
       </c>
     </row>
     <row r="296">
@@ -12863,16 +12864,16 @@
         <v>2.1168875</v>
       </c>
       <c r="G296" t="n">
-        <v>2.435329400604818</v>
+        <v>2.419144666707322</v>
       </c>
       <c r="H296" t="n">
-        <v>0.3184419006048178</v>
+        <v>0.3022571667073226</v>
       </c>
       <c r="I296" t="n">
-        <v>15.04292980164595</v>
+        <v>14.27837647051734</v>
       </c>
       <c r="J296" t="n">
-        <v>15.04292980164595</v>
+        <v>14.27837647051734</v>
       </c>
     </row>
     <row r="297">
@@ -12897,16 +12898,16 @@
         <v>2.303175230396183</v>
       </c>
       <c r="G297" t="n">
-        <v>2.466521620364827</v>
+        <v>2.450329112379243</v>
       </c>
       <c r="H297" t="n">
-        <v>0.1633463899686447</v>
+        <v>0.1471538819830602</v>
       </c>
       <c r="I297" t="n">
-        <v>7.092225889410357</v>
+        <v>6.389174390250256</v>
       </c>
       <c r="J297" t="n">
-        <v>7.092225889410357</v>
+        <v>6.389174390250256</v>
       </c>
     </row>
     <row r="298">
@@ -12923,24 +12924,24 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>2.63515</v>
+        <v>2.689839583333333</v>
       </c>
       <c r="G298" t="n">
-        <v>2.589664619045338</v>
+        <v>2.573351704629975</v>
       </c>
       <c r="H298" t="n">
-        <v>-0.0454853809546627</v>
+        <v>-0.1164878787033579</v>
       </c>
       <c r="I298" t="n">
-        <v>1.726102155651963</v>
+        <v>4.330662669444489</v>
       </c>
       <c r="J298" t="n">
-        <v>-1.726102155651963</v>
+        <v>-4.330662669444489</v>
       </c>
     </row>
   </sheetData>
@@ -13009,16 +13010,16 @@
         <v>33</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2626044591353158</v>
+        <v>0.5655360655043429</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03567883846213558</v>
+        <v>0.04583288742948363</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2625968691832986</v>
+        <v>0.5655306138781744</v>
       </c>
       <c r="G2" t="n">
-        <v>8.663837573647635</v>
+        <v>8.815957672417486</v>
       </c>
     </row>
     <row r="3">
@@ -13036,16 +13037,16 @@
         <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>4.871834711456733</v>
+        <v>4.870448782461905</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1339676923288817</v>
+        <v>0.1367263071032797</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.819971682954274</v>
+        <v>-4.832845473597748</v>
       </c>
       <c r="G3" t="n">
-        <v>10.89503491841374</v>
+        <v>11.09496567262841</v>
       </c>
     </row>
     <row r="4">
@@ -13056,23 +13057,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>4.99778065594507</v>
+        <v>4.30861254323064</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1551908056577576</v>
+        <v>0.1354260687820719</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.832717323887005</v>
+        <v>-4.249352786317051</v>
       </c>
       <c r="G4" t="n">
-        <v>10.87855092924223</v>
+        <v>9.285504233286968</v>
       </c>
     </row>
     <row r="5">
@@ -13090,16 +13091,16 @@
         <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5492163709494562</v>
+        <v>0.5661042924672047</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04468409812307711</v>
+        <v>0.04586563444230999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5492143669713392</v>
+        <v>0.5660974503385079</v>
       </c>
       <c r="G5" t="n">
-        <v>8.665170362618204</v>
+        <v>8.816347912172322</v>
       </c>
     </row>
     <row r="6">
@@ -13117,16 +13118,16 @@
         <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>4.733052164864148</v>
+        <v>4.927465003277339</v>
       </c>
       <c r="E6" t="n">
-        <v>0.133908286642556</v>
+        <v>0.1380964276619535</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.683036976843248</v>
+        <v>-4.89157098074321</v>
       </c>
       <c r="G6" t="n">
-        <v>10.99426684972992</v>
+        <v>11.19040846154465</v>
       </c>
     </row>
     <row r="7">
@@ -13137,23 +13138,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>4.984609750318961</v>
+        <v>4.35619834584421</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1554605978859624</v>
+        <v>0.1368112905835354</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.834293538766869</v>
+        <v>-4.303497801309662</v>
       </c>
       <c r="G7" t="n">
-        <v>10.96694769666185</v>
+        <v>9.372703496519826</v>
       </c>
     </row>
     <row r="8">
@@ -13171,16 +13172,16 @@
         <v>33</v>
       </c>
       <c r="D8" t="n">
-        <v>18.58276570638114</v>
+        <v>17.79437606272393</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3905641614933025</v>
+        <v>0.374825217942641</v>
       </c>
       <c r="F8" t="n">
-        <v>18.58276570638114</v>
+        <v>17.79437606272393</v>
       </c>
       <c r="G8" t="n">
-        <v>54.81164578728831</v>
+        <v>53.78773008610538</v>
       </c>
     </row>
     <row r="9">
@@ -13198,16 +13199,16 @@
         <v>33</v>
       </c>
       <c r="D9" t="n">
-        <v>6.74520563004331</v>
+        <v>6.08285788806541</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1719390852188199</v>
+        <v>0.1574959629667892</v>
       </c>
       <c r="F9" t="n">
-        <v>6.728333078127195</v>
+        <v>6.025985138499244</v>
       </c>
       <c r="G9" t="n">
-        <v>21.09860744671214</v>
+        <v>20.3210905244394</v>
       </c>
     </row>
     <row r="10">
@@ -13218,23 +13219,146 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>brine60</t>
+          <t>brine_avg</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>33</v>
       </c>
       <c r="D10" t="n">
-        <v>3.55324242202597</v>
+        <v>2.406535083258526</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1144846805594586</v>
+        <v>0.08062879638570661</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7950902763662907</v>
+        <v>-1.395553588023597</v>
       </c>
       <c r="G10" t="n">
-        <v>7.339940514799209</v>
+        <v>6.918772142635587</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AR_min</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>AR_mean</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>AR_median</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>AR_max</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>AR_p2.5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>AR_p97.5</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>w95(AR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GSA</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.02397019273512207</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.09732484864407834</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0785681403797011</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4825333284192772</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.04608300987751511</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2746838399799459</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2286008301024308</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.02617032869151523</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1152811409896835</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1008884035969615</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4981426684592046</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.04922000376705891</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2955293274432916</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2463093236762327</v>
       </c>
     </row>
   </sheetData>

--- a/results/level1_emt_comparison/table12_level1_emt_comparison.xlsx
+++ b/results/level1_emt_comparison/table12_level1_emt_comparison.xlsx
@@ -471,19 +471,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.248199130398963</v>
+        <v>3.20232709497832</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1142146469445295</v>
+        <v>0.11296565382788</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.838889215345542</v>
+        <v>-2.963890440548922</v>
       </c>
       <c r="E2" t="n">
         <v>11.09496567262841</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2286008301024308</v>
+        <v>0.1741685744834787</v>
       </c>
     </row>
     <row r="3">
@@ -493,19 +493,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.283255880529584</v>
+        <v>3.238470077741638</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1153134987572593</v>
+        <v>0.1141107307078123</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.876323777238121</v>
+        <v>-3.002495261059239</v>
       </c>
       <c r="E3" t="n">
         <v>11.19040846154465</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2463093236762327</v>
+        <v>0.1901327669337151</v>
       </c>
     </row>
     <row r="4">
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.761256344682623</v>
+        <v>8.886571883078425</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2393044958229245</v>
+        <v>0.241576512620838</v>
       </c>
       <c r="D4" t="n">
-        <v>7.474935871066526</v>
+        <v>7.670735963064563</v>
       </c>
       <c r="E4" t="n">
         <v>53.78773008610538</v>
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.05666441691476886</v>
+        <v>0.0566644169147693</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1578618204724482</v>
+        <v>0.1578618204724496</v>
       </c>
     </row>
     <row r="3">
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.0785681403797011</v>
+        <v>0.07856814037970133</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1832525822951641</v>
+        <v>0.1832525822951645</v>
       </c>
     </row>
     <row r="6">
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07975437634955759</v>
+        <v>0.07975437634955812</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4129043461096684</v>
+        <v>0.4129043461096686</v>
       </c>
     </row>
     <row r="9">
@@ -802,10 +802,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.0662995724211108</v>
+        <v>0.06629982941511016</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2449526536739257</v>
+        <v>0.2449531055810219</v>
       </c>
     </row>
     <row r="15">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.07158956549382131</v>
+        <v>0.07158956549382076</v>
       </c>
       <c r="E23" t="n">
         <v>0.3045635095545758</v>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.07041259839357857</v>
+        <v>0.07041259839357256</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5364264602899795</v>
+        <v>0.5364264602899711</v>
       </c>
     </row>
     <row r="27">
@@ -1080,7 +1080,7 @@
         <v>0.07519263589067139</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2873466586836653</v>
+        <v>0.2873466586836648</v>
       </c>
     </row>
     <row r="30">
@@ -1135,7 +1135,7 @@
         <v>0.08455531212179532</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3877543575287179</v>
+        <v>0.3877543575287175</v>
       </c>
     </row>
     <row r="33">
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.07649558994396405</v>
+        <v>0.07649558994396592</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3221197757293397</v>
+        <v>0.3221197757293424</v>
       </c>
     </row>
     <row r="36">
@@ -1242,10 +1242,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.08746020600723745</v>
+        <v>0.08746020600723763</v>
       </c>
       <c r="E38" t="n">
-        <v>0.07013319285547048</v>
+        <v>0.07013319285547093</v>
       </c>
     </row>
     <row r="39">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.2186428755542171</v>
+        <v>0.2186428755542173</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2306845256826078</v>
+        <v>0.2306845256826073</v>
       </c>
     </row>
     <row r="42">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.07662637658294001</v>
+        <v>0.07662637658294051</v>
       </c>
       <c r="E44" t="n">
         <v>0.2454568864233364</v>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113735</v>
+        <v>113754</v>
       </c>
       <c r="B47" t="n">
-        <v>0.09160330411903464</v>
+        <v>0.1192694322660098</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1407,18 +1407,18 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.4825333284192772</v>
+        <v>0.05726532872156408</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3598127102142179</v>
+        <v>0.2362761207079132</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113735</v>
+        <v>113754</v>
       </c>
       <c r="B48" t="n">
-        <v>0.09160330411903464</v>
+        <v>0.1192694322660098</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1426,18 +1426,18 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.4981426684592046</v>
+        <v>0.07717316817023095</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3598353617996821</v>
+        <v>0.2408135416935724</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113735</v>
+        <v>113754</v>
       </c>
       <c r="B49" t="n">
-        <v>0.09160330411903464</v>
+        <v>0.1192694322660098</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1446,15 +1446,15 @@
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>0.3623312070196065</v>
+        <v>0.8426693118526383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113754</v>
+        <v>129473</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1192694322660098</v>
+        <v>0.117869102602222</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1462,18 +1462,18 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.0572653287215627</v>
+        <v>0.2227214678701135</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2362761207079336</v>
+        <v>0.2457191182242671</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113754</v>
+        <v>129473</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1192694322660098</v>
+        <v>0.117869102602222</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1481,18 +1481,18 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.07717316817023095</v>
+        <v>0.2448759921893136</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2408135416935724</v>
+        <v>0.2462063887984645</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113754</v>
+        <v>129473</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1192694322660098</v>
+        <v>0.117869102602222</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1501,15 +1501,15 @@
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>0.8426693118526383</v>
+        <v>0.3896684154815144</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129473</v>
+        <v>129498</v>
       </c>
       <c r="B53" t="n">
-        <v>0.117869102602222</v>
+        <v>0.136895751762234</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1517,18 +1517,18 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.2227214678701133</v>
+        <v>0.08427582850660252</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2457191182242666</v>
+        <v>0.1637237890510828</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129473</v>
+        <v>129498</v>
       </c>
       <c r="B54" t="n">
-        <v>0.117869102602222</v>
+        <v>0.136895751762234</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1536,18 +1536,18 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.2448759921893136</v>
+        <v>0.1080509055066162</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2462063887984645</v>
+        <v>0.1673240661858491</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129473</v>
+        <v>129498</v>
       </c>
       <c r="B55" t="n">
-        <v>0.117869102602222</v>
+        <v>0.136895751762234</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1556,15 +1556,15 @@
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>0.3896684154815144</v>
+        <v>0.6625910010039939</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129498</v>
+        <v>129524</v>
       </c>
       <c r="B56" t="n">
-        <v>0.136895751762234</v>
+        <v>0.1474964002666242</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1572,18 +1572,18 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.08427582850660222</v>
+        <v>0.09214397915035179</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1637237890510823</v>
+        <v>0.3953739497372799</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129498</v>
+        <v>129524</v>
       </c>
       <c r="B57" t="n">
-        <v>0.136895751762234</v>
+        <v>0.1474964002666242</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1591,18 +1591,18 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.1080509055066162</v>
+        <v>0.1181240394951164</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1673240661858491</v>
+        <v>0.3989724410322442</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129498</v>
+        <v>129524</v>
       </c>
       <c r="B58" t="n">
-        <v>0.136895751762234</v>
+        <v>0.1474964002666242</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1611,15 +1611,15 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>0.6625910010039939</v>
+        <v>0.5855627668852905</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129524</v>
+        <v>129552</v>
       </c>
       <c r="B59" t="n">
-        <v>0.1474964002666242</v>
+        <v>0.1447440980724326</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1627,18 +1627,18 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.09214397915035165</v>
+        <v>0.07638048100184233</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3953739497372795</v>
+        <v>0.4134481225117073</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129524</v>
+        <v>129552</v>
       </c>
       <c r="B60" t="n">
-        <v>0.1474964002666242</v>
+        <v>0.1447440980724326</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1646,18 +1646,18 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.1181240394951164</v>
+        <v>0.1014549402188581</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3989724410322442</v>
+        <v>0.4178871479823627</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129524</v>
+        <v>129552</v>
       </c>
       <c r="B61" t="n">
-        <v>0.1474964002666242</v>
+        <v>0.1447440980724326</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1666,15 +1666,15 @@
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>0.5855627668852905</v>
+        <v>0.678967316090761</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129552</v>
+        <v>129563</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1447440980724326</v>
+        <v>0.1588516934069688</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1682,18 +1682,18 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.07638048100184246</v>
+        <v>0.07972957776622766</v>
       </c>
       <c r="E62" t="n">
-        <v>0.4134481225117077</v>
+        <v>0.3890755131440287</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129552</v>
+        <v>129563</v>
       </c>
       <c r="B63" t="n">
-        <v>0.1447440980724326</v>
+        <v>0.1588516934069688</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1701,18 +1701,18 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.1014549402188581</v>
+        <v>0.1075983135296858</v>
       </c>
       <c r="E63" t="n">
-        <v>0.4178871479823627</v>
+        <v>0.393931853058483</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129552</v>
+        <v>129563</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1447440980724326</v>
+        <v>0.1588516934069688</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1721,15 +1721,15 @@
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>0.678967316090761</v>
+        <v>0.7083843300090813</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129563</v>
+        <v>129688</v>
       </c>
       <c r="B65" t="n">
-        <v>0.1588516934069688</v>
+        <v>0.0865773064992614</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1737,18 +1737,18 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.07972957776622766</v>
+        <v>0.0711001993502882</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3890755131440282</v>
+        <v>0.03145751620537673</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129563</v>
+        <v>129688</v>
       </c>
       <c r="B66" t="n">
-        <v>0.1588516934069688</v>
+        <v>0.0865773064992614</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1756,18 +1756,18 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.1075983135296858</v>
+        <v>0.08546840709107527</v>
       </c>
       <c r="E66" t="n">
-        <v>0.393931853058483</v>
+        <v>0.03151455020869909</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129563</v>
+        <v>129688</v>
       </c>
       <c r="B67" t="n">
-        <v>0.1588516934069688</v>
+        <v>0.0865773064992614</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1776,15 +1776,15 @@
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>0.7083843300090813</v>
+        <v>0.7308964258071851</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129688</v>
+        <v>129693</v>
       </c>
       <c r="B68" t="n">
-        <v>0.0865773064992614</v>
+        <v>0.1065359216241736</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1792,18 +1792,18 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.07110019935028825</v>
+        <v>0.07216402703380319</v>
       </c>
       <c r="E68" t="n">
-        <v>0.03145751620537673</v>
+        <v>0.02729226510950511</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129688</v>
+        <v>129693</v>
       </c>
       <c r="B69" t="n">
-        <v>0.0865773064992614</v>
+        <v>0.1065359216241736</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1811,18 +1811,18 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.08546840709107527</v>
+        <v>0.09009004668823942</v>
       </c>
       <c r="E69" t="n">
-        <v>0.03151455020869909</v>
+        <v>0.02739017736156413</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129688</v>
+        <v>129693</v>
       </c>
       <c r="B70" t="n">
-        <v>0.0865773064992614</v>
+        <v>0.1065359216241736</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1831,15 +1831,15 @@
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>0.7308964258071851</v>
+        <v>0.815310932210227</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129693</v>
+        <v>129744</v>
       </c>
       <c r="B71" t="n">
-        <v>0.1065359216241736</v>
+        <v>0.037313</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1847,18 +1847,18 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.07216402703380637</v>
+        <v>0.0686445033615314</v>
       </c>
       <c r="E71" t="n">
-        <v>0.02729226510951399</v>
+        <v>0.05285234807002404</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129693</v>
+        <v>129744</v>
       </c>
       <c r="B72" t="n">
-        <v>0.1065359216241736</v>
+        <v>0.037313</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1866,18 +1866,18 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.09009004668823942</v>
+        <v>0.07463470711230444</v>
       </c>
       <c r="E72" t="n">
-        <v>0.02739017736156413</v>
+        <v>0.05333841545703777</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129693</v>
+        <v>129744</v>
       </c>
       <c r="B73" t="n">
-        <v>0.1065359216241736</v>
+        <v>0.037313</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1886,15 +1886,15 @@
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>0.815310932210227</v>
+        <v>0.3559010301537064</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129744</v>
+        <v>129750</v>
       </c>
       <c r="B74" t="n">
-        <v>0.037313</v>
+        <v>0.0216235</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1902,18 +1902,18 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.06864450336153091</v>
+        <v>0.05161121416311329</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0528523480700227</v>
+        <v>0.05811188292933656</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129744</v>
+        <v>129750</v>
       </c>
       <c r="B75" t="n">
-        <v>0.037313</v>
+        <v>0.0216235</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1921,18 +1921,18 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.07463470711230444</v>
+        <v>0.05498242253594483</v>
       </c>
       <c r="E75" t="n">
-        <v>0.05333841545703777</v>
+        <v>0.05835869515232384</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129744</v>
+        <v>129750</v>
       </c>
       <c r="B76" t="n">
-        <v>0.037313</v>
+        <v>0.0216235</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1941,15 +1941,15 @@
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>0.3559010301537064</v>
+        <v>0.2690454672306748</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129750</v>
+        <v>129817</v>
       </c>
       <c r="B77" t="n">
-        <v>0.0216235</v>
+        <v>0.0147115</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1957,18 +1957,18 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.05161121416311337</v>
+        <v>0.02397019273512198</v>
       </c>
       <c r="E77" t="n">
-        <v>0.05811188292933567</v>
+        <v>0.09410409760133653</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129750</v>
+        <v>129817</v>
       </c>
       <c r="B78" t="n">
-        <v>0.0216235</v>
+        <v>0.0147115</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1976,18 +1976,18 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.05498242253594483</v>
+        <v>0.02617032869151523</v>
       </c>
       <c r="E78" t="n">
-        <v>0.05835869515232384</v>
+        <v>0.09435507480994509</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129750</v>
+        <v>129817</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0216235</v>
+        <v>0.0147115</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1996,15 +1996,15 @@
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>0.2690454672306748</v>
+        <v>0.3538984046651779</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129817</v>
+        <v>129822</v>
       </c>
       <c r="B80" t="n">
-        <v>0.0147115</v>
+        <v>0.06934715385806561</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2012,18 +2012,18 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.02397019273512207</v>
+        <v>0.09122256426320441</v>
       </c>
       <c r="E80" t="n">
-        <v>0.09410409760133609</v>
+        <v>0.2365349672944657</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129817</v>
+        <v>129822</v>
       </c>
       <c r="B81" t="n">
-        <v>0.0147115</v>
+        <v>0.06934715385806561</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2031,18 +2031,18 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.02617032869151523</v>
+        <v>0.1028391763575825</v>
       </c>
       <c r="E81" t="n">
-        <v>0.09435507480994509</v>
+        <v>0.2375564971107833</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129817</v>
+        <v>129822</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0147115</v>
+        <v>0.06934715385806561</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2051,15 +2051,15 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>0.3538984046651779</v>
+        <v>0.4178006730142449</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129822</v>
+        <v>129845</v>
       </c>
       <c r="B83" t="n">
-        <v>0.06934715385806561</v>
+        <v>0.07459951122802215</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -2067,18 +2067,18 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.09122256426320441</v>
+        <v>0.08540130311845651</v>
       </c>
       <c r="E83" t="n">
-        <v>0.2365349672944657</v>
+        <v>0.1175350712421905</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129822</v>
+        <v>129845</v>
       </c>
       <c r="B84" t="n">
-        <v>0.06934715385806561</v>
+        <v>0.07459951122802215</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -2086,18 +2086,18 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.1028391763575825</v>
+        <v>0.09786992411855877</v>
       </c>
       <c r="E84" t="n">
-        <v>0.2375564971107833</v>
+        <v>0.1188116643274797</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129822</v>
+        <v>129845</v>
       </c>
       <c r="B85" t="n">
-        <v>0.06934715385806561</v>
+        <v>0.07459951122802215</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2106,15 +2106,15 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>0.4178006730142449</v>
+        <v>0.4534280373846236</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129845</v>
+        <v>129897</v>
       </c>
       <c r="B86" t="n">
-        <v>0.07459951122802215</v>
+        <v>0.2364854161234349</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2122,18 +2122,18 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.08540130311845624</v>
+        <v>0.05449563116943758</v>
       </c>
       <c r="E86" t="n">
-        <v>0.117535071242191</v>
+        <v>0.3107034944707896</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129845</v>
+        <v>129897</v>
       </c>
       <c r="B87" t="n">
-        <v>0.07459951122802215</v>
+        <v>0.2364854161234349</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2141,18 +2141,18 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.09786992411855877</v>
+        <v>0.09717239253050693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.1188116643274797</v>
+        <v>0.3231422282963496</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129845</v>
+        <v>129897</v>
       </c>
       <c r="B88" t="n">
-        <v>0.07459951122802215</v>
+        <v>0.2364854161234349</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2161,15 +2161,15 @@
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>0.4534280373846236</v>
+        <v>1.017395106863452</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129897</v>
+        <v>129913</v>
       </c>
       <c r="B89" t="n">
-        <v>0.2364854161234349</v>
+        <v>0.1017106544373163</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2177,18 +2177,18 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.05449563116943758</v>
+        <v>0.1042262168583755</v>
       </c>
       <c r="E89" t="n">
-        <v>0.3107034944707898</v>
+        <v>0.1520996820158942</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129897</v>
+        <v>129913</v>
       </c>
       <c r="B90" t="n">
-        <v>0.2364854161234349</v>
+        <v>0.1017106544373163</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2196,18 +2196,18 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.09717239253050693</v>
+        <v>0.1218097151510352</v>
       </c>
       <c r="E90" t="n">
-        <v>0.3231422282963496</v>
+        <v>0.153739793820459</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129897</v>
+        <v>129913</v>
       </c>
       <c r="B91" t="n">
-        <v>0.2364854161234349</v>
+        <v>0.1017106544373163</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2216,15 +2216,15 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>1.017395106863452</v>
+        <v>0.4169271309976064</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129913</v>
+        <v>129914</v>
       </c>
       <c r="B92" t="n">
-        <v>0.1017106544373163</v>
+        <v>0.05877849795017343</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2232,18 +2232,18 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.1042262168583761</v>
+        <v>0.09372630077322562</v>
       </c>
       <c r="E92" t="n">
-        <v>0.1520996820158946</v>
+        <v>0.02618922200018625</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129913</v>
+        <v>129914</v>
       </c>
       <c r="B93" t="n">
-        <v>0.1017106544373163</v>
+        <v>0.05877849795017343</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2251,18 +2251,18 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.1218097151510352</v>
+        <v>0.1035325935966191</v>
       </c>
       <c r="E93" t="n">
-        <v>0.153739793820459</v>
+        <v>0.02616915901125472</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129913</v>
+        <v>129914</v>
       </c>
       <c r="B94" t="n">
-        <v>0.1017106544373163</v>
+        <v>0.05877849795017343</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2271,15 +2271,15 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>0.4169271309976064</v>
+        <v>0.4468668091321804</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129914</v>
+        <v>129937</v>
       </c>
       <c r="B95" t="n">
-        <v>0.05877849795017343</v>
+        <v>0.127186314179544</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2287,18 +2287,18 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.09372630077322572</v>
+        <v>0.1095102904351769</v>
       </c>
       <c r="E95" t="n">
-        <v>0.02618922200018581</v>
+        <v>0.2750656180479267</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129914</v>
+        <v>129937</v>
       </c>
       <c r="B96" t="n">
-        <v>0.05877849795017343</v>
+        <v>0.127186314179544</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -2306,18 +2306,18 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.1035325935966191</v>
+        <v>0.1319493824569777</v>
       </c>
       <c r="E96" t="n">
-        <v>0.02616915901125472</v>
+        <v>0.2772805254001374</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129914</v>
+        <v>129937</v>
       </c>
       <c r="B97" t="n">
-        <v>0.05877849795017343</v>
+        <v>0.127186314179544</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -2326,61 +2326,6 @@
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>0.4468668091321804</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>129937</v>
-      </c>
-      <c r="B98" t="n">
-        <v>0.127186314179544</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>GSA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>0.1095102904351769</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0.2750656180479267</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>129937</v>
-      </c>
-      <c r="B99" t="n">
-        <v>0.127186314179544</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>0.1319493824569777</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0.2772805254001374</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>129937</v>
-      </c>
-      <c r="B100" t="n">
-        <v>0.127186314179544</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>BRUGGEMAN</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="n">
         <v>0.5658989273937407</v>
       </c>
     </row>
@@ -2395,7 +2340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J298"/>
+  <dimension ref="A1:J289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2468,22 +2413,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.05666441691476886</v>
+        <v>0.0566644169147693</v>
       </c>
       <c r="F2" t="n">
         <v>2.472887500000001</v>
       </c>
       <c r="G2" t="n">
-        <v>2.472889942683989</v>
+        <v>2.472889942683991</v>
       </c>
       <c r="H2" t="n">
-        <v>2.442683987968763e-06</v>
+        <v>2.442683990633299e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>9.877861358305879e-05</v>
+        <v>9.877861369080875e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>9.877861358305879e-05</v>
+        <v>9.877861369080875e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2504,22 +2449,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.05666441691476886</v>
+        <v>0.0566644169147693</v>
       </c>
       <c r="F3" t="n">
         <v>2.668884574253278</v>
       </c>
       <c r="G3" t="n">
-        <v>2.584048673232694</v>
+        <v>2.584048673232695</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.08483590102058436</v>
+        <v>-0.08483590102058303</v>
       </c>
       <c r="I3" t="n">
-        <v>3.178702512615048</v>
+        <v>3.178702512614997</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.178702512615048</v>
+        <v>-3.178702512614997</v>
       </c>
     </row>
     <row r="4">
@@ -2540,7 +2485,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05666441691476886</v>
+        <v>0.0566644169147693</v>
       </c>
       <c r="F4" t="n">
         <v>2.853091666666666</v>
@@ -2786,22 +2731,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0785681403797011</v>
+        <v>0.07856814037970133</v>
       </c>
       <c r="F11" t="n">
         <v>2.404575</v>
       </c>
       <c r="G11" t="n">
-        <v>2.404576854037716</v>
+        <v>2.404576854037717</v>
       </c>
       <c r="H11" t="n">
-        <v>1.854037715798285e-06</v>
+        <v>1.854037717130552e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>7.710459086525828e-05</v>
+        <v>7.710459092066381e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>7.710459086525828e-05</v>
+        <v>7.710459092066381e-05</v>
       </c>
     </row>
     <row r="12">
@@ -2822,7 +2767,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0785681403797011</v>
+        <v>0.07856814037970133</v>
       </c>
       <c r="F12" t="n">
         <v>2.600887636781521</v>
@@ -2831,13 +2776,13 @@
         <v>2.501643196623343</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.09924444015817846</v>
+        <v>-0.09924444015817802</v>
       </c>
       <c r="I12" t="n">
-        <v>3.815791145863914</v>
+        <v>3.815791145863896</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.815791145863914</v>
+        <v>-3.815791145863896</v>
       </c>
     </row>
     <row r="13">
@@ -2858,22 +2803,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0785681403797011</v>
+        <v>0.07856814037970133</v>
       </c>
       <c r="F13" t="n">
         <v>2.794646875</v>
       </c>
       <c r="G13" t="n">
-        <v>2.71064058690073</v>
+        <v>2.710640586900731</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0840062880992698</v>
+        <v>-0.08400628809926936</v>
       </c>
       <c r="I13" t="n">
-        <v>3.005971482506884</v>
+        <v>3.005971482506868</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.005971482506884</v>
+        <v>-3.005971482506868</v>
       </c>
     </row>
     <row r="14">
@@ -3104,22 +3049,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.07975437634955759</v>
+        <v>0.07975437634955812</v>
       </c>
       <c r="F20" t="n">
         <v>1.85855</v>
       </c>
       <c r="G20" t="n">
-        <v>1.858552129540523</v>
+        <v>1.858552129540526</v>
       </c>
       <c r="H20" t="n">
-        <v>2.129540522810558e-06</v>
+        <v>2.129540526141227e-06</v>
       </c>
       <c r="I20" t="n">
-        <v>0.000114580749660249</v>
+        <v>0.000114580749839457</v>
       </c>
       <c r="J20" t="n">
-        <v>0.000114580749660249</v>
+        <v>0.000114580749839457</v>
       </c>
     </row>
     <row r="21">
@@ -3140,22 +3085,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.07975437634955759</v>
+        <v>0.07975437634955812</v>
       </c>
       <c r="F21" t="n">
         <v>2.23458197098924</v>
       </c>
       <c r="G21" t="n">
-        <v>2.015458720268363</v>
+        <v>2.015458720268366</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2191232507208767</v>
+        <v>-0.2191232507208745</v>
       </c>
       <c r="I21" t="n">
-        <v>9.806006383550644</v>
+        <v>9.806006383550544</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.806006383550644</v>
+        <v>-9.806006383550544</v>
       </c>
     </row>
     <row r="22">
@@ -3176,22 +3121,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.07975437634955759</v>
+        <v>0.07975437634955812</v>
       </c>
       <c r="F22" t="n">
         <v>2.589690625</v>
       </c>
       <c r="G22" t="n">
-        <v>2.395911659151731</v>
+        <v>2.395911659151732</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1937789658482689</v>
+        <v>-0.193778965848268</v>
       </c>
       <c r="I22" t="n">
-        <v>7.482707161140876</v>
+        <v>7.482707161140842</v>
       </c>
       <c r="J22" t="n">
-        <v>-7.482707161140876</v>
+        <v>-7.482707161140842</v>
       </c>
     </row>
     <row r="23">
@@ -3740,22 +3685,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.0662995724211108</v>
+        <v>0.06629982941511016</v>
       </c>
       <c r="F38" t="n">
         <v>2.1235625</v>
       </c>
       <c r="G38" t="n">
-        <v>2.12356332180337</v>
+        <v>2.123564941866762</v>
       </c>
       <c r="H38" t="n">
-        <v>8.218033702434013e-07</v>
+        <v>2.441866761682121e-06</v>
       </c>
       <c r="I38" t="n">
-        <v>3.869927869998652e-05</v>
+        <v>0.0001149891638076167</v>
       </c>
       <c r="J38" t="n">
-        <v>3.869927869998652e-05</v>
+        <v>0.0001149891638076167</v>
       </c>
     </row>
     <row r="39">
@@ -3776,22 +3721,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.0662995724211108</v>
+        <v>0.06629982941511016</v>
       </c>
       <c r="F39" t="n">
         <v>2.4008625</v>
       </c>
       <c r="G39" t="n">
-        <v>2.274247861392504</v>
+        <v>2.274248842371021</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.1266146386074958</v>
+        <v>-0.1266136576289787</v>
       </c>
       <c r="I39" t="n">
-        <v>5.273714700758406</v>
+        <v>5.273673841337382</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.273714700758406</v>
+        <v>-5.273673841337382</v>
       </c>
     </row>
     <row r="40">
@@ -3812,22 +3757,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.0662995724211108</v>
+        <v>0.06629982941511016</v>
       </c>
       <c r="F40" t="n">
         <v>2.706496875</v>
       </c>
       <c r="G40" t="n">
-        <v>2.58815968173694</v>
+        <v>2.588159868914718</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.1183371932630597</v>
+        <v>-0.1183370060852815</v>
       </c>
       <c r="I40" t="n">
-        <v>4.372338071258985</v>
+        <v>4.372331155389992</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.372338071258985</v>
+        <v>-4.372331155389992</v>
       </c>
     </row>
     <row r="41">
@@ -4694,22 +4639,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.07158956549382131</v>
+        <v>0.07158956549382076</v>
       </c>
       <c r="F65" t="n">
         <v>2.29725</v>
       </c>
       <c r="G65" t="n">
-        <v>2.297250261141894</v>
+        <v>2.297250261141891</v>
       </c>
       <c r="H65" t="n">
-        <v>2.611418943310184e-07</v>
+        <v>2.611418907783047e-07</v>
       </c>
       <c r="I65" t="n">
-        <v>1.136758708590787e-05</v>
+        <v>1.136758693125714e-05</v>
       </c>
       <c r="J65" t="n">
-        <v>1.136758708590787e-05</v>
+        <v>1.136758693125714e-05</v>
       </c>
     </row>
     <row r="66">
@@ -4730,22 +4675,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.07158956549382131</v>
+        <v>0.07158956549382076</v>
       </c>
       <c r="F66" t="n">
         <v>2.571281674253069</v>
       </c>
       <c r="G66" t="n">
-        <v>2.417001332812303</v>
+        <v>2.417001332812301</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.1542803414407659</v>
+        <v>-0.1542803414407681</v>
       </c>
       <c r="I66" t="n">
-        <v>6.000133823750861</v>
+        <v>6.000133823750948</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.000133823750861</v>
+        <v>-6.000133823750948</v>
       </c>
     </row>
     <row r="67">
@@ -4766,22 +4711,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.07158956549382131</v>
+        <v>0.07158956549382076</v>
       </c>
       <c r="F67" t="n">
         <v>2.817765625</v>
       </c>
       <c r="G67" t="n">
-        <v>2.667482718028084</v>
+        <v>2.667482718028083</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.1502829069719156</v>
+        <v>-0.1502829069719169</v>
       </c>
       <c r="I67" t="n">
-        <v>5.333406924925334</v>
+        <v>5.333406924925381</v>
       </c>
       <c r="J67" t="n">
-        <v>-5.333406924925334</v>
+        <v>-5.333406924925381</v>
       </c>
     </row>
     <row r="68">
@@ -5012,22 +4957,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.07041259839357857</v>
+        <v>0.07041259839357256</v>
       </c>
       <c r="F74" t="n">
         <v>2.3428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.342801509019341</v>
+        <v>2.342801509019313</v>
       </c>
       <c r="H74" t="n">
-        <v>1.509019341039419e-06</v>
+        <v>1.509019313949977e-06</v>
       </c>
       <c r="I74" t="n">
-        <v>6.441093311590489e-05</v>
+        <v>6.441093195962002e-05</v>
       </c>
       <c r="J74" t="n">
-        <v>6.441093311590489e-05</v>
+        <v>6.441093195962002e-05</v>
       </c>
     </row>
     <row r="75">
@@ -5048,22 +4993,22 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.07041259839357857</v>
+        <v>0.07041259839357256</v>
       </c>
       <c r="F75" t="n">
         <v>2.72115</v>
       </c>
       <c r="G75" t="n">
-        <v>2.457505936937394</v>
+        <v>2.457505936937378</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.2636440630626056</v>
+        <v>-0.2636440630626216</v>
       </c>
       <c r="I75" t="n">
-        <v>9.68870011071075</v>
+        <v>9.68870011071134</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.68870011071075</v>
+        <v>-9.68870011071134</v>
       </c>
     </row>
     <row r="76">
@@ -5084,22 +5029,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.07041259839357857</v>
+        <v>0.07041259839357256</v>
       </c>
       <c r="F76" t="n">
         <v>2.965825</v>
       </c>
       <c r="G76" t="n">
-        <v>2.693044111791967</v>
+        <v>2.693044111791964</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.2727808882080329</v>
+        <v>-0.2727808882080356</v>
       </c>
       <c r="I76" t="n">
-        <v>9.197470795074993</v>
+        <v>9.197470795075084</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.197470795074993</v>
+        <v>-9.197470795075084</v>
       </c>
     </row>
     <row r="77">
@@ -5372,16 +5317,16 @@
         <v>2.528852109678786</v>
       </c>
       <c r="G84" t="n">
-        <v>2.373612969180974</v>
+        <v>2.373612969180975</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.1552391404978115</v>
+        <v>-0.1552391404978111</v>
       </c>
       <c r="I84" t="n">
-        <v>6.138719615261722</v>
+        <v>6.138719615261705</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.138719615261722</v>
+        <v>-6.138719615261705</v>
       </c>
     </row>
     <row r="85">
@@ -5726,16 +5671,16 @@
         <v>2.839534374999999</v>
       </c>
       <c r="G94" t="n">
-        <v>2.653983380357526</v>
+        <v>2.653983380357527</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.1855509946424734</v>
+        <v>-0.1855509946424729</v>
       </c>
       <c r="I94" t="n">
-        <v>6.534557083587813</v>
+        <v>6.534557083587797</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.534557083587813</v>
+        <v>-6.534557083587797</v>
       </c>
     </row>
     <row r="95">
@@ -5966,22 +5911,22 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.07649558994396405</v>
+        <v>0.07649558994396592</v>
       </c>
       <c r="F101" t="n">
         <v>1.7076125</v>
       </c>
       <c r="G101" t="n">
-        <v>1.707614570246329</v>
+        <v>1.707614570246341</v>
       </c>
       <c r="H101" t="n">
-        <v>2.070246329255454e-06</v>
+        <v>2.070246341245863e-06</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0001212363067883056</v>
+        <v>0.0001212363074904794</v>
       </c>
       <c r="J101" t="n">
-        <v>0.0001212363067883056</v>
+        <v>0.0001212363074904794</v>
       </c>
     </row>
     <row r="102">
@@ -6002,22 +5947,22 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.07649558994396405</v>
+        <v>0.07649558994396592</v>
       </c>
       <c r="F102" t="n">
         <v>2.05415</v>
       </c>
       <c r="G102" t="n">
-        <v>1.881066852545637</v>
+        <v>1.881066852545645</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.1730831474543628</v>
+        <v>-0.1730831474543548</v>
       </c>
       <c r="I102" t="n">
-        <v>8.426022805265577</v>
+        <v>8.426022805265186</v>
       </c>
       <c r="J102" t="n">
-        <v>-8.426022805265577</v>
+        <v>-8.426022805265186</v>
       </c>
     </row>
     <row r="103">
@@ -6038,22 +5983,22 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.07649558994396405</v>
+        <v>0.07649558994396592</v>
       </c>
       <c r="F103" t="n">
         <v>2.45671875</v>
       </c>
       <c r="G103" t="n">
-        <v>2.307684191971352</v>
+        <v>2.307684191971354</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.1490345580286476</v>
+        <v>-0.1490345580286463</v>
       </c>
       <c r="I103" t="n">
-        <v>6.066406992198339</v>
+        <v>6.066406992198284</v>
       </c>
       <c r="J103" t="n">
-        <v>-6.066406992198339</v>
+        <v>-6.066406992198284</v>
       </c>
     </row>
     <row r="104">
@@ -6284,7 +6229,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.08746020600723745</v>
+        <v>0.08746020600723763</v>
       </c>
       <c r="F110" t="n">
         <v>2.3283</v>
@@ -6293,13 +6238,13 @@
         <v>2.328299080399431</v>
       </c>
       <c r="H110" t="n">
-        <v>-9.196005690270681e-07</v>
+        <v>-9.196005694711573e-07</v>
       </c>
       <c r="I110" t="n">
-        <v>3.949665288094609e-05</v>
+        <v>3.949665290001963e-05</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.949665288094609e-05</v>
+        <v>-3.949665290001963e-05</v>
       </c>
     </row>
     <row r="111">
@@ -6320,7 +6265,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.08746020600723745</v>
+        <v>0.08746020600723763</v>
       </c>
       <c r="F111" t="n">
         <v>2.4123875</v>
@@ -6356,7 +6301,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.08746020600723745</v>
+        <v>0.08746020600723763</v>
       </c>
       <c r="F112" t="n">
         <v>2.71143125</v>
@@ -6602,7 +6547,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.2186428755542171</v>
+        <v>0.2186428755542173</v>
       </c>
       <c r="F119" t="n">
         <v>2.3587375</v>
@@ -6638,7 +6583,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.2186428755542171</v>
+        <v>0.2186428755542173</v>
       </c>
       <c r="F120" t="n">
         <v>2.497631302525579</v>
@@ -6647,13 +6592,13 @@
         <v>2.497630668499415</v>
       </c>
       <c r="H120" t="n">
-        <v>-6.34026164014756e-07</v>
+        <v>-6.340261635706668e-07</v>
       </c>
       <c r="I120" t="n">
-        <v>2.538509840798501e-05</v>
+        <v>2.538509839020459e-05</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.538509840798501e-05</v>
+        <v>-2.538509839020459e-05</v>
       </c>
     </row>
     <row r="121">
@@ -6674,7 +6619,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.2186428755542171</v>
+        <v>0.2186428755542173</v>
       </c>
       <c r="F121" t="n">
         <v>2.770865625</v>
@@ -6920,22 +6865,22 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.07662637658294001</v>
+        <v>0.07662637658294051</v>
       </c>
       <c r="F128" t="n">
         <v>1.4346</v>
       </c>
       <c r="G128" t="n">
-        <v>1.434602459183037</v>
+        <v>1.43460245918304</v>
       </c>
       <c r="H128" t="n">
-        <v>2.459183036984669e-06</v>
+        <v>2.459183039871249e-06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0001714194226254474</v>
+        <v>0.0001714194228266589</v>
       </c>
       <c r="J128" t="n">
-        <v>0.0001714194226254474</v>
+        <v>0.0001714194228266589</v>
       </c>
     </row>
     <row r="129">
@@ -6956,22 +6901,22 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.07662637658294001</v>
+        <v>0.07662637658294051</v>
       </c>
       <c r="F129" t="n">
         <v>1.737378411525397</v>
       </c>
       <c r="G129" t="n">
-        <v>1.622019989859314</v>
+        <v>1.622019989859316</v>
       </c>
       <c r="H129" t="n">
-        <v>-0.1153584216660828</v>
+        <v>-0.1153584216660808</v>
       </c>
       <c r="I129" t="n">
-        <v>6.639798267367644</v>
+        <v>6.639798267367531</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.639798267367644</v>
+        <v>-6.639798267367531</v>
       </c>
     </row>
     <row r="130">
@@ -6992,22 +6937,22 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.07662637658294001</v>
+        <v>0.07662637658294051</v>
       </c>
       <c r="F130" t="n">
         <v>2.244778125</v>
       </c>
       <c r="G130" t="n">
-        <v>2.114682119425783</v>
+        <v>2.114682119425784</v>
       </c>
       <c r="H130" t="n">
-        <v>-0.1300960055742166</v>
+        <v>-0.1300960055742157</v>
       </c>
       <c r="I130" t="n">
-        <v>5.795495070329797</v>
+        <v>5.795495070329757</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.795495070329797</v>
+        <v>-5.795495070329757</v>
       </c>
     </row>
     <row r="131">
@@ -7222,10 +7167,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>113735</v>
+        <v>113754</v>
       </c>
       <c r="B137" t="n">
-        <v>0.09160330411903464</v>
+        <v>0.1192694322660098</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -7238,30 +7183,30 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.4825333284192772</v>
+        <v>0.05726532872156408</v>
       </c>
       <c r="F137" t="n">
-        <v>2.3656875</v>
+        <v>1.88635</v>
       </c>
       <c r="G137" t="n">
-        <v>2.574245508661671</v>
+        <v>1.886349694177938</v>
       </c>
       <c r="H137" t="n">
-        <v>0.2085580086616714</v>
+        <v>-3.058220623408658e-07</v>
       </c>
       <c r="I137" t="n">
-        <v>8.815957672417486</v>
+        <v>1.621237110509003e-05</v>
       </c>
       <c r="J137" t="n">
-        <v>8.815957672417486</v>
+        <v>-1.621237110509003e-05</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>113735</v>
+        <v>113754</v>
       </c>
       <c r="B138" t="n">
-        <v>0.09160330411903464</v>
+        <v>0.1192694322660098</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -7274,30 +7219,30 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.4825333284192772</v>
+        <v>0.05726532872156408</v>
       </c>
       <c r="F138" t="n">
-        <v>2.596562490472174</v>
+        <v>2.2409375</v>
       </c>
       <c r="G138" t="n">
-        <v>2.596562202770281</v>
+        <v>2.083740315145228</v>
       </c>
       <c r="H138" t="n">
-        <v>-2.87701892975889e-07</v>
+        <v>-0.157197184854772</v>
       </c>
       <c r="I138" t="n">
-        <v>1.108010664220801e-05</v>
+        <v>7.01479558688147</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.108010664220801e-05</v>
+        <v>-7.01479558688147</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>113735</v>
+        <v>113754</v>
       </c>
       <c r="B139" t="n">
-        <v>0.09160330411903464</v>
+        <v>0.1192694322660098</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -7310,30 +7255,30 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.4825333284192772</v>
+        <v>0.05726532872156408</v>
       </c>
       <c r="F139" t="n">
-        <v>2.83653125</v>
+        <v>2.565471875</v>
       </c>
       <c r="G139" t="n">
-        <v>2.685276836149347</v>
+        <v>2.486393244968921</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.1512544138506535</v>
+        <v>-0.07907863003107884</v>
       </c>
       <c r="I139" t="n">
-        <v>5.332372553648176</v>
+        <v>3.082420462359535</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.332372553648176</v>
+        <v>-3.082420462359535</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>113735</v>
+        <v>113754</v>
       </c>
       <c r="B140" t="n">
-        <v>0.09160330411903464</v>
+        <v>0.1192694322660098</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -7346,30 +7291,30 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.4981426684592046</v>
+        <v>0.07717316817023095</v>
       </c>
       <c r="F140" t="n">
-        <v>2.3656875</v>
+        <v>1.88635</v>
       </c>
       <c r="G140" t="n">
-        <v>2.574254740514772</v>
+        <v>1.886353589621563</v>
       </c>
       <c r="H140" t="n">
-        <v>0.2085672405147716</v>
+        <v>3.589621562660739e-06</v>
       </c>
       <c r="I140" t="n">
-        <v>8.816347912172322</v>
+        <v>0.0001902945668969565</v>
       </c>
       <c r="J140" t="n">
-        <v>8.816347912172322</v>
+        <v>0.0001902945668969565</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>113735</v>
+        <v>113754</v>
       </c>
       <c r="B141" t="n">
-        <v>0.09160330411903464</v>
+        <v>0.1192694322660098</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7382,30 +7327,30 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.4981426684592046</v>
+        <v>0.07717316817023095</v>
       </c>
       <c r="F141" t="n">
-        <v>2.596562490472174</v>
+        <v>2.2409375</v>
       </c>
       <c r="G141" t="n">
-        <v>2.596562184455288</v>
+        <v>2.081362044028959</v>
       </c>
       <c r="H141" t="n">
-        <v>-3.060168860535839e-07</v>
+        <v>-0.1595754559710412</v>
       </c>
       <c r="I141" t="n">
-        <v>1.178546201666558e-05</v>
+        <v>7.120923986993888</v>
       </c>
       <c r="J141" t="n">
-        <v>-1.178546201666558e-05</v>
+        <v>-7.120923986993888</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>113735</v>
+        <v>113754</v>
       </c>
       <c r="B142" t="n">
-        <v>0.09160330411903464</v>
+        <v>0.1192694322660098</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7418,30 +7363,30 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.4981426684592046</v>
+        <v>0.07717316817023095</v>
       </c>
       <c r="F142" t="n">
-        <v>2.83653125</v>
+        <v>2.565471875</v>
       </c>
       <c r="G142" t="n">
-        <v>2.685263434731976</v>
+        <v>2.484237378899032</v>
       </c>
       <c r="H142" t="n">
-        <v>-0.1512678152680245</v>
+        <v>-0.08123449610096856</v>
       </c>
       <c r="I142" t="n">
-        <v>5.332845011597332</v>
+        <v>3.166454362356577</v>
       </c>
       <c r="J142" t="n">
-        <v>-5.332845011597332</v>
+        <v>-3.166454362356577</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>113735</v>
+        <v>113754</v>
       </c>
       <c r="B143" t="n">
-        <v>0.09160330411903464</v>
+        <v>0.1192694322660098</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7455,27 +7400,27 @@
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>2.3656875</v>
+        <v>1.88635</v>
       </c>
       <c r="G143" t="n">
-        <v>2.575929155914063</v>
+        <v>2.454017432754297</v>
       </c>
       <c r="H143" t="n">
-        <v>0.2102416559140634</v>
+        <v>0.567667432754297</v>
       </c>
       <c r="I143" t="n">
-        <v>8.887127142281615</v>
+        <v>30.09343084551101</v>
       </c>
       <c r="J143" t="n">
-        <v>8.887127142281615</v>
+        <v>30.09343084551101</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>113735</v>
+        <v>113754</v>
       </c>
       <c r="B144" t="n">
-        <v>0.09160330411903464</v>
+        <v>0.1192694322660098</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7489,27 +7434,27 @@
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2.596562490472174</v>
+        <v>2.2409375</v>
       </c>
       <c r="G144" t="n">
-        <v>2.597954531574995</v>
+        <v>2.483129577437567</v>
       </c>
       <c r="H144" t="n">
-        <v>0.001392041102821207</v>
+        <v>0.2421920774375663</v>
       </c>
       <c r="I144" t="n">
-        <v>0.05361092243799878</v>
+        <v>10.80762303444725</v>
       </c>
       <c r="J144" t="n">
-        <v>0.05361092243799878</v>
+        <v>10.80762303444725</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>113735</v>
+        <v>113754</v>
       </c>
       <c r="B145" t="n">
-        <v>0.09160330411903464</v>
+        <v>0.1192694322660098</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -7523,27 +7468,27 @@
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2.83653125</v>
+        <v>2.565471875</v>
       </c>
       <c r="G145" t="n">
-        <v>2.685833739997278</v>
+        <v>2.598281676660775</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.1506975100027219</v>
+        <v>0.03280980166077496</v>
       </c>
       <c r="I145" t="n">
-        <v>5.312739283331425</v>
+        <v>1.278899292582382</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.312739283331425</v>
+        <v>1.278899292582382</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>113754</v>
+        <v>129473</v>
       </c>
       <c r="B146" t="n">
-        <v>0.1192694322660098</v>
+        <v>0.117869102602222</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -7556,30 +7501,30 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.0572653287215627</v>
+        <v>0.2227214678701135</v>
       </c>
       <c r="F146" t="n">
-        <v>1.88635</v>
+        <v>2.235925</v>
       </c>
       <c r="G146" t="n">
-        <v>1.886349694177926</v>
+        <v>2.363888913067183</v>
       </c>
       <c r="H146" t="n">
-        <v>-3.058220743312745e-07</v>
+        <v>0.1279639130671826</v>
       </c>
       <c r="I146" t="n">
-        <v>1.621237174073075e-05</v>
+        <v>5.723086108307863</v>
       </c>
       <c r="J146" t="n">
-        <v>-1.621237174073075e-05</v>
+        <v>5.723086108307863</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>113754</v>
+        <v>129473</v>
       </c>
       <c r="B147" t="n">
-        <v>0.1192694322660098</v>
+        <v>0.117869102602222</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -7592,30 +7537,30 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.0572653287215627</v>
+        <v>0.2227214678701135</v>
       </c>
       <c r="F147" t="n">
-        <v>2.2409375</v>
+        <v>2.411340264975417</v>
       </c>
       <c r="G147" t="n">
-        <v>2.083740315145221</v>
+        <v>2.411339823758257</v>
       </c>
       <c r="H147" t="n">
-        <v>-0.1571971848547791</v>
+        <v>-4.412171601408943e-07</v>
       </c>
       <c r="I147" t="n">
-        <v>7.014795586881788</v>
+        <v>1.829759020531233e-05</v>
       </c>
       <c r="J147" t="n">
-        <v>-7.014795586881788</v>
+        <v>-1.829759020531233e-05</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>113754</v>
+        <v>129473</v>
       </c>
       <c r="B148" t="n">
-        <v>0.1192694322660098</v>
+        <v>0.117869102602222</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -7628,30 +7573,30 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.0572653287215627</v>
+        <v>0.2227214678701135</v>
       </c>
       <c r="F148" t="n">
-        <v>2.565471875</v>
+        <v>2.690510416666667</v>
       </c>
       <c r="G148" t="n">
-        <v>2.48639324496892</v>
+        <v>2.572755652726743</v>
       </c>
       <c r="H148" t="n">
-        <v>-0.07907863003108018</v>
+        <v>-0.1177547639399243</v>
       </c>
       <c r="I148" t="n">
-        <v>3.082420462359587</v>
+        <v>4.376670062694399</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.082420462359587</v>
+        <v>-4.376670062694399</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>113754</v>
+        <v>129473</v>
       </c>
       <c r="B149" t="n">
-        <v>0.1192694322660098</v>
+        <v>0.117869102602222</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -7664,30 +7609,30 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.07717316817023095</v>
+        <v>0.2448759921893136</v>
       </c>
       <c r="F149" t="n">
-        <v>1.88635</v>
+        <v>2.235925</v>
       </c>
       <c r="G149" t="n">
-        <v>1.886353589621563</v>
+        <v>2.364124019916902</v>
       </c>
       <c r="H149" t="n">
-        <v>3.589621562660739e-06</v>
+        <v>0.1281990199169023</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0001902945668969565</v>
+        <v>5.733601078609627</v>
       </c>
       <c r="J149" t="n">
-        <v>0.0001902945668969565</v>
+        <v>5.733601078609627</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>113754</v>
+        <v>129473</v>
       </c>
       <c r="B150" t="n">
-        <v>0.1192694322660098</v>
+        <v>0.117869102602222</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -7700,30 +7645,30 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.07717316817023095</v>
+        <v>0.2448759921893136</v>
       </c>
       <c r="F150" t="n">
-        <v>2.2409375</v>
+        <v>2.411340264975417</v>
       </c>
       <c r="G150" t="n">
-        <v>2.081362044028959</v>
+        <v>2.411339883316624</v>
       </c>
       <c r="H150" t="n">
-        <v>-0.1595754559710412</v>
+        <v>-3.816587930138837e-07</v>
       </c>
       <c r="I150" t="n">
-        <v>7.120923986993888</v>
+        <v>1.582766225727063e-05</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.120923986993888</v>
+        <v>-1.582766225727063e-05</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>113754</v>
+        <v>129473</v>
       </c>
       <c r="B151" t="n">
-        <v>0.1192694322660098</v>
+        <v>0.117869102602222</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -7736,30 +7681,30 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.07717316817023095</v>
+        <v>0.2448759921893136</v>
       </c>
       <c r="F151" t="n">
-        <v>2.565471875</v>
+        <v>2.690510416666667</v>
       </c>
       <c r="G151" t="n">
-        <v>2.484237378899032</v>
+        <v>2.572503429443898</v>
       </c>
       <c r="H151" t="n">
-        <v>-0.08123449610096856</v>
+        <v>-0.1180069872227691</v>
       </c>
       <c r="I151" t="n">
-        <v>3.166454362356577</v>
+        <v>4.386044614128297</v>
       </c>
       <c r="J151" t="n">
-        <v>-3.166454362356577</v>
+        <v>-4.386044614128297</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>113754</v>
+        <v>129473</v>
       </c>
       <c r="B152" t="n">
-        <v>0.1192694322660098</v>
+        <v>0.117869102602222</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -7773,27 +7718,27 @@
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="n">
-        <v>1.88635</v>
+        <v>2.235925</v>
       </c>
       <c r="G152" t="n">
-        <v>2.454017432754297</v>
+        <v>2.460186332276165</v>
       </c>
       <c r="H152" t="n">
-        <v>0.567667432754297</v>
+        <v>0.2242613322761655</v>
       </c>
       <c r="I152" t="n">
-        <v>30.09343084551101</v>
+        <v>10.02991300138267</v>
       </c>
       <c r="J152" t="n">
-        <v>30.09343084551101</v>
+        <v>10.02991300138267</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>113754</v>
+        <v>129473</v>
       </c>
       <c r="B153" t="n">
-        <v>0.1192694322660098</v>
+        <v>0.117869102602222</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -7807,27 +7752,27 @@
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
-        <v>2.2409375</v>
+        <v>2.411340264975417</v>
       </c>
       <c r="G153" t="n">
-        <v>2.483129577437567</v>
+        <v>2.488934066582003</v>
       </c>
       <c r="H153" t="n">
-        <v>0.2421920774375663</v>
+        <v>0.07759380160658624</v>
       </c>
       <c r="I153" t="n">
-        <v>10.80762303444725</v>
+        <v>3.217870274619965</v>
       </c>
       <c r="J153" t="n">
-        <v>10.80762303444725</v>
+        <v>3.217870274619965</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>113754</v>
+        <v>129473</v>
       </c>
       <c r="B154" t="n">
-        <v>0.1192694322660098</v>
+        <v>0.117869102602222</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -7841,27 +7786,27 @@
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="n">
-        <v>2.565471875</v>
+        <v>2.690510416666667</v>
       </c>
       <c r="G154" t="n">
-        <v>2.598281676660775</v>
+        <v>2.602697135067904</v>
       </c>
       <c r="H154" t="n">
-        <v>0.03280980166077496</v>
+        <v>-0.08781328159876267</v>
       </c>
       <c r="I154" t="n">
-        <v>1.278899292582382</v>
+        <v>3.263814964431786</v>
       </c>
       <c r="J154" t="n">
-        <v>1.278899292582382</v>
+        <v>-3.263814964431786</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129473</v>
+        <v>129498</v>
       </c>
       <c r="B155" t="n">
-        <v>0.117869102602222</v>
+        <v>0.136895751762234</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -7874,30 +7819,30 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.2227214678701133</v>
+        <v>0.08427582850660252</v>
       </c>
       <c r="F155" t="n">
-        <v>2.235925</v>
+        <v>1.9574</v>
       </c>
       <c r="G155" t="n">
-        <v>2.363888913067183</v>
+        <v>1.957401650385334</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1279639130671826</v>
+        <v>1.650385333729076e-06</v>
       </c>
       <c r="I155" t="n">
-        <v>5.723086108307863</v>
+        <v>8.431518002089897e-05</v>
       </c>
       <c r="J155" t="n">
-        <v>5.723086108307863</v>
+        <v>8.431518002089897e-05</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129473</v>
+        <v>129498</v>
       </c>
       <c r="B156" t="n">
-        <v>0.117869102602222</v>
+        <v>0.136895751762234</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -7910,30 +7855,30 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.2227214678701133</v>
+        <v>0.08427582850660252</v>
       </c>
       <c r="F156" t="n">
-        <v>2.411340264975417</v>
+        <v>2.2367375</v>
       </c>
       <c r="G156" t="n">
-        <v>2.411339823758257</v>
+        <v>2.099555520196756</v>
       </c>
       <c r="H156" t="n">
-        <v>-4.412171596968051e-07</v>
+        <v>-0.1371819798032448</v>
       </c>
       <c r="I156" t="n">
-        <v>1.829759018689564e-05</v>
+        <v>6.133128263966816</v>
       </c>
       <c r="J156" t="n">
-        <v>-1.829759018689564e-05</v>
+        <v>-6.133128263966816</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129473</v>
+        <v>129498</v>
       </c>
       <c r="B157" t="n">
-        <v>0.117869102602222</v>
+        <v>0.136895751762234</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -7946,30 +7891,30 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.2227214678701133</v>
+        <v>0.08427582850660252</v>
       </c>
       <c r="F157" t="n">
-        <v>2.690510416666667</v>
+        <v>2.472651041666666</v>
       </c>
       <c r="G157" t="n">
-        <v>2.572755652726743</v>
+        <v>2.446110882804162</v>
       </c>
       <c r="H157" t="n">
-        <v>-0.1177547639399243</v>
+        <v>-0.02654015886250427</v>
       </c>
       <c r="I157" t="n">
-        <v>4.376670062694399</v>
+        <v>1.073348338090406</v>
       </c>
       <c r="J157" t="n">
-        <v>-4.376670062694399</v>
+        <v>-1.073348338090406</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129473</v>
+        <v>129498</v>
       </c>
       <c r="B158" t="n">
-        <v>0.117869102602222</v>
+        <v>0.136895751762234</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -7982,30 +7927,30 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.2448759921893136</v>
+        <v>0.1080509055066162</v>
       </c>
       <c r="F158" t="n">
-        <v>2.235925</v>
+        <v>1.9574</v>
       </c>
       <c r="G158" t="n">
-        <v>2.364124019916902</v>
+        <v>1.957402950459858</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1281990199169023</v>
+        <v>2.950459858208632e-06</v>
       </c>
       <c r="I158" t="n">
-        <v>5.733601078609627</v>
+        <v>0.0001507336189950256</v>
       </c>
       <c r="J158" t="n">
-        <v>5.733601078609627</v>
+        <v>0.0001507336189950256</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129473</v>
+        <v>129498</v>
       </c>
       <c r="B159" t="n">
-        <v>0.117869102602222</v>
+        <v>0.136895751762234</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -8018,30 +7963,30 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.2448759921893136</v>
+        <v>0.1080509055066162</v>
       </c>
       <c r="F159" t="n">
-        <v>2.411340264975417</v>
+        <v>2.2367375</v>
       </c>
       <c r="G159" t="n">
-        <v>2.411339883316624</v>
+        <v>2.09786496083404</v>
       </c>
       <c r="H159" t="n">
-        <v>-3.816587930138837e-07</v>
+        <v>-0.1388725391659604</v>
       </c>
       <c r="I159" t="n">
-        <v>1.582766225727063e-05</v>
+        <v>6.208709746492846</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.582766225727063e-05</v>
+        <v>-6.208709746492846</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129473</v>
+        <v>129498</v>
       </c>
       <c r="B160" t="n">
-        <v>0.117869102602222</v>
+        <v>0.136895751762234</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -8054,30 +7999,30 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.2448759921893136</v>
+        <v>0.1080509055066162</v>
       </c>
       <c r="F160" t="n">
-        <v>2.690510416666667</v>
+        <v>2.472651041666666</v>
       </c>
       <c r="G160" t="n">
-        <v>2.572503429443898</v>
+        <v>2.444202465106636</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.1180069872227691</v>
+        <v>-0.02844857656003041</v>
       </c>
       <c r="I160" t="n">
-        <v>4.386044614128297</v>
+        <v>1.150529374369581</v>
       </c>
       <c r="J160" t="n">
-        <v>-4.386044614128297</v>
+        <v>-1.150529374369581</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129473</v>
+        <v>129498</v>
       </c>
       <c r="B161" t="n">
-        <v>0.117869102602222</v>
+        <v>0.136895751762234</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -8091,27 +8036,27 @@
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>2.235925</v>
+        <v>1.9574</v>
       </c>
       <c r="G161" t="n">
-        <v>2.460186332276165</v>
+        <v>2.376384652094541</v>
       </c>
       <c r="H161" t="n">
-        <v>0.2242613322761655</v>
+        <v>0.4189846520945408</v>
       </c>
       <c r="I161" t="n">
-        <v>10.02991300138267</v>
+        <v>21.40516256741294</v>
       </c>
       <c r="J161" t="n">
-        <v>10.02991300138267</v>
+        <v>21.40516256741294</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129473</v>
+        <v>129498</v>
       </c>
       <c r="B162" t="n">
-        <v>0.117869102602222</v>
+        <v>0.136895751762234</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -8125,27 +8070,27 @@
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2.411340264975417</v>
+        <v>2.2367375</v>
       </c>
       <c r="G162" t="n">
-        <v>2.488934066582003</v>
+        <v>2.410139454659309</v>
       </c>
       <c r="H162" t="n">
-        <v>0.07759380160658624</v>
+        <v>0.1734019546593086</v>
       </c>
       <c r="I162" t="n">
-        <v>3.217870274619965</v>
+        <v>7.752449925809739</v>
       </c>
       <c r="J162" t="n">
-        <v>3.217870274619965</v>
+        <v>7.752449925809739</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129473</v>
+        <v>129498</v>
       </c>
       <c r="B163" t="n">
-        <v>0.117869102602222</v>
+        <v>0.136895751762234</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -8159,27 +8104,27 @@
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>2.690510416666667</v>
+        <v>2.472651041666666</v>
       </c>
       <c r="G163" t="n">
-        <v>2.602697135067904</v>
+        <v>2.542855435916811</v>
       </c>
       <c r="H163" t="n">
-        <v>-0.08781328159876267</v>
+        <v>0.07020439425014446</v>
       </c>
       <c r="I163" t="n">
-        <v>3.263814964431786</v>
+        <v>2.839235826937548</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.263814964431786</v>
+        <v>2.839235826937548</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129498</v>
+        <v>129524</v>
       </c>
       <c r="B164" t="n">
-        <v>0.136895751762234</v>
+        <v>0.1474964002666242</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -8192,30 +8137,30 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.08427582850660222</v>
+        <v>0.09214397915035179</v>
       </c>
       <c r="F164" t="n">
-        <v>1.9574</v>
+        <v>1.9375625</v>
       </c>
       <c r="G164" t="n">
-        <v>1.957401650385331</v>
+        <v>1.937566510611282</v>
       </c>
       <c r="H164" t="n">
-        <v>1.650385331064541e-06</v>
+        <v>4.010611281968224e-06</v>
       </c>
       <c r="I164" t="n">
-        <v>8.431517988477271e-05</v>
+        <v>0.0002069926147914312</v>
       </c>
       <c r="J164" t="n">
-        <v>8.431517988477271e-05</v>
+        <v>0.0002069926147914312</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129498</v>
+        <v>129524</v>
       </c>
       <c r="B165" t="n">
-        <v>0.136895751762234</v>
+        <v>0.1474964002666242</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -8228,30 +8173,30 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.08427582850660222</v>
+        <v>0.09214397915035179</v>
       </c>
       <c r="F165" t="n">
-        <v>2.2367375</v>
+        <v>2.27314447629368</v>
       </c>
       <c r="G165" t="n">
-        <v>2.099555520196754</v>
+        <v>2.072134322987468</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.1371819798032465</v>
+        <v>-0.2010101533062127</v>
       </c>
       <c r="I165" t="n">
-        <v>6.133128263966895</v>
+        <v>8.842823472177891</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.133128263966895</v>
+        <v>-8.842823472177891</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129498</v>
+        <v>129524</v>
       </c>
       <c r="B166" t="n">
-        <v>0.136895751762234</v>
+        <v>0.1474964002666242</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -8264,30 +8209,30 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.08427582850660222</v>
+        <v>0.09214397915035179</v>
       </c>
       <c r="F166" t="n">
-        <v>2.472651041666666</v>
+        <v>2.609909375</v>
       </c>
       <c r="G166" t="n">
-        <v>2.446110882804162</v>
+        <v>2.415549589180215</v>
       </c>
       <c r="H166" t="n">
-        <v>-0.02654015886250471</v>
+        <v>-0.1943597858197852</v>
       </c>
       <c r="I166" t="n">
-        <v>1.073348338090424</v>
+        <v>7.446993665049584</v>
       </c>
       <c r="J166" t="n">
-        <v>-1.073348338090424</v>
+        <v>-7.446993665049584</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129498</v>
+        <v>129524</v>
       </c>
       <c r="B167" t="n">
-        <v>0.136895751762234</v>
+        <v>0.1474964002666242</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -8300,30 +8245,30 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.1080509055066162</v>
+        <v>0.1181240394951164</v>
       </c>
       <c r="F167" t="n">
-        <v>1.9574</v>
+        <v>1.9375625</v>
       </c>
       <c r="G167" t="n">
-        <v>1.957402950459858</v>
+        <v>1.937563131132626</v>
       </c>
       <c r="H167" t="n">
-        <v>2.950459858208632e-06</v>
+        <v>6.311326261609906e-07</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0001507336189950256</v>
+        <v>3.257353639745766e-05</v>
       </c>
       <c r="J167" t="n">
-        <v>0.0001507336189950256</v>
+        <v>3.257353639745766e-05</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129498</v>
+        <v>129524</v>
       </c>
       <c r="B168" t="n">
-        <v>0.136895751762234</v>
+        <v>0.1474964002666242</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -8336,30 +8281,30 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.1080509055066162</v>
+        <v>0.1181240394951164</v>
       </c>
       <c r="F168" t="n">
-        <v>2.2367375</v>
+        <v>2.27314447629368</v>
       </c>
       <c r="G168" t="n">
-        <v>2.09786496083404</v>
+        <v>2.070492713526872</v>
       </c>
       <c r="H168" t="n">
-        <v>-0.1388725391659604</v>
+        <v>-0.2026517627668087</v>
       </c>
       <c r="I168" t="n">
-        <v>6.208709746492846</v>
+        <v>8.915041031497859</v>
       </c>
       <c r="J168" t="n">
-        <v>-6.208709746492846</v>
+        <v>-8.915041031497859</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129498</v>
+        <v>129524</v>
       </c>
       <c r="B169" t="n">
-        <v>0.136895751762234</v>
+        <v>0.1474964002666242</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -8372,30 +8317,30 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.1080509055066162</v>
+        <v>0.1181240394951164</v>
       </c>
       <c r="F169" t="n">
-        <v>2.472651041666666</v>
+        <v>2.609909375</v>
       </c>
       <c r="G169" t="n">
-        <v>2.444202465106636</v>
+        <v>2.413589327867191</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.02844857656003041</v>
+        <v>-0.1963200471328093</v>
       </c>
       <c r="I169" t="n">
-        <v>1.150529374369581</v>
+        <v>7.522102070414198</v>
       </c>
       <c r="J169" t="n">
-        <v>-1.150529374369581</v>
+        <v>-7.522102070414198</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129498</v>
+        <v>129524</v>
       </c>
       <c r="B170" t="n">
-        <v>0.136895751762234</v>
+        <v>0.1474964002666242</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -8409,27 +8354,27 @@
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
-        <v>1.9574</v>
+        <v>1.9375625</v>
       </c>
       <c r="G170" t="n">
-        <v>2.376384652094541</v>
+        <v>2.329711311343251</v>
       </c>
       <c r="H170" t="n">
-        <v>0.4189846520945408</v>
+        <v>0.3921488113432512</v>
       </c>
       <c r="I170" t="n">
-        <v>21.40516256741294</v>
+        <v>20.23928576978813</v>
       </c>
       <c r="J170" t="n">
-        <v>21.40516256741294</v>
+        <v>20.23928576978813</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129498</v>
+        <v>129524</v>
       </c>
       <c r="B171" t="n">
-        <v>0.136895751762234</v>
+        <v>0.1474964002666242</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -8443,27 +8388,27 @@
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2.2367375</v>
+        <v>2.27314447629368</v>
       </c>
       <c r="G171" t="n">
-        <v>2.410139454659309</v>
+        <v>2.366310285658055</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1734019546593086</v>
+        <v>0.09316580936437457</v>
       </c>
       <c r="I171" t="n">
-        <v>7.752449925809739</v>
+        <v>4.098543244214714</v>
       </c>
       <c r="J171" t="n">
-        <v>7.752449925809739</v>
+        <v>4.098543244214714</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129498</v>
+        <v>129524</v>
       </c>
       <c r="B172" t="n">
-        <v>0.136895751762234</v>
+        <v>0.1474964002666242</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -8477,27 +8422,27 @@
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
-        <v>2.472651041666666</v>
+        <v>2.609909375</v>
       </c>
       <c r="G172" t="n">
-        <v>2.542855435916811</v>
+        <v>2.509661228822335</v>
       </c>
       <c r="H172" t="n">
-        <v>0.07020439425014446</v>
+        <v>-0.1002481461776648</v>
       </c>
       <c r="I172" t="n">
-        <v>2.839235826937548</v>
+        <v>3.841058510993883</v>
       </c>
       <c r="J172" t="n">
-        <v>2.839235826937548</v>
+        <v>-3.841058510993883</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129524</v>
+        <v>129552</v>
       </c>
       <c r="B173" t="n">
-        <v>0.1474964002666242</v>
+        <v>0.1447440980724326</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -8510,30 +8455,30 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>0.09214397915035165</v>
+        <v>0.07638048100184233</v>
       </c>
       <c r="F173" t="n">
-        <v>1.9375625</v>
+        <v>1.869</v>
       </c>
       <c r="G173" t="n">
-        <v>1.937566510611282</v>
+        <v>1.869000432363892</v>
       </c>
       <c r="H173" t="n">
-        <v>4.010611281524135e-06</v>
+        <v>4.323638922443251e-07</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0002069926147685112</v>
+        <v>2.313343457701044e-05</v>
       </c>
       <c r="J173" t="n">
-        <v>0.0002069926147685112</v>
+        <v>2.313343457701044e-05</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129524</v>
+        <v>129552</v>
       </c>
       <c r="B174" t="n">
-        <v>0.1474964002666242</v>
+        <v>0.1447440980724326</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -8546,30 +8491,30 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>0.09214397915035165</v>
+        <v>0.07638048100184233</v>
       </c>
       <c r="F174" t="n">
-        <v>2.27314447629368</v>
+        <v>2.254459673470501</v>
       </c>
       <c r="G174" t="n">
-        <v>2.072134322987468</v>
+        <v>2.030155710740681</v>
       </c>
       <c r="H174" t="n">
-        <v>-0.2010101533062127</v>
+        <v>-0.2243039627298202</v>
       </c>
       <c r="I174" t="n">
-        <v>8.842823472177891</v>
+        <v>9.949344642059092</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.842823472177891</v>
+        <v>-9.949344642059092</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129524</v>
+        <v>129552</v>
       </c>
       <c r="B175" t="n">
-        <v>0.1474964002666242</v>
+        <v>0.1447440980724326</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -8582,30 +8527,30 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0.09214397915035165</v>
+        <v>0.07638048100184233</v>
       </c>
       <c r="F175" t="n">
-        <v>2.609909375</v>
+        <v>2.601183333333334</v>
       </c>
       <c r="G175" t="n">
-        <v>2.415549589180215</v>
+        <v>2.412039605915339</v>
       </c>
       <c r="H175" t="n">
-        <v>-0.1943597858197852</v>
+        <v>-0.1891437274179948</v>
       </c>
       <c r="I175" t="n">
-        <v>7.446993665049584</v>
+        <v>7.271449305175008</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.446993665049584</v>
+        <v>-7.271449305175008</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129524</v>
+        <v>129552</v>
       </c>
       <c r="B176" t="n">
-        <v>0.1474964002666242</v>
+        <v>0.1447440980724326</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -8618,30 +8563,30 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.1181240394951164</v>
+        <v>0.1014549402188581</v>
       </c>
       <c r="F176" t="n">
-        <v>1.9375625</v>
+        <v>1.869</v>
       </c>
       <c r="G176" t="n">
-        <v>1.937563131132626</v>
+        <v>1.869000565008434</v>
       </c>
       <c r="H176" t="n">
-        <v>6.311326261609906e-07</v>
+        <v>5.650084338171268e-07</v>
       </c>
       <c r="I176" t="n">
-        <v>3.257353639745766e-05</v>
+        <v>3.023052080348458e-05</v>
       </c>
       <c r="J176" t="n">
-        <v>3.257353639745766e-05</v>
+        <v>3.023052080348458e-05</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129524</v>
+        <v>129552</v>
       </c>
       <c r="B177" t="n">
-        <v>0.1474964002666242</v>
+        <v>0.1447440980724326</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -8654,30 +8599,30 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0.1181240394951164</v>
+        <v>0.1014549402188581</v>
       </c>
       <c r="F177" t="n">
-        <v>2.27314447629368</v>
+        <v>2.254459673470501</v>
       </c>
       <c r="G177" t="n">
-        <v>2.070492713526872</v>
+        <v>2.028032155923051</v>
       </c>
       <c r="H177" t="n">
-        <v>-0.2026517627668087</v>
+        <v>-0.2264275175474508</v>
       </c>
       <c r="I177" t="n">
-        <v>8.915041031497859</v>
+        <v>10.04353815736654</v>
       </c>
       <c r="J177" t="n">
-        <v>-8.915041031497859</v>
+        <v>-10.04353815736654</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129524</v>
+        <v>129552</v>
       </c>
       <c r="B178" t="n">
-        <v>0.1474964002666242</v>
+        <v>0.1447440980724326</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -8690,30 +8635,30 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0.1181240394951164</v>
+        <v>0.1014549402188581</v>
       </c>
       <c r="F178" t="n">
-        <v>2.609909375</v>
+        <v>2.601183333333334</v>
       </c>
       <c r="G178" t="n">
-        <v>2.413589327867191</v>
+        <v>2.409724267906856</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.1963200471328093</v>
+        <v>-0.1914590654264781</v>
       </c>
       <c r="I178" t="n">
-        <v>7.522102070414198</v>
+        <v>7.360460255645624</v>
       </c>
       <c r="J178" t="n">
-        <v>-7.522102070414198</v>
+        <v>-7.360460255645624</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129524</v>
+        <v>129552</v>
       </c>
       <c r="B179" t="n">
-        <v>0.1474964002666242</v>
+        <v>0.1447440980724326</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -8727,27 +8672,27 @@
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>1.9375625</v>
+        <v>1.869</v>
       </c>
       <c r="G179" t="n">
-        <v>2.329711311343251</v>
+        <v>2.341828161607408</v>
       </c>
       <c r="H179" t="n">
-        <v>0.3921488113432512</v>
+        <v>0.4728281616074084</v>
       </c>
       <c r="I179" t="n">
-        <v>20.23928576978813</v>
+        <v>25.29845701484261</v>
       </c>
       <c r="J179" t="n">
-        <v>20.23928576978813</v>
+        <v>25.29845701484261</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129524</v>
+        <v>129552</v>
       </c>
       <c r="B180" t="n">
-        <v>0.1474964002666242</v>
+        <v>0.1447440980724326</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -8761,27 +8706,27 @@
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2.27314447629368</v>
+        <v>2.254459673470501</v>
       </c>
       <c r="G180" t="n">
-        <v>2.366310285658055</v>
+        <v>2.377684783663784</v>
       </c>
       <c r="H180" t="n">
-        <v>0.09316580936437457</v>
+        <v>0.1232251101932826</v>
       </c>
       <c r="I180" t="n">
-        <v>4.098543244214714</v>
+        <v>5.465837852117827</v>
       </c>
       <c r="J180" t="n">
-        <v>4.098543244214714</v>
+        <v>5.465837852117827</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129524</v>
+        <v>129552</v>
       </c>
       <c r="B181" t="n">
-        <v>0.1474964002666242</v>
+        <v>0.1447440980724326</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -8795,27 +8740,27 @@
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
-        <v>2.609909375</v>
+        <v>2.601183333333334</v>
       </c>
       <c r="G181" t="n">
-        <v>2.509661228822335</v>
+        <v>2.518269289043264</v>
       </c>
       <c r="H181" t="n">
-        <v>-0.1002481461776648</v>
+        <v>-0.08291404429006999</v>
       </c>
       <c r="I181" t="n">
-        <v>3.841058510993883</v>
+        <v>3.187550959117452</v>
       </c>
       <c r="J181" t="n">
-        <v>-3.841058510993883</v>
+        <v>-3.187550959117452</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129552</v>
+        <v>129563</v>
       </c>
       <c r="B182" t="n">
-        <v>0.1447440980724326</v>
+        <v>0.1588516934069688</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -8828,30 +8773,30 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>0.07638048100184246</v>
+        <v>0.07972957776622766</v>
       </c>
       <c r="F182" t="n">
-        <v>1.869</v>
+        <v>1.8122</v>
       </c>
       <c r="G182" t="n">
-        <v>1.869000432363893</v>
+        <v>1.812200181731645</v>
       </c>
       <c r="H182" t="n">
-        <v>4.323638926884144e-07</v>
+        <v>1.817316450658524e-07</v>
       </c>
       <c r="I182" t="n">
-        <v>2.313343460077123e-05</v>
+        <v>1.002823336639733e-05</v>
       </c>
       <c r="J182" t="n">
-        <v>2.313343460077123e-05</v>
+        <v>1.002823336639733e-05</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129552</v>
+        <v>129563</v>
       </c>
       <c r="B183" t="n">
-        <v>0.1447440980724326</v>
+        <v>0.1588516934069688</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -8864,30 +8809,30 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>0.07638048100184246</v>
+        <v>0.07972957776622766</v>
       </c>
       <c r="F183" t="n">
-        <v>2.254459673470501</v>
+        <v>2.166325</v>
       </c>
       <c r="G183" t="n">
-        <v>2.030155710740681</v>
+        <v>1.972873735471231</v>
       </c>
       <c r="H183" t="n">
-        <v>-0.2243039627298202</v>
+        <v>-0.1934512645287689</v>
       </c>
       <c r="I183" t="n">
-        <v>9.949344642059092</v>
+        <v>8.929928082294619</v>
       </c>
       <c r="J183" t="n">
-        <v>-9.949344642059092</v>
+        <v>-8.929928082294619</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129552</v>
+        <v>129563</v>
       </c>
       <c r="B184" t="n">
-        <v>0.1447440980724326</v>
+        <v>0.1588516934069688</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -8900,30 +8845,30 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0.07638048100184246</v>
+        <v>0.07972957776622766</v>
       </c>
       <c r="F184" t="n">
-        <v>2.601183333333334</v>
+        <v>2.561983333333334</v>
       </c>
       <c r="G184" t="n">
-        <v>2.412039605915339</v>
+        <v>2.366359266449719</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.1891437274179948</v>
+        <v>-0.1956240668836147</v>
       </c>
       <c r="I184" t="n">
-        <v>7.271449305175008</v>
+        <v>7.6356494727502</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.271449305175008</v>
+        <v>-7.6356494727502</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129552</v>
+        <v>129563</v>
       </c>
       <c r="B185" t="n">
-        <v>0.1447440980724326</v>
+        <v>0.1588516934069688</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -8936,30 +8881,30 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0.1014549402188581</v>
+        <v>0.1075983135296858</v>
       </c>
       <c r="F185" t="n">
-        <v>1.869</v>
+        <v>1.8122</v>
       </c>
       <c r="G185" t="n">
-        <v>1.869000565008434</v>
+        <v>1.812202321204978</v>
       </c>
       <c r="H185" t="n">
-        <v>5.650084338171268e-07</v>
+        <v>2.321204978006364e-06</v>
       </c>
       <c r="I185" t="n">
-        <v>3.023052080348458e-05</v>
+        <v>0.0001280876822650019</v>
       </c>
       <c r="J185" t="n">
-        <v>3.023052080348458e-05</v>
+        <v>0.0001280876822650019</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129552</v>
+        <v>129563</v>
       </c>
       <c r="B186" t="n">
-        <v>0.1447440980724326</v>
+        <v>0.1588516934069688</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -8972,30 +8917,30 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0.1014549402188581</v>
+        <v>0.1075983135296858</v>
       </c>
       <c r="F186" t="n">
-        <v>2.254459673470501</v>
+        <v>2.166325</v>
       </c>
       <c r="G186" t="n">
-        <v>2.028032155923051</v>
+        <v>1.97060279558481</v>
       </c>
       <c r="H186" t="n">
-        <v>-0.2264275175474508</v>
+        <v>-0.1957222044151898</v>
       </c>
       <c r="I186" t="n">
-        <v>10.04353815736654</v>
+        <v>9.034757223186265</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.04353815736654</v>
+        <v>-9.034757223186265</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129552</v>
+        <v>129563</v>
       </c>
       <c r="B187" t="n">
-        <v>0.1447440980724326</v>
+        <v>0.1588516934069688</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -9008,30 +8953,30 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>0.1014549402188581</v>
+        <v>0.1075983135296858</v>
       </c>
       <c r="F187" t="n">
-        <v>2.601183333333334</v>
+        <v>2.561983333333334</v>
       </c>
       <c r="G187" t="n">
-        <v>2.409724267906856</v>
+        <v>2.363776005895018</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.1914590654264781</v>
+        <v>-0.1982073274383152</v>
       </c>
       <c r="I187" t="n">
-        <v>7.360460255645624</v>
+        <v>7.736479970790149</v>
       </c>
       <c r="J187" t="n">
-        <v>-7.360460255645624</v>
+        <v>-7.736479970790149</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129552</v>
+        <v>129563</v>
       </c>
       <c r="B188" t="n">
-        <v>0.1447440980724326</v>
+        <v>0.1588516934069688</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -9045,27 +8990,27 @@
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="n">
-        <v>1.869</v>
+        <v>1.8122</v>
       </c>
       <c r="G188" t="n">
-        <v>2.341828161607408</v>
+        <v>2.279729526623774</v>
       </c>
       <c r="H188" t="n">
-        <v>0.4728281616074084</v>
+        <v>0.4675295266237736</v>
       </c>
       <c r="I188" t="n">
-        <v>25.29845701484261</v>
+        <v>25.79900268313506</v>
       </c>
       <c r="J188" t="n">
-        <v>25.29845701484261</v>
+        <v>25.79900268313506</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129552</v>
+        <v>129563</v>
       </c>
       <c r="B189" t="n">
-        <v>0.1447440980724326</v>
+        <v>0.1588516934069688</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -9079,27 +9024,27 @@
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="n">
-        <v>2.254459673470501</v>
+        <v>2.166325</v>
       </c>
       <c r="G189" t="n">
-        <v>2.377684783663784</v>
+        <v>2.31942122398937</v>
       </c>
       <c r="H189" t="n">
-        <v>0.1232251101932826</v>
+        <v>0.1530962239893698</v>
       </c>
       <c r="I189" t="n">
-        <v>5.465837852117827</v>
+        <v>7.067093995100912</v>
       </c>
       <c r="J189" t="n">
-        <v>5.465837852117827</v>
+        <v>7.067093995100912</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129552</v>
+        <v>129563</v>
       </c>
       <c r="B190" t="n">
-        <v>0.1447440980724326</v>
+        <v>0.1588516934069688</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -9113,27 +9058,27 @@
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="n">
-        <v>2.601183333333334</v>
+        <v>2.561983333333334</v>
       </c>
       <c r="G190" t="n">
-        <v>2.518269289043264</v>
+        <v>2.474224753937396</v>
       </c>
       <c r="H190" t="n">
-        <v>-0.08291404429006999</v>
+        <v>-0.0877585793959379</v>
       </c>
       <c r="I190" t="n">
-        <v>3.187550959117452</v>
+        <v>3.42541570251971</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.187550959117452</v>
+        <v>-3.42541570251971</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129563</v>
+        <v>129688</v>
       </c>
       <c r="B191" t="n">
-        <v>0.1588516934069688</v>
+        <v>0.0865773064992614</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -9146,30 +9091,30 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>0.07972957776622766</v>
+        <v>0.0711001993502882</v>
       </c>
       <c r="F191" t="n">
-        <v>1.8122</v>
+        <v>2.2072875</v>
       </c>
       <c r="G191" t="n">
-        <v>1.812200181731645</v>
+        <v>2.207288582010092</v>
       </c>
       <c r="H191" t="n">
-        <v>1.817316448438078e-07</v>
+        <v>1.082010092190444e-06</v>
       </c>
       <c r="I191" t="n">
-        <v>1.002823335414456e-05</v>
+        <v>4.901989850395312e-05</v>
       </c>
       <c r="J191" t="n">
-        <v>1.002823335414456e-05</v>
+        <v>4.901989850395312e-05</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129563</v>
+        <v>129688</v>
       </c>
       <c r="B192" t="n">
-        <v>0.1588516934069688</v>
+        <v>0.0865773064992614</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -9182,30 +9127,30 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>0.07972957776622766</v>
+        <v>0.0711001993502882</v>
       </c>
       <c r="F192" t="n">
-        <v>2.166325</v>
+        <v>2.365288415656712</v>
       </c>
       <c r="G192" t="n">
-        <v>1.972873735471231</v>
+        <v>2.339819610614401</v>
       </c>
       <c r="H192" t="n">
-        <v>-0.1934512645287687</v>
+        <v>-0.02546880504231153</v>
       </c>
       <c r="I192" t="n">
-        <v>8.929928082294609</v>
+        <v>1.076773761445926</v>
       </c>
       <c r="J192" t="n">
-        <v>-8.929928082294609</v>
+        <v>-1.076773761445926</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129563</v>
+        <v>129688</v>
       </c>
       <c r="B193" t="n">
-        <v>0.1588516934069688</v>
+        <v>0.0865773064992614</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -9218,30 +9163,30 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>0.07972957776622766</v>
+        <v>0.0711001993502882</v>
       </c>
       <c r="F193" t="n">
-        <v>2.561983333333334</v>
+        <v>2.615265625</v>
       </c>
       <c r="G193" t="n">
-        <v>2.366359266449719</v>
+        <v>2.621253254152973</v>
       </c>
       <c r="H193" t="n">
-        <v>-0.1956240668836147</v>
+        <v>0.005987629152973017</v>
       </c>
       <c r="I193" t="n">
-        <v>7.6356494727502</v>
+        <v>0.2289491780771989</v>
       </c>
       <c r="J193" t="n">
-        <v>-7.6356494727502</v>
+        <v>0.2289491780771989</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129563</v>
+        <v>129688</v>
       </c>
       <c r="B194" t="n">
-        <v>0.1588516934069688</v>
+        <v>0.0865773064992614</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -9254,30 +9199,30 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>0.1075983135296858</v>
+        <v>0.08546840709107527</v>
       </c>
       <c r="F194" t="n">
-        <v>1.8122</v>
+        <v>2.2072875</v>
       </c>
       <c r="G194" t="n">
-        <v>1.812202321204978</v>
+        <v>2.207289809509084</v>
       </c>
       <c r="H194" t="n">
-        <v>2.321204978006364e-06</v>
+        <v>2.309509084419403e-06</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0001280876822650019</v>
+        <v>0.000104631095152734</v>
       </c>
       <c r="J194" t="n">
-        <v>0.0001280876822650019</v>
+        <v>0.000104631095152734</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129563</v>
+        <v>129688</v>
       </c>
       <c r="B195" t="n">
-        <v>0.1588516934069688</v>
+        <v>0.0865773064992614</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -9290,30 +9235,30 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>0.1075983135296858</v>
+        <v>0.08546840709107527</v>
       </c>
       <c r="F195" t="n">
-        <v>2.166325</v>
+        <v>2.365288415656712</v>
       </c>
       <c r="G195" t="n">
-        <v>1.97060279558481</v>
+        <v>2.338742266664792</v>
       </c>
       <c r="H195" t="n">
-        <v>-0.1957222044151898</v>
+        <v>-0.02654614899191987</v>
       </c>
       <c r="I195" t="n">
-        <v>9.034757223186265</v>
+        <v>1.122321862154364</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.034757223186265</v>
+        <v>-1.122321862154364</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129563</v>
+        <v>129688</v>
       </c>
       <c r="B196" t="n">
-        <v>0.1588516934069688</v>
+        <v>0.0865773064992614</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -9326,30 +9271,30 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>0.1075983135296858</v>
+        <v>0.08546840709107527</v>
       </c>
       <c r="F196" t="n">
-        <v>2.561983333333334</v>
+        <v>2.615265625</v>
       </c>
       <c r="G196" t="n">
-        <v>2.363776005895018</v>
+        <v>2.620231716707695</v>
       </c>
       <c r="H196" t="n">
-        <v>-0.1982073274383152</v>
+        <v>0.004966091707694797</v>
       </c>
       <c r="I196" t="n">
-        <v>7.736479970790149</v>
+        <v>0.1898886162928401</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.736479970790149</v>
+        <v>0.1898886162928401</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129563</v>
+        <v>129688</v>
       </c>
       <c r="B197" t="n">
-        <v>0.1588516934069688</v>
+        <v>0.0865773064992614</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -9363,27 +9308,27 @@
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="n">
-        <v>1.8122</v>
+        <v>2.2072875</v>
       </c>
       <c r="G197" t="n">
-        <v>2.279729526623774</v>
+        <v>2.598083579963204</v>
       </c>
       <c r="H197" t="n">
-        <v>0.4675295266237736</v>
+        <v>0.3907960799632049</v>
       </c>
       <c r="I197" t="n">
-        <v>25.79900268313506</v>
+        <v>17.70481099372895</v>
       </c>
       <c r="J197" t="n">
-        <v>25.79900268313506</v>
+        <v>17.70481099372895</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129563</v>
+        <v>129688</v>
       </c>
       <c r="B198" t="n">
-        <v>0.1588516934069688</v>
+        <v>0.0865773064992614</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -9397,27 +9342,27 @@
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
-        <v>2.166325</v>
+        <v>2.365288415656712</v>
       </c>
       <c r="G198" t="n">
-        <v>2.31942122398937</v>
+        <v>2.618845893417667</v>
       </c>
       <c r="H198" t="n">
-        <v>0.1530962239893698</v>
+        <v>0.2535574777609546</v>
       </c>
       <c r="I198" t="n">
-        <v>7.067093995100912</v>
+        <v>10.71993910267199</v>
       </c>
       <c r="J198" t="n">
-        <v>7.067093995100912</v>
+        <v>10.71993910267199</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129563</v>
+        <v>129688</v>
       </c>
       <c r="B199" t="n">
-        <v>0.1588516934069688</v>
+        <v>0.0865773064992614</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -9431,27 +9376,27 @@
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="n">
-        <v>2.561983333333334</v>
+        <v>2.615265625</v>
       </c>
       <c r="G199" t="n">
-        <v>2.474224753937396</v>
+        <v>2.701808493083026</v>
       </c>
       <c r="H199" t="n">
-        <v>-0.0877585793959379</v>
+        <v>0.08654286808302558</v>
       </c>
       <c r="I199" t="n">
-        <v>3.42541570251971</v>
+        <v>3.309142568760126</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.42541570251971</v>
+        <v>3.309142568760126</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129688</v>
+        <v>129693</v>
       </c>
       <c r="B200" t="n">
-        <v>0.0865773064992614</v>
+        <v>0.1065359216241736</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -9464,30 +9409,30 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>0.07110019935028825</v>
+        <v>0.07216402703380319</v>
       </c>
       <c r="F200" t="n">
-        <v>2.2072875</v>
+        <v>2.075675</v>
       </c>
       <c r="G200" t="n">
-        <v>2.207288582010091</v>
+        <v>2.07567598358892</v>
       </c>
       <c r="H200" t="n">
-        <v>1.082010091746355e-06</v>
+        <v>9.835889196452285e-07</v>
       </c>
       <c r="I200" t="n">
-        <v>4.901989848383389e-05</v>
+        <v>4.738646077277168e-05</v>
       </c>
       <c r="J200" t="n">
-        <v>4.901989848383389e-05</v>
+        <v>4.738646077277168e-05</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129688</v>
+        <v>129693</v>
       </c>
       <c r="B201" t="n">
-        <v>0.0865773064992614</v>
+        <v>0.1065359216241736</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -9500,30 +9445,30 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>0.07110019935028825</v>
+        <v>0.07216402703380319</v>
       </c>
       <c r="F201" t="n">
-        <v>2.365288415656712</v>
+        <v>2.248592380402163</v>
       </c>
       <c r="G201" t="n">
-        <v>2.339819610614401</v>
+        <v>2.222711070038185</v>
       </c>
       <c r="H201" t="n">
-        <v>-0.02546880504231153</v>
+        <v>-0.02588131036397812</v>
       </c>
       <c r="I201" t="n">
-        <v>1.076773761445926</v>
+        <v>1.151000536582322</v>
       </c>
       <c r="J201" t="n">
-        <v>-1.076773761445926</v>
+        <v>-1.151000536582322</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129688</v>
+        <v>129693</v>
       </c>
       <c r="B202" t="n">
-        <v>0.0865773064992614</v>
+        <v>0.1065359216241736</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -9536,30 +9481,30 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>0.07110019935028825</v>
+        <v>0.07216402703380319</v>
       </c>
       <c r="F202" t="n">
-        <v>2.615265625</v>
+        <v>2.544978125</v>
       </c>
       <c r="G202" t="n">
-        <v>2.621253254152974</v>
+        <v>2.546388096156607</v>
       </c>
       <c r="H202" t="n">
-        <v>0.005987629152973462</v>
+        <v>0.001409971156607348</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2289491780772158</v>
+        <v>0.05540209335226991</v>
       </c>
       <c r="J202" t="n">
-        <v>0.2289491780772158</v>
+        <v>0.05540209335226991</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129688</v>
+        <v>129693</v>
       </c>
       <c r="B203" t="n">
-        <v>0.0865773064992614</v>
+        <v>0.1065359216241736</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -9572,30 +9517,30 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>0.08546840709107527</v>
+        <v>0.09009004668823942</v>
       </c>
       <c r="F203" t="n">
-        <v>2.2072875</v>
+        <v>2.075675</v>
       </c>
       <c r="G203" t="n">
-        <v>2.207289809509084</v>
+        <v>2.075677695368238</v>
       </c>
       <c r="H203" t="n">
-        <v>2.309509084419403e-06</v>
+        <v>2.695368238381235e-06</v>
       </c>
       <c r="I203" t="n">
-        <v>0.000104631095152734</v>
+        <v>0.0001298550225050278</v>
       </c>
       <c r="J203" t="n">
-        <v>0.000104631095152734</v>
+        <v>0.0001298550225050278</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129688</v>
+        <v>129693</v>
       </c>
       <c r="B204" t="n">
-        <v>0.0865773064992614</v>
+        <v>0.1065359216241736</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -9608,30 +9553,30 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>0.08546840709107527</v>
+        <v>0.09009004668823942</v>
       </c>
       <c r="F204" t="n">
-        <v>2.365288415656712</v>
+        <v>2.248592380402163</v>
       </c>
       <c r="G204" t="n">
-        <v>2.338742266664792</v>
+        <v>2.221247759638625</v>
       </c>
       <c r="H204" t="n">
-        <v>-0.02654614899191987</v>
+        <v>-0.02734462076353816</v>
       </c>
       <c r="I204" t="n">
-        <v>1.122321862154364</v>
+        <v>1.216077266909868</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.122321862154364</v>
+        <v>-1.216077266909868</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129688</v>
+        <v>129693</v>
       </c>
       <c r="B205" t="n">
-        <v>0.0865773064992614</v>
+        <v>0.1065359216241736</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -9644,30 +9589,30 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>0.08546840709107527</v>
+        <v>0.09009004668823942</v>
       </c>
       <c r="F205" t="n">
-        <v>2.615265625</v>
+        <v>2.544978125</v>
       </c>
       <c r="G205" t="n">
-        <v>2.620231716707695</v>
+        <v>2.544935263770212</v>
       </c>
       <c r="H205" t="n">
-        <v>0.004966091707694797</v>
+        <v>-4.2861229787583e-05</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1898886162928401</v>
+        <v>0.001684149241462851</v>
       </c>
       <c r="J205" t="n">
-        <v>0.1898886162928401</v>
+        <v>-0.001684149241462851</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129688</v>
+        <v>129693</v>
       </c>
       <c r="B206" t="n">
-        <v>0.0865773064992614</v>
+        <v>0.1065359216241736</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -9681,27 +9626,27 @@
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="n">
-        <v>2.2072875</v>
+        <v>2.075675</v>
       </c>
       <c r="G206" t="n">
-        <v>2.598083579963204</v>
+        <v>2.510119458573358</v>
       </c>
       <c r="H206" t="n">
-        <v>0.3907960799632049</v>
+        <v>0.434444458573358</v>
       </c>
       <c r="I206" t="n">
-        <v>17.70481099372895</v>
+        <v>20.93027369763369</v>
       </c>
       <c r="J206" t="n">
-        <v>17.70481099372895</v>
+        <v>20.93027369763369</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129688</v>
+        <v>129693</v>
       </c>
       <c r="B207" t="n">
-        <v>0.0865773064992614</v>
+        <v>0.1065359216241736</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -9715,27 +9660,27 @@
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="n">
-        <v>2.365288415656712</v>
+        <v>2.248592380402163</v>
       </c>
       <c r="G207" t="n">
-        <v>2.618845893417667</v>
+        <v>2.535940842992425</v>
       </c>
       <c r="H207" t="n">
-        <v>0.2535574777609546</v>
+        <v>0.2873484625902618</v>
       </c>
       <c r="I207" t="n">
-        <v>10.71993910267199</v>
+        <v>12.77903745893105</v>
       </c>
       <c r="J207" t="n">
-        <v>10.71993910267199</v>
+        <v>12.77903745893105</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129688</v>
+        <v>129693</v>
       </c>
       <c r="B208" t="n">
-        <v>0.0865773064992614</v>
+        <v>0.1065359216241736</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -9749,27 +9694,27 @@
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>2.615265625</v>
+        <v>2.544978125</v>
       </c>
       <c r="G208" t="n">
-        <v>2.701808493083026</v>
+        <v>2.638496136046607</v>
       </c>
       <c r="H208" t="n">
-        <v>0.08654286808302558</v>
+        <v>0.09351801104660717</v>
       </c>
       <c r="I208" t="n">
-        <v>3.309142568760126</v>
+        <v>3.674609621511272</v>
       </c>
       <c r="J208" t="n">
-        <v>3.309142568760126</v>
+        <v>3.674609621511272</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129693</v>
+        <v>129744</v>
       </c>
       <c r="B209" t="n">
-        <v>0.1065359216241736</v>
+        <v>0.037313</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -9782,30 +9727,30 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>0.07216402703380637</v>
+        <v>0.0686445033615314</v>
       </c>
       <c r="F209" t="n">
-        <v>2.075675</v>
+        <v>2.598375</v>
       </c>
       <c r="G209" t="n">
-        <v>2.075675983588938</v>
+        <v>2.598376774155648</v>
       </c>
       <c r="H209" t="n">
-        <v>9.835889378528861e-07</v>
+        <v>1.77415564861505e-06</v>
       </c>
       <c r="I209" t="n">
-        <v>4.73864616499638e-05</v>
+        <v>6.827943035993843e-05</v>
       </c>
       <c r="J209" t="n">
-        <v>4.73864616499638e-05</v>
+        <v>6.827943035993843e-05</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129693</v>
+        <v>129744</v>
       </c>
       <c r="B210" t="n">
-        <v>0.1065359216241736</v>
+        <v>0.037313</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -9818,30 +9763,30 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>0.07216402703380637</v>
+        <v>0.0686445033615314</v>
       </c>
       <c r="F210" t="n">
-        <v>2.248592380402163</v>
+        <v>2.715150068499876</v>
       </c>
       <c r="G210" t="n">
-        <v>2.222711070038197</v>
+        <v>2.673577863216871</v>
       </c>
       <c r="H210" t="n">
-        <v>-0.02588131036396657</v>
+        <v>-0.04157220528300432</v>
       </c>
       <c r="I210" t="n">
-        <v>1.151000536581809</v>
+        <v>1.531119983580614</v>
       </c>
       <c r="J210" t="n">
-        <v>-1.151000536581809</v>
+        <v>-1.531119983580614</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129693</v>
+        <v>129744</v>
       </c>
       <c r="B211" t="n">
-        <v>0.1065359216241736</v>
+        <v>0.037313</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -9854,30 +9799,30 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>0.07216402703380637</v>
+        <v>0.0686445033615314</v>
       </c>
       <c r="F211" t="n">
-        <v>2.544978125</v>
+        <v>2.829431944444444</v>
       </c>
       <c r="G211" t="n">
-        <v>2.546388096156609</v>
+        <v>2.818153575813073</v>
       </c>
       <c r="H211" t="n">
-        <v>0.001409971156609569</v>
+        <v>-0.01127836863137111</v>
       </c>
       <c r="I211" t="n">
-        <v>0.05540209335235715</v>
+        <v>0.3986089382187138</v>
       </c>
       <c r="J211" t="n">
-        <v>0.05540209335235715</v>
+        <v>-0.3986089382187138</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129693</v>
+        <v>129744</v>
       </c>
       <c r="B212" t="n">
-        <v>0.1065359216241736</v>
+        <v>0.037313</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -9890,30 +9835,30 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>0.09009004668823942</v>
+        <v>0.07463470711230444</v>
       </c>
       <c r="F212" t="n">
-        <v>2.075675</v>
+        <v>2.598375</v>
       </c>
       <c r="G212" t="n">
-        <v>2.075677695368238</v>
+        <v>2.598374770824879</v>
       </c>
       <c r="H212" t="n">
-        <v>2.695368238381235e-06</v>
+        <v>-2.291751206584536e-07</v>
       </c>
       <c r="I212" t="n">
-        <v>0.0001298550225050278</v>
+        <v>8.819940180245483e-06</v>
       </c>
       <c r="J212" t="n">
-        <v>0.0001298550225050278</v>
+        <v>-8.819940180245483e-06</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129693</v>
+        <v>129744</v>
       </c>
       <c r="B213" t="n">
-        <v>0.1065359216241736</v>
+        <v>0.037313</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -9926,30 +9871,30 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>0.09009004668823942</v>
+        <v>0.07463470711230444</v>
       </c>
       <c r="F213" t="n">
-        <v>2.248592380402163</v>
+        <v>2.715150068499876</v>
       </c>
       <c r="G213" t="n">
-        <v>2.221247759638625</v>
+        <v>2.673311859129013</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.02734462076353816</v>
+        <v>-0.04183820937086224</v>
       </c>
       <c r="I213" t="n">
-        <v>1.216077266909868</v>
+        <v>1.540917014357807</v>
       </c>
       <c r="J213" t="n">
-        <v>-1.216077266909868</v>
+        <v>-1.540917014357807</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129693</v>
+        <v>129744</v>
       </c>
       <c r="B214" t="n">
-        <v>0.1065359216241736</v>
+        <v>0.037313</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -9962,30 +9907,30 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>0.09009004668823942</v>
+        <v>0.07463470711230444</v>
       </c>
       <c r="F214" t="n">
-        <v>2.544978125</v>
+        <v>2.829431944444444</v>
       </c>
       <c r="G214" t="n">
-        <v>2.544935263770212</v>
+        <v>2.817931967533389</v>
       </c>
       <c r="H214" t="n">
-        <v>-4.2861229787583e-05</v>
+        <v>-0.01149997691105487</v>
       </c>
       <c r="I214" t="n">
-        <v>0.001684149241462851</v>
+        <v>0.40644119161922</v>
       </c>
       <c r="J214" t="n">
-        <v>-0.001684149241462851</v>
+        <v>-0.40644119161922</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129693</v>
+        <v>129744</v>
       </c>
       <c r="B215" t="n">
-        <v>0.1065359216241736</v>
+        <v>0.037313</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -9999,27 +9944,27 @@
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="n">
-        <v>2.075675</v>
+        <v>2.598375</v>
       </c>
       <c r="G215" t="n">
-        <v>2.510119458573358</v>
+        <v>2.815341205822899</v>
       </c>
       <c r="H215" t="n">
-        <v>0.434444458573358</v>
+        <v>0.2169662058228994</v>
       </c>
       <c r="I215" t="n">
-        <v>20.93027369763369</v>
+        <v>8.350072865652548</v>
       </c>
       <c r="J215" t="n">
-        <v>20.93027369763369</v>
+        <v>8.350072865652548</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129693</v>
+        <v>129744</v>
       </c>
       <c r="B216" t="n">
-        <v>0.1065359216241736</v>
+        <v>0.037313</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -10033,27 +9978,27 @@
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="n">
-        <v>2.248592380402163</v>
+        <v>2.715150068499876</v>
       </c>
       <c r="G216" t="n">
-        <v>2.535940842992425</v>
+        <v>2.824075737069516</v>
       </c>
       <c r="H216" t="n">
-        <v>0.2873484625902618</v>
+        <v>0.1089256685696407</v>
       </c>
       <c r="I216" t="n">
-        <v>12.77903745893105</v>
+        <v>4.011773412945175</v>
       </c>
       <c r="J216" t="n">
-        <v>12.77903745893105</v>
+        <v>4.011773412945175</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129693</v>
+        <v>129744</v>
       </c>
       <c r="B217" t="n">
-        <v>0.1065359216241736</v>
+        <v>0.037313</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -10067,27 +10012,27 @@
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
-        <v>2.544978125</v>
+        <v>2.829431944444444</v>
       </c>
       <c r="G217" t="n">
-        <v>2.638496136046607</v>
+        <v>2.85944110020561</v>
       </c>
       <c r="H217" t="n">
-        <v>0.09351801104660717</v>
+        <v>0.03000915576116636</v>
       </c>
       <c r="I217" t="n">
-        <v>3.674609621511272</v>
+        <v>1.060607088291662</v>
       </c>
       <c r="J217" t="n">
-        <v>3.674609621511272</v>
+        <v>1.060607088291662</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129744</v>
+        <v>129750</v>
       </c>
       <c r="B218" t="n">
-        <v>0.037313</v>
+        <v>0.0216235</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -10100,30 +10045,30 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>0.06864450336153091</v>
+        <v>0.05161121416311329</v>
       </c>
       <c r="F218" t="n">
-        <v>2.598375</v>
+        <v>2.7035125</v>
       </c>
       <c r="G218" t="n">
-        <v>2.598376774155647</v>
+        <v>2.703512319891357</v>
       </c>
       <c r="H218" t="n">
-        <v>1.774155646838693e-06</v>
+        <v>-1.80108643110799e-07</v>
       </c>
       <c r="I218" t="n">
-        <v>6.827943029157428e-05</v>
+        <v>6.662023686252569e-06</v>
       </c>
       <c r="J218" t="n">
-        <v>6.827943029157428e-05</v>
+        <v>-6.662023686252569e-06</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129744</v>
+        <v>129750</v>
       </c>
       <c r="B219" t="n">
-        <v>0.037313</v>
+        <v>0.0216235</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -10136,30 +10081,30 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>0.06864450336153091</v>
+        <v>0.05161121416311329</v>
       </c>
       <c r="F219" t="n">
-        <v>2.715150068499876</v>
+        <v>2.817383744798192</v>
       </c>
       <c r="G219" t="n">
-        <v>2.673577863216871</v>
+        <v>2.77229971846656</v>
       </c>
       <c r="H219" t="n">
-        <v>-0.04157220528300476</v>
+        <v>-0.04508402633163122</v>
       </c>
       <c r="I219" t="n">
-        <v>1.53111998358063</v>
+        <v>1.600208931952242</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.53111998358063</v>
+        <v>-1.600208931952242</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129744</v>
+        <v>129750</v>
       </c>
       <c r="B220" t="n">
-        <v>0.037313</v>
+        <v>0.0216235</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -10172,30 +10117,30 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>0.06864450336153091</v>
+        <v>0.05161121416311329</v>
       </c>
       <c r="F220" t="n">
-        <v>2.829431944444444</v>
+        <v>2.8942375</v>
       </c>
       <c r="G220" t="n">
-        <v>2.818153575813073</v>
+        <v>2.881209823510938</v>
       </c>
       <c r="H220" t="n">
-        <v>-0.01127836863137111</v>
+        <v>-0.01302767648906222</v>
       </c>
       <c r="I220" t="n">
-        <v>0.3986089382187138</v>
+        <v>0.45012465248834</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.3986089382187138</v>
+        <v>-0.45012465248834</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129744</v>
+        <v>129750</v>
       </c>
       <c r="B221" t="n">
-        <v>0.037313</v>
+        <v>0.0216235</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -10208,30 +10153,30 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>0.07463470711230444</v>
+        <v>0.05498242253594483</v>
       </c>
       <c r="F221" t="n">
-        <v>2.598375</v>
+        <v>2.7035125</v>
       </c>
       <c r="G221" t="n">
-        <v>2.598374770824879</v>
+        <v>2.70351262587046</v>
       </c>
       <c r="H221" t="n">
-        <v>-2.291751206584536e-07</v>
+        <v>1.258704602769001e-07</v>
       </c>
       <c r="I221" t="n">
-        <v>8.819940180245483e-06</v>
+        <v>4.655812032565045e-06</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.819940180245483e-06</v>
+        <v>4.655812032565045e-06</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129744</v>
+        <v>129750</v>
       </c>
       <c r="B222" t="n">
-        <v>0.037313</v>
+        <v>0.0216235</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -10244,30 +10189,30 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>0.07463470711230444</v>
+        <v>0.05498242253594483</v>
       </c>
       <c r="F222" t="n">
-        <v>2.715150068499876</v>
+        <v>2.817383744798192</v>
       </c>
       <c r="G222" t="n">
-        <v>2.673311859129013</v>
+        <v>2.77215149840852</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.04183820937086224</v>
+        <v>-0.04523224638967127</v>
       </c>
       <c r="I222" t="n">
-        <v>1.540917014357807</v>
+        <v>1.605469843189971</v>
       </c>
       <c r="J222" t="n">
-        <v>-1.540917014357807</v>
+        <v>-1.605469843189971</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129744</v>
+        <v>129750</v>
       </c>
       <c r="B223" t="n">
-        <v>0.037313</v>
+        <v>0.0216235</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -10280,30 +10225,30 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>0.07463470711230444</v>
+        <v>0.05498242253594483</v>
       </c>
       <c r="F223" t="n">
-        <v>2.829431944444444</v>
+        <v>2.8942375</v>
       </c>
       <c r="G223" t="n">
-        <v>2.817931967533389</v>
+        <v>2.881111177107808</v>
       </c>
       <c r="H223" t="n">
-        <v>-0.01149997691105487</v>
+        <v>-0.01312632289219229</v>
       </c>
       <c r="I223" t="n">
-        <v>0.40644119161922</v>
+        <v>0.4535330252680468</v>
       </c>
       <c r="J223" t="n">
-        <v>-0.40644119161922</v>
+        <v>-0.4535330252680468</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129744</v>
+        <v>129750</v>
       </c>
       <c r="B224" t="n">
-        <v>0.037313</v>
+        <v>0.0216235</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -10317,27 +10262,27 @@
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="n">
-        <v>2.598375</v>
+        <v>2.7035125</v>
       </c>
       <c r="G224" t="n">
-        <v>2.815341205822899</v>
+        <v>2.884567384465444</v>
       </c>
       <c r="H224" t="n">
-        <v>0.2169662058228994</v>
+        <v>0.1810548844654436</v>
       </c>
       <c r="I224" t="n">
-        <v>8.350072865652548</v>
+        <v>6.697024129366652</v>
       </c>
       <c r="J224" t="n">
-        <v>8.350072865652548</v>
+        <v>6.697024129366652</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129744</v>
+        <v>129750</v>
       </c>
       <c r="B225" t="n">
-        <v>0.037313</v>
+        <v>0.0216235</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -10351,27 +10296,27 @@
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="n">
-        <v>2.715150068499876</v>
+        <v>2.817383744798192</v>
       </c>
       <c r="G225" t="n">
-        <v>2.824075737069516</v>
+        <v>2.889593194814664</v>
       </c>
       <c r="H225" t="n">
-        <v>0.1089256685696407</v>
+        <v>0.0722094500164725</v>
       </c>
       <c r="I225" t="n">
-        <v>4.011773412945175</v>
+        <v>2.562996615203544</v>
       </c>
       <c r="J225" t="n">
-        <v>4.011773412945175</v>
+        <v>2.562996615203544</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129744</v>
+        <v>129750</v>
       </c>
       <c r="B226" t="n">
-        <v>0.037313</v>
+        <v>0.0216235</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -10385,27 +10330,27 @@
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="n">
-        <v>2.829431944444444</v>
+        <v>2.8942375</v>
       </c>
       <c r="G226" t="n">
-        <v>2.85944110020561</v>
+        <v>2.910018632748759</v>
       </c>
       <c r="H226" t="n">
-        <v>0.03000915576116636</v>
+        <v>0.0157811327487587</v>
       </c>
       <c r="I226" t="n">
-        <v>1.060607088291662</v>
+        <v>0.5452604614776325</v>
       </c>
       <c r="J226" t="n">
-        <v>1.060607088291662</v>
+        <v>0.5452604614776325</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129750</v>
+        <v>129817</v>
       </c>
       <c r="B227" t="n">
-        <v>0.0216235</v>
+        <v>0.0147115</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -10418,30 +10363,30 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>0.05161121416311337</v>
+        <v>0.02397019273512198</v>
       </c>
       <c r="F227" t="n">
-        <v>2.7035125</v>
+        <v>2.659425</v>
       </c>
       <c r="G227" t="n">
-        <v>2.703512319891357</v>
+        <v>2.659424564319452</v>
       </c>
       <c r="H227" t="n">
-        <v>-1.801086426667098e-07</v>
+        <v>-4.35680548527273e-07</v>
       </c>
       <c r="I227" t="n">
-        <v>6.66202366982619e-06</v>
+        <v>1.638250932164934e-05</v>
       </c>
       <c r="J227" t="n">
-        <v>-6.66202366982619e-06</v>
+        <v>-1.638250932164934e-05</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129750</v>
+        <v>129817</v>
       </c>
       <c r="B228" t="n">
-        <v>0.0216235</v>
+        <v>0.0147115</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -10454,30 +10399,30 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>0.05161121416311337</v>
+        <v>0.02397019273512198</v>
       </c>
       <c r="F228" t="n">
-        <v>2.817383744798192</v>
+        <v>2.836889861687792</v>
       </c>
       <c r="G228" t="n">
-        <v>2.772299718466561</v>
+        <v>2.784915451923733</v>
       </c>
       <c r="H228" t="n">
-        <v>-0.04508402633163078</v>
+        <v>-0.05197440976405909</v>
       </c>
       <c r="I228" t="n">
-        <v>1.600208931952226</v>
+        <v>1.832091208967034</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.600208931952226</v>
+        <v>-1.832091208967034</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129750</v>
+        <v>129817</v>
       </c>
       <c r="B229" t="n">
-        <v>0.0216235</v>
+        <v>0.0147115</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -10490,30 +10435,30 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>0.05161121416311337</v>
+        <v>0.02397019273512198</v>
       </c>
       <c r="F229" t="n">
-        <v>2.8942375</v>
+        <v>2.949019444444444</v>
       </c>
       <c r="G229" t="n">
-        <v>2.881209823510938</v>
+        <v>2.906890192287715</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.01302767648906222</v>
+        <v>-0.04212925215672891</v>
       </c>
       <c r="I229" t="n">
-        <v>0.45012465248834</v>
+        <v>1.428585092448093</v>
       </c>
       <c r="J229" t="n">
-        <v>-0.45012465248834</v>
+        <v>-1.428585092448093</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129750</v>
+        <v>129817</v>
       </c>
       <c r="B230" t="n">
-        <v>0.0216235</v>
+        <v>0.0147115</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -10526,30 +10471,30 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>0.05498242253594483</v>
+        <v>0.02617032869151523</v>
       </c>
       <c r="F230" t="n">
-        <v>2.7035125</v>
+        <v>2.659425</v>
       </c>
       <c r="G230" t="n">
-        <v>2.70351262587046</v>
+        <v>2.659424818259136</v>
       </c>
       <c r="H230" t="n">
-        <v>1.258704602769001e-07</v>
+        <v>-1.817408641358043e-07</v>
       </c>
       <c r="I230" t="n">
-        <v>4.655812032565045e-06</v>
+        <v>6.833840553345338e-06</v>
       </c>
       <c r="J230" t="n">
-        <v>4.655812032565045e-06</v>
+        <v>-6.833840553345338e-06</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129750</v>
+        <v>129817</v>
       </c>
       <c r="B231" t="n">
-        <v>0.0216235</v>
+        <v>0.0147115</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -10562,30 +10507,30 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>0.05498242253594483</v>
+        <v>0.02617032869151523</v>
       </c>
       <c r="F231" t="n">
-        <v>2.817383744798192</v>
+        <v>2.836889861687792</v>
       </c>
       <c r="G231" t="n">
-        <v>2.77215149840852</v>
+        <v>2.784735928838403</v>
       </c>
       <c r="H231" t="n">
-        <v>-0.04523224638967127</v>
+        <v>-0.05215393284938941</v>
       </c>
       <c r="I231" t="n">
-        <v>1.605469843189971</v>
+        <v>1.838419374461041</v>
       </c>
       <c r="J231" t="n">
-        <v>-1.605469843189971</v>
+        <v>-1.838419374461041</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129750</v>
+        <v>129817</v>
       </c>
       <c r="B232" t="n">
-        <v>0.0216235</v>
+        <v>0.0147115</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -10598,30 +10543,30 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>0.05498242253594483</v>
+        <v>0.02617032869151523</v>
       </c>
       <c r="F232" t="n">
-        <v>2.8942375</v>
+        <v>2.949019444444444</v>
       </c>
       <c r="G232" t="n">
-        <v>2.881111177107808</v>
+        <v>2.906818484224753</v>
       </c>
       <c r="H232" t="n">
-        <v>-0.01312632289219229</v>
+        <v>-0.04220096021969155</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4535330252680468</v>
+        <v>1.431016682483816</v>
       </c>
       <c r="J232" t="n">
-        <v>-0.4535330252680468</v>
+        <v>-1.431016682483816</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129750</v>
+        <v>129817</v>
       </c>
       <c r="B233" t="n">
-        <v>0.0216235</v>
+        <v>0.0147115</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -10635,27 +10580,27 @@
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>2.7035125</v>
+        <v>2.659425</v>
       </c>
       <c r="G233" t="n">
-        <v>2.884567384465444</v>
+        <v>2.915069701404654</v>
       </c>
       <c r="H233" t="n">
-        <v>0.1810548844654436</v>
+        <v>0.2556447014046541</v>
       </c>
       <c r="I233" t="n">
-        <v>6.697024129366652</v>
+        <v>9.612781011107819</v>
       </c>
       <c r="J233" t="n">
-        <v>6.697024129366652</v>
+        <v>9.612781011107819</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129750</v>
+        <v>129817</v>
       </c>
       <c r="B234" t="n">
-        <v>0.0216235</v>
+        <v>0.0147115</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -10669,27 +10614,27 @@
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2.817383744798192</v>
+        <v>2.836889861687792</v>
       </c>
       <c r="G234" t="n">
-        <v>2.889593194814664</v>
+        <v>2.918478536082983</v>
       </c>
       <c r="H234" t="n">
-        <v>0.0722094500164725</v>
+        <v>0.08158867439519035</v>
       </c>
       <c r="I234" t="n">
-        <v>2.562996615203544</v>
+        <v>2.875990199586021</v>
       </c>
       <c r="J234" t="n">
-        <v>2.562996615203544</v>
+        <v>2.875990199586021</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129750</v>
+        <v>129817</v>
       </c>
       <c r="B235" t="n">
-        <v>0.0216235</v>
+        <v>0.0147115</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -10703,27 +10648,27 @@
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2.8942375</v>
+        <v>2.949019444444444</v>
       </c>
       <c r="G235" t="n">
-        <v>2.910018632748759</v>
+        <v>2.932354415579111</v>
       </c>
       <c r="H235" t="n">
-        <v>0.0157811327487587</v>
+        <v>-0.01666502886533339</v>
       </c>
       <c r="I235" t="n">
-        <v>0.5452604614776325</v>
+        <v>0.5651040686329845</v>
       </c>
       <c r="J235" t="n">
-        <v>0.5452604614776325</v>
+        <v>-0.5651040686329845</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129817</v>
+        <v>129822</v>
       </c>
       <c r="B236" t="n">
-        <v>0.0147115</v>
+        <v>0.06934715385806561</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -10736,30 +10681,30 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>0.02397019273512207</v>
+        <v>0.09122256426320441</v>
       </c>
       <c r="F236" t="n">
-        <v>2.659425</v>
+        <v>2.4153</v>
       </c>
       <c r="G236" t="n">
-        <v>2.659424564319452</v>
+        <v>2.41530191659616</v>
       </c>
       <c r="H236" t="n">
-        <v>-4.356805480831838e-07</v>
+        <v>1.91659615955686e-06</v>
       </c>
       <c r="I236" t="n">
-        <v>1.638250930495065e-05</v>
+        <v>7.935230238715109e-05</v>
       </c>
       <c r="J236" t="n">
-        <v>-1.638250930495065e-05</v>
+        <v>7.935230238715109e-05</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129817</v>
+        <v>129822</v>
       </c>
       <c r="B237" t="n">
-        <v>0.0147115</v>
+        <v>0.06934715385806561</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -10772,30 +10717,30 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>0.02397019273512207</v>
+        <v>0.09122256426320441</v>
       </c>
       <c r="F237" t="n">
-        <v>2.836889861687792</v>
+        <v>2.605161460353123</v>
       </c>
       <c r="G237" t="n">
-        <v>2.784915451923733</v>
+        <v>2.500492926972977</v>
       </c>
       <c r="H237" t="n">
-        <v>-0.05197440976405909</v>
+        <v>-0.1046685333801456</v>
       </c>
       <c r="I237" t="n">
-        <v>1.832091208967034</v>
+        <v>4.017736903184421</v>
       </c>
       <c r="J237" t="n">
-        <v>-1.832091208967034</v>
+        <v>-4.017736903184421</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129817</v>
+        <v>129822</v>
       </c>
       <c r="B238" t="n">
-        <v>0.0147115</v>
+        <v>0.06934715385806561</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -10808,30 +10753,30 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>0.02397019273512207</v>
+        <v>0.09122256426320441</v>
       </c>
       <c r="F238" t="n">
-        <v>2.949019444444444</v>
+        <v>2.830407291666667</v>
       </c>
       <c r="G238" t="n">
-        <v>2.906890192287715</v>
+        <v>2.698542774348506</v>
       </c>
       <c r="H238" t="n">
-        <v>-0.04212925215672891</v>
+        <v>-0.1318645173181605</v>
       </c>
       <c r="I238" t="n">
-        <v>1.428585092448093</v>
+        <v>4.658853081194295</v>
       </c>
       <c r="J238" t="n">
-        <v>-1.428585092448093</v>
+        <v>-4.658853081194295</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129817</v>
+        <v>129822</v>
       </c>
       <c r="B239" t="n">
-        <v>0.0147115</v>
+        <v>0.06934715385806561</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -10844,30 +10789,30 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>0.02617032869151523</v>
+        <v>0.1028391763575825</v>
       </c>
       <c r="F239" t="n">
-        <v>2.659425</v>
+        <v>2.4153</v>
       </c>
       <c r="G239" t="n">
-        <v>2.659424818259136</v>
+        <v>2.415300166837147</v>
       </c>
       <c r="H239" t="n">
-        <v>-1.817408641358043e-07</v>
+        <v>1.668371467644647e-07</v>
       </c>
       <c r="I239" t="n">
-        <v>6.833840553345338e-06</v>
+        <v>6.907512390364124e-06</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.833840553345338e-06</v>
+        <v>6.907512390364124e-06</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129817</v>
+        <v>129822</v>
       </c>
       <c r="B240" t="n">
-        <v>0.0147115</v>
+        <v>0.06934715385806561</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -10880,30 +10825,30 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>0.02617032869151523</v>
+        <v>0.1028391763575825</v>
       </c>
       <c r="F240" t="n">
-        <v>2.836889861687792</v>
+        <v>2.605161460353123</v>
       </c>
       <c r="G240" t="n">
-        <v>2.784735928838403</v>
+        <v>2.499995119429789</v>
       </c>
       <c r="H240" t="n">
-        <v>-0.05215393284938941</v>
+        <v>-0.1051663409233341</v>
       </c>
       <c r="I240" t="n">
-        <v>1.838419374461041</v>
+        <v>4.036845413377145</v>
       </c>
       <c r="J240" t="n">
-        <v>-1.838419374461041</v>
+        <v>-4.036845413377145</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129817</v>
+        <v>129822</v>
       </c>
       <c r="B241" t="n">
-        <v>0.0147115</v>
+        <v>0.06934715385806561</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -10916,30 +10861,30 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>0.02617032869151523</v>
+        <v>0.1028391763575825</v>
       </c>
       <c r="F241" t="n">
-        <v>2.949019444444444</v>
+        <v>2.830407291666667</v>
       </c>
       <c r="G241" t="n">
-        <v>2.906818484224753</v>
+        <v>2.698017302316364</v>
       </c>
       <c r="H241" t="n">
-        <v>-0.04220096021969155</v>
+        <v>-0.1323899893503024</v>
       </c>
       <c r="I241" t="n">
-        <v>1.431016682483816</v>
+        <v>4.677418325627103</v>
       </c>
       <c r="J241" t="n">
-        <v>-1.431016682483816</v>
+        <v>-4.677418325627103</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129817</v>
+        <v>129822</v>
       </c>
       <c r="B242" t="n">
-        <v>0.0147115</v>
+        <v>0.06934715385806561</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -10953,27 +10898,27 @@
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>2.659425</v>
+        <v>2.4153</v>
       </c>
       <c r="G242" t="n">
-        <v>2.915069701404654</v>
+        <v>2.674048926925646</v>
       </c>
       <c r="H242" t="n">
-        <v>0.2556447014046541</v>
+        <v>0.2587489269256453</v>
       </c>
       <c r="I242" t="n">
-        <v>9.612781011107819</v>
+        <v>10.71291048423158</v>
       </c>
       <c r="J242" t="n">
-        <v>9.612781011107819</v>
+        <v>10.71291048423158</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129817</v>
+        <v>129822</v>
       </c>
       <c r="B243" t="n">
-        <v>0.0147115</v>
+        <v>0.06934715385806561</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -10987,27 +10932,27 @@
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2.836889861687792</v>
+        <v>2.605161460353123</v>
       </c>
       <c r="G243" t="n">
-        <v>2.918478536082983</v>
+        <v>2.690534059044964</v>
       </c>
       <c r="H243" t="n">
-        <v>0.08158867439519035</v>
+        <v>0.08537259869184055</v>
       </c>
       <c r="I243" t="n">
-        <v>2.875990199586021</v>
+        <v>3.277055951851388</v>
       </c>
       <c r="J243" t="n">
-        <v>2.875990199586021</v>
+        <v>3.277055951851388</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129817</v>
+        <v>129822</v>
       </c>
       <c r="B244" t="n">
-        <v>0.0147115</v>
+        <v>0.06934715385806561</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -11021,27 +10966,27 @@
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>2.949019444444444</v>
+        <v>2.830407291666667</v>
       </c>
       <c r="G244" t="n">
-        <v>2.932354415579111</v>
+        <v>2.756728144269908</v>
       </c>
       <c r="H244" t="n">
-        <v>-0.01666502886533339</v>
+        <v>-0.07367914739675907</v>
       </c>
       <c r="I244" t="n">
-        <v>0.5651040686329845</v>
+        <v>2.603128801062888</v>
       </c>
       <c r="J244" t="n">
-        <v>-0.5651040686329845</v>
+        <v>-2.603128801062888</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129822</v>
+        <v>129845</v>
       </c>
       <c r="B245" t="n">
-        <v>0.06934715385806561</v>
+        <v>0.07459951122802215</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -11054,30 +10999,30 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>0.09122256426320441</v>
+        <v>0.08540130311845651</v>
       </c>
       <c r="F245" t="n">
-        <v>2.4153</v>
+        <v>2.357925</v>
       </c>
       <c r="G245" t="n">
-        <v>2.415301916596159</v>
+        <v>2.357924735953094</v>
       </c>
       <c r="H245" t="n">
-        <v>1.916596159112771e-06</v>
+        <v>-2.640469061176987e-07</v>
       </c>
       <c r="I245" t="n">
-        <v>7.935230236876458e-05</v>
+        <v>1.119827416553532e-05</v>
       </c>
       <c r="J245" t="n">
-        <v>7.935230236876458e-05</v>
+        <v>-1.119827416553532e-05</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129822</v>
+        <v>129845</v>
       </c>
       <c r="B246" t="n">
-        <v>0.06934715385806561</v>
+        <v>0.07459951122802215</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -11090,30 +11035,30 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>0.09122256426320441</v>
+        <v>0.08540130311845651</v>
       </c>
       <c r="F246" t="n">
-        <v>2.605161460353123</v>
+        <v>2.533756797828872</v>
       </c>
       <c r="G246" t="n">
-        <v>2.500492926972977</v>
+        <v>2.455058425014661</v>
       </c>
       <c r="H246" t="n">
-        <v>-0.104668533380146</v>
+        <v>-0.07869837281421121</v>
       </c>
       <c r="I246" t="n">
-        <v>4.017736903184438</v>
+        <v>3.105995527338944</v>
       </c>
       <c r="J246" t="n">
-        <v>-4.017736903184438</v>
+        <v>-3.105995527338944</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129822</v>
+        <v>129845</v>
       </c>
       <c r="B247" t="n">
-        <v>0.06934715385806561</v>
+        <v>0.07459951122802215</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -11126,30 +11071,30 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>0.09122256426320441</v>
+        <v>0.08540130311845651</v>
       </c>
       <c r="F247" t="n">
-        <v>2.830407291666667</v>
+        <v>2.714411458333333</v>
       </c>
       <c r="G247" t="n">
-        <v>2.698542774348506</v>
+        <v>2.67557502395226</v>
       </c>
       <c r="H247" t="n">
-        <v>-0.1318645173181605</v>
+        <v>-0.0388364343810732</v>
       </c>
       <c r="I247" t="n">
-        <v>4.658853081194295</v>
+        <v>1.430749721522287</v>
       </c>
       <c r="J247" t="n">
-        <v>-4.658853081194295</v>
+        <v>-1.430749721522287</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129822</v>
+        <v>129845</v>
       </c>
       <c r="B248" t="n">
-        <v>0.06934715385806561</v>
+        <v>0.07459951122802215</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -11162,30 +11107,30 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>0.1028391763575825</v>
+        <v>0.09786992411855877</v>
       </c>
       <c r="F248" t="n">
-        <v>2.4153</v>
+        <v>2.357925</v>
       </c>
       <c r="G248" t="n">
-        <v>2.415300166837147</v>
+        <v>2.35792703738119</v>
       </c>
       <c r="H248" t="n">
-        <v>1.668371467644647e-07</v>
+        <v>2.037381190422849e-06</v>
       </c>
       <c r="I248" t="n">
-        <v>6.907512390364124e-06</v>
+        <v>8.640568255660588e-05</v>
       </c>
       <c r="J248" t="n">
-        <v>6.907512390364124e-06</v>
+        <v>8.640568255660588e-05</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129822</v>
+        <v>129845</v>
       </c>
       <c r="B249" t="n">
-        <v>0.06934715385806561</v>
+        <v>0.07459951122802215</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -11198,30 +11143,30 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>0.1028391763575825</v>
+        <v>0.09786992411855877</v>
       </c>
       <c r="F249" t="n">
-        <v>2.605161460353123</v>
+        <v>2.533756797828872</v>
       </c>
       <c r="G249" t="n">
-        <v>2.499995119429789</v>
+        <v>2.454430214872558</v>
       </c>
       <c r="H249" t="n">
-        <v>-0.1051663409233341</v>
+        <v>-0.0793265829563139</v>
       </c>
       <c r="I249" t="n">
-        <v>4.036845413377145</v>
+        <v>3.130789151677356</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.036845413377145</v>
+        <v>-3.130789151677356</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129822</v>
+        <v>129845</v>
       </c>
       <c r="B250" t="n">
-        <v>0.06934715385806561</v>
+        <v>0.07459951122802215</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -11234,30 +11179,30 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>0.1028391763575825</v>
+        <v>0.09786992411855877</v>
       </c>
       <c r="F250" t="n">
-        <v>2.830407291666667</v>
+        <v>2.714411458333333</v>
       </c>
       <c r="G250" t="n">
-        <v>2.698017302316364</v>
+        <v>2.674928414343358</v>
       </c>
       <c r="H250" t="n">
-        <v>-0.1323899893503024</v>
+        <v>-0.03948304398997537</v>
       </c>
       <c r="I250" t="n">
-        <v>4.677418325627103</v>
+        <v>1.454571077231535</v>
       </c>
       <c r="J250" t="n">
-        <v>-4.677418325627103</v>
+        <v>-1.454571077231535</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129822</v>
+        <v>129845</v>
       </c>
       <c r="B251" t="n">
-        <v>0.06934715385806561</v>
+        <v>0.07459951122802215</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -11271,27 +11216,27 @@
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="n">
-        <v>2.4153</v>
+        <v>2.357925</v>
       </c>
       <c r="G251" t="n">
-        <v>2.674048926925646</v>
+        <v>2.650889553310626</v>
       </c>
       <c r="H251" t="n">
-        <v>0.2587489269256453</v>
+        <v>0.2929645533106262</v>
       </c>
       <c r="I251" t="n">
-        <v>10.71291048423158</v>
+        <v>12.42467649779472</v>
       </c>
       <c r="J251" t="n">
-        <v>10.71291048423158</v>
+        <v>12.42467649779472</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129822</v>
+        <v>129845</v>
       </c>
       <c r="B252" t="n">
-        <v>0.06934715385806561</v>
+        <v>0.07459951122802215</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -11305,27 +11250,27 @@
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>2.605161460353123</v>
+        <v>2.533756797828872</v>
       </c>
       <c r="G252" t="n">
-        <v>2.690534059044964</v>
+        <v>2.668670059912487</v>
       </c>
       <c r="H252" t="n">
-        <v>0.08537259869184055</v>
+        <v>0.1349132620836149</v>
       </c>
       <c r="I252" t="n">
-        <v>3.277055951851388</v>
+        <v>5.324633453345621</v>
       </c>
       <c r="J252" t="n">
-        <v>3.277055951851388</v>
+        <v>5.324633453345621</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129822</v>
+        <v>129845</v>
       </c>
       <c r="B253" t="n">
-        <v>0.06934715385806561</v>
+        <v>0.07459951122802215</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -11339,27 +11284,27 @@
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="n">
-        <v>2.830407291666667</v>
+        <v>2.714411458333333</v>
       </c>
       <c r="G253" t="n">
-        <v>2.756728144269908</v>
+        <v>2.739961680323716</v>
       </c>
       <c r="H253" t="n">
-        <v>-0.07367914739675907</v>
+        <v>0.02555022199038248</v>
       </c>
       <c r="I253" t="n">
-        <v>2.603128801062888</v>
+        <v>0.9412803616026028</v>
       </c>
       <c r="J253" t="n">
-        <v>-2.603128801062888</v>
+        <v>0.9412803616026028</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>129845</v>
+        <v>129897</v>
       </c>
       <c r="B254" t="n">
-        <v>0.07459951122802215</v>
+        <v>0.2364854161234349</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -11372,30 +11317,30 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>0.08540130311845624</v>
+        <v>0.05449563116943758</v>
       </c>
       <c r="F254" t="n">
-        <v>2.357925</v>
+        <v>1.2605</v>
       </c>
       <c r="G254" t="n">
-        <v>2.357924735953093</v>
+        <v>1.26050312744451</v>
       </c>
       <c r="H254" t="n">
-        <v>-2.640469065617879e-07</v>
+        <v>3.127444509587463e-06</v>
       </c>
       <c r="I254" t="n">
-        <v>1.119827418436922e-05</v>
+        <v>0.000248111424798688</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.119827418436922e-05</v>
+        <v>0.000248111424798688</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>129845</v>
+        <v>129897</v>
       </c>
       <c r="B255" t="n">
-        <v>0.07459951122802215</v>
+        <v>0.2364854161234349</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -11408,30 +11353,30 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>0.08540130311845624</v>
+        <v>0.05449563116943758</v>
       </c>
       <c r="F255" t="n">
-        <v>2.533756797828872</v>
+        <v>1.6629125</v>
       </c>
       <c r="G255" t="n">
-        <v>2.45505842501466</v>
+        <v>1.504178206199788</v>
       </c>
       <c r="H255" t="n">
-        <v>-0.07869837281421166</v>
+        <v>-0.1587342938002119</v>
       </c>
       <c r="I255" t="n">
-        <v>3.105995527338962</v>
+        <v>9.545558999659445</v>
       </c>
       <c r="J255" t="n">
-        <v>-3.105995527338962</v>
+        <v>-9.545558999659445</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>129845</v>
+        <v>129897</v>
       </c>
       <c r="B256" t="n">
-        <v>0.07459951122802215</v>
+        <v>0.2364854161234349</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -11444,30 +11389,30 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>0.08540130311845624</v>
+        <v>0.05449563116943758</v>
       </c>
       <c r="F256" t="n">
-        <v>2.714411458333333</v>
+        <v>2.2371125</v>
       </c>
       <c r="G256" t="n">
-        <v>2.67557502395226</v>
+        <v>2.085146426773932</v>
       </c>
       <c r="H256" t="n">
-        <v>-0.03883643438107276</v>
+        <v>-0.1519660732260681</v>
       </c>
       <c r="I256" t="n">
-        <v>1.43074972152227</v>
+        <v>6.792956242748996</v>
       </c>
       <c r="J256" t="n">
-        <v>-1.43074972152227</v>
+        <v>-6.792956242748996</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>129845</v>
+        <v>129897</v>
       </c>
       <c r="B257" t="n">
-        <v>0.07459951122802215</v>
+        <v>0.2364854161234349</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -11480,30 +11425,30 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>0.09786992411855877</v>
+        <v>0.09717239253050693</v>
       </c>
       <c r="F257" t="n">
-        <v>2.357925</v>
+        <v>1.2605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.35792703738119</v>
+        <v>1.260505061716089</v>
       </c>
       <c r="H257" t="n">
-        <v>2.037381190422849e-06</v>
+        <v>5.061716088938795e-06</v>
       </c>
       <c r="I257" t="n">
-        <v>8.640568255660588e-05</v>
+        <v>0.0004015641482696386</v>
       </c>
       <c r="J257" t="n">
-        <v>8.640568255660588e-05</v>
+        <v>0.0004015641482696386</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>129845</v>
+        <v>129897</v>
       </c>
       <c r="B258" t="n">
-        <v>0.07459951122802215</v>
+        <v>0.2364854161234349</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -11516,30 +11461,30 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>0.09786992411855877</v>
+        <v>0.09717239253050693</v>
       </c>
       <c r="F258" t="n">
-        <v>2.533756797828872</v>
+        <v>1.6629125</v>
       </c>
       <c r="G258" t="n">
-        <v>2.454430214872558</v>
+        <v>1.498279370583388</v>
       </c>
       <c r="H258" t="n">
-        <v>-0.0793265829563139</v>
+        <v>-0.1646331294166119</v>
       </c>
       <c r="I258" t="n">
-        <v>3.130789151677356</v>
+        <v>9.900288164086318</v>
       </c>
       <c r="J258" t="n">
-        <v>-3.130789151677356</v>
+        <v>-9.900288164086318</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>129845</v>
+        <v>129897</v>
       </c>
       <c r="B259" t="n">
-        <v>0.07459951122802215</v>
+        <v>0.2364854161234349</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -11552,30 +11497,30 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>0.09786992411855877</v>
+        <v>0.09717239253050693</v>
       </c>
       <c r="F259" t="n">
-        <v>2.714411458333333</v>
+        <v>2.2371125</v>
       </c>
       <c r="G259" t="n">
-        <v>2.674928414343358</v>
+        <v>2.078608462836351</v>
       </c>
       <c r="H259" t="n">
-        <v>-0.03948304398997537</v>
+        <v>-0.1585040371636488</v>
       </c>
       <c r="I259" t="n">
-        <v>1.454571077231535</v>
+        <v>7.085206361488249</v>
       </c>
       <c r="J259" t="n">
-        <v>-1.454571077231535</v>
+        <v>-7.085206361488249</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>129845</v>
+        <v>129897</v>
       </c>
       <c r="B260" t="n">
-        <v>0.07459951122802215</v>
+        <v>0.2364854161234349</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -11589,27 +11534,27 @@
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="n">
-        <v>2.357925</v>
+        <v>1.2605</v>
       </c>
       <c r="G260" t="n">
-        <v>2.650889553310626</v>
+        <v>1.938494337735358</v>
       </c>
       <c r="H260" t="n">
-        <v>0.2929645533106262</v>
+        <v>0.6779943377353583</v>
       </c>
       <c r="I260" t="n">
-        <v>12.42467649779472</v>
+        <v>53.78773008610538</v>
       </c>
       <c r="J260" t="n">
-        <v>12.42467649779472</v>
+        <v>53.78773008610538</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>129845</v>
+        <v>129897</v>
       </c>
       <c r="B261" t="n">
-        <v>0.07459951122802215</v>
+        <v>0.2364854161234349</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -11623,27 +11568,27 @@
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="n">
-        <v>2.533756797828872</v>
+        <v>1.6629125</v>
       </c>
       <c r="G261" t="n">
-        <v>2.668670059912487</v>
+        <v>2.000834454467218</v>
       </c>
       <c r="H261" t="n">
-        <v>0.1349132620836149</v>
+        <v>0.3379219544672183</v>
       </c>
       <c r="I261" t="n">
-        <v>5.324633453345621</v>
+        <v>20.3210905244394</v>
       </c>
       <c r="J261" t="n">
-        <v>5.324633453345621</v>
+        <v>20.3210905244394</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>129845</v>
+        <v>129897</v>
       </c>
       <c r="B262" t="n">
-        <v>0.07459951122802215</v>
+        <v>0.2364854161234349</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -11657,27 +11602,27 @@
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="n">
-        <v>2.714411458333333</v>
+        <v>2.2371125</v>
       </c>
       <c r="G262" t="n">
-        <v>2.739961680323716</v>
+        <v>2.235633685339125</v>
       </c>
       <c r="H262" t="n">
-        <v>0.02555022199038248</v>
+        <v>-0.001478814660875738</v>
       </c>
       <c r="I262" t="n">
-        <v>0.9412803616026028</v>
+        <v>0.06610372347728323</v>
       </c>
       <c r="J262" t="n">
-        <v>0.9412803616026028</v>
+        <v>-0.06610372347728323</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>129897</v>
+        <v>129913</v>
       </c>
       <c r="B263" t="n">
-        <v>0.2364854161234349</v>
+        <v>0.1017106544373163</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -11690,30 +11635,30 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>0.05449563116943758</v>
+        <v>0.1042262168583755</v>
       </c>
       <c r="F263" t="n">
-        <v>1.2605</v>
+        <v>2.2462375</v>
       </c>
       <c r="G263" t="n">
-        <v>1.26050312744451</v>
+        <v>2.246240299890795</v>
       </c>
       <c r="H263" t="n">
-        <v>3.127444510253596e-06</v>
+        <v>2.799890794324966e-06</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0002481114248515348</v>
+        <v>0.0001246480300647178</v>
       </c>
       <c r="J263" t="n">
-        <v>0.0002481114248515348</v>
+        <v>0.0001246480300647178</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>129897</v>
+        <v>129913</v>
       </c>
       <c r="B264" t="n">
-        <v>0.2364854161234349</v>
+        <v>0.1017106544373163</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -11726,30 +11671,30 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>0.05449563116943758</v>
+        <v>0.1042262168583755</v>
       </c>
       <c r="F264" t="n">
-        <v>1.6629125</v>
+        <v>2.426137507705096</v>
       </c>
       <c r="G264" t="n">
-        <v>1.504178206199789</v>
+        <v>2.341365007545882</v>
       </c>
       <c r="H264" t="n">
-        <v>-0.1587342938002114</v>
+        <v>-0.08477250015921456</v>
       </c>
       <c r="I264" t="n">
-        <v>9.545558999659418</v>
+        <v>3.494134190250477</v>
       </c>
       <c r="J264" t="n">
-        <v>-9.545558999659418</v>
+        <v>-3.494134190250477</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>129897</v>
+        <v>129913</v>
       </c>
       <c r="B265" t="n">
-        <v>0.2364854161234349</v>
+        <v>0.1017106544373163</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -11762,30 +11707,30 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>0.05449563116943758</v>
+        <v>0.1042262168583755</v>
       </c>
       <c r="F265" t="n">
-        <v>2.2371125</v>
+        <v>2.651822916666667</v>
       </c>
       <c r="G265" t="n">
-        <v>2.085146426773932</v>
+        <v>2.584498534700781</v>
       </c>
       <c r="H265" t="n">
-        <v>-0.1519660732260681</v>
+        <v>-0.0673243819658853</v>
       </c>
       <c r="I265" t="n">
-        <v>6.792956242748996</v>
+        <v>2.538796295286257</v>
       </c>
       <c r="J265" t="n">
-        <v>-6.792956242748996</v>
+        <v>-2.538796295286257</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>129897</v>
+        <v>129913</v>
       </c>
       <c r="B266" t="n">
-        <v>0.2364854161234349</v>
+        <v>0.1017106544373163</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -11798,30 +11743,30 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>0.09717239253050693</v>
+        <v>0.1218097151510352</v>
       </c>
       <c r="F266" t="n">
-        <v>1.2605</v>
+        <v>2.2462375</v>
       </c>
       <c r="G266" t="n">
-        <v>1.260505061716089</v>
+        <v>2.246239475390706</v>
       </c>
       <c r="H266" t="n">
-        <v>5.061716088938795e-06</v>
+        <v>1.975390705677427e-06</v>
       </c>
       <c r="I266" t="n">
-        <v>0.0004015641482696386</v>
+        <v>8.794220137796767e-05</v>
       </c>
       <c r="J266" t="n">
-        <v>0.0004015641482696386</v>
+        <v>8.794220137796767e-05</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>129897</v>
+        <v>129913</v>
       </c>
       <c r="B267" t="n">
-        <v>0.2364854161234349</v>
+        <v>0.1017106544373163</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -11834,30 +11779,30 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>0.09717239253050693</v>
+        <v>0.1218097151510352</v>
       </c>
       <c r="F267" t="n">
-        <v>1.6629125</v>
+        <v>2.426137507705096</v>
       </c>
       <c r="G267" t="n">
-        <v>1.498279370583388</v>
+        <v>2.340616639292388</v>
       </c>
       <c r="H267" t="n">
-        <v>-0.1646331294166119</v>
+        <v>-0.08552086841270867</v>
       </c>
       <c r="I267" t="n">
-        <v>9.900288164086318</v>
+        <v>3.524980267652</v>
       </c>
       <c r="J267" t="n">
-        <v>-9.900288164086318</v>
+        <v>-3.524980267652</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>129897</v>
+        <v>129913</v>
       </c>
       <c r="B268" t="n">
-        <v>0.2364854161234349</v>
+        <v>0.1017106544373163</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -11870,30 +11815,30 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>0.09717239253050693</v>
+        <v>0.1218097151510352</v>
       </c>
       <c r="F268" t="n">
-        <v>2.2371125</v>
+        <v>2.651822916666667</v>
       </c>
       <c r="G268" t="n">
-        <v>2.078608462836351</v>
+        <v>2.583605966649622</v>
       </c>
       <c r="H268" t="n">
-        <v>-0.1585040371636488</v>
+        <v>-0.06821695001704464</v>
       </c>
       <c r="I268" t="n">
-        <v>7.085206361488249</v>
+        <v>2.572454954978409</v>
       </c>
       <c r="J268" t="n">
-        <v>-7.085206361488249</v>
+        <v>-2.572454954978409</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>129897</v>
+        <v>129913</v>
       </c>
       <c r="B269" t="n">
-        <v>0.2364854161234349</v>
+        <v>0.1017106544373163</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -11907,27 +11852,27 @@
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="n">
-        <v>1.2605</v>
+        <v>2.2462375</v>
       </c>
       <c r="G269" t="n">
-        <v>1.938494337735358</v>
+        <v>2.531382801555054</v>
       </c>
       <c r="H269" t="n">
-        <v>0.6779943377353583</v>
+        <v>0.2851453015550534</v>
       </c>
       <c r="I269" t="n">
-        <v>53.78773008610538</v>
+        <v>12.69435229155659</v>
       </c>
       <c r="J269" t="n">
-        <v>53.78773008610538</v>
+        <v>12.69435229155659</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>129897</v>
+        <v>129913</v>
       </c>
       <c r="B270" t="n">
-        <v>0.2364854161234349</v>
+        <v>0.1017106544373163</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -11941,27 +11886,27 @@
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="n">
-        <v>1.6629125</v>
+        <v>2.426137507705096</v>
       </c>
       <c r="G270" t="n">
-        <v>2.000834454467218</v>
+        <v>2.555970305317487</v>
       </c>
       <c r="H270" t="n">
-        <v>0.3379219544672183</v>
+        <v>0.1298327976123903</v>
       </c>
       <c r="I270" t="n">
-        <v>20.3210905244394</v>
+        <v>5.351419579478009</v>
       </c>
       <c r="J270" t="n">
-        <v>20.3210905244394</v>
+        <v>5.351419579478009</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>129897</v>
+        <v>129913</v>
       </c>
       <c r="B271" t="n">
-        <v>0.2364854161234349</v>
+        <v>0.1017106544373163</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -11975,27 +11920,27 @@
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="n">
-        <v>2.2371125</v>
+        <v>2.651822916666667</v>
       </c>
       <c r="G271" t="n">
-        <v>2.235633685339125</v>
+        <v>2.653771948496829</v>
       </c>
       <c r="H271" t="n">
-        <v>-0.001478814660875738</v>
+        <v>0.001949031830162706</v>
       </c>
       <c r="I271" t="n">
-        <v>0.06610372347728323</v>
+        <v>0.07349781231292146</v>
       </c>
       <c r="J271" t="n">
-        <v>-0.06610372347728323</v>
+        <v>0.07349781231292146</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>129913</v>
+        <v>129914</v>
       </c>
       <c r="B272" t="n">
-        <v>0.1017106544373163</v>
+        <v>0.05877849795017343</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -12008,30 +11953,30 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>0.1042262168583761</v>
+        <v>0.09372630077322562</v>
       </c>
       <c r="F272" t="n">
-        <v>2.2462375</v>
+        <v>2.4985875</v>
       </c>
       <c r="G272" t="n">
-        <v>2.246240299890796</v>
+        <v>2.498588413145333</v>
       </c>
       <c r="H272" t="n">
-        <v>2.799890795657234e-06</v>
+        <v>9.131453331256978e-07</v>
       </c>
       <c r="I272" t="n">
-        <v>0.0001246480301240289</v>
+        <v>3.654646207610091e-05</v>
       </c>
       <c r="J272" t="n">
-        <v>0.0001246480301240289</v>
+        <v>3.654646207610091e-05</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>129913</v>
+        <v>129914</v>
       </c>
       <c r="B273" t="n">
-        <v>0.1017106544373163</v>
+        <v>0.05877849795017343</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -12044,30 +11989,30 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>0.1042262168583761</v>
+        <v>0.09372630077322562</v>
       </c>
       <c r="F273" t="n">
-        <v>2.426137507705096</v>
+        <v>2.578681397618311</v>
       </c>
       <c r="G273" t="n">
-        <v>2.341365007545882</v>
+        <v>2.571365651378545</v>
       </c>
       <c r="H273" t="n">
-        <v>-0.08477250015921411</v>
+        <v>-0.007315746239766163</v>
       </c>
       <c r="I273" t="n">
-        <v>3.494134190250458</v>
+        <v>0.2837010514956613</v>
       </c>
       <c r="J273" t="n">
-        <v>-3.494134190250458</v>
+        <v>-0.2837010514956613</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>129913</v>
+        <v>129914</v>
       </c>
       <c r="B274" t="n">
-        <v>0.1017106544373163</v>
+        <v>0.05877849795017343</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -12080,30 +12025,30 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>0.1042262168583761</v>
+        <v>0.09372630077322562</v>
       </c>
       <c r="F274" t="n">
-        <v>2.651822916666667</v>
+        <v>2.72160625</v>
       </c>
       <c r="G274" t="n">
-        <v>2.584498534700782</v>
+        <v>2.740478812615087</v>
       </c>
       <c r="H274" t="n">
-        <v>-0.06732438196588486</v>
+        <v>0.01887256261508696</v>
       </c>
       <c r="I274" t="n">
-        <v>2.53879629528624</v>
+        <v>0.6934347176446617</v>
       </c>
       <c r="J274" t="n">
-        <v>-2.53879629528624</v>
+        <v>0.6934347176446617</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>129913</v>
+        <v>129914</v>
       </c>
       <c r="B275" t="n">
-        <v>0.1017106544373163</v>
+        <v>0.05877849795017343</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -12116,30 +12061,30 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>0.1218097151510352</v>
+        <v>0.1035325935966191</v>
       </c>
       <c r="F275" t="n">
-        <v>2.2462375</v>
+        <v>2.4985875</v>
       </c>
       <c r="G275" t="n">
-        <v>2.246239475390706</v>
+        <v>2.498587925730706</v>
       </c>
       <c r="H275" t="n">
-        <v>1.975390705677427e-06</v>
+        <v>4.257307053556758e-07</v>
       </c>
       <c r="I275" t="n">
-        <v>8.794220137796767e-05</v>
+        <v>1.703885516739661e-05</v>
       </c>
       <c r="J275" t="n">
-        <v>8.794220137796767e-05</v>
+        <v>1.703885516739661e-05</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>129913</v>
+        <v>129914</v>
       </c>
       <c r="B276" t="n">
-        <v>0.1017106544373163</v>
+        <v>0.05877849795017343</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -12152,30 +12097,30 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>0.1218097151510352</v>
+        <v>0.1035325935966191</v>
       </c>
       <c r="F276" t="n">
-        <v>2.426137507705096</v>
+        <v>2.578681397618311</v>
       </c>
       <c r="G276" t="n">
-        <v>2.340616639292388</v>
+        <v>2.571010615566995</v>
       </c>
       <c r="H276" t="n">
-        <v>-0.08552086841270867</v>
+        <v>-0.007670782051315328</v>
       </c>
       <c r="I276" t="n">
-        <v>3.524980267652</v>
+        <v>0.2974691661560098</v>
       </c>
       <c r="J276" t="n">
-        <v>-3.524980267652</v>
+        <v>-0.2974691661560098</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>129913</v>
+        <v>129914</v>
       </c>
       <c r="B277" t="n">
-        <v>0.1017106544373163</v>
+        <v>0.05877849795017343</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -12188,30 +12133,30 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>0.1218097151510352</v>
+        <v>0.1035325935966191</v>
       </c>
       <c r="F277" t="n">
-        <v>2.651822916666667</v>
+        <v>2.72160625</v>
       </c>
       <c r="G277" t="n">
-        <v>2.583605966649622</v>
+        <v>2.740104201229234</v>
       </c>
       <c r="H277" t="n">
-        <v>-0.06821695001704464</v>
+        <v>0.01849795122923403</v>
       </c>
       <c r="I277" t="n">
-        <v>2.572454954978409</v>
+        <v>0.67967036852719</v>
       </c>
       <c r="J277" t="n">
-        <v>-2.572454954978409</v>
+        <v>0.67967036852719</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>129913</v>
+        <v>129914</v>
       </c>
       <c r="B278" t="n">
-        <v>0.1017106544373163</v>
+        <v>0.05877849795017343</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -12225,27 +12170,27 @@
       </c>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="n">
-        <v>2.2462375</v>
+        <v>2.4985875</v>
       </c>
       <c r="G278" t="n">
-        <v>2.531382801555054</v>
+        <v>2.720655859404284</v>
       </c>
       <c r="H278" t="n">
-        <v>0.2851453015550534</v>
+        <v>0.2220683594042838</v>
       </c>
       <c r="I278" t="n">
-        <v>12.69435229155659</v>
+        <v>8.887755958287785</v>
       </c>
       <c r="J278" t="n">
-        <v>12.69435229155659</v>
+        <v>8.887755958287785</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>129913</v>
+        <v>129914</v>
       </c>
       <c r="B279" t="n">
-        <v>0.1017106544373163</v>
+        <v>0.05877849795017343</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -12259,27 +12204,27 @@
       </c>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="n">
-        <v>2.426137507705096</v>
+        <v>2.578681397618311</v>
       </c>
       <c r="G279" t="n">
-        <v>2.555970305317487</v>
+        <v>2.734556087326367</v>
       </c>
       <c r="H279" t="n">
-        <v>0.1298327976123903</v>
+        <v>0.1558746897080558</v>
       </c>
       <c r="I279" t="n">
-        <v>5.351419579478009</v>
+        <v>6.044744025067341</v>
       </c>
       <c r="J279" t="n">
-        <v>5.351419579478009</v>
+        <v>6.044744025067341</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>129913</v>
+        <v>129914</v>
       </c>
       <c r="B280" t="n">
-        <v>0.1017106544373163</v>
+        <v>0.05877849795017343</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -12293,27 +12238,27 @@
       </c>
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="n">
-        <v>2.651822916666667</v>
+        <v>2.72160625</v>
       </c>
       <c r="G280" t="n">
-        <v>2.653771948496829</v>
+        <v>2.79053001001984</v>
       </c>
       <c r="H280" t="n">
-        <v>0.001949031830162706</v>
+        <v>0.06892376001984069</v>
       </c>
       <c r="I280" t="n">
-        <v>0.07349781231292146</v>
+        <v>2.532466260313765</v>
       </c>
       <c r="J280" t="n">
-        <v>0.07349781231292146</v>
+        <v>2.532466260313765</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>129914</v>
+        <v>129937</v>
       </c>
       <c r="B281" t="n">
-        <v>0.05877849795017343</v>
+        <v>0.127186314179544</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -12326,30 +12271,30 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>0.09372630077322572</v>
+        <v>0.1095102904351769</v>
       </c>
       <c r="F281" t="n">
-        <v>2.4985875</v>
+        <v>2.1168875</v>
       </c>
       <c r="G281" t="n">
-        <v>2.498588413145333</v>
+        <v>2.116891206340847</v>
       </c>
       <c r="H281" t="n">
-        <v>9.131453331256978e-07</v>
+        <v>3.706340847120515e-06</v>
       </c>
       <c r="I281" t="n">
-        <v>3.654646207610091e-05</v>
+        <v>0.0001750844505019995</v>
       </c>
       <c r="J281" t="n">
-        <v>3.654646207610091e-05</v>
+        <v>0.0001750844505019995</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>129914</v>
+        <v>129937</v>
       </c>
       <c r="B282" t="n">
-        <v>0.05877849795017343</v>
+        <v>0.127186314179544</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -12362,30 +12307,30 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>0.09372630077322572</v>
+        <v>0.1095102904351769</v>
       </c>
       <c r="F282" t="n">
-        <v>2.578681397618311</v>
+        <v>2.303175230396183</v>
       </c>
       <c r="G282" t="n">
-        <v>2.571365651378545</v>
+        <v>2.220522839792302</v>
       </c>
       <c r="H282" t="n">
-        <v>-0.007315746239766163</v>
+        <v>-0.08265239060388074</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2837010514956613</v>
+        <v>3.588627973810886</v>
       </c>
       <c r="J282" t="n">
-        <v>-0.2837010514956613</v>
+        <v>-3.588627973810886</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>129914</v>
+        <v>129937</v>
       </c>
       <c r="B283" t="n">
-        <v>0.05877849795017343</v>
+        <v>0.127186314179544</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -12398,30 +12343,30 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>0.09372630077322572</v>
+        <v>0.1095102904351769</v>
       </c>
       <c r="F283" t="n">
-        <v>2.72160625</v>
+        <v>2.689839583333333</v>
       </c>
       <c r="G283" t="n">
-        <v>2.740478812615086</v>
+        <v>2.497430062230134</v>
       </c>
       <c r="H283" t="n">
-        <v>0.01887256261508652</v>
+        <v>-0.1924095211031989</v>
       </c>
       <c r="I283" t="n">
-        <v>0.6934347176446454</v>
+        <v>7.153196878185537</v>
       </c>
       <c r="J283" t="n">
-        <v>0.6934347176446454</v>
+        <v>-7.153196878185537</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>129914</v>
+        <v>129937</v>
       </c>
       <c r="B284" t="n">
-        <v>0.05877849795017343</v>
+        <v>0.127186314179544</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -12434,30 +12379,30 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>0.1035325935966191</v>
+        <v>0.1319493824569777</v>
       </c>
       <c r="F284" t="n">
-        <v>2.4985875</v>
+        <v>2.1168875</v>
       </c>
       <c r="G284" t="n">
-        <v>2.498587925730706</v>
+        <v>2.116891739070655</v>
       </c>
       <c r="H284" t="n">
-        <v>4.257307053556758e-07</v>
+        <v>4.239070654943333e-06</v>
       </c>
       <c r="I284" t="n">
-        <v>1.703885516739661e-05</v>
+        <v>0.0002002501623229073</v>
       </c>
       <c r="J284" t="n">
-        <v>1.703885516739661e-05</v>
+        <v>0.0002002501623229073</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>129914</v>
+        <v>129937</v>
       </c>
       <c r="B285" t="n">
-        <v>0.05877849795017343</v>
+        <v>0.127186314179544</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -12470,30 +12415,30 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>0.1035325935966191</v>
+        <v>0.1319493824569777</v>
       </c>
       <c r="F285" t="n">
-        <v>2.578681397618311</v>
+        <v>2.303175230396183</v>
       </c>
       <c r="G285" t="n">
-        <v>2.571010615566995</v>
+        <v>2.219545016545049</v>
       </c>
       <c r="H285" t="n">
-        <v>-0.007670782051315328</v>
+        <v>-0.08363021385113401</v>
       </c>
       <c r="I285" t="n">
-        <v>0.2974691661560098</v>
+        <v>3.631083416816197</v>
       </c>
       <c r="J285" t="n">
-        <v>-0.2974691661560098</v>
+        <v>-3.631083416816197</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>129914</v>
+        <v>129937</v>
       </c>
       <c r="B286" t="n">
-        <v>0.05877849795017343</v>
+        <v>0.127186314179544</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -12506,30 +12451,30 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>0.1035325935966191</v>
+        <v>0.1319493824569777</v>
       </c>
       <c r="F286" t="n">
-        <v>2.72160625</v>
+        <v>2.689839583333333</v>
       </c>
       <c r="G286" t="n">
-        <v>2.740104201229234</v>
+        <v>2.496193510854985</v>
       </c>
       <c r="H286" t="n">
-        <v>0.01849795122923403</v>
+        <v>-0.1936460724783484</v>
       </c>
       <c r="I286" t="n">
-        <v>0.67967036852719</v>
+        <v>7.199168072260137</v>
       </c>
       <c r="J286" t="n">
-        <v>0.67967036852719</v>
+        <v>-7.199168072260137</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>129914</v>
+        <v>129937</v>
       </c>
       <c r="B287" t="n">
-        <v>0.05877849795017343</v>
+        <v>0.127186314179544</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -12543,27 +12488,27 @@
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="n">
-        <v>2.4985875</v>
+        <v>2.1168875</v>
       </c>
       <c r="G287" t="n">
-        <v>2.720655859404284</v>
+        <v>2.419144666707322</v>
       </c>
       <c r="H287" t="n">
-        <v>0.2220683594042838</v>
+        <v>0.3022571667073226</v>
       </c>
       <c r="I287" t="n">
-        <v>8.887755958287785</v>
+        <v>14.27837647051734</v>
       </c>
       <c r="J287" t="n">
-        <v>8.887755958287785</v>
+        <v>14.27837647051734</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>129914</v>
+        <v>129937</v>
       </c>
       <c r="B288" t="n">
-        <v>0.05877849795017343</v>
+        <v>0.127186314179544</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -12577,27 +12522,27 @@
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="n">
-        <v>2.578681397618311</v>
+        <v>2.303175230396183</v>
       </c>
       <c r="G288" t="n">
-        <v>2.734556087326367</v>
+        <v>2.450329112379243</v>
       </c>
       <c r="H288" t="n">
-        <v>0.1558746897080558</v>
+        <v>0.1471538819830602</v>
       </c>
       <c r="I288" t="n">
-        <v>6.044744025067341</v>
+        <v>6.389174390250256</v>
       </c>
       <c r="J288" t="n">
-        <v>6.044744025067341</v>
+        <v>6.389174390250256</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>129914</v>
+        <v>129937</v>
       </c>
       <c r="B289" t="n">
-        <v>0.05877849795017343</v>
+        <v>0.127186314179544</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -12611,336 +12556,18 @@
       </c>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="n">
-        <v>2.72160625</v>
+        <v>2.689839583333333</v>
       </c>
       <c r="G289" t="n">
-        <v>2.79053001001984</v>
+        <v>2.573351704629975</v>
       </c>
       <c r="H289" t="n">
-        <v>0.06892376001984069</v>
+        <v>-0.1164878787033579</v>
       </c>
       <c r="I289" t="n">
-        <v>2.532466260313765</v>
+        <v>4.330662669444489</v>
       </c>
       <c r="J289" t="n">
-        <v>2.532466260313765</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="n">
-        <v>129937</v>
-      </c>
-      <c r="B290" t="n">
-        <v>0.127186314179544</v>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>GSA</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
-      </c>
-      <c r="E290" t="n">
-        <v>0.1095102904351769</v>
-      </c>
-      <c r="F290" t="n">
-        <v>2.1168875</v>
-      </c>
-      <c r="G290" t="n">
-        <v>2.116891206340847</v>
-      </c>
-      <c r="H290" t="n">
-        <v>3.706340847120515e-06</v>
-      </c>
-      <c r="I290" t="n">
-        <v>0.0001750844505019995</v>
-      </c>
-      <c r="J290" t="n">
-        <v>0.0001750844505019995</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="n">
-        <v>129937</v>
-      </c>
-      <c r="B291" t="n">
-        <v>0.127186314179544</v>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>GSA</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>oil</t>
-        </is>
-      </c>
-      <c r="E291" t="n">
-        <v>0.1095102904351769</v>
-      </c>
-      <c r="F291" t="n">
-        <v>2.303175230396183</v>
-      </c>
-      <c r="G291" t="n">
-        <v>2.220522839792302</v>
-      </c>
-      <c r="H291" t="n">
-        <v>-0.08265239060388074</v>
-      </c>
-      <c r="I291" t="n">
-        <v>3.588627973810886</v>
-      </c>
-      <c r="J291" t="n">
-        <v>-3.588627973810886</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>129937</v>
-      </c>
-      <c r="B292" t="n">
-        <v>0.127186314179544</v>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>GSA</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>brine_avg</t>
-        </is>
-      </c>
-      <c r="E292" t="n">
-        <v>0.1095102904351769</v>
-      </c>
-      <c r="F292" t="n">
-        <v>2.689839583333333</v>
-      </c>
-      <c r="G292" t="n">
-        <v>2.497430062230134</v>
-      </c>
-      <c r="H292" t="n">
-        <v>-0.1924095211031989</v>
-      </c>
-      <c r="I292" t="n">
-        <v>7.153196878185537</v>
-      </c>
-      <c r="J292" t="n">
-        <v>-7.153196878185537</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>129937</v>
-      </c>
-      <c r="B293" t="n">
-        <v>0.127186314179544</v>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
-      </c>
-      <c r="E293" t="n">
-        <v>0.1319493824569777</v>
-      </c>
-      <c r="F293" t="n">
-        <v>2.1168875</v>
-      </c>
-      <c r="G293" t="n">
-        <v>2.116891739070655</v>
-      </c>
-      <c r="H293" t="n">
-        <v>4.239070654943333e-06</v>
-      </c>
-      <c r="I293" t="n">
-        <v>0.0002002501623229073</v>
-      </c>
-      <c r="J293" t="n">
-        <v>0.0002002501623229073</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>129937</v>
-      </c>
-      <c r="B294" t="n">
-        <v>0.127186314179544</v>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>oil</t>
-        </is>
-      </c>
-      <c r="E294" t="n">
-        <v>0.1319493824569777</v>
-      </c>
-      <c r="F294" t="n">
-        <v>2.303175230396183</v>
-      </c>
-      <c r="G294" t="n">
-        <v>2.219545016545049</v>
-      </c>
-      <c r="H294" t="n">
-        <v>-0.08363021385113401</v>
-      </c>
-      <c r="I294" t="n">
-        <v>3.631083416816197</v>
-      </c>
-      <c r="J294" t="n">
-        <v>-3.631083416816197</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>129937</v>
-      </c>
-      <c r="B295" t="n">
-        <v>0.127186314179544</v>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>brine_avg</t>
-        </is>
-      </c>
-      <c r="E295" t="n">
-        <v>0.1319493824569777</v>
-      </c>
-      <c r="F295" t="n">
-        <v>2.689839583333333</v>
-      </c>
-      <c r="G295" t="n">
-        <v>2.496193510854985</v>
-      </c>
-      <c r="H295" t="n">
-        <v>-0.1936460724783484</v>
-      </c>
-      <c r="I295" t="n">
-        <v>7.199168072260137</v>
-      </c>
-      <c r="J295" t="n">
-        <v>-7.199168072260137</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>129937</v>
-      </c>
-      <c r="B296" t="n">
-        <v>0.127186314179544</v>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>BRUGGEMAN</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr"/>
-      <c r="F296" t="n">
-        <v>2.1168875</v>
-      </c>
-      <c r="G296" t="n">
-        <v>2.419144666707322</v>
-      </c>
-      <c r="H296" t="n">
-        <v>0.3022571667073226</v>
-      </c>
-      <c r="I296" t="n">
-        <v>14.27837647051734</v>
-      </c>
-      <c r="J296" t="n">
-        <v>14.27837647051734</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>129937</v>
-      </c>
-      <c r="B297" t="n">
-        <v>0.127186314179544</v>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>BRUGGEMAN</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>oil</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr"/>
-      <c r="F297" t="n">
-        <v>2.303175230396183</v>
-      </c>
-      <c r="G297" t="n">
-        <v>2.450329112379243</v>
-      </c>
-      <c r="H297" t="n">
-        <v>0.1471538819830602</v>
-      </c>
-      <c r="I297" t="n">
-        <v>6.389174390250256</v>
-      </c>
-      <c r="J297" t="n">
-        <v>6.389174390250256</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="n">
-        <v>129937</v>
-      </c>
-      <c r="B298" t="n">
-        <v>0.127186314179544</v>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>BRUGGEMAN</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>brine_avg</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr"/>
-      <c r="F298" t="n">
-        <v>2.689839583333333</v>
-      </c>
-      <c r="G298" t="n">
-        <v>2.573351704629975</v>
-      </c>
-      <c r="H298" t="n">
-        <v>-0.1164878787033579</v>
-      </c>
-      <c r="I298" t="n">
-        <v>4.330662669444489</v>
-      </c>
-      <c r="J298" t="n">
         <v>-4.330662669444489</v>
       </c>
     </row>
@@ -13007,19 +12634,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5655360655043429</v>
+        <v>0.307712774347173</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04583288742948363</v>
+        <v>0.028408364108595</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5655306138781744</v>
+        <v>0.3077071523577243</v>
       </c>
       <c r="G2" t="n">
-        <v>8.815957672417486</v>
+        <v>5.723086108307863</v>
       </c>
     </row>
     <row r="3">
@@ -13034,16 +12661,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>4.870448782461905</v>
+        <v>5.022648683803604</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1367263071032797</v>
+        <v>0.1388461932739913</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.832845473597748</v>
+        <v>-4.983870271537443</v>
       </c>
       <c r="G3" t="n">
         <v>11.09496567262841</v>
@@ -13061,16 +12688,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>4.30861254323064</v>
+        <v>4.276619826784182</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1354260687820719</v>
+        <v>0.1349015059081114</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.249352786317051</v>
+        <v>-4.215508202467048</v>
       </c>
       <c r="G4" t="n">
         <v>9.285504233286968</v>
@@ -13088,19 +12715,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5661042924672047</v>
+        <v>0.3082841793514198</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04586563444230999</v>
+        <v>0.02846070105003819</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5660974503385079</v>
+        <v>0.3082771234062011</v>
       </c>
       <c r="G5" t="n">
-        <v>8.816347912172322</v>
+        <v>5.733601078609627</v>
       </c>
     </row>
     <row r="6">
@@ -13115,16 +12742,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>4.927465003277339</v>
+        <v>5.081447916334067</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1380964276619535</v>
+        <v>0.1402375852335823</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.89157098074321</v>
+        <v>-5.044432205595746</v>
       </c>
       <c r="G6" t="n">
         <v>11.19040846154465</v>
@@ -13142,16 +12769,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>4.35619834584421</v>
+        <v>4.325678137539425</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1368112905835354</v>
+        <v>0.1363348259675665</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.303497801309662</v>
+        <v>-4.271330700988173</v>
       </c>
       <c r="G7" t="n">
         <v>9.372703496519826</v>
@@ -13169,16 +12796,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>17.79437606272393</v>
+        <v>18.07272759148776</v>
       </c>
       <c r="E8" t="n">
-        <v>0.374825217942641</v>
+        <v>0.378818005376106</v>
       </c>
       <c r="F8" t="n">
-        <v>17.79437606272393</v>
+        <v>18.07272759148776</v>
       </c>
       <c r="G8" t="n">
         <v>53.78773008610538</v>
@@ -13196,16 +12823,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>6.08285788806541</v>
+        <v>6.271271855741267</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1574959629667892</v>
+        <v>0.1599377171549096</v>
       </c>
       <c r="F9" t="n">
-        <v>6.025985138499244</v>
+        <v>6.212621832751158</v>
       </c>
       <c r="G9" t="n">
         <v>20.3210905244394</v>
@@ -13223,16 +12850,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>2.406535083258526</v>
+        <v>2.315716202006248</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08062879638570661</v>
+        <v>0.07742402588526598</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.395553588023597</v>
+        <v>-1.273141535045227</v>
       </c>
       <c r="G10" t="n">
         <v>6.918772142635587</v>
@@ -13306,28 +12933,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02397019273512207</v>
+        <v>0.02397019273512198</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09732484864407834</v>
+        <v>0.08528709168216574</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0785681403797011</v>
+        <v>0.07759725848132093</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4825333284192772</v>
+        <v>0.2227214678701135</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04608300987751511</v>
+        <v>0.04539198434181525</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2746838399799459</v>
+        <v>0.2195605588252939</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2286008301024308</v>
+        <v>0.1741685744834787</v>
       </c>
     </row>
     <row r="3">
@@ -13337,28 +12964,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="n">
         <v>0.02617032869151523</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1152811409896835</v>
+        <v>0.1033167182562609</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1008884035969615</v>
+        <v>0.09943921080260062</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4981426684592046</v>
+        <v>0.2448759921893136</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04922000376705891</v>
+        <v>0.04849970142094817</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2955293274432916</v>
+        <v>0.2386324683546633</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2463093236762327</v>
+        <v>0.1901327669337151</v>
       </c>
     </row>
   </sheetData>

--- a/results/level1_emt_comparison/table12_level1_emt_comparison.xlsx
+++ b/results/level1_emt_comparison/table12_level1_emt_comparison.xlsx
@@ -471,19 +471,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.20232709497832</v>
+        <v>3.4977343895806</v>
       </c>
       <c r="C2" t="n">
-        <v>0.11296565382788</v>
+        <v>0.09952700124000316</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.963890440548922</v>
+        <v>-1.509833818315604</v>
       </c>
       <c r="E2" t="n">
-        <v>11.09496567262841</v>
+        <v>8.578699666702336</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1741685744834787</v>
+        <v>0.1173328842989967</v>
       </c>
     </row>
     <row r="3">
@@ -493,19 +493,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.238470077741638</v>
+        <v>3.532550896882047</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1141107307078123</v>
+        <v>0.1002824979290117</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.002495261059239</v>
+        <v>-1.510462118499286</v>
       </c>
       <c r="E3" t="n">
-        <v>11.19040846154465</v>
+        <v>8.63015605569206</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1901327669337151</v>
+        <v>0.1351758727380787</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,7 +565,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>objective_L1</t>
+          <t>objective_mode</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>objective_value</t>
         </is>
       </c>
     </row>
@@ -582,10 +587,15 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.0566644169147693</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.1578618204724496</v>
+        <v>0.06484675134887007</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.001426253613819096</v>
       </c>
     </row>
     <row r="3">
@@ -601,10 +611,15 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.06386482684796346</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.1587387084394845</v>
+        <v>0.07220250520233248</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.001439813595050444</v>
       </c>
     </row>
     <row r="4">
@@ -620,8 +635,13 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>0.4486895288228592</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.01577787253860843</v>
       </c>
     </row>
     <row r="5">
@@ -637,10 +657,15 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07856814037970133</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.1832525822951645</v>
+        <v>0.09307463258693392</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.001905731806762198</v>
       </c>
     </row>
     <row r="6">
@@ -656,10 +681,15 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.08924886172458077</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.184364795550779</v>
+        <v>0.1040653526712325</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.001924012170565153</v>
       </c>
     </row>
     <row r="7">
@@ -675,8 +705,13 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
-        <v>0.4218503377937282</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.01470088710302295</v>
       </c>
     </row>
     <row r="8">
@@ -692,10 +727,15 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07975437634955812</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.4129043461096686</v>
+        <v>0.1014934520242985</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01269622106757719</v>
       </c>
     </row>
     <row r="9">
@@ -711,10 +751,15 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1059624887607095</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.4173639020295501</v>
+        <v>0.1286925630994195</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01289592448653994</v>
       </c>
     </row>
     <row r="10">
@@ -730,8 +775,13 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="n">
-        <v>0.668064401571262</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.05269356062177111</v>
       </c>
     </row>
     <row r="11">
@@ -747,10 +797,15 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.07352012846648061</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.501375503026221</v>
+        <v>0.09691346063131066</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01819642298101178</v>
       </c>
     </row>
     <row r="12">
@@ -766,10 +821,15 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.09799001800823975</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.5058823287536682</v>
+        <v>0.1224241063353341</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.01842962847666407</v>
       </c>
     </row>
     <row r="13">
@@ -785,8 +845,13 @@
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>0.7294476150130045</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.05855133298044912</v>
       </c>
     </row>
     <row r="14">
@@ -802,10 +867,15 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.06629982941511016</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.2449531055810219</v>
+        <v>0.07673171926436299</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.003974014848342928</v>
       </c>
     </row>
     <row r="15">
@@ -821,10 +891,15 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.08194993605837791</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.2475917006896253</v>
+        <v>0.09275945529426537</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.004046396530460079</v>
       </c>
     </row>
     <row r="16">
@@ -840,8 +915,13 @@
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>0.6554331814997258</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.04118215485012004</v>
       </c>
     </row>
     <row r="17">
@@ -857,10 +937,15 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.08850039773988014</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.2235541593239216</v>
+        <v>0.1041321540632679</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.003089874585947388</v>
       </c>
     </row>
     <row r="18">
@@ -876,10 +961,15 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.1042585113052578</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.2253346994602143</v>
+        <v>0.1203515230058849</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.003129145333312811</v>
       </c>
     </row>
     <row r="19">
@@ -895,8 +985,13 @@
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
-        <v>0.5068763313642757</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.02148872008864886</v>
       </c>
     </row>
     <row r="20">
@@ -912,10 +1007,15 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.08631537829714603</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.2750502051737929</v>
+        <v>0.1091827019556289</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.004479703718432914</v>
       </c>
     </row>
     <row r="21">
@@ -931,10 +1031,15 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1012018247808178</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.2767359375840668</v>
+        <v>0.1246478537064422</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.004518443326050569</v>
       </c>
     </row>
     <row r="22">
@@ -950,8 +1055,13 @@
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
-        <v>0.460378011253082</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.01926661452947061</v>
       </c>
     </row>
     <row r="23">
@@ -967,10 +1077,15 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.07158956549382076</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.3045635095545758</v>
+        <v>0.09014147517354235</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.005471959125607058</v>
       </c>
     </row>
     <row r="24">
@@ -986,10 +1101,15 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.08391244363649571</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.306181146869914</v>
+        <v>0.1029214781576894</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.005515063392005226</v>
       </c>
     </row>
     <row r="25">
@@ -1005,8 +1125,13 @@
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>0.5279381478452496</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.02257991284150608</v>
       </c>
     </row>
     <row r="26">
@@ -1022,10 +1147,15 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.07041259839357256</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.5364264602899711</v>
+        <v>0.1135228868599596</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.01572252652926967</v>
       </c>
     </row>
     <row r="27">
@@ -1041,10 +1171,15 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.08158045301163148</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.5378298389161928</v>
+        <v>0.1255800995875918</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.01576460720699622</v>
       </c>
     </row>
     <row r="28">
@@ -1060,8 +1195,13 @@
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="n">
-        <v>0.5673634416758437</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.02325441540539569</v>
       </c>
     </row>
     <row r="29">
@@ -1077,10 +1217,15 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.07519263589067139</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.2873466586836648</v>
+        <v>0.09373764106886844</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.004983327640802717</v>
       </c>
     </row>
     <row r="30">
@@ -1096,10 +1241,15 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.08904076119261407</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.2891774823790838</v>
+        <v>0.108079059935932</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.005030503043494086</v>
       </c>
     </row>
     <row r="31">
@@ -1115,8 +1265,13 @@
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="n">
-        <v>0.5205557766390179</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0.02407628651466769</v>
       </c>
     </row>
     <row r="32">
@@ -1132,10 +1287,15 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.08455531212179532</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.3877543575287175</v>
+        <v>0.1207109757987655</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0.008420137453357786</v>
       </c>
     </row>
     <row r="33">
@@ -1151,10 +1311,15 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.09798106554163073</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.3892214329300319</v>
+        <v>0.1349242852469897</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.008457667796057576</v>
       </c>
     </row>
     <row r="34">
@@ -1170,8 +1335,13 @@
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="n">
-        <v>0.452486235092286</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0.01772280606778306</v>
       </c>
     </row>
     <row r="35">
@@ -1187,10 +1357,15 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.07649558994396592</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.3221197757293424</v>
+        <v>0.09064935244750821</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0.008888237553969018</v>
       </c>
     </row>
     <row r="36">
@@ -1206,10 +1381,15 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.1075030182024911</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.3280258594281007</v>
+        <v>0.1225019912041175</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0.009151235446444375</v>
       </c>
     </row>
     <row r="37">
@@ -1225,8 +1405,13 @@
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
-        <v>0.730563761674206</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0.07444947537576159</v>
       </c>
     </row>
     <row r="38">
@@ -1242,10 +1427,15 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.08746020600723763</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.07013319285547093</v>
+        <v>0.08687490823942555</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.0004595220447024215</v>
       </c>
     </row>
     <row r="39">
@@ -1261,10 +1451,15 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.1008884035969615</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.07016814373742708</v>
+        <v>0.1004009470577079</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0.0004676634938264865</v>
       </c>
     </row>
     <row r="40">
@@ -1280,8 +1475,13 @@
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>0.5447983464121351</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0.02320542248894809</v>
       </c>
     </row>
     <row r="41">
@@ -1297,10 +1497,15 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.2186428755542173</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.2306845256826073</v>
+        <v>0.1743131185505807</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0.003547939585438308</v>
       </c>
     </row>
     <row r="42">
@@ -1316,10 +1521,15 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.236819832402668</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.2310529706696847</v>
+        <v>0.1923657220418985</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.003566037008314917</v>
       </c>
     </row>
     <row r="43">
@@ -1335,8 +1545,13 @@
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="n">
-        <v>0.3686419342756744</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0.008318008314292325</v>
       </c>
     </row>
     <row r="44">
@@ -1352,10 +1567,15 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.07662637658294051</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.2454568864233364</v>
+        <v>0.08545778587403147</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.006498992878393673</v>
       </c>
     </row>
     <row r="45">
@@ -1371,10 +1591,15 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.1201360836897293</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.2543144897076088</v>
+        <v>0.1298105555202281</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0.006922437002607516</v>
       </c>
     </row>
     <row r="46">
@@ -1390,8 +1615,13 @@
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="n">
-        <v>0.7800198272534931</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0.1118199875995252</v>
       </c>
     </row>
     <row r="47">
@@ -1407,10 +1637,15 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.05726532872156408</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.2362761207079132</v>
+        <v>0.06558424354601573</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0.004855947569001242</v>
       </c>
     </row>
     <row r="48">
@@ -1426,10 +1661,15 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.07717316817023095</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.2408135416935724</v>
+        <v>0.08590321249115156</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0.005001926422283014</v>
       </c>
     </row>
     <row r="49">
@@ -1445,8 +1685,13 @@
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="n">
-        <v>0.8426693118526383</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0.07990597040983526</v>
       </c>
     </row>
     <row r="50">
@@ -1462,10 +1707,15 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.2227214678701135</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.2457191182242671</v>
+        <v>0.1657802292793794</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0.003818779891596224</v>
       </c>
     </row>
     <row r="51">
@@ -1481,10 +1731,15 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.2448759921893136</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.2462063887984645</v>
+        <v>0.1876345746351141</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0.003848739528055707</v>
       </c>
     </row>
     <row r="52">
@@ -1500,8 +1755,13 @@
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="n">
-        <v>0.3896684154815144</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0.01124012621266991</v>
       </c>
     </row>
     <row r="53">
@@ -1517,10 +1777,15 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.08427582850660252</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.1637237890510828</v>
+        <v>0.09694365238765493</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0.002913427409798685</v>
       </c>
     </row>
     <row r="54">
@@ -1536,10 +1801,15 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.1080509055066162</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.1673240661858491</v>
+        <v>0.1212686453864763</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0.002979338398988146</v>
       </c>
     </row>
     <row r="55">
@@ -1555,8 +1825,13 @@
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="n">
-        <v>0.6625910010039939</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0.04398060178705012</v>
       </c>
     </row>
     <row r="56">
@@ -1572,10 +1847,15 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.09214397915035179</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.3953739497372799</v>
+        <v>0.1188916866241674</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0.01096670508388457</v>
       </c>
     </row>
     <row r="57">
@@ -1591,10 +1871,15 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.1181240394951164</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.3989724410322442</v>
+        <v>0.1459483453413025</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>0.01110618972895</v>
       </c>
     </row>
     <row r="58">
@@ -1610,8 +1895,13 @@
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="n">
-        <v>0.5855627668852905</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>0.03711907264044709</v>
       </c>
     </row>
     <row r="59">
@@ -1627,10 +1917,15 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.07638048100184233</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.4134481225117073</v>
+        <v>0.09718731902762963</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>0.01270369443783915</v>
       </c>
     </row>
     <row r="60">
@@ -1646,10 +1941,15 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.1014549402188581</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.4178871479823627</v>
+        <v>0.1231981587056181</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>0.01290255068114014</v>
       </c>
     </row>
     <row r="61">
@@ -1665,8 +1965,13 @@
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="n">
-        <v>0.678967316090761</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>0.05474449030692286</v>
       </c>
     </row>
     <row r="62">
@@ -1682,10 +1987,15 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.07972957776622766</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.3890755131440287</v>
+        <v>0.09834369845642285</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>0.01167467116764676</v>
       </c>
     </row>
     <row r="63">
@@ -1701,10 +2011,15 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.1075983135296858</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.393931853058483</v>
+        <v>0.1271492990360422</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>0.01190004321424802</v>
       </c>
     </row>
     <row r="64">
@@ -1720,8 +2035,13 @@
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="n">
-        <v>0.7083843300090813</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>0.05855499221293872</v>
       </c>
     </row>
     <row r="65">
@@ -1737,10 +2057,15 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.0711001993502882</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.03145751620537673</v>
+        <v>0.07296935360972662</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>9.524659717881804e-05</v>
       </c>
     </row>
     <row r="66">
@@ -1756,10 +2081,15 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.08546840709107527</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0.03151455020869909</v>
+        <v>0.0874707755582199</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>0.0001006762217036522</v>
       </c>
     </row>
     <row r="67">
@@ -1775,8 +2105,13 @@
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="n">
-        <v>0.7308964258071851</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>0.03800214997446086</v>
       </c>
     </row>
     <row r="68">
@@ -1792,10 +2127,15 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.07216402703380319</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0.02729226510950511</v>
+        <v>0.07396191726943012</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>0.0001008313904364574</v>
       </c>
     </row>
     <row r="69">
@@ -1811,10 +2151,15 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.09009004668823942</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0.02739017736156413</v>
+        <v>0.09205323862126645</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>0.0001111323748640102</v>
       </c>
     </row>
     <row r="70">
@@ -1830,8 +2175,13 @@
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="n">
-        <v>0.815310932210227</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>0.05188151501753885</v>
       </c>
     </row>
     <row r="71">
@@ -1847,10 +2197,15 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0686445033615314</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0.05285234807002404</v>
+        <v>0.07453370480727649</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>0.0001912344943611312</v>
       </c>
     </row>
     <row r="72">
@@ -1866,10 +2221,15 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.07463470711230444</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.05333841545703777</v>
+        <v>0.08061948493320611</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>0.0001937070451906009</v>
       </c>
     </row>
     <row r="73">
@@ -1885,8 +2245,13 @@
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="n">
-        <v>0.3559010301537064</v>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>0.008090057061064235</v>
       </c>
     </row>
     <row r="74">
@@ -1902,10 +2267,15 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.05161121416311329</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0.05811188292933656</v>
+        <v>0.05747388742708958</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>0.0002244689254296437</v>
       </c>
     </row>
     <row r="75">
@@ -1921,10 +2291,15 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.05498242253594483</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0.05835869515232384</v>
+        <v>0.06090205673614606</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>0.0002258821632057887</v>
       </c>
     </row>
     <row r="76">
@@ -1940,8 +2315,13 @@
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="n">
-        <v>0.2690454672306748</v>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>0.004872047044768095</v>
       </c>
     </row>
     <row r="77">
@@ -1957,10 +2337,15 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.02397019273512198</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0.09410409760133653</v>
+        <v>0.02588881026848242</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>0.0005131944295026433</v>
       </c>
     </row>
     <row r="78">
@@ -1976,10 +2361,15 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.02617032869151523</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0.09435507480994509</v>
+        <v>0.02810718263577177</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>0.0005158618294649623</v>
       </c>
     </row>
     <row r="79">
@@ -1995,8 +2385,13 @@
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="n">
-        <v>0.3538984046651779</v>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>0.009260335902341777</v>
       </c>
     </row>
     <row r="80">
@@ -2012,10 +2407,15 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.09122256426320441</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.2365349672944657</v>
+        <v>0.1132306970720933</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>0.003197097664292184</v>
       </c>
     </row>
     <row r="81">
@@ -2031,10 +2431,15 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.1028391763575825</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0.2375564971107833</v>
+        <v>0.1252955957059185</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>0.003216954519642976</v>
       </c>
     </row>
     <row r="82">
@@ -2050,8 +2455,13 @@
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="n">
-        <v>0.4178006730142449</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0.0120926305768613</v>
       </c>
     </row>
     <row r="83">
@@ -2067,10 +2477,15 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.08540130311845651</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0.1175350712421905</v>
+        <v>0.09635149004190553</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0.0008741734501925686</v>
       </c>
     </row>
     <row r="84">
@@ -2086,10 +2501,15 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.09786992411855877</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0.1188116643274797</v>
+        <v>0.1090943562588904</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0.0008884612030804766</v>
       </c>
     </row>
     <row r="85">
@@ -2105,8 +2525,13 @@
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="n">
-        <v>0.4534280373846236</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0.01649452967340058</v>
       </c>
     </row>
     <row r="86">
@@ -2122,10 +2547,15 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.05449563116943758</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0.3107034944707896</v>
+        <v>0.06161966169463239</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0.01203366230970261</v>
       </c>
     </row>
     <row r="87">
@@ -2141,10 +2571,15 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.09717239253050693</v>
-      </c>
-      <c r="E87" t="n">
-        <v>0.3231422282963496</v>
+        <v>0.105081064363988</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0.01290834573199064</v>
       </c>
     </row>
     <row r="88">
@@ -2160,8 +2595,13 @@
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="n">
-        <v>1.017395106863452</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0.2194699397244391</v>
       </c>
     </row>
     <row r="89">
@@ -2177,10 +2617,15 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.1042262168583755</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0.1520996820158942</v>
+        <v>0.1192750673708974</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>0.001406770847992006</v>
       </c>
     </row>
     <row r="90">
@@ -2196,10 +2641,15 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.1218097151510352</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0.153739793820459</v>
+        <v>0.1373010909392187</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0.001431139783567672</v>
       </c>
     </row>
     <row r="91">
@@ -2215,8 +2665,13 @@
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="n">
-        <v>0.4169271309976064</v>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0.01700065570326282</v>
       </c>
     </row>
     <row r="92">
@@ -2232,10 +2687,15 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.09372630077322562</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0.02618922200018625</v>
+        <v>0.09431377044305972</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>5.525407759219617e-05</v>
       </c>
     </row>
     <row r="93">
@@ -2251,10 +2711,15 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.1035325935966191</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0.02616915901125472</v>
+        <v>0.1041909157093198</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>5.405317109911678e-05</v>
       </c>
     </row>
     <row r="94">
@@ -2270,8 +2735,13 @@
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="n">
-        <v>0.4468668091321804</v>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>0.0113201713442734</v>
       </c>
     </row>
     <row r="95">
@@ -2287,10 +2757,15 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.1095102904351769</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0.2750656180479267</v>
+        <v>0.1280476374761181</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>0.005932144748522123</v>
       </c>
     </row>
     <row r="96">
@@ -2306,10 +2781,15 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.1319493824569777</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0.2772805254001374</v>
+        <v>0.1511864461993925</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>0.006000262302862233</v>
       </c>
     </row>
     <row r="97">
@@ -2325,8 +2805,13 @@
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="n">
-        <v>0.5658989273937407</v>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>log_sse</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>0.02360930565929341</v>
       </c>
     </row>
   </sheetData>
@@ -2413,22 +2898,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0566644169147693</v>
+        <v>0.06484675134887007</v>
       </c>
       <c r="F2" t="n">
         <v>2.472887500000001</v>
       </c>
       <c r="G2" t="n">
-        <v>2.472889942683991</v>
+        <v>2.511210803997858</v>
       </c>
       <c r="H2" t="n">
-        <v>2.442683990633299e-06</v>
+        <v>0.03832330399785766</v>
       </c>
       <c r="I2" t="n">
-        <v>9.877861369080875e-05</v>
+        <v>1.549739080239503</v>
       </c>
       <c r="J2" t="n">
-        <v>9.877861369080875e-05</v>
+        <v>1.549739080239503</v>
       </c>
     </row>
     <row r="3">
@@ -2449,22 +2934,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0566644169147693</v>
+        <v>0.06484675134887007</v>
       </c>
       <c r="F3" t="n">
         <v>2.668884574253278</v>
       </c>
       <c r="G3" t="n">
-        <v>2.584048673232695</v>
+        <v>2.605340434994754</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.08483590102058303</v>
+        <v>-0.06354413925852409</v>
       </c>
       <c r="I3" t="n">
-        <v>3.178702512614997</v>
+        <v>2.380924970361559</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.178702512614997</v>
+        <v>-2.380924970361559</v>
       </c>
     </row>
     <row r="4">
@@ -2485,22 +2970,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0566644169147693</v>
+        <v>0.06484675134887007</v>
       </c>
       <c r="F4" t="n">
         <v>2.853091666666666</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78006818989879</v>
+        <v>2.783540667581652</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.07302347676787591</v>
+        <v>-0.06955099908501472</v>
       </c>
       <c r="I4" t="n">
-        <v>2.55945077478674</v>
+        <v>2.437741482252226</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.55945077478674</v>
+        <v>-2.437741482252226</v>
       </c>
     </row>
     <row r="5">
@@ -2521,22 +3006,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.06386482684796346</v>
+        <v>0.07220250520233248</v>
       </c>
       <c r="F5" t="n">
         <v>2.472887500000001</v>
       </c>
       <c r="G5" t="n">
-        <v>2.472887645142705</v>
+        <v>2.511570212522523</v>
       </c>
       <c r="H5" t="n">
-        <v>1.451427045218168e-07</v>
+        <v>0.03868271252252287</v>
       </c>
       <c r="I5" t="n">
-        <v>5.869361405313292e-06</v>
+        <v>1.564273042041858</v>
       </c>
       <c r="J5" t="n">
-        <v>5.869361405313292e-06</v>
+        <v>1.564273042041858</v>
       </c>
     </row>
     <row r="6">
@@ -2557,22 +3042,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.06386482684796346</v>
+        <v>0.07220250520233248</v>
       </c>
       <c r="F6" t="n">
         <v>2.668884574253278</v>
       </c>
       <c r="G6" t="n">
-        <v>2.583547370525208</v>
+        <v>2.605136272795962</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.08533720372806997</v>
+        <v>-0.06374830145731636</v>
       </c>
       <c r="I6" t="n">
-        <v>3.197485741845778</v>
+        <v>2.388574690426706</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.197485741845778</v>
+        <v>-2.388574690426706</v>
       </c>
     </row>
     <row r="7">
@@ -2593,22 +3078,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.06386482684796346</v>
+        <v>0.07220250520233248</v>
       </c>
       <c r="F7" t="n">
         <v>2.853091666666666</v>
       </c>
       <c r="G7" t="n">
-        <v>2.779690307097956</v>
+        <v>2.783239363556381</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.07340135956870997</v>
+        <v>-0.0698523031102849</v>
       </c>
       <c r="I7" t="n">
-        <v>2.572695452665441</v>
+        <v>2.448302097208639</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.572695452665441</v>
+        <v>-2.448302097208639</v>
       </c>
     </row>
     <row r="8">
@@ -2731,22 +3216,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.07856814037970133</v>
+        <v>0.09307463258693392</v>
       </c>
       <c r="F11" t="n">
         <v>2.404575</v>
       </c>
       <c r="G11" t="n">
-        <v>2.404576854037717</v>
+        <v>2.453784862328249</v>
       </c>
       <c r="H11" t="n">
-        <v>1.854037717130552e-06</v>
+        <v>0.0492098623282482</v>
       </c>
       <c r="I11" t="n">
-        <v>7.710459092066381e-05</v>
+        <v>2.04650977109253</v>
       </c>
       <c r="J11" t="n">
-        <v>7.710459092066381e-05</v>
+        <v>2.04650977109253</v>
       </c>
     </row>
     <row r="12">
@@ -2767,22 +3252,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.07856814037970133</v>
+        <v>0.09307463258693392</v>
       </c>
       <c r="F12" t="n">
         <v>2.600887636781521</v>
       </c>
       <c r="G12" t="n">
-        <v>2.501643196623343</v>
+        <v>2.532789250615629</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.09924444015817802</v>
+        <v>-0.06809838616589214</v>
       </c>
       <c r="I12" t="n">
-        <v>3.815791145863896</v>
+        <v>2.618274822904721</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.815791145863896</v>
+        <v>-2.618274822904721</v>
       </c>
     </row>
     <row r="13">
@@ -2803,22 +3288,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.07856814037970133</v>
+        <v>0.09307463258693392</v>
       </c>
       <c r="F13" t="n">
         <v>2.794646875</v>
       </c>
       <c r="G13" t="n">
-        <v>2.710640586900731</v>
+        <v>2.717123973866871</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.08400628809926936</v>
+        <v>-0.07752290113312954</v>
       </c>
       <c r="I13" t="n">
-        <v>3.005971482506868</v>
+        <v>2.773978416615857</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.005971482506868</v>
+        <v>-2.773978416615857</v>
       </c>
     </row>
     <row r="14">
@@ -2839,22 +3324,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.08924886172458077</v>
+        <v>0.1040653526712325</v>
       </c>
       <c r="F14" t="n">
         <v>2.404575</v>
       </c>
       <c r="G14" t="n">
-        <v>2.404577084665223</v>
+        <v>2.454244987935627</v>
       </c>
       <c r="H14" t="n">
-        <v>2.084665222223947e-06</v>
+        <v>0.04966998793562638</v>
       </c>
       <c r="I14" t="n">
-        <v>8.669578708187297e-05</v>
+        <v>2.065645194499085</v>
       </c>
       <c r="J14" t="n">
-        <v>8.669578708187297e-05</v>
+        <v>2.065645194499085</v>
       </c>
     </row>
     <row r="15">
@@ -2875,22 +3360,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.08924886172458077</v>
+        <v>0.1040653526712325</v>
       </c>
       <c r="F15" t="n">
         <v>2.600887636781521</v>
       </c>
       <c r="G15" t="n">
-        <v>2.501076409077493</v>
+        <v>2.532663305483015</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09981122770402795</v>
+        <v>-0.0682243312985058</v>
       </c>
       <c r="I15" t="n">
-        <v>3.837583227068577</v>
+        <v>2.623117213280704</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.837583227068577</v>
+        <v>-2.623117213280704</v>
       </c>
     </row>
     <row r="16">
@@ -2911,22 +3396,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.08924886172458077</v>
+        <v>0.1040653526712325</v>
       </c>
       <c r="F16" t="n">
         <v>2.794646875</v>
       </c>
       <c r="G16" t="n">
-        <v>2.710095391818471</v>
+        <v>2.716738287005909</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.08455148318152883</v>
+        <v>-0.07790858799409106</v>
       </c>
       <c r="I16" t="n">
-        <v>3.025480032482774</v>
+        <v>2.787779332374186</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.025480032482774</v>
+        <v>-2.787779332374186</v>
       </c>
     </row>
     <row r="17">
@@ -3049,22 +3534,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.07975437634955812</v>
+        <v>0.1014934520242985</v>
       </c>
       <c r="F20" t="n">
         <v>1.85855</v>
       </c>
       <c r="G20" t="n">
-        <v>1.858552129540526</v>
+        <v>1.963588056859826</v>
       </c>
       <c r="H20" t="n">
-        <v>2.129540526141227e-06</v>
+        <v>0.1050380568598261</v>
       </c>
       <c r="I20" t="n">
-        <v>0.000114580749839457</v>
+        <v>5.651613185538519</v>
       </c>
       <c r="J20" t="n">
-        <v>0.000114580749839457</v>
+        <v>5.651613185538519</v>
       </c>
     </row>
     <row r="21">
@@ -3085,22 +3570,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.07975437634955812</v>
+        <v>0.1014934520242985</v>
       </c>
       <c r="F21" t="n">
         <v>2.23458197098924</v>
       </c>
       <c r="G21" t="n">
-        <v>2.015458720268366</v>
+        <v>2.086666668596299</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2191232507208745</v>
+        <v>-0.1479153023929412</v>
       </c>
       <c r="I21" t="n">
-        <v>9.806006383550544</v>
+        <v>6.619372406708342</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.806006383550544</v>
+        <v>-6.619372406708342</v>
       </c>
     </row>
     <row r="22">
@@ -3121,22 +3606,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.07975437634955812</v>
+        <v>0.1014934520242985</v>
       </c>
       <c r="F22" t="n">
         <v>2.589690625</v>
       </c>
       <c r="G22" t="n">
-        <v>2.395911659151732</v>
+        <v>2.413179616275031</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.193778965848268</v>
+        <v>-0.1765110087249688</v>
       </c>
       <c r="I22" t="n">
-        <v>7.482707161140842</v>
+        <v>6.815911021223581</v>
       </c>
       <c r="J22" t="n">
-        <v>-7.482707161140842</v>
+        <v>-6.815911021223581</v>
       </c>
     </row>
     <row r="23">
@@ -3157,22 +3642,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.1059624887607095</v>
+        <v>0.1286925630994195</v>
       </c>
       <c r="F23" t="n">
         <v>1.85855</v>
       </c>
       <c r="G23" t="n">
-        <v>1.858550076365922</v>
+        <v>1.965452812336381</v>
       </c>
       <c r="H23" t="n">
-        <v>7.636592203041914e-08</v>
+        <v>0.1069028123363809</v>
       </c>
       <c r="I23" t="n">
-        <v>4.108897905916932e-06</v>
+        <v>5.751947073599359</v>
       </c>
       <c r="J23" t="n">
-        <v>4.108897905916932e-06</v>
+        <v>5.751947073599359</v>
       </c>
     </row>
     <row r="24">
@@ -3193,22 +3678,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.1059624887607095</v>
+        <v>0.1286925630994195</v>
       </c>
       <c r="F24" t="n">
         <v>2.23458197098924</v>
       </c>
       <c r="G24" t="n">
-        <v>2.013355784773371</v>
+        <v>2.086536306799684</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2212261862158695</v>
+        <v>-0.148045664189556</v>
       </c>
       <c r="I24" t="n">
-        <v>9.900115059011849</v>
+        <v>6.62520624043238</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.900115059011849</v>
+        <v>-6.62520624043238</v>
       </c>
     </row>
     <row r="25">
@@ -3229,22 +3714,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.1059624887607095</v>
+        <v>0.1286925630994195</v>
       </c>
       <c r="F25" t="n">
         <v>2.589690625</v>
       </c>
       <c r="G25" t="n">
-        <v>2.393552985552242</v>
+        <v>2.411718603676392</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1961376394477585</v>
+        <v>-0.1779720213236087</v>
       </c>
       <c r="I25" t="n">
-        <v>7.573786519297397</v>
+        <v>6.87232751300587</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.573786519297397</v>
+        <v>-6.87232751300587</v>
       </c>
     </row>
     <row r="26">
@@ -3367,22 +3852,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.07352012846648061</v>
+        <v>0.09691346063131066</v>
       </c>
       <c r="F29" t="n">
         <v>1.867175</v>
       </c>
       <c r="G29" t="n">
-        <v>1.867176584347419</v>
+        <v>1.988787202364004</v>
       </c>
       <c r="H29" t="n">
-        <v>1.584347419036902e-06</v>
+        <v>0.1216122023640041</v>
       </c>
       <c r="I29" t="n">
-        <v>8.485264739710537e-05</v>
+        <v>6.51316573775913</v>
       </c>
       <c r="J29" t="n">
-        <v>8.485264739710537e-05</v>
+        <v>6.51316573775913</v>
       </c>
     </row>
     <row r="30">
@@ -3403,22 +3888,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.07352012846648061</v>
+        <v>0.09691346063131066</v>
       </c>
       <c r="F30" t="n">
         <v>2.28687304883645</v>
       </c>
       <c r="G30" t="n">
-        <v>2.033145269091456</v>
+        <v>2.114108943768076</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2537277797449948</v>
+        <v>-0.1727641050683748</v>
       </c>
       <c r="I30" t="n">
-        <v>11.09496567262841</v>
+        <v>7.55459972543191</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.09496567262841</v>
+        <v>-7.55459972543191</v>
       </c>
     </row>
     <row r="31">
@@ -3439,22 +3924,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.07352012846648061</v>
+        <v>0.09691346063131066</v>
       </c>
       <c r="F31" t="n">
         <v>2.66701875</v>
       </c>
       <c r="G31" t="n">
-        <v>2.419372611066193</v>
+        <v>2.438223221382861</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2476461389338072</v>
+        <v>-0.2287955286171388</v>
       </c>
       <c r="I31" t="n">
-        <v>9.285504233286968</v>
+        <v>8.578699666702336</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.285504233286968</v>
+        <v>-8.578699666702336</v>
       </c>
     </row>
     <row r="32">
@@ -3475,22 +3960,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.09799001800823975</v>
+        <v>0.1224241063353341</v>
       </c>
       <c r="F32" t="n">
         <v>1.867175</v>
       </c>
       <c r="G32" t="n">
-        <v>1.867174866042199</v>
+        <v>1.990846297584993</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.339578006298581e-07</v>
+        <v>0.1236712975849932</v>
       </c>
       <c r="I32" t="n">
-        <v>7.174357016876193e-06</v>
+        <v>6.623444379074976</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.174357016876193e-06</v>
+        <v>6.623444379074976</v>
       </c>
     </row>
     <row r="33">
@@ -3511,22 +3996,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.09799001800823975</v>
+        <v>0.1224241063353341</v>
       </c>
       <c r="F33" t="n">
         <v>2.28687304883645</v>
       </c>
       <c r="G33" t="n">
-        <v>2.030962613674672</v>
+        <v>2.114105809479522</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2559104351617782</v>
+        <v>-0.1727672393569279</v>
       </c>
       <c r="I33" t="n">
-        <v>11.19040846154465</v>
+        <v>7.554736781074537</v>
       </c>
       <c r="J33" t="n">
-        <v>-11.19040846154465</v>
+        <v>-7.554736781074537</v>
       </c>
     </row>
     <row r="34">
@@ -3547,22 +4032,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.09799001800823975</v>
+        <v>0.1224241063353341</v>
       </c>
       <c r="F34" t="n">
         <v>2.66701875</v>
       </c>
       <c r="G34" t="n">
-        <v>2.417046990365911</v>
+        <v>2.436850869840432</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2499717596340894</v>
+        <v>-0.2301678801595677</v>
       </c>
       <c r="I34" t="n">
-        <v>9.372703496519826</v>
+        <v>8.63015605569206</v>
       </c>
       <c r="J34" t="n">
-        <v>-9.372703496519826</v>
+        <v>-8.63015605569206</v>
       </c>
     </row>
     <row r="35">
@@ -3685,22 +4170,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.06629982941511016</v>
+        <v>0.07673171926436299</v>
       </c>
       <c r="F38" t="n">
         <v>2.1235625</v>
       </c>
       <c r="G38" t="n">
-        <v>2.123564941866762</v>
+        <v>2.182476425450682</v>
       </c>
       <c r="H38" t="n">
-        <v>2.441866761682121e-06</v>
+        <v>0.05891392545068141</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0001149891638076167</v>
+        <v>2.774296751363871</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0001149891638076167</v>
+        <v>2.774296751363871</v>
       </c>
     </row>
     <row r="39">
@@ -3721,22 +4206,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.06629982941511016</v>
+        <v>0.07673171926436299</v>
       </c>
       <c r="F39" t="n">
         <v>2.4008625</v>
       </c>
       <c r="G39" t="n">
-        <v>2.274248842371021</v>
+        <v>2.310628387202411</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.1266136576289787</v>
+        <v>-0.09023411279758875</v>
       </c>
       <c r="I39" t="n">
-        <v>5.273673841337382</v>
+        <v>3.758404023453603</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.273673841337382</v>
+        <v>-3.758404023453603</v>
       </c>
     </row>
     <row r="40">
@@ -3757,22 +4242,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.06629982941511016</v>
+        <v>0.07673171926436299</v>
       </c>
       <c r="F40" t="n">
         <v>2.706496875</v>
       </c>
       <c r="G40" t="n">
-        <v>2.588159868914718</v>
+        <v>2.595375287527376</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.1183370060852815</v>
+        <v>-0.1111215874726241</v>
       </c>
       <c r="I40" t="n">
-        <v>4.372331155389992</v>
+        <v>4.10573492617183</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.372331155389992</v>
+        <v>-4.10573492617183</v>
       </c>
     </row>
     <row r="41">
@@ -3793,22 +4278,22 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.08194993605837791</v>
+        <v>0.09275945529426537</v>
       </c>
       <c r="F41" t="n">
         <v>2.1235625</v>
       </c>
       <c r="G41" t="n">
-        <v>2.123562887612386</v>
+        <v>2.183490252827478</v>
       </c>
       <c r="H41" t="n">
-        <v>3.876123852997182e-07</v>
+        <v>0.05992775282747731</v>
       </c>
       <c r="I41" t="n">
-        <v>1.825293040820405e-05</v>
+        <v>2.822038570914551</v>
       </c>
       <c r="J41" t="n">
-        <v>1.825293040820405e-05</v>
+        <v>2.822038570914551</v>
       </c>
     </row>
     <row r="42">
@@ -3829,22 +4314,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.08194993605837791</v>
+        <v>0.09275945529426537</v>
       </c>
       <c r="F42" t="n">
         <v>2.4008625</v>
       </c>
       <c r="G42" t="n">
-        <v>2.272877745537396</v>
+        <v>2.310169403438366</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.127984754462604</v>
+        <v>-0.09069309656163371</v>
       </c>
       <c r="I42" t="n">
-        <v>5.330782352700501</v>
+        <v>3.777521476620745</v>
       </c>
       <c r="J42" t="n">
-        <v>-5.330782352700501</v>
+        <v>-3.777521476620745</v>
       </c>
     </row>
     <row r="43">
@@ -3865,22 +4350,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.08194993605837791</v>
+        <v>0.09275945529426537</v>
       </c>
       <c r="F43" t="n">
         <v>2.706496875</v>
       </c>
       <c r="G43" t="n">
-        <v>2.586890316385364</v>
+        <v>2.594405142425781</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.119606558614636</v>
+        <v>-0.1120917325742186</v>
       </c>
       <c r="I43" t="n">
-        <v>4.419238748045331</v>
+        <v>4.141579974084343</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.419238748045331</v>
+        <v>-4.141579974084343</v>
       </c>
     </row>
     <row r="44">
@@ -4003,22 +4488,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.08850039773988014</v>
+        <v>0.1041321540632679</v>
       </c>
       <c r="F47" t="n">
         <v>2.244775</v>
       </c>
       <c r="G47" t="n">
-        <v>2.244776304299928</v>
+        <v>2.299649822364726</v>
       </c>
       <c r="H47" t="n">
-        <v>1.304299927618047e-06</v>
+        <v>0.05487482236472552</v>
       </c>
       <c r="I47" t="n">
-        <v>5.810381564379711e-05</v>
+        <v>2.444557800435478</v>
       </c>
       <c r="J47" t="n">
-        <v>5.810381564379711e-05</v>
+        <v>2.444557800435478</v>
       </c>
     </row>
     <row r="48">
@@ -4039,22 +4524,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.08850039773988014</v>
+        <v>0.1041321540632679</v>
       </c>
       <c r="F48" t="n">
         <v>2.456699651526272</v>
       </c>
       <c r="G48" t="n">
-        <v>2.352802527307538</v>
+        <v>2.389298917857957</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.1038971242187339</v>
+        <v>-0.06740073366831467</v>
       </c>
       <c r="I48" t="n">
-        <v>4.229134161930856</v>
+        <v>2.743547980170904</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.229134161930856</v>
+        <v>-2.743547980170904</v>
       </c>
     </row>
     <row r="49">
@@ -4075,22 +4560,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.08850039773988014</v>
+        <v>0.1041321540632679</v>
       </c>
       <c r="F49" t="n">
         <v>2.72750625</v>
       </c>
       <c r="G49" t="n">
-        <v>2.60785051919474</v>
+        <v>2.616302780189103</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1196557308052602</v>
+        <v>-0.1112034698108975</v>
       </c>
       <c r="I49" t="n">
-        <v>4.387001159218614</v>
+        <v>4.077111457064396</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.387001159218614</v>
+        <v>-4.077111457064396</v>
       </c>
     </row>
     <row r="50">
@@ -4111,22 +4596,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.1042585113052578</v>
+        <v>0.1203515230058849</v>
       </c>
       <c r="F50" t="n">
         <v>2.244775</v>
       </c>
       <c r="G50" t="n">
-        <v>2.244777471000068</v>
+        <v>2.300375949960357</v>
       </c>
       <c r="H50" t="n">
-        <v>2.47100006767198e-06</v>
+        <v>0.05560094996035669</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0001100778504603793</v>
+        <v>2.476905255999229</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0001100778504603793</v>
+        <v>2.476905255999229</v>
       </c>
     </row>
     <row r="51">
@@ -4147,22 +4632,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.1042585113052578</v>
+        <v>0.1203515230058849</v>
       </c>
       <c r="F51" t="n">
         <v>2.456699651526272</v>
       </c>
       <c r="G51" t="n">
-        <v>2.351947469376718</v>
+        <v>2.389148486268567</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1047521821495541</v>
+        <v>-0.06755116525770521</v>
       </c>
       <c r="I51" t="n">
-        <v>4.263939309165235</v>
+        <v>2.749671300508296</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.263939309165235</v>
+        <v>-2.749671300508296</v>
       </c>
     </row>
     <row r="52">
@@ -4183,22 +4668,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.1042585113052578</v>
+        <v>0.1203515230058849</v>
       </c>
       <c r="F52" t="n">
         <v>2.72750625</v>
       </c>
       <c r="G52" t="n">
-        <v>2.606926203689408</v>
+        <v>2.6156631799352</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1205800463105926</v>
+        <v>-0.1118430700648001</v>
       </c>
       <c r="I52" t="n">
-        <v>4.420889826030375</v>
+        <v>4.100561458467789</v>
       </c>
       <c r="J52" t="n">
-        <v>-4.420889826030375</v>
+        <v>-4.100561458467789</v>
       </c>
     </row>
     <row r="53">
@@ -4321,22 +4806,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.08631537829714603</v>
+        <v>0.1091827019556289</v>
       </c>
       <c r="F56" t="n">
         <v>2.26715</v>
       </c>
       <c r="G56" t="n">
-        <v>2.267151507008899</v>
+        <v>2.343512087728207</v>
       </c>
       <c r="H56" t="n">
-        <v>1.507008899004347e-06</v>
+        <v>0.07636208772820652</v>
       </c>
       <c r="I56" t="n">
-        <v>6.647151264823004e-05</v>
+        <v>3.368197416501181</v>
       </c>
       <c r="J56" t="n">
-        <v>6.647151264823004e-05</v>
+        <v>3.368197416501181</v>
       </c>
     </row>
     <row r="57">
@@ -4357,22 +4842,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.08631537829714603</v>
+        <v>0.1091827019556289</v>
       </c>
       <c r="F57" t="n">
         <v>2.52625</v>
       </c>
       <c r="G57" t="n">
-        <v>2.374637713976577</v>
+        <v>2.425391000127505</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.1516122860234232</v>
+        <v>-0.1008589998724956</v>
       </c>
       <c r="I57" t="n">
-        <v>6.001475943529866</v>
+        <v>3.992439381395173</v>
       </c>
       <c r="J57" t="n">
-        <v>-6.001475943529866</v>
+        <v>-3.992439381395173</v>
       </c>
     </row>
     <row r="58">
@@ -4393,22 +4878,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.08631537829714603</v>
+        <v>0.1091827019556289</v>
       </c>
       <c r="F58" t="n">
         <v>2.74761875</v>
       </c>
       <c r="G58" t="n">
-        <v>2.624182337858529</v>
+        <v>2.635925165023929</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.1234364121414706</v>
+        <v>-0.1116935849760714</v>
       </c>
       <c r="I58" t="n">
-        <v>4.492486890383559</v>
+        <v>4.065104919526095</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.492486890383559</v>
+        <v>-4.065104919526095</v>
       </c>
     </row>
     <row r="59">
@@ -4429,22 +4914,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.1012018247808178</v>
+        <v>0.1246478537064422</v>
       </c>
       <c r="F59" t="n">
         <v>2.26715</v>
       </c>
       <c r="G59" t="n">
-        <v>2.267152033652461</v>
+        <v>2.344253865545764</v>
       </c>
       <c r="H59" t="n">
-        <v>2.033652460653457e-06</v>
+        <v>0.07710386554576365</v>
       </c>
       <c r="I59" t="n">
-        <v>8.970083411567196e-05</v>
+        <v>3.400915931710017</v>
       </c>
       <c r="J59" t="n">
-        <v>8.970083411567196e-05</v>
+        <v>3.400915931710017</v>
       </c>
     </row>
     <row r="60">
@@ -4465,22 +4950,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.1012018247808178</v>
+        <v>0.1246478537064422</v>
       </c>
       <c r="F60" t="n">
         <v>2.52625</v>
       </c>
       <c r="G60" t="n">
-        <v>2.373818812401554</v>
+        <v>2.42535804197251</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.1524311875984461</v>
+        <v>-0.1008919580274901</v>
       </c>
       <c r="I60" t="n">
-        <v>6.033891641699993</v>
+        <v>3.993744009005049</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.033891641699993</v>
+        <v>-3.993744009005049</v>
       </c>
     </row>
     <row r="61">
@@ -4501,22 +4986,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.1012018247808178</v>
+        <v>0.1246478537064422</v>
       </c>
       <c r="F61" t="n">
         <v>2.74761875</v>
       </c>
       <c r="G61" t="n">
-        <v>2.62331603366684</v>
+        <v>2.635400433275456</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.12430271633316</v>
+        <v>-0.1122183167245443</v>
       </c>
       <c r="I61" t="n">
-        <v>4.52401616247378</v>
+        <v>4.084202610880578</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.52401616247378</v>
+        <v>-4.084202610880578</v>
       </c>
     </row>
     <row r="62">
@@ -4639,22 +5124,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.07158956549382076</v>
+        <v>0.09014147517354235</v>
       </c>
       <c r="F65" t="n">
         <v>2.29725</v>
       </c>
       <c r="G65" t="n">
-        <v>2.297250261141891</v>
+        <v>2.373681864459013</v>
       </c>
       <c r="H65" t="n">
-        <v>2.611418907783047e-07</v>
+        <v>0.07643186445901273</v>
       </c>
       <c r="I65" t="n">
-        <v>1.136758693125714e-05</v>
+        <v>3.327102599151714</v>
       </c>
       <c r="J65" t="n">
-        <v>1.136758693125714e-05</v>
+        <v>3.327102599151714</v>
       </c>
     </row>
     <row r="66">
@@ -4675,22 +5160,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.07158956549382076</v>
+        <v>0.09014147517354235</v>
       </c>
       <c r="F66" t="n">
         <v>2.571281674253069</v>
       </c>
       <c r="G66" t="n">
-        <v>2.417001332812301</v>
+        <v>2.464912855792651</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.1542803414407681</v>
+        <v>-0.1063688184604179</v>
       </c>
       <c r="I66" t="n">
-        <v>6.000133823750948</v>
+        <v>4.13680148408155</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.000133823750948</v>
+        <v>-4.13680148408155</v>
       </c>
     </row>
     <row r="67">
@@ -4711,22 +5196,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.07158956549382076</v>
+        <v>0.09014147517354235</v>
       </c>
       <c r="F67" t="n">
         <v>2.817765625</v>
       </c>
       <c r="G67" t="n">
-        <v>2.667482718028083</v>
+        <v>2.677273536533558</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.1502829069719169</v>
+        <v>-0.1404920884664422</v>
       </c>
       <c r="I67" t="n">
-        <v>5.333406924925381</v>
+        <v>4.985939469910392</v>
       </c>
       <c r="J67" t="n">
-        <v>-5.333406924925381</v>
+        <v>-4.985939469910392</v>
       </c>
     </row>
     <row r="68">
@@ -4747,22 +5232,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.08391244363649571</v>
+        <v>0.1029214781576894</v>
       </c>
       <c r="F68" t="n">
         <v>2.29725</v>
       </c>
       <c r="G68" t="n">
-        <v>2.297251120734176</v>
+        <v>2.37444431416273</v>
       </c>
       <c r="H68" t="n">
-        <v>1.120734175685811e-06</v>
+        <v>0.07719431416273048</v>
       </c>
       <c r="I68" t="n">
-        <v>4.878590382787295e-05</v>
+        <v>3.360292269571465</v>
       </c>
       <c r="J68" t="n">
-        <v>4.878590382787295e-05</v>
+        <v>3.360292269571465</v>
       </c>
     </row>
     <row r="69">
@@ -4783,22 +5268,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.08391244363649571</v>
+        <v>0.1029214781576894</v>
       </c>
       <c r="F69" t="n">
         <v>2.571281674253069</v>
       </c>
       <c r="G69" t="n">
-        <v>2.416163507745431</v>
+        <v>2.464832124194581</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.1551181665076382</v>
+        <v>-0.1064495500584881</v>
       </c>
       <c r="I69" t="n">
-        <v>6.032717771097499</v>
+        <v>4.139941225591731</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.032717771097499</v>
+        <v>-4.139941225591731</v>
       </c>
     </row>
     <row r="70">
@@ -4819,22 +5304,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.08391244363649571</v>
+        <v>0.1029214781576894</v>
       </c>
       <c r="F70" t="n">
         <v>2.817765625</v>
       </c>
       <c r="G70" t="n">
-        <v>2.6667037653719</v>
+        <v>2.676771719576949</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.1510618596281001</v>
+        <v>-0.1409939054230511</v>
       </c>
       <c r="I70" t="n">
-        <v>5.361051263023345</v>
+        <v>5.00374850811274</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.361051263023345</v>
+        <v>-5.00374850811274</v>
       </c>
     </row>
     <row r="71">
@@ -4957,22 +5442,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.07041259839357256</v>
+        <v>0.1135228868599596</v>
       </c>
       <c r="F74" t="n">
         <v>2.3428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.342801509019313</v>
+        <v>2.48216120494328</v>
       </c>
       <c r="H74" t="n">
-        <v>1.509019313949977e-06</v>
+        <v>0.1393612049432806</v>
       </c>
       <c r="I74" t="n">
-        <v>6.441093195962002e-05</v>
+        <v>5.948489198535115</v>
       </c>
       <c r="J74" t="n">
-        <v>6.441093195962002e-05</v>
+        <v>5.948489198535115</v>
       </c>
     </row>
     <row r="75">
@@ -4993,22 +5478,22 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.07041259839357256</v>
+        <v>0.1135228868599596</v>
       </c>
       <c r="F75" t="n">
         <v>2.72115</v>
       </c>
       <c r="G75" t="n">
-        <v>2.457505936937378</v>
+        <v>2.546705618283628</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.2636440630626216</v>
+        <v>-0.1744443817163721</v>
       </c>
       <c r="I75" t="n">
-        <v>9.68870011071134</v>
+        <v>6.410685986306236</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.68870011071134</v>
+        <v>-6.410685986306236</v>
       </c>
     </row>
     <row r="76">
@@ -5029,22 +5514,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.07041259839357256</v>
+        <v>0.1135228868599596</v>
       </c>
       <c r="F76" t="n">
         <v>2.965825</v>
       </c>
       <c r="G76" t="n">
-        <v>2.693044111791964</v>
+        <v>2.712160681070053</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.2727808882080356</v>
+        <v>-0.2536643189299466</v>
       </c>
       <c r="I76" t="n">
-        <v>9.197470795075084</v>
+        <v>8.552909188166753</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.197470795075084</v>
+        <v>-8.552909188166753</v>
       </c>
     </row>
     <row r="77">
@@ -5065,22 +5550,22 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.08158045301163148</v>
+        <v>0.1255800995875918</v>
       </c>
       <c r="F77" t="n">
         <v>2.3428</v>
       </c>
       <c r="G77" t="n">
-        <v>2.342799813544805</v>
+        <v>2.483078199813127</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.864551943953074e-07</v>
+        <v>0.1402781998131277</v>
       </c>
       <c r="I77" t="n">
-        <v>7.95864753266636e-06</v>
+        <v>5.987630178125651</v>
       </c>
       <c r="J77" t="n">
-        <v>-7.95864753266636e-06</v>
+        <v>5.987630178125651</v>
       </c>
     </row>
     <row r="78">
@@ -5101,22 +5586,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.08158045301163148</v>
+        <v>0.1255800995875918</v>
       </c>
       <c r="F78" t="n">
         <v>2.72115</v>
       </c>
       <c r="G78" t="n">
-        <v>2.456769354850167</v>
+        <v>2.547011524595036</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.2643806451498323</v>
+        <v>-0.1741384754049635</v>
       </c>
       <c r="I78" t="n">
-        <v>9.715768889985203</v>
+        <v>6.399444183707753</v>
       </c>
       <c r="J78" t="n">
-        <v>-9.715768889985203</v>
+        <v>-6.399444183707753</v>
       </c>
     </row>
     <row r="79">
@@ -5137,22 +5622,22 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.08158045301163148</v>
+        <v>0.1255800995875918</v>
       </c>
       <c r="F79" t="n">
         <v>2.965825</v>
       </c>
       <c r="G79" t="n">
-        <v>2.692375992688834</v>
+        <v>2.711930874788076</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.2734490073111662</v>
+        <v>-0.2538941252119238</v>
       </c>
       <c r="I79" t="n">
-        <v>9.219998054880723</v>
+        <v>8.560657665638525</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.219998054880723</v>
+        <v>-8.560657665638525</v>
       </c>
     </row>
     <row r="80">
@@ -5275,22 +5760,22 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.07519263589067139</v>
+        <v>0.09373764106886844</v>
       </c>
       <c r="F83" t="n">
         <v>2.252275</v>
       </c>
       <c r="G83" t="n">
-        <v>2.252276590197015</v>
+        <v>2.328152345929773</v>
       </c>
       <c r="H83" t="n">
-        <v>1.590197014955663e-06</v>
+        <v>0.07587734592977347</v>
       </c>
       <c r="I83" t="n">
-        <v>7.060403436328437e-05</v>
+        <v>3.368920133188596</v>
       </c>
       <c r="J83" t="n">
-        <v>7.060403436328437e-05</v>
+        <v>3.368920133188596</v>
       </c>
     </row>
     <row r="84">
@@ -5311,22 +5796,22 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.07519263589067139</v>
+        <v>0.09373764106886844</v>
       </c>
       <c r="F84" t="n">
         <v>2.528852109678786</v>
       </c>
       <c r="G84" t="n">
-        <v>2.373612969180975</v>
+        <v>2.422077206094573</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.1552391404978111</v>
+        <v>-0.1067749035842125</v>
       </c>
       <c r="I84" t="n">
-        <v>6.138719615261705</v>
+        <v>4.222267612073805</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.138719615261705</v>
+        <v>-4.222267612073805</v>
       </c>
     </row>
     <row r="85">
@@ -5347,22 +5832,22 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.07519263589067139</v>
+        <v>0.09373764106886844</v>
       </c>
       <c r="F85" t="n">
         <v>2.768703125</v>
       </c>
       <c r="G85" t="n">
-        <v>2.636597197011161</v>
+        <v>2.646890894935022</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.1321059279888388</v>
+        <v>-0.121812230064978</v>
       </c>
       <c r="I85" t="n">
-        <v>4.771400978168751</v>
+        <v>4.399613268937166</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.771400978168751</v>
+        <v>-4.399613268937166</v>
       </c>
     </row>
     <row r="86">
@@ -5383,22 +5868,22 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.08904076119261407</v>
+        <v>0.108079059935932</v>
       </c>
       <c r="F86" t="n">
         <v>2.252275</v>
       </c>
       <c r="G86" t="n">
-        <v>2.252276633895959</v>
+        <v>2.32896554608072</v>
       </c>
       <c r="H86" t="n">
-        <v>1.633895958530474e-06</v>
+        <v>0.07669054608072035</v>
       </c>
       <c r="I86" t="n">
-        <v>7.254424786184962e-05</v>
+        <v>3.405025855222846</v>
       </c>
       <c r="J86" t="n">
-        <v>7.254424786184962e-05</v>
+        <v>3.405025855222846</v>
       </c>
     </row>
     <row r="87">
@@ -5419,22 +5904,22 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.08904076119261407</v>
+        <v>0.108079059935932</v>
       </c>
       <c r="F87" t="n">
         <v>2.528852109678786</v>
       </c>
       <c r="G87" t="n">
-        <v>2.37268426284412</v>
+        <v>2.42196800403284</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.1561678468346654</v>
+        <v>-0.1068841056459462</v>
       </c>
       <c r="I87" t="n">
-        <v>6.17544403790785</v>
+        <v>4.226585858337228</v>
       </c>
       <c r="J87" t="n">
-        <v>-6.17544403790785</v>
+        <v>-4.226585858337228</v>
       </c>
     </row>
     <row r="88">
@@ -5455,22 +5940,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.08904076119261407</v>
+        <v>0.108079059935932</v>
       </c>
       <c r="F88" t="n">
         <v>2.768703125</v>
       </c>
       <c r="G88" t="n">
-        <v>2.63569512335154</v>
+        <v>2.646303579612281</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.1330080016484598</v>
+        <v>-0.1223995453877191</v>
       </c>
       <c r="I88" t="n">
-        <v>4.803982068263813</v>
+        <v>4.420825919634094</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.803982068263813</v>
+        <v>-4.420825919634094</v>
       </c>
     </row>
     <row r="89">
@@ -5593,22 +6078,22 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.08455531212179532</v>
+        <v>0.1207109757987655</v>
       </c>
       <c r="F92" t="n">
         <v>2.31575</v>
       </c>
       <c r="G92" t="n">
-        <v>2.315750635678214</v>
+        <v>2.421858282228072</v>
       </c>
       <c r="H92" t="n">
-        <v>6.35678213622981e-07</v>
+        <v>0.1061082822280719</v>
       </c>
       <c r="I92" t="n">
-        <v>2.745020894409936e-05</v>
+        <v>4.582026653484697</v>
       </c>
       <c r="J92" t="n">
-        <v>2.745020894409936e-05</v>
+        <v>4.582026653484697</v>
       </c>
     </row>
     <row r="93">
@@ -5629,22 +6114,22 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.08455531212179532</v>
+        <v>0.1207109757987655</v>
       </c>
       <c r="F93" t="n">
         <v>2.621187071667337</v>
       </c>
       <c r="G93" t="n">
-        <v>2.418984344459306</v>
+        <v>2.489751972752026</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.2022027272080309</v>
+        <v>-0.1314350989153117</v>
       </c>
       <c r="I93" t="n">
-        <v>7.714166203307639</v>
+        <v>5.014334930001993</v>
       </c>
       <c r="J93" t="n">
-        <v>-7.714166203307639</v>
+        <v>-5.014334930001993</v>
       </c>
     </row>
     <row r="94">
@@ -5665,22 +6150,22 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.08455531212179532</v>
+        <v>0.1207109757987655</v>
       </c>
       <c r="F94" t="n">
         <v>2.839534374999999</v>
       </c>
       <c r="G94" t="n">
-        <v>2.653983380357527</v>
+        <v>2.670507773724476</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.1855509946424729</v>
+        <v>-0.1690266012755233</v>
       </c>
       <c r="I94" t="n">
-        <v>6.534557083587797</v>
+        <v>5.952616836185451</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.534557083587797</v>
+        <v>-5.952616836185451</v>
       </c>
     </row>
     <row r="95">
@@ -5701,22 +6186,22 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.09798106554163073</v>
+        <v>0.1349242852469897</v>
       </c>
       <c r="F95" t="n">
         <v>2.31575</v>
       </c>
       <c r="G95" t="n">
-        <v>2.315752347417197</v>
+        <v>2.422635665800264</v>
       </c>
       <c r="H95" t="n">
-        <v>2.347417196624235e-06</v>
+        <v>0.1068856658002644</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0001013674704361108</v>
+        <v>4.615596061762469</v>
       </c>
       <c r="J95" t="n">
-        <v>0.0001013674704361108</v>
+        <v>4.615596061762469</v>
       </c>
     </row>
     <row r="96">
@@ -5737,22 +6222,22 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.09798106554163073</v>
+        <v>0.1349242852469897</v>
       </c>
       <c r="F96" t="n">
         <v>2.621187071667337</v>
       </c>
       <c r="G96" t="n">
-        <v>2.418263409140534</v>
+        <v>2.489915616363612</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.2029236625268029</v>
+        <v>-0.1312714553037257</v>
       </c>
       <c r="I96" t="n">
-        <v>7.741670356924322</v>
+        <v>5.008091819262025</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.741670356924322</v>
+        <v>-5.008091819262025</v>
       </c>
     </row>
     <row r="97">
@@ -5773,22 +6258,22 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.09798106554163073</v>
+        <v>0.1349242852469897</v>
       </c>
       <c r="F97" t="n">
         <v>2.839534374999999</v>
       </c>
       <c r="G97" t="n">
-        <v>2.653238952013967</v>
+        <v>2.670172459200731</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.1862954229860323</v>
+        <v>-0.1693619157992683</v>
       </c>
       <c r="I97" t="n">
-        <v>6.560773647476352</v>
+        <v>5.964425621692582</v>
       </c>
       <c r="J97" t="n">
-        <v>-6.560773647476352</v>
+        <v>-5.964425621692582</v>
       </c>
     </row>
     <row r="98">
@@ -5911,22 +6396,22 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.07649558994396592</v>
+        <v>0.09064935244750821</v>
       </c>
       <c r="F101" t="n">
         <v>1.7076125</v>
       </c>
       <c r="G101" t="n">
-        <v>1.707614570246341</v>
+        <v>1.787236445425896</v>
       </c>
       <c r="H101" t="n">
-        <v>2.070246341245863e-06</v>
+        <v>0.07962394542589579</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0001212363074904794</v>
+        <v>4.66288138707674</v>
       </c>
       <c r="J101" t="n">
-        <v>0.0001212363074904794</v>
+        <v>4.66288138707674</v>
       </c>
     </row>
     <row r="102">
@@ -5947,22 +6432,22 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.07649558994396592</v>
+        <v>0.09064935244750821</v>
       </c>
       <c r="F102" t="n">
         <v>2.05415</v>
       </c>
       <c r="G102" t="n">
-        <v>1.881066852545645</v>
+        <v>1.935014180390821</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.1730831474543548</v>
+        <v>-0.1191358196091785</v>
       </c>
       <c r="I102" t="n">
-        <v>8.426022805265186</v>
+        <v>5.799762413123605</v>
       </c>
       <c r="J102" t="n">
-        <v>-8.426022805265186</v>
+        <v>-5.799762413123605</v>
       </c>
     </row>
     <row r="103">
@@ -5983,22 +6468,22 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.07649558994396592</v>
+        <v>0.09064935244750821</v>
       </c>
       <c r="F103" t="n">
         <v>2.45671875</v>
       </c>
       <c r="G103" t="n">
-        <v>2.307684191971354</v>
+        <v>2.320755643943109</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.1490345580286463</v>
+        <v>-0.1359631060568911</v>
       </c>
       <c r="I103" t="n">
-        <v>6.066406992198284</v>
+        <v>5.534337459544</v>
       </c>
       <c r="J103" t="n">
-        <v>-6.066406992198284</v>
+        <v>-5.534337459544</v>
       </c>
     </row>
     <row r="104">
@@ -6019,22 +6504,22 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.1075030182024911</v>
+        <v>0.1225019912041175</v>
       </c>
       <c r="F104" t="n">
         <v>1.7076125</v>
       </c>
       <c r="G104" t="n">
-        <v>1.707614667005786</v>
+        <v>1.789341404643739</v>
       </c>
       <c r="H104" t="n">
-        <v>2.167005785924658e-06</v>
+        <v>0.08172890464373883</v>
       </c>
       <c r="I104" t="n">
-        <v>0.000126902665910718</v>
+        <v>4.786150525586972</v>
       </c>
       <c r="J104" t="n">
-        <v>0.000126902665910718</v>
+        <v>4.786150525586972</v>
       </c>
     </row>
     <row r="105">
@@ -6055,22 +6540,22 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.1075030182024911</v>
+        <v>0.1225019912041175</v>
       </c>
       <c r="F105" t="n">
         <v>2.05415</v>
       </c>
       <c r="G105" t="n">
-        <v>1.878313133974517</v>
+        <v>1.934333730903205</v>
       </c>
       <c r="H105" t="n">
-        <v>-0.1758368660254825</v>
+        <v>-0.1198162690967952</v>
       </c>
       <c r="I105" t="n">
-        <v>8.560079158069399</v>
+        <v>5.832888011917105</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.560079158069399</v>
+        <v>-5.832888011917105</v>
       </c>
     </row>
     <row r="106">
@@ -6091,22 +6576,22 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.1075030182024911</v>
+        <v>0.1225019912041175</v>
       </c>
       <c r="F106" t="n">
         <v>2.45671875</v>
       </c>
       <c r="G106" t="n">
-        <v>2.304531923603168</v>
+        <v>2.318490007032654</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.1521868263968322</v>
+        <v>-0.1382287429673461</v>
       </c>
       <c r="I106" t="n">
-        <v>6.19471913082571</v>
+        <v>5.626559530566782</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.19471913082571</v>
+        <v>-5.626559530566782</v>
       </c>
     </row>
     <row r="107">
@@ -6229,22 +6714,22 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.08746020600723763</v>
+        <v>0.08687490823942555</v>
       </c>
       <c r="F110" t="n">
         <v>2.3283</v>
       </c>
       <c r="G110" t="n">
-        <v>2.328299080399431</v>
+        <v>2.326095557830055</v>
       </c>
       <c r="H110" t="n">
-        <v>-9.196005694711573e-07</v>
+        <v>-0.002204442169945864</v>
       </c>
       <c r="I110" t="n">
-        <v>3.949665290001963e-05</v>
+        <v>0.09468033199956463</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.949665290001963e-05</v>
+        <v>-0.09468033199956463</v>
       </c>
     </row>
     <row r="111">
@@ -6265,22 +6750,22 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.08746020600723763</v>
+        <v>0.08687490823942555</v>
       </c>
       <c r="F111" t="n">
         <v>2.4123875</v>
       </c>
       <c r="G111" t="n">
-        <v>2.427355269123317</v>
+        <v>2.42593632513999</v>
       </c>
       <c r="H111" t="n">
-        <v>0.01496776912331743</v>
+        <v>0.01354882513998978</v>
       </c>
       <c r="I111" t="n">
-        <v>0.6204545962585792</v>
+        <v>0.5616355224850811</v>
       </c>
       <c r="J111" t="n">
-        <v>0.6204545962585792</v>
+        <v>0.5616355224850811</v>
       </c>
     </row>
     <row r="112">
@@ -6301,22 +6786,22 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.08746020600723763</v>
+        <v>0.08687490823942555</v>
       </c>
       <c r="F112" t="n">
         <v>2.71143125</v>
       </c>
       <c r="G112" t="n">
-        <v>2.656266745868415</v>
+        <v>2.655960667069876</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.05516450413158402</v>
+        <v>-0.05547058293012341</v>
       </c>
       <c r="I112" t="n">
-        <v>2.034516056108155</v>
+        <v>2.045804514871009</v>
       </c>
       <c r="J112" t="n">
-        <v>-2.034516056108155</v>
+        <v>-2.045804514871009</v>
       </c>
     </row>
     <row r="113">
@@ -6337,22 +6822,22 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.1008884035969615</v>
+        <v>0.1004009470577079</v>
       </c>
       <c r="F113" t="n">
         <v>2.3283</v>
       </c>
       <c r="G113" t="n">
-        <v>2.328298088271562</v>
+        <v>2.326487953329856</v>
       </c>
       <c r="H113" t="n">
-        <v>-1.911728438663829e-06</v>
+        <v>-0.001812046670144785</v>
       </c>
       <c r="I113" t="n">
-        <v>8.21083382151711e-05</v>
+        <v>0.07782702702163743</v>
       </c>
       <c r="J113" t="n">
-        <v>-8.21083382151711e-05</v>
+        <v>-0.07782702702163743</v>
       </c>
     </row>
     <row r="114">
@@ -6373,22 +6858,22 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.1008884035969615</v>
+        <v>0.1004009470577079</v>
       </c>
       <c r="F114" t="n">
         <v>2.4123875</v>
       </c>
       <c r="G114" t="n">
-        <v>2.426674898062199</v>
+        <v>2.42550276928761</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0142873980621987</v>
+        <v>0.01311526928761042</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5922513718131394</v>
+        <v>0.543663457367874</v>
       </c>
       <c r="J114" t="n">
-        <v>0.5922513718131394</v>
+        <v>0.543663457367874</v>
       </c>
     </row>
     <row r="115">
@@ -6409,22 +6894,22 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.1008884035969615</v>
+        <v>0.1004009470577079</v>
       </c>
       <c r="F115" t="n">
         <v>2.71143125</v>
       </c>
       <c r="G115" t="n">
-        <v>2.65555241605321</v>
+        <v>2.655296439634749</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.05587883394678972</v>
+        <v>-0.05613481036525014</v>
       </c>
       <c r="I115" t="n">
-        <v>2.060861176059313</v>
+        <v>2.070301814410753</v>
       </c>
       <c r="J115" t="n">
-        <v>-2.060861176059313</v>
+        <v>-2.070301814410753</v>
       </c>
     </row>
     <row r="116">
@@ -6547,22 +7032,22 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.2186428755542173</v>
+        <v>0.1743131185505807</v>
       </c>
       <c r="F119" t="n">
         <v>2.3587375</v>
       </c>
       <c r="G119" t="n">
-        <v>2.455950470799049</v>
+        <v>2.410654015445584</v>
       </c>
       <c r="H119" t="n">
-        <v>0.097212970799049</v>
+        <v>0.0519165154455834</v>
       </c>
       <c r="I119" t="n">
-        <v>4.121398451461809</v>
+        <v>2.201029807071936</v>
       </c>
       <c r="J119" t="n">
-        <v>4.121398451461809</v>
+        <v>2.201029807071936</v>
       </c>
     </row>
     <row r="120">
@@ -6583,22 +7068,22 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.2186428755542173</v>
+        <v>0.1743131185505807</v>
       </c>
       <c r="F120" t="n">
         <v>2.497631302525579</v>
       </c>
       <c r="G120" t="n">
-        <v>2.497630668499415</v>
+        <v>2.463061666812439</v>
       </c>
       <c r="H120" t="n">
-        <v>-6.340261635706668e-07</v>
+        <v>-0.0345696357131402</v>
       </c>
       <c r="I120" t="n">
-        <v>2.538509839020459e-05</v>
+        <v>1.384096831192968</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.538509839020459e-05</v>
+        <v>-1.384096831192968</v>
       </c>
     </row>
     <row r="121">
@@ -6619,22 +7104,22 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.2186428755542173</v>
+        <v>0.1743131185505807</v>
       </c>
       <c r="F121" t="n">
         <v>2.770865625</v>
       </c>
       <c r="G121" t="n">
-        <v>2.637394704142605</v>
+        <v>2.626092809621872</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.1334709208573948</v>
+        <v>-0.1447728153781278</v>
       </c>
       <c r="I121" t="n">
-        <v>4.816939502701246</v>
+        <v>5.224822671728363</v>
       </c>
       <c r="J121" t="n">
-        <v>-4.816939502701246</v>
+        <v>-5.224822671728363</v>
       </c>
     </row>
     <row r="122">
@@ -6655,22 +7140,22 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.236819832402668</v>
+        <v>0.1923657220418985</v>
       </c>
       <c r="F122" t="n">
         <v>2.3587375</v>
       </c>
       <c r="G122" t="n">
-        <v>2.456130411964771</v>
+        <v>2.41113771427487</v>
       </c>
       <c r="H122" t="n">
-        <v>0.09739291196477051</v>
+        <v>0.05240021427486985</v>
       </c>
       <c r="I122" t="n">
-        <v>4.12902715816281</v>
+        <v>2.221536490383938</v>
       </c>
       <c r="J122" t="n">
-        <v>4.12902715816281</v>
+        <v>2.221536490383938</v>
       </c>
     </row>
     <row r="123">
@@ -6691,22 +7176,22 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.236819832402668</v>
+        <v>0.1923657220418985</v>
       </c>
       <c r="F123" t="n">
         <v>2.497631302525579</v>
       </c>
       <c r="G123" t="n">
-        <v>2.497630544049202</v>
+        <v>2.463180821554812</v>
       </c>
       <c r="H123" t="n">
-        <v>-7.584763768164748e-07</v>
+        <v>-0.03445048097076686</v>
       </c>
       <c r="I123" t="n">
-        <v>3.036782795160804e-05</v>
+        <v>1.379326121350693</v>
       </c>
       <c r="J123" t="n">
-        <v>-3.036782795160804e-05</v>
+        <v>-1.379326121350693</v>
       </c>
     </row>
     <row r="124">
@@ -6727,22 +7212,22 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.236819832402668</v>
+        <v>0.1923657220418985</v>
       </c>
       <c r="F124" t="n">
         <v>2.770865625</v>
       </c>
       <c r="G124" t="n">
-        <v>2.637206324771463</v>
+        <v>2.625832052175499</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.1336593002285373</v>
+        <v>-0.1450335728245009</v>
       </c>
       <c r="I124" t="n">
-        <v>4.823738077465858</v>
+        <v>5.234233357112037</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.823738077465858</v>
+        <v>-5.234233357112037</v>
       </c>
     </row>
     <row r="125">
@@ -6865,22 +7350,22 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.07662637658294051</v>
+        <v>0.08545778587403147</v>
       </c>
       <c r="F128" t="n">
         <v>1.4346</v>
       </c>
       <c r="G128" t="n">
-        <v>1.43460245918304</v>
+        <v>1.487571980157216</v>
       </c>
       <c r="H128" t="n">
-        <v>2.459183039871249e-06</v>
+        <v>0.05297198015721549</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0001714194228266589</v>
+        <v>3.692456444807995</v>
       </c>
       <c r="J128" t="n">
-        <v>0.0001714194228266589</v>
+        <v>3.692456444807995</v>
       </c>
     </row>
     <row r="129">
@@ -6901,22 +7386,22 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.07662637658294051</v>
+        <v>0.08545778587403147</v>
       </c>
       <c r="F129" t="n">
         <v>1.737378411525397</v>
       </c>
       <c r="G129" t="n">
-        <v>1.622019989859316</v>
+        <v>1.658892773659786</v>
       </c>
       <c r="H129" t="n">
-        <v>-0.1153584216660808</v>
+        <v>-0.07848563786561091</v>
       </c>
       <c r="I129" t="n">
-        <v>6.639798267367531</v>
+        <v>4.517475142142552</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.639798267367531</v>
+        <v>-4.517475142142552</v>
       </c>
     </row>
     <row r="130">
@@ -6937,22 +7422,22 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.07662637658294051</v>
+        <v>0.08545778587403147</v>
       </c>
       <c r="F130" t="n">
         <v>2.244778125</v>
       </c>
       <c r="G130" t="n">
-        <v>2.114682119425784</v>
+        <v>2.124218602421106</v>
       </c>
       <c r="H130" t="n">
-        <v>-0.1300960055742157</v>
+        <v>-0.120559522578894</v>
       </c>
       <c r="I130" t="n">
-        <v>5.795495070329757</v>
+        <v>5.370665422841913</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.795495070329757</v>
+        <v>-5.370665422841913</v>
       </c>
     </row>
     <row r="131">
@@ -6973,22 +7458,22 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.1201360836897293</v>
+        <v>0.1298105555202281</v>
       </c>
       <c r="F131" t="n">
         <v>1.4346</v>
       </c>
       <c r="G131" t="n">
-        <v>1.434601680361081</v>
+        <v>1.490208706440479</v>
       </c>
       <c r="H131" t="n">
-        <v>1.680361081390913e-06</v>
+        <v>0.05560870644047844</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0001171309829493178</v>
+        <v>3.876251668791192</v>
       </c>
       <c r="J131" t="n">
-        <v>0.0001171309829493178</v>
+        <v>3.876251668791192</v>
       </c>
     </row>
     <row r="132">
@@ -7009,22 +7494,22 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.1201360836897293</v>
+        <v>0.1298105555202281</v>
       </c>
       <c r="F132" t="n">
         <v>1.737378411525397</v>
       </c>
       <c r="G132" t="n">
-        <v>1.618080998668611</v>
+        <v>1.657374735914716</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.1192974128567854</v>
+        <v>-0.08000367561068034</v>
       </c>
       <c r="I132" t="n">
-        <v>6.866518661990498</v>
+        <v>4.604850335422213</v>
       </c>
       <c r="J132" t="n">
-        <v>-6.866518661990498</v>
+        <v>-4.604850335422213</v>
       </c>
     </row>
     <row r="133">
@@ -7045,22 +7530,22 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.1201360836897293</v>
+        <v>0.1298105555202281</v>
       </c>
       <c r="F133" t="n">
         <v>2.244778125</v>
       </c>
       <c r="G133" t="n">
-        <v>2.109762728510258</v>
+        <v>2.120316038117671</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.135015396489742</v>
+        <v>-0.1244620868823287</v>
       </c>
       <c r="I133" t="n">
-        <v>6.014643273029135</v>
+        <v>5.544516203904506</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.014643273029135</v>
+        <v>-5.544516203904506</v>
       </c>
     </row>
     <row r="134">
@@ -7183,22 +7668,22 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.05726532872156408</v>
+        <v>0.06558424354601573</v>
       </c>
       <c r="F137" t="n">
         <v>1.88635</v>
       </c>
       <c r="G137" t="n">
-        <v>1.886349694177938</v>
+        <v>1.950594309479681</v>
       </c>
       <c r="H137" t="n">
-        <v>-3.058220623408658e-07</v>
+        <v>0.06424430947968096</v>
       </c>
       <c r="I137" t="n">
-        <v>1.621237110509003e-05</v>
+        <v>3.405747050106341</v>
       </c>
       <c r="J137" t="n">
-        <v>-1.621237110509003e-05</v>
+        <v>3.405747050106341</v>
       </c>
     </row>
     <row r="138">
@@ -7219,22 +7704,22 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.05726532872156408</v>
+        <v>0.06558424354601573</v>
       </c>
       <c r="F138" t="n">
         <v>2.2409375</v>
       </c>
       <c r="G138" t="n">
-        <v>2.083740315145228</v>
+        <v>2.122783949817104</v>
       </c>
       <c r="H138" t="n">
-        <v>-0.157197184854772</v>
+        <v>-0.1181535501828965</v>
       </c>
       <c r="I138" t="n">
-        <v>7.01479558688147</v>
+        <v>5.272505377008351</v>
       </c>
       <c r="J138" t="n">
-        <v>-7.01479558688147</v>
+        <v>-5.272505377008351</v>
       </c>
     </row>
     <row r="139">
@@ -7255,22 +7740,22 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.05726532872156408</v>
+        <v>0.06558424354601573</v>
       </c>
       <c r="F139" t="n">
         <v>2.565471875</v>
       </c>
       <c r="G139" t="n">
-        <v>2.486393244968921</v>
+        <v>2.493908339672332</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.07907863003107884</v>
+        <v>-0.07156353532766824</v>
       </c>
       <c r="I139" t="n">
-        <v>3.082420462359535</v>
+        <v>2.789488203906669</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.082420462359535</v>
+        <v>-2.789488203906669</v>
       </c>
     </row>
     <row r="140">
@@ -7291,22 +7776,22 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.07717316817023095</v>
+        <v>0.08590321249115156</v>
       </c>
       <c r="F140" t="n">
         <v>1.88635</v>
       </c>
       <c r="G140" t="n">
-        <v>1.886353589621563</v>
+        <v>1.952150306031139</v>
       </c>
       <c r="H140" t="n">
-        <v>3.589621562660739e-06</v>
+        <v>0.06580030603113918</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0001902945668969565</v>
+        <v>3.488234210572756</v>
       </c>
       <c r="J140" t="n">
-        <v>0.0001902945668969565</v>
+        <v>3.488234210572756</v>
       </c>
     </row>
     <row r="141">
@@ -7327,22 +7812,22 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.07717316817023095</v>
+        <v>0.08590321249115156</v>
       </c>
       <c r="F141" t="n">
         <v>2.2409375</v>
       </c>
       <c r="G141" t="n">
-        <v>2.081362044028959</v>
+        <v>2.121765749565748</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.1595754559710412</v>
+        <v>-0.1191717504342522</v>
       </c>
       <c r="I141" t="n">
-        <v>7.120923986993888</v>
+        <v>5.317941729042073</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.120923986993888</v>
+        <v>-5.317941729042073</v>
       </c>
     </row>
     <row r="142">
@@ -7363,22 +7848,22 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.07717316817023095</v>
+        <v>0.08590321249115156</v>
       </c>
       <c r="F142" t="n">
         <v>2.565471875</v>
       </c>
       <c r="G142" t="n">
-        <v>2.484237378899032</v>
+        <v>2.492179061406731</v>
       </c>
       <c r="H142" t="n">
-        <v>-0.08123449610096856</v>
+        <v>-0.07329281359326956</v>
       </c>
       <c r="I142" t="n">
-        <v>3.166454362356577</v>
+        <v>2.856894059431837</v>
       </c>
       <c r="J142" t="n">
-        <v>-3.166454362356577</v>
+        <v>-2.856894059431837</v>
       </c>
     </row>
     <row r="143">
@@ -7501,22 +7986,22 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.2227214678701135</v>
+        <v>0.1657802292793794</v>
       </c>
       <c r="F146" t="n">
         <v>2.235925</v>
       </c>
       <c r="G146" t="n">
-        <v>2.363888913067183</v>
+        <v>2.29605658915826</v>
       </c>
       <c r="H146" t="n">
-        <v>0.1279639130671826</v>
+        <v>0.06013158915825967</v>
       </c>
       <c r="I146" t="n">
-        <v>5.723086108307863</v>
+        <v>2.689338379340079</v>
       </c>
       <c r="J146" t="n">
-        <v>5.723086108307863</v>
+        <v>2.689338379340079</v>
       </c>
     </row>
     <row r="147">
@@ -7537,22 +8022,22 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.2227214678701135</v>
+        <v>0.1657802292793794</v>
       </c>
       <c r="F147" t="n">
         <v>2.411340264975417</v>
       </c>
       <c r="G147" t="n">
-        <v>2.411339823758257</v>
+        <v>2.359492098600819</v>
       </c>
       <c r="H147" t="n">
-        <v>-4.412171601408943e-07</v>
+        <v>-0.05184816637459777</v>
       </c>
       <c r="I147" t="n">
-        <v>1.829759020531233e-05</v>
+        <v>2.150180425703062</v>
       </c>
       <c r="J147" t="n">
-        <v>-1.829759020531233e-05</v>
+        <v>-2.150180425703062</v>
       </c>
     </row>
     <row r="148">
@@ -7573,22 +8058,22 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.2227214678701135</v>
+        <v>0.1657802292793794</v>
       </c>
       <c r="F148" t="n">
         <v>2.690510416666667</v>
       </c>
       <c r="G148" t="n">
-        <v>2.572755652726743</v>
+        <v>2.555710179063645</v>
       </c>
       <c r="H148" t="n">
-        <v>-0.1177547639399243</v>
+        <v>-0.1348002376030224</v>
       </c>
       <c r="I148" t="n">
-        <v>4.376670062694399</v>
+        <v>5.0102105819025</v>
       </c>
       <c r="J148" t="n">
-        <v>-4.376670062694399</v>
+        <v>-5.0102105819025</v>
       </c>
     </row>
     <row r="149">
@@ -7609,22 +8094,22 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.2448759921893136</v>
+        <v>0.1876345746351141</v>
       </c>
       <c r="F149" t="n">
         <v>2.235925</v>
       </c>
       <c r="G149" t="n">
-        <v>2.364124019916902</v>
+        <v>2.296702480317847</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1281990199169023</v>
+        <v>0.06077748031784713</v>
       </c>
       <c r="I149" t="n">
-        <v>5.733601078609627</v>
+        <v>2.718225357194322</v>
       </c>
       <c r="J149" t="n">
-        <v>5.733601078609627</v>
+        <v>2.718225357194322</v>
       </c>
     </row>
     <row r="150">
@@ -7645,22 +8130,22 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.2448759921893136</v>
+        <v>0.1876345746351141</v>
       </c>
       <c r="F150" t="n">
         <v>2.411340264975417</v>
       </c>
       <c r="G150" t="n">
-        <v>2.411339883316624</v>
+        <v>2.359601047938866</v>
       </c>
       <c r="H150" t="n">
-        <v>-3.816587930138837e-07</v>
+        <v>-0.05173921703655093</v>
       </c>
       <c r="I150" t="n">
-        <v>1.582766225727063e-05</v>
+        <v>2.145662218976732</v>
       </c>
       <c r="J150" t="n">
-        <v>-1.582766225727063e-05</v>
+        <v>-2.145662218976732</v>
       </c>
     </row>
     <row r="151">
@@ -7681,22 +8166,22 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.2448759921893136</v>
+        <v>0.1876345746351141</v>
       </c>
       <c r="F151" t="n">
         <v>2.690510416666667</v>
       </c>
       <c r="G151" t="n">
-        <v>2.572503429443898</v>
+        <v>2.555289321258104</v>
       </c>
       <c r="H151" t="n">
-        <v>-0.1180069872227691</v>
+        <v>-0.1352210954085633</v>
       </c>
       <c r="I151" t="n">
-        <v>4.386044614128297</v>
+        <v>5.025852885419849</v>
       </c>
       <c r="J151" t="n">
-        <v>-4.386044614128297</v>
+        <v>-5.025852885419849</v>
       </c>
     </row>
     <row r="152">
@@ -7819,22 +8304,22 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.08427582850660252</v>
+        <v>0.09694365238765493</v>
       </c>
       <c r="F155" t="n">
         <v>1.9574</v>
       </c>
       <c r="G155" t="n">
-        <v>1.957401650385334</v>
+        <v>2.016344406221422</v>
       </c>
       <c r="H155" t="n">
-        <v>1.650385333729076e-06</v>
+        <v>0.05894440622142239</v>
       </c>
       <c r="I155" t="n">
-        <v>8.431518002089897e-05</v>
+        <v>3.011362328671829</v>
       </c>
       <c r="J155" t="n">
-        <v>8.431518002089897e-05</v>
+        <v>3.011362328671829</v>
       </c>
     </row>
     <row r="156">
@@ -7855,22 +8340,22 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.08427582850660252</v>
+        <v>0.09694365238765493</v>
       </c>
       <c r="F156" t="n">
         <v>2.2367375</v>
       </c>
       <c r="G156" t="n">
-        <v>2.099555520196756</v>
+        <v>2.139264920367317</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.1371819798032448</v>
+        <v>-0.09747257963268341</v>
       </c>
       <c r="I156" t="n">
-        <v>6.133128263966816</v>
+        <v>4.357801469000426</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.133128263966816</v>
+        <v>-4.357801469000426</v>
       </c>
     </row>
     <row r="157">
@@ -7891,22 +8376,22 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.08427582850660252</v>
+        <v>0.09694365238765493</v>
       </c>
       <c r="F157" t="n">
         <v>2.472651041666666</v>
       </c>
       <c r="G157" t="n">
-        <v>2.446110882804162</v>
+        <v>2.455591773724753</v>
       </c>
       <c r="H157" t="n">
-        <v>-0.02654015886250427</v>
+        <v>-0.0170592679419137</v>
       </c>
       <c r="I157" t="n">
-        <v>1.073348338090406</v>
+        <v>0.6899181346032179</v>
       </c>
       <c r="J157" t="n">
-        <v>-1.073348338090406</v>
+        <v>-0.6899181346032179</v>
       </c>
     </row>
     <row r="158">
@@ -7927,22 +8412,22 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.1080509055066162</v>
+        <v>0.1212686453864763</v>
       </c>
       <c r="F158" t="n">
         <v>1.9574</v>
       </c>
       <c r="G158" t="n">
-        <v>1.957402950459858</v>
+        <v>2.017472181258239</v>
       </c>
       <c r="H158" t="n">
-        <v>2.950459858208632e-06</v>
+        <v>0.06007218125823877</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0001507336189950256</v>
+        <v>3.068978300717215</v>
       </c>
       <c r="J158" t="n">
-        <v>0.0001507336189950256</v>
+        <v>3.068978300717215</v>
       </c>
     </row>
     <row r="159">
@@ -7963,22 +8448,22 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.1080509055066162</v>
+        <v>0.1212686453864763</v>
       </c>
       <c r="F159" t="n">
         <v>2.2367375</v>
       </c>
       <c r="G159" t="n">
-        <v>2.09786496083404</v>
+        <v>2.138691004038292</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.1388725391659604</v>
+        <v>-0.09804649596170778</v>
       </c>
       <c r="I159" t="n">
-        <v>6.208709746492846</v>
+        <v>4.383460104804779</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.208709746492846</v>
+        <v>-4.383460104804779</v>
       </c>
     </row>
     <row r="160">
@@ -7999,22 +8484,22 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.1080509055066162</v>
+        <v>0.1212686453864763</v>
       </c>
       <c r="F160" t="n">
         <v>2.472651041666666</v>
       </c>
       <c r="G160" t="n">
-        <v>2.444202465106636</v>
+        <v>2.454156563489119</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.02844857656003041</v>
+        <v>-0.01849447817754779</v>
       </c>
       <c r="I160" t="n">
-        <v>1.150529374369581</v>
+        <v>0.7479615144190248</v>
       </c>
       <c r="J160" t="n">
-        <v>-1.150529374369581</v>
+        <v>-0.7479615144190248</v>
       </c>
     </row>
     <row r="161">
@@ -8137,22 +8622,22 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.09214397915035179</v>
+        <v>0.1188916866241674</v>
       </c>
       <c r="F164" t="n">
         <v>1.9375625</v>
       </c>
       <c r="G164" t="n">
-        <v>1.937566510611282</v>
+        <v>2.039779010804077</v>
       </c>
       <c r="H164" t="n">
-        <v>4.010611281968224e-06</v>
+        <v>0.1022165108040765</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0002069926147914312</v>
+        <v>5.275520702123232</v>
       </c>
       <c r="J164" t="n">
-        <v>0.0002069926147914312</v>
+        <v>5.275520702123232</v>
       </c>
     </row>
     <row r="165">
@@ -8173,22 +8658,22 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.09214397915035179</v>
+        <v>0.1188916866241674</v>
       </c>
       <c r="F165" t="n">
         <v>2.27314447629368</v>
       </c>
       <c r="G165" t="n">
-        <v>2.072134322987468</v>
+        <v>2.143394174025118</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.2010101533062127</v>
+        <v>-0.1297503022685627</v>
       </c>
       <c r="I165" t="n">
-        <v>8.842823472177891</v>
+        <v>5.707965491050445</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.842823472177891</v>
+        <v>-5.707965491050445</v>
       </c>
     </row>
     <row r="166">
@@ -8209,22 +8694,22 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.09214397915035179</v>
+        <v>0.1188916866241674</v>
       </c>
       <c r="F166" t="n">
         <v>2.609909375</v>
       </c>
       <c r="G166" t="n">
-        <v>2.415549589180215</v>
+        <v>2.433997530466867</v>
       </c>
       <c r="H166" t="n">
-        <v>-0.1943597858197852</v>
+        <v>-0.1759118445331329</v>
       </c>
       <c r="I166" t="n">
-        <v>7.446993665049584</v>
+        <v>6.740151448098956</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.446993665049584</v>
+        <v>-6.740151448098956</v>
       </c>
     </row>
     <row r="167">
@@ -8245,22 +8730,22 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.1181240394951164</v>
+        <v>0.1459483453413025</v>
       </c>
       <c r="F167" t="n">
         <v>1.9375625</v>
       </c>
       <c r="G167" t="n">
-        <v>1.937563131132626</v>
+        <v>2.041331227919781</v>
       </c>
       <c r="H167" t="n">
-        <v>6.311326261609906e-07</v>
+        <v>0.1037687279197812</v>
       </c>
       <c r="I167" t="n">
-        <v>3.257353639745766e-05</v>
+        <v>5.355632549648396</v>
       </c>
       <c r="J167" t="n">
-        <v>3.257353639745766e-05</v>
+        <v>5.355632549648396</v>
       </c>
     </row>
     <row r="168">
@@ -8281,22 +8766,22 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.1181240394951164</v>
+        <v>0.1459483453413025</v>
       </c>
       <c r="F168" t="n">
         <v>2.27314447629368</v>
       </c>
       <c r="G168" t="n">
-        <v>2.070492713526872</v>
+        <v>2.143453210073537</v>
       </c>
       <c r="H168" t="n">
-        <v>-0.2026517627668087</v>
+        <v>-0.1296912662201435</v>
       </c>
       <c r="I168" t="n">
-        <v>8.915041031497859</v>
+        <v>5.705368381670253</v>
       </c>
       <c r="J168" t="n">
-        <v>-8.915041031497859</v>
+        <v>-5.705368381670253</v>
       </c>
     </row>
     <row r="169">
@@ -8317,22 +8802,22 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.1181240394951164</v>
+        <v>0.1459483453413025</v>
       </c>
       <c r="F169" t="n">
         <v>2.609909375</v>
       </c>
       <c r="G169" t="n">
-        <v>2.413589327867191</v>
+        <v>2.432886487551365</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.1963200471328093</v>
+        <v>-0.1770228874486346</v>
       </c>
       <c r="I169" t="n">
-        <v>7.522102070414198</v>
+        <v>6.782721620310459</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.522102070414198</v>
+        <v>-6.782721620310459</v>
       </c>
     </row>
     <row r="170">
@@ -8455,22 +8940,22 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>0.07638048100184233</v>
+        <v>0.09718731902762963</v>
       </c>
       <c r="F173" t="n">
         <v>1.869</v>
       </c>
       <c r="G173" t="n">
-        <v>1.869000432363892</v>
+        <v>1.974785205171172</v>
       </c>
       <c r="H173" t="n">
-        <v>4.323638922443251e-07</v>
+        <v>0.1057852051711718</v>
       </c>
       <c r="I173" t="n">
-        <v>2.313343457701044e-05</v>
+        <v>5.659989575771634</v>
       </c>
       <c r="J173" t="n">
-        <v>2.313343457701044e-05</v>
+        <v>5.659989575771634</v>
       </c>
     </row>
     <row r="174">
@@ -8491,22 +8976,22 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>0.07638048100184233</v>
+        <v>0.09718731902762963</v>
       </c>
       <c r="F174" t="n">
         <v>2.254459673470501</v>
       </c>
       <c r="G174" t="n">
-        <v>2.030155710740681</v>
+        <v>2.101017805659864</v>
       </c>
       <c r="H174" t="n">
-        <v>-0.2243039627298202</v>
+        <v>-0.1534418678106375</v>
       </c>
       <c r="I174" t="n">
-        <v>9.949344642059092</v>
+        <v>6.806148258772359</v>
       </c>
       <c r="J174" t="n">
-        <v>-9.949344642059092</v>
+        <v>-6.806148258772359</v>
       </c>
     </row>
     <row r="175">
@@ -8527,22 +9012,22 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0.07638048100184233</v>
+        <v>0.09718731902762963</v>
       </c>
       <c r="F175" t="n">
         <v>2.601183333333334</v>
       </c>
       <c r="G175" t="n">
-        <v>2.412039605915339</v>
+        <v>2.428761570145554</v>
       </c>
       <c r="H175" t="n">
-        <v>-0.1891437274179948</v>
+        <v>-0.17242176318778</v>
       </c>
       <c r="I175" t="n">
-        <v>7.271449305175008</v>
+        <v>6.628589418448527</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.271449305175008</v>
+        <v>-6.628589418448527</v>
       </c>
     </row>
     <row r="176">
@@ -8563,22 +9048,22 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.1014549402188581</v>
+        <v>0.1231981587056181</v>
       </c>
       <c r="F176" t="n">
         <v>1.869</v>
       </c>
       <c r="G176" t="n">
-        <v>1.869000565008434</v>
+        <v>1.97664680946133</v>
       </c>
       <c r="H176" t="n">
-        <v>5.650084338171268e-07</v>
+        <v>0.1076468094613299</v>
       </c>
       <c r="I176" t="n">
-        <v>3.023052080348458e-05</v>
+        <v>5.75959387166024</v>
       </c>
       <c r="J176" t="n">
-        <v>3.023052080348458e-05</v>
+        <v>5.75959387166024</v>
       </c>
     </row>
     <row r="177">
@@ -8599,22 +9084,22 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0.1014549402188581</v>
+        <v>0.1231981587056181</v>
       </c>
       <c r="F177" t="n">
         <v>2.254459673470501</v>
       </c>
       <c r="G177" t="n">
-        <v>2.028032155923051</v>
+        <v>2.100845516282517</v>
       </c>
       <c r="H177" t="n">
-        <v>-0.2264275175474508</v>
+        <v>-0.1536141571879841</v>
       </c>
       <c r="I177" t="n">
-        <v>10.04353815736654</v>
+        <v>6.813790417085235</v>
       </c>
       <c r="J177" t="n">
-        <v>-10.04353815736654</v>
+        <v>-6.813790417085235</v>
       </c>
     </row>
     <row r="178">
@@ -8635,22 +9120,22 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0.1014549402188581</v>
+        <v>0.1231981587056181</v>
       </c>
       <c r="F178" t="n">
         <v>2.601183333333334</v>
       </c>
       <c r="G178" t="n">
-        <v>2.409724267906856</v>
+        <v>2.427304990857416</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.1914590654264781</v>
+        <v>-0.1738783424759172</v>
       </c>
       <c r="I178" t="n">
-        <v>7.360460255645624</v>
+        <v>6.684586213040877</v>
       </c>
       <c r="J178" t="n">
-        <v>-7.360460255645624</v>
+        <v>-6.684586213040877</v>
       </c>
     </row>
     <row r="179">
@@ -8773,22 +9258,22 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>0.07972957776622766</v>
+        <v>0.09834369845642285</v>
       </c>
       <c r="F182" t="n">
         <v>1.8122</v>
       </c>
       <c r="G182" t="n">
-        <v>1.812200181731645</v>
+        <v>1.905893571754815</v>
       </c>
       <c r="H182" t="n">
-        <v>1.817316450658524e-07</v>
+        <v>0.09369357175481507</v>
       </c>
       <c r="I182" t="n">
-        <v>1.002823336639733e-05</v>
+        <v>5.170156260612243</v>
       </c>
       <c r="J182" t="n">
-        <v>1.002823336639733e-05</v>
+        <v>5.170156260612243</v>
       </c>
     </row>
     <row r="183">
@@ -8809,22 +9294,22 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>0.07972957776622766</v>
+        <v>0.09834369845642285</v>
       </c>
       <c r="F183" t="n">
         <v>2.166325</v>
       </c>
       <c r="G183" t="n">
-        <v>1.972873735471231</v>
+        <v>2.036505900376918</v>
       </c>
       <c r="H183" t="n">
-        <v>-0.1934512645287689</v>
+        <v>-0.1298190996230817</v>
       </c>
       <c r="I183" t="n">
-        <v>8.929928082294619</v>
+        <v>5.992595738085545</v>
       </c>
       <c r="J183" t="n">
-        <v>-8.929928082294619</v>
+        <v>-5.992595738085545</v>
       </c>
     </row>
     <row r="184">
@@ -8845,22 +9330,22 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0.07972957776622766</v>
+        <v>0.09834369845642285</v>
       </c>
       <c r="F184" t="n">
         <v>2.561983333333334</v>
       </c>
       <c r="G184" t="n">
-        <v>2.366359266449719</v>
+        <v>2.3818546121056</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.1956240668836147</v>
+        <v>-0.1801287212277334</v>
       </c>
       <c r="I184" t="n">
-        <v>7.6356494727502</v>
+        <v>7.030831109793846</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.6356494727502</v>
+        <v>-7.030831109793846</v>
       </c>
     </row>
     <row r="185">
@@ -8881,22 +9366,22 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0.1075983135296858</v>
+        <v>0.1271492990360422</v>
       </c>
       <c r="F185" t="n">
         <v>1.8122</v>
       </c>
       <c r="G185" t="n">
-        <v>1.812202321204978</v>
+        <v>1.90784501082692</v>
       </c>
       <c r="H185" t="n">
-        <v>2.321204978006364e-06</v>
+        <v>0.09564501082691979</v>
       </c>
       <c r="I185" t="n">
-        <v>0.0001280876822650019</v>
+        <v>5.277839688054287</v>
       </c>
       <c r="J185" t="n">
-        <v>0.0001280876822650019</v>
+        <v>5.277839688054287</v>
       </c>
     </row>
     <row r="186">
@@ -8917,22 +9402,22 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0.1075983135296858</v>
+        <v>0.1271492990360422</v>
       </c>
       <c r="F186" t="n">
         <v>2.166325</v>
       </c>
       <c r="G186" t="n">
-        <v>1.97060279558481</v>
+        <v>2.036229852956137</v>
       </c>
       <c r="H186" t="n">
-        <v>-0.1957222044151898</v>
+        <v>-0.1300951470438632</v>
       </c>
       <c r="I186" t="n">
-        <v>9.034757223186265</v>
+        <v>6.005338397694859</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.034757223186265</v>
+        <v>-6.005338397694859</v>
       </c>
     </row>
     <row r="187">
@@ -8953,22 +9438,22 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>0.1075983135296858</v>
+        <v>0.1271492990360422</v>
       </c>
       <c r="F187" t="n">
         <v>2.561983333333334</v>
       </c>
       <c r="G187" t="n">
-        <v>2.363776005895018</v>
+        <v>2.380158410317609</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.1982073274383152</v>
+        <v>-0.1818249230157241</v>
       </c>
       <c r="I187" t="n">
-        <v>7.736479970790149</v>
+        <v>7.097037699271685</v>
       </c>
       <c r="J187" t="n">
-        <v>-7.736479970790149</v>
+        <v>-7.097037699271685</v>
       </c>
     </row>
     <row r="188">
@@ -9091,22 +9576,22 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>0.0711001993502882</v>
+        <v>0.07296935360972662</v>
       </c>
       <c r="F191" t="n">
         <v>2.2072875</v>
       </c>
       <c r="G191" t="n">
-        <v>2.207288582010092</v>
+        <v>2.217255838162237</v>
       </c>
       <c r="H191" t="n">
-        <v>1.082010092190444e-06</v>
+        <v>0.009968338162237522</v>
       </c>
       <c r="I191" t="n">
-        <v>4.901989850395312e-05</v>
+        <v>0.4516103209136791</v>
       </c>
       <c r="J191" t="n">
-        <v>4.901989850395312e-05</v>
+        <v>0.4516103209136791</v>
       </c>
     </row>
     <row r="192">
@@ -9127,22 +9612,22 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>0.0711001993502882</v>
+        <v>0.07296935360972662</v>
       </c>
       <c r="F192" t="n">
         <v>2.365288415656712</v>
       </c>
       <c r="G192" t="n">
-        <v>2.339819610614401</v>
+        <v>2.345949432531357</v>
       </c>
       <c r="H192" t="n">
-        <v>-0.02546880504231153</v>
+        <v>-0.01933898312535565</v>
       </c>
       <c r="I192" t="n">
-        <v>1.076773761445926</v>
+        <v>0.8176162787313302</v>
       </c>
       <c r="J192" t="n">
-        <v>-1.076773761445926</v>
+        <v>-0.8176162787313302</v>
       </c>
     </row>
     <row r="193">
@@ -9163,22 +9648,22 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>0.0711001993502882</v>
+        <v>0.07296935360972662</v>
       </c>
       <c r="F193" t="n">
         <v>2.615265625</v>
       </c>
       <c r="G193" t="n">
-        <v>2.621253254152973</v>
+        <v>2.622458102973446</v>
       </c>
       <c r="H193" t="n">
-        <v>0.005987629152973017</v>
+        <v>0.007192477973445577</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2289491780771989</v>
+        <v>0.2750190231038415</v>
       </c>
       <c r="J193" t="n">
-        <v>0.2289491780771989</v>
+        <v>0.2750190231038415</v>
       </c>
     </row>
     <row r="194">
@@ -9199,22 +9684,22 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>0.08546840709107527</v>
+        <v>0.0874707755582199</v>
       </c>
       <c r="F194" t="n">
         <v>2.2072875</v>
       </c>
       <c r="G194" t="n">
-        <v>2.207289809509084</v>
+        <v>2.217796335812492</v>
       </c>
       <c r="H194" t="n">
-        <v>2.309509084419403e-06</v>
+        <v>0.01050883581249229</v>
       </c>
       <c r="I194" t="n">
-        <v>0.000104631095152734</v>
+        <v>0.4760972828637997</v>
       </c>
       <c r="J194" t="n">
-        <v>0.000104631095152734</v>
+        <v>0.4760972828637997</v>
       </c>
     </row>
     <row r="195">
@@ -9235,22 +9720,22 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>0.08546840709107527</v>
+        <v>0.0874707755582199</v>
       </c>
       <c r="F195" t="n">
         <v>2.365288415656712</v>
       </c>
       <c r="G195" t="n">
-        <v>2.338742266664792</v>
+        <v>2.34524869947696</v>
       </c>
       <c r="H195" t="n">
-        <v>-0.02654614899191987</v>
+        <v>-0.02003971617975209</v>
       </c>
       <c r="I195" t="n">
-        <v>1.122321862154364</v>
+        <v>0.8472419704549286</v>
       </c>
       <c r="J195" t="n">
-        <v>-1.122321862154364</v>
+        <v>-0.8472419704549286</v>
       </c>
     </row>
     <row r="196">
@@ -9271,22 +9756,22 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>0.08546840709107527</v>
+        <v>0.0874707755582199</v>
       </c>
       <c r="F196" t="n">
         <v>2.615265625</v>
       </c>
       <c r="G196" t="n">
-        <v>2.620231716707695</v>
+        <v>2.621529004017126</v>
       </c>
       <c r="H196" t="n">
-        <v>0.004966091707694797</v>
+        <v>0.006263379017126258</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1898886162928401</v>
+        <v>0.2394930349427224</v>
       </c>
       <c r="J196" t="n">
-        <v>0.1898886162928401</v>
+        <v>0.2394930349427224</v>
       </c>
     </row>
     <row r="197">
@@ -9409,22 +9894,22 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>0.07216402703380319</v>
+        <v>0.07396191726943012</v>
       </c>
       <c r="F200" t="n">
         <v>2.075675</v>
       </c>
       <c r="G200" t="n">
-        <v>2.07567598358892</v>
+        <v>2.086049553324376</v>
       </c>
       <c r="H200" t="n">
-        <v>9.835889196452285e-07</v>
+        <v>0.01037455332437576</v>
       </c>
       <c r="I200" t="n">
-        <v>4.738646077277168e-05</v>
+        <v>0.4998158827550438</v>
       </c>
       <c r="J200" t="n">
-        <v>4.738646077277168e-05</v>
+        <v>0.4998158827550438</v>
       </c>
     </row>
     <row r="201">
@@ -9445,22 +9930,22 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>0.07216402703380319</v>
+        <v>0.07396191726943012</v>
       </c>
       <c r="F201" t="n">
         <v>2.248592380402163</v>
       </c>
       <c r="G201" t="n">
-        <v>2.222711070038185</v>
+        <v>2.229227555469506</v>
       </c>
       <c r="H201" t="n">
-        <v>-0.02588131036397812</v>
+        <v>-0.01936482493265723</v>
       </c>
       <c r="I201" t="n">
-        <v>1.151000536582322</v>
+        <v>0.8611976586522901</v>
       </c>
       <c r="J201" t="n">
-        <v>-1.151000536582322</v>
+        <v>-0.8611976586522901</v>
       </c>
     </row>
     <row r="202">
@@ -9481,22 +9966,22 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>0.07216402703380319</v>
+        <v>0.07396191726943012</v>
       </c>
       <c r="F202" t="n">
         <v>2.544978125</v>
       </c>
       <c r="G202" t="n">
-        <v>2.546388096156607</v>
+        <v>2.547725532669681</v>
       </c>
       <c r="H202" t="n">
-        <v>0.001409971156607348</v>
+        <v>0.002747407669681401</v>
       </c>
       <c r="I202" t="n">
-        <v>0.05540209335226991</v>
+        <v>0.1079540779817666</v>
       </c>
       <c r="J202" t="n">
-        <v>0.05540209335226991</v>
+        <v>0.1079540779817666</v>
       </c>
     </row>
     <row r="203">
@@ -9517,22 +10002,22 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>0.09009004668823942</v>
+        <v>0.09205323862126645</v>
       </c>
       <c r="F203" t="n">
         <v>2.075675</v>
       </c>
       <c r="G203" t="n">
-        <v>2.075677695368238</v>
+        <v>2.086783493370556</v>
       </c>
       <c r="H203" t="n">
-        <v>2.695368238381235e-06</v>
+        <v>0.01110849337055608</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0001298550225050278</v>
+        <v>0.5351749850316684</v>
       </c>
       <c r="J203" t="n">
-        <v>0.0001298550225050278</v>
+        <v>0.5351749850316684</v>
       </c>
     </row>
     <row r="204">
@@ -9553,22 +10038,22 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>0.09009004668823942</v>
+        <v>0.09205323862126645</v>
       </c>
       <c r="F204" t="n">
         <v>2.248592380402163</v>
       </c>
       <c r="G204" t="n">
-        <v>2.221247759638625</v>
+        <v>2.228281894440324</v>
       </c>
       <c r="H204" t="n">
-        <v>-0.02734462076353816</v>
+        <v>-0.02031048596183949</v>
       </c>
       <c r="I204" t="n">
-        <v>1.216077266909868</v>
+        <v>0.9032533481327074</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.216077266909868</v>
+        <v>-0.9032533481327074</v>
       </c>
     </row>
     <row r="205">
@@ -9589,22 +10074,22 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>0.09009004668823942</v>
+        <v>0.09205323862126645</v>
       </c>
       <c r="F205" t="n">
         <v>2.544978125</v>
       </c>
       <c r="G205" t="n">
-        <v>2.544935263770212</v>
+        <v>2.546404469276232</v>
       </c>
       <c r="H205" t="n">
-        <v>-4.2861229787583e-05</v>
+        <v>0.001426344276232783</v>
       </c>
       <c r="I205" t="n">
-        <v>0.001684149241462851</v>
+        <v>0.05604544346457921</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.001684149241462851</v>
+        <v>0.05604544346457921</v>
       </c>
     </row>
     <row r="206">
@@ -9727,22 +10212,22 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>0.0686445033615314</v>
+        <v>0.07453370480727649</v>
       </c>
       <c r="F209" t="n">
         <v>2.598375</v>
       </c>
       <c r="G209" t="n">
-        <v>2.598376774155648</v>
+        <v>2.616513189640816</v>
       </c>
       <c r="H209" t="n">
-        <v>1.77415564861505e-06</v>
+        <v>0.01813818964081637</v>
       </c>
       <c r="I209" t="n">
-        <v>6.827943035993843e-05</v>
+        <v>0.6980589653462788</v>
       </c>
       <c r="J209" t="n">
-        <v>6.827943035993843e-05</v>
+        <v>0.6980589653462788</v>
       </c>
     </row>
     <row r="210">
@@ -9763,22 +10248,22 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>0.0686445033615314</v>
+        <v>0.07453370480727649</v>
       </c>
       <c r="F210" t="n">
         <v>2.715150068499876</v>
       </c>
       <c r="G210" t="n">
-        <v>2.673577863216871</v>
+        <v>2.68416053739086</v>
       </c>
       <c r="H210" t="n">
-        <v>-0.04157220528300432</v>
+        <v>-0.03098953110901581</v>
       </c>
       <c r="I210" t="n">
-        <v>1.531119983580614</v>
+        <v>1.141356106557218</v>
       </c>
       <c r="J210" t="n">
-        <v>-1.531119983580614</v>
+        <v>-1.141356106557218</v>
       </c>
     </row>
     <row r="211">
@@ -9799,22 +10284,22 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>0.0686445033615314</v>
+        <v>0.07453370480727649</v>
       </c>
       <c r="F211" t="n">
         <v>2.829431944444444</v>
       </c>
       <c r="G211" t="n">
-        <v>2.818153575813073</v>
+        <v>2.820032798265895</v>
       </c>
       <c r="H211" t="n">
-        <v>-0.01127836863137111</v>
+        <v>-0.009399146178548978</v>
       </c>
       <c r="I211" t="n">
-        <v>0.3986089382187138</v>
+        <v>0.3321919863456723</v>
       </c>
       <c r="J211" t="n">
-        <v>-0.3986089382187138</v>
+        <v>-0.3321919863456723</v>
       </c>
     </row>
     <row r="212">
@@ -9835,22 +10320,22 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>0.07463470711230444</v>
+        <v>0.08061948493320611</v>
       </c>
       <c r="F212" t="n">
         <v>2.598375</v>
       </c>
       <c r="G212" t="n">
-        <v>2.598374770824879</v>
+        <v>2.616674624970293</v>
       </c>
       <c r="H212" t="n">
-        <v>-2.291751206584536e-07</v>
+        <v>0.01829962497029269</v>
       </c>
       <c r="I212" t="n">
-        <v>8.819940180245483e-06</v>
+        <v>0.7042718995638696</v>
       </c>
       <c r="J212" t="n">
-        <v>-8.819940180245483e-06</v>
+        <v>0.7042718995638696</v>
       </c>
     </row>
     <row r="213">
@@ -9871,22 +10356,22 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>0.07463470711230444</v>
+        <v>0.08061948493320611</v>
       </c>
       <c r="F213" t="n">
         <v>2.715150068499876</v>
       </c>
       <c r="G213" t="n">
-        <v>2.673311859129013</v>
+        <v>2.684024587857936</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.04183820937086224</v>
+        <v>-0.03112548064193987</v>
       </c>
       <c r="I213" t="n">
-        <v>1.540917014357807</v>
+        <v>1.146363179076019</v>
       </c>
       <c r="J213" t="n">
-        <v>-1.540917014357807</v>
+        <v>-1.146363179076019</v>
       </c>
     </row>
     <row r="214">
@@ -9907,22 +10392,22 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>0.07463470711230444</v>
+        <v>0.08061948493320611</v>
       </c>
       <c r="F214" t="n">
         <v>2.829431944444444</v>
       </c>
       <c r="G214" t="n">
-        <v>2.817931967533389</v>
+        <v>2.819846105533428</v>
       </c>
       <c r="H214" t="n">
-        <v>-0.01149997691105487</v>
+        <v>-0.00958583891101572</v>
       </c>
       <c r="I214" t="n">
-        <v>0.40644119161922</v>
+        <v>0.3387902271280071</v>
       </c>
       <c r="J214" t="n">
-        <v>-0.40644119161922</v>
+        <v>-0.3387902271280071</v>
       </c>
     </row>
     <row r="215">
@@ -10045,22 +10530,22 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>0.05161121416311329</v>
+        <v>0.05747388742708958</v>
       </c>
       <c r="F218" t="n">
         <v>2.7035125</v>
       </c>
       <c r="G218" t="n">
-        <v>2.703512319891357</v>
+        <v>2.722035426268946</v>
       </c>
       <c r="H218" t="n">
-        <v>-1.80108643110799e-07</v>
+        <v>0.01852292626894592</v>
       </c>
       <c r="I218" t="n">
-        <v>6.662023686252569e-06</v>
+        <v>0.6851429859838235</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.662023686252569e-06</v>
+        <v>0.6851429859838235</v>
       </c>
     </row>
     <row r="219">
@@ -10081,22 +10566,22 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>0.05161121416311329</v>
+        <v>0.05747388742708958</v>
       </c>
       <c r="F219" t="n">
         <v>2.817383744798192</v>
       </c>
       <c r="G219" t="n">
-        <v>2.77229971846656</v>
+        <v>2.781802759799575</v>
       </c>
       <c r="H219" t="n">
-        <v>-0.04508402633163122</v>
+        <v>-0.03558098499861639</v>
       </c>
       <c r="I219" t="n">
-        <v>1.600208931952242</v>
+        <v>1.262908720344202</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.600208931952242</v>
+        <v>-1.262908720344202</v>
       </c>
     </row>
     <row r="220">
@@ -10117,22 +10602,22 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>0.05161121416311329</v>
+        <v>0.05747388742708958</v>
       </c>
       <c r="F220" t="n">
         <v>2.8942375</v>
       </c>
       <c r="G220" t="n">
-        <v>2.881209823510938</v>
+        <v>2.882570811038054</v>
       </c>
       <c r="H220" t="n">
-        <v>-0.01302767648906222</v>
+        <v>-0.01166668896194656</v>
       </c>
       <c r="I220" t="n">
-        <v>0.45012465248834</v>
+        <v>0.4031006080857758</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.45012465248834</v>
+        <v>-0.4031006080857758</v>
       </c>
     </row>
     <row r="221">
@@ -10153,22 +10638,22 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>0.05498242253594483</v>
+        <v>0.06090205673614606</v>
       </c>
       <c r="F221" t="n">
         <v>2.7035125</v>
       </c>
       <c r="G221" t="n">
-        <v>2.70351262587046</v>
+        <v>2.722129984726351</v>
       </c>
       <c r="H221" t="n">
-        <v>1.258704602769001e-07</v>
+        <v>0.01861748472635094</v>
       </c>
       <c r="I221" t="n">
-        <v>4.655812032565045e-06</v>
+        <v>0.6886406009349297</v>
       </c>
       <c r="J221" t="n">
-        <v>4.655812032565045e-06</v>
+        <v>0.6886406009349297</v>
       </c>
     </row>
     <row r="222">
@@ -10189,22 +10674,22 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>0.05498242253594483</v>
+        <v>0.06090205673614606</v>
       </c>
       <c r="F222" t="n">
         <v>2.817383744798192</v>
       </c>
       <c r="G222" t="n">
-        <v>2.77215149840852</v>
+        <v>2.781725824769438</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.04523224638967127</v>
+        <v>-0.03565792002875323</v>
       </c>
       <c r="I222" t="n">
-        <v>1.605469843189971</v>
+        <v>1.265639446333478</v>
       </c>
       <c r="J222" t="n">
-        <v>-1.605469843189971</v>
+        <v>-1.265639446333478</v>
       </c>
     </row>
     <row r="223">
@@ -10225,22 +10710,22 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>0.05498242253594483</v>
+        <v>0.06090205673614606</v>
       </c>
       <c r="F223" t="n">
         <v>2.8942375</v>
       </c>
       <c r="G223" t="n">
-        <v>2.881111177107808</v>
+        <v>2.882487656282029</v>
       </c>
       <c r="H223" t="n">
-        <v>-0.01312632289219229</v>
+        <v>-0.0117498437179715</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4535330252680468</v>
+        <v>0.4059737225425175</v>
       </c>
       <c r="J223" t="n">
-        <v>-0.4535330252680468</v>
+        <v>-0.4059737225425175</v>
       </c>
     </row>
     <row r="224">
@@ -10363,22 +10848,22 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>0.02397019273512198</v>
+        <v>0.02588881026848242</v>
       </c>
       <c r="F227" t="n">
         <v>2.659425</v>
       </c>
       <c r="G227" t="n">
-        <v>2.659424564319452</v>
+        <v>2.674987673642212</v>
       </c>
       <c r="H227" t="n">
-        <v>-4.35680548527273e-07</v>
+        <v>0.01556267364221231</v>
       </c>
       <c r="I227" t="n">
-        <v>1.638250932164934e-05</v>
+        <v>0.5851894165923953</v>
       </c>
       <c r="J227" t="n">
-        <v>-1.638250932164934e-05</v>
+        <v>0.5851894165923953</v>
       </c>
     </row>
     <row r="228">
@@ -10399,22 +10884,22 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>0.02397019273512198</v>
+        <v>0.02588881026848242</v>
       </c>
       <c r="F228" t="n">
         <v>2.836889861687792</v>
       </c>
       <c r="G228" t="n">
-        <v>2.784915451923733</v>
+        <v>2.790109682942619</v>
       </c>
       <c r="H228" t="n">
-        <v>-0.05197440976405909</v>
+        <v>-0.04678017874517382</v>
       </c>
       <c r="I228" t="n">
-        <v>1.832091208967034</v>
+        <v>1.648995238656964</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.832091208967034</v>
+        <v>-1.648995238656964</v>
       </c>
     </row>
     <row r="229">
@@ -10435,22 +10920,22 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>0.02397019273512198</v>
+        <v>0.02588881026848242</v>
       </c>
       <c r="F229" t="n">
         <v>2.949019444444444</v>
       </c>
       <c r="G229" t="n">
-        <v>2.906890192287715</v>
+        <v>2.907333177178433</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.04212925215672891</v>
+        <v>-0.04168626726601099</v>
       </c>
       <c r="I229" t="n">
-        <v>1.428585092448093</v>
+        <v>1.413563662475753</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.428585092448093</v>
+        <v>-1.413563662475753</v>
       </c>
     </row>
     <row r="230">
@@ -10471,22 +10956,22 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>0.02617032869151523</v>
+        <v>0.02810718263577177</v>
       </c>
       <c r="F230" t="n">
         <v>2.659425</v>
       </c>
       <c r="G230" t="n">
-        <v>2.659424818259136</v>
+        <v>2.675079834474328</v>
       </c>
       <c r="H230" t="n">
-        <v>-1.817408641358043e-07</v>
+        <v>0.01565483447432747</v>
       </c>
       <c r="I230" t="n">
-        <v>6.833840553345338e-06</v>
+        <v>0.5886548586377683</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.833840553345338e-06</v>
+        <v>0.5886548586377683</v>
       </c>
     </row>
     <row r="231">
@@ -10507,22 +10992,22 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>0.02617032869151523</v>
+        <v>0.02810718263577177</v>
       </c>
       <c r="F231" t="n">
         <v>2.836889861687792</v>
       </c>
       <c r="G231" t="n">
-        <v>2.784735928838403</v>
+        <v>2.789974780916908</v>
       </c>
       <c r="H231" t="n">
-        <v>-0.05215393284938941</v>
+        <v>-0.04691508077088402</v>
       </c>
       <c r="I231" t="n">
-        <v>1.838419374461041</v>
+        <v>1.653750517581678</v>
       </c>
       <c r="J231" t="n">
-        <v>-1.838419374461041</v>
+        <v>-1.653750517581678</v>
       </c>
     </row>
     <row r="232">
@@ -10543,22 +11028,22 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>0.02617032869151523</v>
+        <v>0.02810718263577177</v>
       </c>
       <c r="F232" t="n">
         <v>2.949019444444444</v>
       </c>
       <c r="G232" t="n">
-        <v>2.906818484224753</v>
+        <v>2.907266461419521</v>
       </c>
       <c r="H232" t="n">
-        <v>-0.04220096021969155</v>
+        <v>-0.04175298302492347</v>
       </c>
       <c r="I232" t="n">
-        <v>1.431016682483816</v>
+        <v>1.41582596559614</v>
       </c>
       <c r="J232" t="n">
-        <v>-1.431016682483816</v>
+        <v>-1.41582596559614</v>
       </c>
     </row>
     <row r="233">
@@ -10681,22 +11166,22 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>0.09122256426320441</v>
+        <v>0.1132306970720933</v>
       </c>
       <c r="F236" t="n">
         <v>2.4153</v>
       </c>
       <c r="G236" t="n">
-        <v>2.41530191659616</v>
+        <v>2.473579832073951</v>
       </c>
       <c r="H236" t="n">
-        <v>1.91659615955686e-06</v>
+        <v>0.05827983207395082</v>
       </c>
       <c r="I236" t="n">
-        <v>7.935230238715109e-05</v>
+        <v>2.412943819564891</v>
       </c>
       <c r="J236" t="n">
-        <v>7.935230238715109e-05</v>
+        <v>2.412943819564891</v>
       </c>
     </row>
     <row r="237">
@@ -10717,22 +11202,22 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>0.09122256426320441</v>
+        <v>0.1132306970720933</v>
       </c>
       <c r="F237" t="n">
         <v>2.605161460353123</v>
       </c>
       <c r="G237" t="n">
-        <v>2.500492926972977</v>
+        <v>2.539217949767355</v>
       </c>
       <c r="H237" t="n">
-        <v>-0.1046685333801456</v>
+        <v>-0.06594351058576775</v>
       </c>
       <c r="I237" t="n">
-        <v>4.017736903184421</v>
+        <v>2.531263861735053</v>
       </c>
       <c r="J237" t="n">
-        <v>-4.017736903184421</v>
+        <v>-2.531263861735053</v>
       </c>
     </row>
     <row r="238">
@@ -10753,22 +11238,22 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>0.09122256426320441</v>
+        <v>0.1132306970720933</v>
       </c>
       <c r="F238" t="n">
         <v>2.830407291666667</v>
       </c>
       <c r="G238" t="n">
-        <v>2.698542774348506</v>
+        <v>2.707488709627944</v>
       </c>
       <c r="H238" t="n">
-        <v>-0.1318645173181605</v>
+        <v>-0.1229185820387229</v>
       </c>
       <c r="I238" t="n">
-        <v>4.658853081194295</v>
+        <v>4.342787781836976</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.658853081194295</v>
+        <v>-4.342787781836976</v>
       </c>
     </row>
     <row r="239">
@@ -10789,22 +11274,22 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>0.1028391763575825</v>
+        <v>0.1252955957059185</v>
       </c>
       <c r="F239" t="n">
         <v>2.4153</v>
       </c>
       <c r="G239" t="n">
-        <v>2.415300166837147</v>
+        <v>2.474065609121035</v>
       </c>
       <c r="H239" t="n">
-        <v>1.668371467644647e-07</v>
+        <v>0.05876560912103512</v>
       </c>
       <c r="I239" t="n">
-        <v>6.907512390364124e-06</v>
+        <v>2.43305631271623</v>
       </c>
       <c r="J239" t="n">
-        <v>6.907512390364124e-06</v>
+        <v>2.43305631271623</v>
       </c>
     </row>
     <row r="240">
@@ -10825,22 +11310,22 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>0.1028391763575825</v>
+        <v>0.1252955957059185</v>
       </c>
       <c r="F240" t="n">
         <v>2.605161460353123</v>
       </c>
       <c r="G240" t="n">
-        <v>2.499995119429789</v>
+        <v>2.539216334992743</v>
       </c>
       <c r="H240" t="n">
-        <v>-0.1051663409233341</v>
+        <v>-0.06594512536037955</v>
       </c>
       <c r="I240" t="n">
-        <v>4.036845413377145</v>
+        <v>2.531325845402336</v>
       </c>
       <c r="J240" t="n">
-        <v>-4.036845413377145</v>
+        <v>-2.531325845402336</v>
       </c>
     </row>
     <row r="241">
@@ -10861,22 +11346,22 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>0.1028391763575825</v>
+        <v>0.1252955957059185</v>
       </c>
       <c r="F241" t="n">
         <v>2.830407291666667</v>
       </c>
       <c r="G241" t="n">
-        <v>2.698017302316364</v>
+        <v>2.707171383825481</v>
       </c>
       <c r="H241" t="n">
-        <v>-0.1323899893503024</v>
+        <v>-0.123235907841186</v>
       </c>
       <c r="I241" t="n">
-        <v>4.677418325627103</v>
+        <v>4.353999094194649</v>
       </c>
       <c r="J241" t="n">
-        <v>-4.677418325627103</v>
+        <v>-4.353999094194649</v>
       </c>
     </row>
     <row r="242">
@@ -10999,22 +11484,22 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>0.08540130311845651</v>
+        <v>0.09635149004190553</v>
       </c>
       <c r="F245" t="n">
         <v>2.357925</v>
       </c>
       <c r="G245" t="n">
-        <v>2.357924735953094</v>
+        <v>2.394877964715868</v>
       </c>
       <c r="H245" t="n">
-        <v>-2.640469061176987e-07</v>
+        <v>0.03695296471586795</v>
       </c>
       <c r="I245" t="n">
-        <v>1.119827416553532e-05</v>
+        <v>1.567181514079878</v>
       </c>
       <c r="J245" t="n">
-        <v>-1.119827416553532e-05</v>
+        <v>1.567181514079878</v>
       </c>
     </row>
     <row r="246">
@@ -11035,22 +11520,22 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>0.08540130311845651</v>
+        <v>0.09635149004190553</v>
       </c>
       <c r="F246" t="n">
         <v>2.533756797828872</v>
       </c>
       <c r="G246" t="n">
-        <v>2.455058425014661</v>
+        <v>2.479006143182977</v>
       </c>
       <c r="H246" t="n">
-        <v>-0.07869837281421121</v>
+        <v>-0.05475065464589512</v>
       </c>
       <c r="I246" t="n">
-        <v>3.105995527338944</v>
+        <v>2.160848850718819</v>
       </c>
       <c r="J246" t="n">
-        <v>-3.105995527338944</v>
+        <v>-2.160848850718819</v>
       </c>
     </row>
     <row r="247">
@@ -11071,22 +11556,22 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>0.08540130311845651</v>
+        <v>0.09635149004190553</v>
       </c>
       <c r="F247" t="n">
         <v>2.714411458333333</v>
       </c>
       <c r="G247" t="n">
-        <v>2.67557502395226</v>
+        <v>2.680811518281774</v>
       </c>
       <c r="H247" t="n">
-        <v>-0.0388364343810732</v>
+        <v>-0.03359994005155897</v>
       </c>
       <c r="I247" t="n">
-        <v>1.430749721522287</v>
+        <v>1.237835183328822</v>
       </c>
       <c r="J247" t="n">
-        <v>-1.430749721522287</v>
+        <v>-1.237835183328822</v>
       </c>
     </row>
     <row r="248">
@@ -11107,22 +11592,22 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>0.09786992411855877</v>
+        <v>0.1090943562588904</v>
       </c>
       <c r="F248" t="n">
         <v>2.357925</v>
       </c>
       <c r="G248" t="n">
-        <v>2.35792703738119</v>
+        <v>2.395319200498373</v>
       </c>
       <c r="H248" t="n">
-        <v>2.037381190422849e-06</v>
+        <v>0.03739420049837339</v>
       </c>
       <c r="I248" t="n">
-        <v>8.640568255660588e-05</v>
+        <v>1.585894398607818</v>
       </c>
       <c r="J248" t="n">
-        <v>8.640568255660588e-05</v>
+        <v>1.585894398607818</v>
       </c>
     </row>
     <row r="249">
@@ -11143,22 +11628,22 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>0.09786992411855877</v>
+        <v>0.1090943562588904</v>
       </c>
       <c r="F249" t="n">
         <v>2.533756797828872</v>
       </c>
       <c r="G249" t="n">
-        <v>2.454430214872558</v>
+        <v>2.478786428465272</v>
       </c>
       <c r="H249" t="n">
-        <v>-0.0793265829563139</v>
+        <v>-0.05497036936359967</v>
       </c>
       <c r="I249" t="n">
-        <v>3.130789151677356</v>
+        <v>2.169520350599661</v>
       </c>
       <c r="J249" t="n">
-        <v>-3.130789151677356</v>
+        <v>-2.169520350599661</v>
       </c>
     </row>
     <row r="250">
@@ -11179,22 +11664,22 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>0.09786992411855877</v>
+        <v>0.1090943562588904</v>
       </c>
       <c r="F250" t="n">
         <v>2.714411458333333</v>
       </c>
       <c r="G250" t="n">
-        <v>2.674928414343358</v>
+        <v>2.680315488185662</v>
       </c>
       <c r="H250" t="n">
-        <v>-0.03948304398997537</v>
+        <v>-0.0340959701476713</v>
       </c>
       <c r="I250" t="n">
-        <v>1.454571077231535</v>
+        <v>1.256109129770858</v>
       </c>
       <c r="J250" t="n">
-        <v>-1.454571077231535</v>
+        <v>-1.256109129770858</v>
       </c>
     </row>
     <row r="251">
@@ -11317,22 +11802,22 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>0.05449563116943758</v>
+        <v>0.06161966169463239</v>
       </c>
       <c r="F254" t="n">
         <v>1.2605</v>
       </c>
       <c r="G254" t="n">
-        <v>1.26050312744451</v>
+        <v>1.322960502420314</v>
       </c>
       <c r="H254" t="n">
-        <v>3.127444509587463e-06</v>
+        <v>0.06246050242031376</v>
       </c>
       <c r="I254" t="n">
-        <v>0.000248111424798688</v>
+        <v>4.955216376066145</v>
       </c>
       <c r="J254" t="n">
-        <v>0.000248111424798688</v>
+        <v>4.955216376066145</v>
       </c>
     </row>
     <row r="255">
@@ -11353,22 +11838,22 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>0.05449563116943758</v>
+        <v>0.06161966169463239</v>
       </c>
       <c r="F255" t="n">
         <v>1.6629125</v>
       </c>
       <c r="G255" t="n">
-        <v>1.504178206199788</v>
+        <v>1.545469487964179</v>
       </c>
       <c r="H255" t="n">
-        <v>-0.1587342938002119</v>
+        <v>-0.1174430120358212</v>
       </c>
       <c r="I255" t="n">
-        <v>9.545558999659445</v>
+        <v>7.062488978573509</v>
       </c>
       <c r="J255" t="n">
-        <v>-9.545558999659445</v>
+        <v>-7.062488978573509</v>
       </c>
     </row>
     <row r="256">
@@ -11389,22 +11874,22 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>0.05449563116943758</v>
+        <v>0.06161966169463239</v>
       </c>
       <c r="F256" t="n">
         <v>2.2371125</v>
       </c>
       <c r="G256" t="n">
-        <v>2.085146426773932</v>
+        <v>2.094641400801776</v>
       </c>
       <c r="H256" t="n">
-        <v>-0.1519660732260681</v>
+        <v>-0.1424710991982243</v>
       </c>
       <c r="I256" t="n">
-        <v>6.792956242748996</v>
+        <v>6.368526356999225</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.792956242748996</v>
+        <v>-6.368526356999225</v>
       </c>
     </row>
     <row r="257">
@@ -11425,22 +11910,22 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>0.09717239253050693</v>
+        <v>0.105081064363988</v>
       </c>
       <c r="F257" t="n">
         <v>1.2605</v>
       </c>
       <c r="G257" t="n">
-        <v>1.260505061716089</v>
+        <v>1.326548605219641</v>
       </c>
       <c r="H257" t="n">
-        <v>5.061716088938795e-06</v>
+        <v>0.06604860521964095</v>
       </c>
       <c r="I257" t="n">
-        <v>0.0004015641482696386</v>
+        <v>5.23987348033645</v>
       </c>
       <c r="J257" t="n">
-        <v>0.0004015641482696386</v>
+        <v>5.23987348033645</v>
       </c>
     </row>
     <row r="258">
@@ -11461,22 +11946,22 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>0.09717239253050693</v>
+        <v>0.105081064363988</v>
       </c>
       <c r="F258" t="n">
         <v>1.6629125</v>
       </c>
       <c r="G258" t="n">
-        <v>1.498279370583388</v>
+        <v>1.542749019956184</v>
       </c>
       <c r="H258" t="n">
-        <v>-0.1646331294166119</v>
+        <v>-0.1201634800438161</v>
       </c>
       <c r="I258" t="n">
-        <v>9.900288164086318</v>
+        <v>7.22608556035366</v>
       </c>
       <c r="J258" t="n">
-        <v>-9.900288164086318</v>
+        <v>-7.22608556035366</v>
       </c>
     </row>
     <row r="259">
@@ -11497,22 +11982,22 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>0.09717239253050693</v>
+        <v>0.105081064363988</v>
       </c>
       <c r="F259" t="n">
         <v>2.2371125</v>
       </c>
       <c r="G259" t="n">
-        <v>2.078608462836351</v>
+        <v>2.089275197115513</v>
       </c>
       <c r="H259" t="n">
-        <v>-0.1585040371636488</v>
+        <v>-0.1478373028844877</v>
       </c>
       <c r="I259" t="n">
-        <v>7.085206361488249</v>
+        <v>6.608398231402654</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.085206361488249</v>
+        <v>-6.608398231402654</v>
       </c>
     </row>
     <row r="260">
@@ -11635,22 +12120,22 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>0.1042262168583755</v>
+        <v>0.1192750673708974</v>
       </c>
       <c r="F263" t="n">
         <v>2.2462375</v>
       </c>
       <c r="G263" t="n">
-        <v>2.246240299890795</v>
+        <v>2.289666100399841</v>
       </c>
       <c r="H263" t="n">
-        <v>2.799890794324966e-06</v>
+        <v>0.04342860039984098</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0001246480300647178</v>
+        <v>1.933393080644454</v>
       </c>
       <c r="J263" t="n">
-        <v>0.0001246480300647178</v>
+        <v>1.933393080644454</v>
       </c>
     </row>
     <row r="264">
@@ -11671,22 +12156,22 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>0.1042262168583755</v>
+        <v>0.1192750673708974</v>
       </c>
       <c r="F264" t="n">
         <v>2.426137507705096</v>
       </c>
       <c r="G264" t="n">
-        <v>2.341365007545882</v>
+        <v>2.371383621043549</v>
       </c>
       <c r="H264" t="n">
-        <v>-0.08477250015921456</v>
+        <v>-0.05475388666154712</v>
       </c>
       <c r="I264" t="n">
-        <v>3.494134190250477</v>
+        <v>2.256833608468437</v>
       </c>
       <c r="J264" t="n">
-        <v>-3.494134190250477</v>
+        <v>-2.256833608468437</v>
       </c>
     </row>
     <row r="265">
@@ -11707,22 +12192,22 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>0.1042262168583755</v>
+        <v>0.1192750673708974</v>
       </c>
       <c r="F265" t="n">
         <v>2.651822916666667</v>
       </c>
       <c r="G265" t="n">
-        <v>2.584498534700781</v>
+        <v>2.592092956973789</v>
       </c>
       <c r="H265" t="n">
-        <v>-0.0673243819658853</v>
+        <v>-0.05972995969287753</v>
       </c>
       <c r="I265" t="n">
-        <v>2.538796295286257</v>
+        <v>2.252411324959734</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.538796295286257</v>
+        <v>-2.252411324959734</v>
       </c>
     </row>
     <row r="266">
@@ -11743,22 +12228,22 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>0.1218097151510352</v>
+        <v>0.1373010909392187</v>
       </c>
       <c r="F266" t="n">
         <v>2.2462375</v>
       </c>
       <c r="G266" t="n">
-        <v>2.246239475390706</v>
+        <v>2.290250927395046</v>
       </c>
       <c r="H266" t="n">
-        <v>1.975390705677427e-06</v>
+        <v>0.04401342739504521</v>
       </c>
       <c r="I266" t="n">
-        <v>8.794220137796767e-05</v>
+        <v>1.959428929267061</v>
       </c>
       <c r="J266" t="n">
-        <v>8.794220137796767e-05</v>
+        <v>1.959428929267061</v>
       </c>
     </row>
     <row r="267">
@@ -11779,22 +12264,22 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>0.1218097151510352</v>
+        <v>0.1373010909392187</v>
       </c>
       <c r="F267" t="n">
         <v>2.426137507705096</v>
       </c>
       <c r="G267" t="n">
-        <v>2.340616639292388</v>
+        <v>2.371213303052259</v>
       </c>
       <c r="H267" t="n">
-        <v>-0.08552086841270867</v>
+        <v>-0.05492420465283754</v>
       </c>
       <c r="I267" t="n">
-        <v>3.524980267652</v>
+        <v>2.263853737820112</v>
       </c>
       <c r="J267" t="n">
-        <v>-3.524980267652</v>
+        <v>-2.263853737820112</v>
       </c>
     </row>
     <row r="268">
@@ -11815,22 +12300,22 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>0.1218097151510352</v>
+        <v>0.1373010909392187</v>
       </c>
       <c r="F268" t="n">
         <v>2.651822916666667</v>
       </c>
       <c r="G268" t="n">
-        <v>2.583605966649622</v>
+        <v>2.591457105271258</v>
       </c>
       <c r="H268" t="n">
-        <v>-0.06821695001704464</v>
+        <v>-0.0603658113954082</v>
       </c>
       <c r="I268" t="n">
-        <v>2.572454954978409</v>
+        <v>2.276389234590666</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.572454954978409</v>
+        <v>-2.276389234590666</v>
       </c>
     </row>
     <row r="269">
@@ -11953,22 +12438,22 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>0.09372630077322562</v>
+        <v>0.09431377044305972</v>
       </c>
       <c r="F272" t="n">
         <v>2.4985875</v>
       </c>
       <c r="G272" t="n">
-        <v>2.498588413145333</v>
+        <v>2.500175765327185</v>
       </c>
       <c r="H272" t="n">
-        <v>9.131453331256978e-07</v>
+        <v>0.00158826532718459</v>
       </c>
       <c r="I272" t="n">
-        <v>3.654646207610091e-05</v>
+        <v>0.06356652817580294</v>
       </c>
       <c r="J272" t="n">
-        <v>3.654646207610091e-05</v>
+        <v>0.06356652817580294</v>
       </c>
     </row>
     <row r="273">
@@ -11989,22 +12474,22 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>0.09372630077322562</v>
+        <v>0.09431377044305972</v>
       </c>
       <c r="F273" t="n">
         <v>2.578681397618311</v>
       </c>
       <c r="G273" t="n">
-        <v>2.571365651378545</v>
+        <v>2.572393004836511</v>
       </c>
       <c r="H273" t="n">
-        <v>-0.007315746239766163</v>
+        <v>-0.006288392781800045</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2837010514956613</v>
+        <v>0.2438607882155605</v>
       </c>
       <c r="J273" t="n">
-        <v>-0.2837010514956613</v>
+        <v>-0.2438607882155605</v>
       </c>
     </row>
     <row r="274">
@@ -12025,22 +12510,22 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>0.09372630077322562</v>
+        <v>0.09431377044305972</v>
       </c>
       <c r="F274" t="n">
         <v>2.72160625</v>
       </c>
       <c r="G274" t="n">
-        <v>2.740478812615087</v>
+        <v>2.740702571238777</v>
       </c>
       <c r="H274" t="n">
-        <v>0.01887256261508696</v>
+        <v>0.01909632123877714</v>
       </c>
       <c r="I274" t="n">
-        <v>0.6934347176446617</v>
+        <v>0.7016562825271708</v>
       </c>
       <c r="J274" t="n">
-        <v>0.6934347176446617</v>
+        <v>0.7016562825271708</v>
       </c>
     </row>
     <row r="275">
@@ -12061,22 +12546,22 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>0.1035325935966191</v>
+        <v>0.1041909157093198</v>
       </c>
       <c r="F275" t="n">
         <v>2.4985875</v>
       </c>
       <c r="G275" t="n">
-        <v>2.498587925730706</v>
+        <v>2.500349716289349</v>
       </c>
       <c r="H275" t="n">
-        <v>4.257307053556758e-07</v>
+        <v>0.001762216289348473</v>
       </c>
       <c r="I275" t="n">
-        <v>1.703885516739661e-05</v>
+        <v>0.07052850017653865</v>
       </c>
       <c r="J275" t="n">
-        <v>1.703885516739661e-05</v>
+        <v>0.07052850017653865</v>
       </c>
     </row>
     <row r="276">
@@ -12097,22 +12582,22 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>0.1035325935966191</v>
+        <v>0.1041909157093198</v>
       </c>
       <c r="F276" t="n">
         <v>2.578681397618311</v>
       </c>
       <c r="G276" t="n">
-        <v>2.571010615566995</v>
+        <v>2.572155334566266</v>
       </c>
       <c r="H276" t="n">
-        <v>-0.007670782051315328</v>
+        <v>-0.00652606305204495</v>
       </c>
       <c r="I276" t="n">
-        <v>0.2974691661560098</v>
+        <v>0.2530775247408412</v>
       </c>
       <c r="J276" t="n">
-        <v>-0.2974691661560098</v>
+        <v>-0.2530775247408412</v>
       </c>
     </row>
     <row r="277">
@@ -12133,22 +12618,22 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>0.1035325935966191</v>
+        <v>0.1041909157093198</v>
       </c>
       <c r="F277" t="n">
         <v>2.72160625</v>
       </c>
       <c r="G277" t="n">
-        <v>2.740104201229234</v>
+        <v>2.74035571321677</v>
       </c>
       <c r="H277" t="n">
-        <v>0.01849795122923403</v>
+        <v>0.0187494632167704</v>
       </c>
       <c r="I277" t="n">
-        <v>0.67967036852719</v>
+        <v>0.6889116754773179</v>
       </c>
       <c r="J277" t="n">
-        <v>0.67967036852719</v>
+        <v>0.6889116754773179</v>
       </c>
     </row>
     <row r="278">
@@ -12271,22 +12756,22 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>0.1095102904351769</v>
+        <v>0.1280476374761181</v>
       </c>
       <c r="F281" t="n">
         <v>2.1168875</v>
       </c>
       <c r="G281" t="n">
-        <v>2.116891206340847</v>
+        <v>2.171455427004366</v>
       </c>
       <c r="H281" t="n">
-        <v>3.706340847120515e-06</v>
+        <v>0.05456792700436575</v>
       </c>
       <c r="I281" t="n">
-        <v>0.0001750844505019995</v>
+        <v>2.577743361627189</v>
       </c>
       <c r="J281" t="n">
-        <v>0.0001750844505019995</v>
+        <v>2.577743361627189</v>
       </c>
     </row>
     <row r="282">
@@ -12307,22 +12792,22 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>0.1095102904351769</v>
+        <v>0.1280476374761181</v>
       </c>
       <c r="F282" t="n">
         <v>2.303175230396183</v>
       </c>
       <c r="G282" t="n">
-        <v>2.220522839792302</v>
+        <v>2.259137619967984</v>
       </c>
       <c r="H282" t="n">
-        <v>-0.08265239060388074</v>
+        <v>-0.04403761042819809</v>
       </c>
       <c r="I282" t="n">
-        <v>3.588627973810886</v>
+        <v>1.912039077487948</v>
       </c>
       <c r="J282" t="n">
-        <v>-3.588627973810886</v>
+        <v>-1.912039077487948</v>
       </c>
     </row>
     <row r="283">
@@ -12343,22 +12828,22 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>0.1095102904351769</v>
+        <v>0.1280476374761181</v>
       </c>
       <c r="F283" t="n">
         <v>2.689839583333333</v>
       </c>
       <c r="G283" t="n">
-        <v>2.497430062230134</v>
+        <v>2.507780387170051</v>
       </c>
       <c r="H283" t="n">
-        <v>-0.1924095211031989</v>
+        <v>-0.1820591961632823</v>
       </c>
       <c r="I283" t="n">
-        <v>7.153196878185537</v>
+        <v>6.76840348738079</v>
       </c>
       <c r="J283" t="n">
-        <v>-7.153196878185537</v>
+        <v>-6.76840348738079</v>
       </c>
     </row>
     <row r="284">
@@ -12379,22 +12864,22 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>0.1319493824569777</v>
+        <v>0.1511864461993925</v>
       </c>
       <c r="F284" t="n">
         <v>2.1168875</v>
       </c>
       <c r="G284" t="n">
-        <v>2.116891739070655</v>
+        <v>2.172442461073368</v>
       </c>
       <c r="H284" t="n">
-        <v>4.239070654943333e-06</v>
+        <v>0.05555496107336788</v>
       </c>
       <c r="I284" t="n">
-        <v>0.0002002501623229073</v>
+        <v>2.624370027853057</v>
       </c>
       <c r="J284" t="n">
-        <v>0.0002002501623229073</v>
+        <v>2.624370027853057</v>
       </c>
     </row>
     <row r="285">
@@ -12415,22 +12900,22 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>0.1319493824569777</v>
+        <v>0.1511864461993925</v>
       </c>
       <c r="F285" t="n">
         <v>2.303175230396183</v>
       </c>
       <c r="G285" t="n">
-        <v>2.219545016545049</v>
+        <v>2.259120375058378</v>
       </c>
       <c r="H285" t="n">
-        <v>-0.08363021385113401</v>
+        <v>-0.04405485533780462</v>
       </c>
       <c r="I285" t="n">
-        <v>3.631083416816197</v>
+        <v>1.912787822497835</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.631083416816197</v>
+        <v>-1.912787822497835</v>
       </c>
     </row>
     <row r="286">
@@ -12451,22 +12936,22 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>0.1319493824569777</v>
+        <v>0.1511864461993925</v>
       </c>
       <c r="F286" t="n">
         <v>2.689839583333333</v>
       </c>
       <c r="G286" t="n">
-        <v>2.496193510854985</v>
+        <v>2.506986423325552</v>
       </c>
       <c r="H286" t="n">
-        <v>-0.1936460724783484</v>
+        <v>-0.1828531600077814</v>
       </c>
       <c r="I286" t="n">
-        <v>7.199168072260137</v>
+        <v>6.797920632173316</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.199168072260137</v>
+        <v>-6.797920632173316</v>
       </c>
     </row>
     <row r="287">
@@ -12637,16 +13122,16 @@
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>0.307712774347173</v>
+        <v>2.933363838956922</v>
       </c>
       <c r="E2" t="n">
-        <v>0.028408364108595</v>
+        <v>0.06901939379150389</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3077071523577243</v>
+        <v>2.927446318206949</v>
       </c>
       <c r="G2" t="n">
-        <v>5.723086108307863</v>
+        <v>6.51316573775913</v>
       </c>
     </row>
     <row r="3">
@@ -12664,16 +13149,16 @@
         <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>5.022648683803604</v>
+        <v>3.55941341123736</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1388461932739913</v>
+        <v>0.09520930544653378</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.983870271537443</v>
+        <v>-3.524311191082043</v>
       </c>
       <c r="G3" t="n">
-        <v>11.09496567262841</v>
+        <v>7.55459972543191</v>
       </c>
     </row>
     <row r="4">
@@ -12691,16 +13176,16 @@
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>4.276619826784182</v>
+        <v>4.000425918547519</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1349015059081114</v>
+        <v>0.1260491307567201</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.215508202467048</v>
+        <v>-3.93263658207172</v>
       </c>
       <c r="G4" t="n">
-        <v>9.285504233286968</v>
+        <v>8.578699666702336</v>
       </c>
     </row>
     <row r="5">
@@ -12718,16 +13203,16 @@
         <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3082841793514198</v>
+        <v>2.987811711816927</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02846070105003819</v>
+        <v>0.07011490046213269</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3082771234062011</v>
+        <v>2.982947522628074</v>
       </c>
       <c r="G5" t="n">
-        <v>5.733601078609627</v>
+        <v>6.623444379074976</v>
       </c>
     </row>
     <row r="6">
@@ -12745,16 +13230,16 @@
         <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>5.081447916334067</v>
+        <v>3.574744477392882</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1402375852335823</v>
+        <v>0.09548865058163364</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.044432205595746</v>
+        <v>-3.54076551130739</v>
       </c>
       <c r="G6" t="n">
-        <v>11.19040846154465</v>
+        <v>7.554736781074537</v>
       </c>
     </row>
     <row r="7">
@@ -12772,16 +13257,16 @@
         <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>4.325678137539425</v>
+        <v>4.035096501436333</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1363348259675665</v>
+        <v>0.1270258104320953</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.271330700988173</v>
+        <v>-3.973568366818544</v>
       </c>
       <c r="G7" t="n">
-        <v>9.372703496519826</v>
+        <v>8.63015605569206</v>
       </c>
     </row>
     <row r="8">
@@ -12936,25 +13421,25 @@
         <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02397019273512198</v>
+        <v>0.02588881026848242</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08528709168216574</v>
+        <v>0.09569312008404177</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07759725848132093</v>
+        <v>0.09533263024248262</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2227214678701135</v>
+        <v>0.1743131185505807</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04539198434181525</v>
+        <v>0.05036724506640297</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2195605588252939</v>
+        <v>0.1677001293653997</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1741685744834787</v>
+        <v>0.1173328842989967</v>
       </c>
     </row>
     <row r="3">
@@ -12967,25 +13452,25 @@
         <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02617032869151523</v>
+        <v>0.02810718263577177</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1033167182562609</v>
+        <v>0.1141916231663784</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09943921080260062</v>
+        <v>0.1208100841961806</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2448759921893136</v>
+        <v>0.1923657220418985</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04849970142094817</v>
+        <v>0.05352321006356184</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2386324683546633</v>
+        <v>0.1886990828016405</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1901327669337151</v>
+        <v>0.1351758727380787</v>
       </c>
     </row>
   </sheetData>
